--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F1EB113-D71F-41B1-89D4-39577C3AD1C2}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A9AE015-0C39-4191-9E45-59AF43879E3F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="91">
   <si>
     <t>Dt</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>Ativo - Promessa Especial Servicos - Compra para terceiro</t>
+  </si>
+  <si>
+    <t>Ativo - Preventivo - PV-Preventivo Confirmado</t>
   </si>
 </sst>
 </file>
@@ -699,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V206"/>
+  <dimension ref="A1:V208"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -12943,7 +12946,7 @@
         <v>8</v>
       </c>
       <c r="F202" s="1">
-        <v>45999</v>
+        <v>45998</v>
       </c>
       <c r="G202" s="1">
         <v>23526</v>
@@ -13070,7 +13073,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="1">
-        <v>45999</v>
+        <v>45998</v>
       </c>
       <c r="G204" s="1">
         <v>38879</v>
@@ -13126,58 +13129,58 @@
         <v>30</v>
       </c>
       <c r="E205" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F205" s="1">
         <v>25830</v>
       </c>
       <c r="G205" s="1">
-        <v>16530</v>
+        <v>50365</v>
       </c>
       <c r="H205" s="1">
-        <v>45</v>
+        <v>506</v>
       </c>
       <c r="I205" s="1">
+        <v>39</v>
+      </c>
+      <c r="J205" s="1">
         <v>6</v>
       </c>
-      <c r="J205" s="1">
-        <v>3</v>
-      </c>
       <c r="K205" s="1">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="L205" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M205" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N205" s="4">
-        <v>1.6203703703703703E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
       <c r="O205" s="4">
-        <v>2.8935185185185184E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="P205" s="5">
-        <v>2.7000000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="Q205" s="6">
-        <v>0</v>
-      </c>
-      <c r="R205" s="1" t="s">
-        <v>20</v>
+        <v>0.2424</v>
+      </c>
+      <c r="R205" s="5">
+        <v>0.125</v>
       </c>
       <c r="S205" s="1">
-        <v>0.64</v>
+        <v>1.95</v>
       </c>
       <c r="T205" s="6">
         <v>0</v>
       </c>
       <c r="U205" s="6">
-        <v>0.5</v>
+        <v>0.15379999999999999</v>
       </c>
       <c r="V205" s="2">
-        <v>7.0823999999999998</v>
+        <v>80.662400000000005</v>
       </c>
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.3">
@@ -13197,46 +13200,173 @@
         <v>14</v>
       </c>
       <c r="F206" s="1">
-        <v>45999</v>
+        <v>45998</v>
       </c>
       <c r="G206" s="1">
-        <v>29210</v>
+        <v>66649</v>
       </c>
       <c r="H206" s="1">
-        <v>334</v>
+        <v>706</v>
       </c>
       <c r="I206" s="1">
+        <v>7</v>
+      </c>
+      <c r="J206" s="1">
+        <v>0</v>
+      </c>
+      <c r="K206" s="1">
+        <v>0</v>
+      </c>
+      <c r="L206" s="1">
+        <v>0</v>
+      </c>
+      <c r="M206" s="1">
+        <v>0</v>
+      </c>
+      <c r="O206" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P206" s="5">
+        <v>1.06E-2</v>
+      </c>
+      <c r="Q206" s="5">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="R206" s="6">
+        <v>0</v>
+      </c>
+      <c r="S206" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="V206" s="2">
+        <v>82.300399999999996</v>
+      </c>
+    </row>
+    <row r="207" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A207" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B207" s="1">
+        <v>11</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" s="1">
+        <v>30</v>
+      </c>
+      <c r="E207" s="1">
+        <v>4</v>
+      </c>
+      <c r="F207" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G207" s="1">
+        <v>22284</v>
+      </c>
+      <c r="H207" s="1">
+        <v>99</v>
+      </c>
+      <c r="I207" s="1">
+        <v>9</v>
+      </c>
+      <c r="J207" s="1">
+        <v>2</v>
+      </c>
+      <c r="K207" s="1">
+        <v>6</v>
+      </c>
+      <c r="L207" s="1">
+        <v>2</v>
+      </c>
+      <c r="M207" s="1">
+        <v>2</v>
+      </c>
+      <c r="N207" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="O207" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P207" s="5">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="Q207" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="R207" s="6">
+        <v>1</v>
+      </c>
+      <c r="S207" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="T207" s="5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="U207" s="5">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="V207" s="2">
+        <v>20.404800000000002</v>
+      </c>
+    </row>
+    <row r="208" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A208" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B208" s="1">
+        <v>11</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D208" s="1">
+        <v>0</v>
+      </c>
+      <c r="E208" s="1">
+        <v>13</v>
+      </c>
+      <c r="F208" s="1">
+        <v>45998</v>
+      </c>
+      <c r="G208" s="1">
+        <v>33844</v>
+      </c>
+      <c r="H208" s="1">
+        <v>298</v>
+      </c>
+      <c r="I208" s="1">
         <v>3</v>
       </c>
-      <c r="J206" s="1">
-        <v>0</v>
-      </c>
-      <c r="K206" s="1">
-        <v>0</v>
-      </c>
-      <c r="L206" s="1">
-        <v>0</v>
-      </c>
-      <c r="M206" s="1">
-        <v>0</v>
-      </c>
-      <c r="O206" s="4">
-        <v>2.4305555555555555E-4</v>
-      </c>
-      <c r="P206" s="5">
-        <v>1.14E-2</v>
-      </c>
-      <c r="Q206" s="5">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="R206" s="6">
-        <v>0</v>
-      </c>
-      <c r="S206" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="V206" s="2">
-        <v>38.131599999999999</v>
+      <c r="J208" s="1">
+        <v>0</v>
+      </c>
+      <c r="K208" s="1">
+        <v>0</v>
+      </c>
+      <c r="L208" s="1">
+        <v>0</v>
+      </c>
+      <c r="M208" s="1">
+        <v>2</v>
+      </c>
+      <c r="O208" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P208" s="5">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="Q208" s="5">
+        <v>1.01E-2</v>
+      </c>
+      <c r="R208" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="S208" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="V208" s="2">
+        <v>44.023200000000003</v>
       </c>
     </row>
   </sheetData>
@@ -13247,7 +13377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I589"/>
+  <dimension ref="A1:I640"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -29811,7 +29941,7 @@
         <v>6</v>
       </c>
       <c r="G571">
-        <v>123</v>
+        <v>1468</v>
       </c>
       <c r="H571" s="8">
         <v>0</v>
@@ -29840,7 +29970,7 @@
         <v>6</v>
       </c>
       <c r="G572">
-        <v>660</v>
+        <v>5044</v>
       </c>
       <c r="H572" s="8">
         <v>0</v>
@@ -29869,7 +29999,7 @@
         <v>6</v>
       </c>
       <c r="G573">
-        <v>105</v>
+        <v>627</v>
       </c>
       <c r="H573" s="8">
         <v>0</v>
@@ -29898,7 +30028,7 @@
         <v>6</v>
       </c>
       <c r="G574">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H574" s="8">
         <v>0</v>
@@ -29927,7 +30057,7 @@
         <v>6</v>
       </c>
       <c r="G575">
-        <v>1482</v>
+        <v>13955</v>
       </c>
       <c r="H575" s="8">
         <v>0</v>
@@ -29956,7 +30086,7 @@
         <v>6</v>
       </c>
       <c r="G576">
-        <v>13545</v>
+        <v>21808</v>
       </c>
       <c r="H576" s="8">
         <v>0</v>
@@ -29979,19 +30109,19 @@
         <v>86</v>
       </c>
       <c r="E577" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F577" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G577">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H577" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>0</v>
       </c>
       <c r="I577" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.3">
@@ -30008,19 +30138,19 @@
         <v>86</v>
       </c>
       <c r="E578" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F578" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G578">
         <v>1</v>
       </c>
       <c r="H578" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="I578" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.3">
@@ -30043,13 +30173,13 @@
         <v>88</v>
       </c>
       <c r="G579">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H579" s="8">
-        <v>6.9444444444444447E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="I579" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.3">
@@ -30066,19 +30196,19 @@
         <v>86</v>
       </c>
       <c r="E580" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F580" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G580">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H580" s="8">
-        <v>5.3240740740740744E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="I580" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.3">
@@ -30095,19 +30225,19 @@
         <v>86</v>
       </c>
       <c r="E581" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F581" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G581">
         <v>1</v>
       </c>
       <c r="H581" s="8">
-        <v>1.3888888888888889E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I581" s="8">
-        <v>1.3888888888888889E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.3">
@@ -30124,19 +30254,19 @@
         <v>86</v>
       </c>
       <c r="E582" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F582" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G582">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H582" s="8">
-        <v>6.7129629629629625E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="I582" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.3">
@@ -30153,7 +30283,7 @@
         <v>86</v>
       </c>
       <c r="E583" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F583" t="s">
         <v>88</v>
@@ -30162,10 +30292,10 @@
         <v>1</v>
       </c>
       <c r="H583" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="I583" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.3">
@@ -30182,19 +30312,19 @@
         <v>86</v>
       </c>
       <c r="E584" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F584" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G584">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H584" s="8">
-        <v>4.0277777777777777E-3</v>
+        <v>4.861111111111111E-4</v>
       </c>
       <c r="I584" s="8">
-        <v>1.273148148148148E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.3">
@@ -30211,19 +30341,19 @@
         <v>86</v>
       </c>
       <c r="E585" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F585" t="s">
         <v>88</v>
       </c>
       <c r="G585">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H585" s="8">
-        <v>3.1250000000000001E-4</v>
+        <v>7.1759259259259259E-4</v>
       </c>
       <c r="I585" s="8">
-        <v>3.1250000000000001E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.3">
@@ -30240,19 +30370,19 @@
         <v>86</v>
       </c>
       <c r="E586" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F586" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G586">
-        <v>501</v>
+        <v>4</v>
       </c>
       <c r="H586" s="8">
-        <v>0</v>
+        <v>9.7222222222222219E-4</v>
       </c>
       <c r="I586" s="8">
-        <v>0</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.3">
@@ -30269,19 +30399,19 @@
         <v>86</v>
       </c>
       <c r="E587" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F587" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G587">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H587" s="8">
-        <v>1.1574074074074073E-5</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="I587" s="8">
-        <v>1.1574074074074073E-5</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.3">
@@ -30298,19 +30428,19 @@
         <v>86</v>
       </c>
       <c r="E588" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F588" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G588">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="H588" s="8">
-        <v>0</v>
+        <v>1.1458333333333333E-3</v>
       </c>
       <c r="I588" s="8">
-        <v>0</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
@@ -30324,22 +30454,1501 @@
         <v>17</v>
       </c>
       <c r="D589" t="s">
+        <v>86</v>
+      </c>
+      <c r="E589" t="s">
+        <v>41</v>
+      </c>
+      <c r="F589" t="s">
+        <v>88</v>
+      </c>
+      <c r="G589">
+        <v>6</v>
+      </c>
+      <c r="H589" s="8">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="I589" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A590" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B590">
+        <v>10</v>
+      </c>
+      <c r="C590" t="s">
+        <v>17</v>
+      </c>
+      <c r="D590" t="s">
+        <v>86</v>
+      </c>
+      <c r="E590" t="s">
+        <v>41</v>
+      </c>
+      <c r="F590" t="s">
+        <v>88</v>
+      </c>
+      <c r="G590">
+        <v>7</v>
+      </c>
+      <c r="H590" s="8">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="I590" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A591" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B591">
+        <v>10</v>
+      </c>
+      <c r="C591" t="s">
+        <v>17</v>
+      </c>
+      <c r="D591" t="s">
+        <v>86</v>
+      </c>
+      <c r="E591" t="s">
+        <v>57</v>
+      </c>
+      <c r="F591" t="s">
+        <v>37</v>
+      </c>
+      <c r="G591">
+        <v>2</v>
+      </c>
+      <c r="H591" s="8">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="I591" s="8">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A592" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B592">
+        <v>10</v>
+      </c>
+      <c r="C592" t="s">
+        <v>17</v>
+      </c>
+      <c r="D592" t="s">
+        <v>86</v>
+      </c>
+      <c r="E592" t="s">
+        <v>38</v>
+      </c>
+      <c r="F592" t="s">
+        <v>37</v>
+      </c>
+      <c r="G592">
+        <v>55</v>
+      </c>
+      <c r="H592" s="8">
+        <v>1.4305555555555556E-2</v>
+      </c>
+      <c r="I592" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A593" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B593">
+        <v>10</v>
+      </c>
+      <c r="C593" t="s">
+        <v>17</v>
+      </c>
+      <c r="D593" t="s">
+        <v>86</v>
+      </c>
+      <c r="E593" t="s">
+        <v>50</v>
+      </c>
+      <c r="F593" t="s">
+        <v>37</v>
+      </c>
+      <c r="G593">
+        <v>5</v>
+      </c>
+      <c r="H593" s="8">
+        <v>2.2569444444444442E-3</v>
+      </c>
+      <c r="I593" s="8">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A594" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B594">
+        <v>10</v>
+      </c>
+      <c r="C594" t="s">
+        <v>17</v>
+      </c>
+      <c r="D594" t="s">
+        <v>86</v>
+      </c>
+      <c r="E594" t="s">
+        <v>59</v>
+      </c>
+      <c r="F594" t="s">
+        <v>37</v>
+      </c>
+      <c r="G594">
+        <v>1</v>
+      </c>
+      <c r="H594" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="I594" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A595" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B595">
+        <v>10</v>
+      </c>
+      <c r="C595" t="s">
+        <v>17</v>
+      </c>
+      <c r="D595" t="s">
+        <v>86</v>
+      </c>
+      <c r="E595" t="s">
+        <v>39</v>
+      </c>
+      <c r="F595" t="s">
+        <v>37</v>
+      </c>
+      <c r="G595">
+        <v>32</v>
+      </c>
+      <c r="H595" s="8">
+        <v>8.2523148148148148E-3</v>
+      </c>
+      <c r="I595" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A596" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B596">
+        <v>10</v>
+      </c>
+      <c r="C596" t="s">
+        <v>17</v>
+      </c>
+      <c r="D596" t="s">
+        <v>86</v>
+      </c>
+      <c r="E596" t="s">
+        <v>39</v>
+      </c>
+      <c r="F596" t="s">
+        <v>88</v>
+      </c>
+      <c r="G596">
+        <v>1</v>
+      </c>
+      <c r="H596" s="8">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="I596" s="8">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A597" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B597">
+        <v>10</v>
+      </c>
+      <c r="C597" t="s">
+        <v>17</v>
+      </c>
+      <c r="D597" t="s">
+        <v>86</v>
+      </c>
+      <c r="E597" t="s">
+        <v>39</v>
+      </c>
+      <c r="F597" t="s">
+        <v>88</v>
+      </c>
+      <c r="G597">
+        <v>1</v>
+      </c>
+      <c r="H597" s="8">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="I597" s="8">
+        <v>5.4398148148148144E-4</v>
+      </c>
+    </row>
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A598" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B598">
+        <v>10</v>
+      </c>
+      <c r="C598" t="s">
+        <v>17</v>
+      </c>
+      <c r="D598" t="s">
+        <v>86</v>
+      </c>
+      <c r="E598" t="s">
+        <v>36</v>
+      </c>
+      <c r="F598" t="s">
+        <v>37</v>
+      </c>
+      <c r="G598">
+        <v>364</v>
+      </c>
+      <c r="H598" s="8">
+        <v>3.9571759259259258E-2</v>
+      </c>
+      <c r="I598" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A599" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B599">
+        <v>10</v>
+      </c>
+      <c r="C599" t="s">
+        <v>17</v>
+      </c>
+      <c r="D599" t="s">
+        <v>86</v>
+      </c>
+      <c r="E599" t="s">
+        <v>36</v>
+      </c>
+      <c r="F599" t="s">
+        <v>88</v>
+      </c>
+      <c r="G599">
+        <v>3</v>
+      </c>
+      <c r="H599" s="8">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="I599" s="8">
+        <v>4.2824074074074075E-4</v>
+      </c>
+    </row>
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A600" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B600">
+        <v>10</v>
+      </c>
+      <c r="C600" t="s">
+        <v>17</v>
+      </c>
+      <c r="D600" t="s">
+        <v>86</v>
+      </c>
+      <c r="E600" t="s">
+        <v>31</v>
+      </c>
+      <c r="F600" t="s">
+        <v>6</v>
+      </c>
+      <c r="G600">
+        <v>5930</v>
+      </c>
+      <c r="H600" s="8">
+        <v>0</v>
+      </c>
+      <c r="I600" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A601" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B601">
+        <v>10</v>
+      </c>
+      <c r="C601" t="s">
+        <v>17</v>
+      </c>
+      <c r="D601" t="s">
+        <v>86</v>
+      </c>
+      <c r="E601" t="s">
+        <v>44</v>
+      </c>
+      <c r="F601" t="s">
+        <v>37</v>
+      </c>
+      <c r="G601">
+        <v>7</v>
+      </c>
+      <c r="H601" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="I601" s="8">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A602" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B602">
+        <v>10</v>
+      </c>
+      <c r="C602" t="s">
+        <v>17</v>
+      </c>
+      <c r="D602" t="s">
+        <v>86</v>
+      </c>
+      <c r="E602" t="s">
+        <v>35</v>
+      </c>
+      <c r="F602" t="s">
+        <v>6</v>
+      </c>
+      <c r="G602">
+        <v>1003</v>
+      </c>
+      <c r="H602" s="8">
+        <v>0</v>
+      </c>
+      <c r="I602" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A603" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B603">
+        <v>10</v>
+      </c>
+      <c r="C603" t="s">
+        <v>17</v>
+      </c>
+      <c r="D603" t="s">
         <v>87</v>
       </c>
-      <c r="E589" t="s">
+      <c r="E603" t="s">
+        <v>62</v>
+      </c>
+      <c r="F603" t="s">
+        <v>10</v>
+      </c>
+      <c r="G603">
+        <v>1</v>
+      </c>
+      <c r="H603" s="8">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="I603" s="8">
+        <v>1.3078703703703703E-3</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A604" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B604">
+        <v>10</v>
+      </c>
+      <c r="C604" t="s">
+        <v>17</v>
+      </c>
+      <c r="D604" t="s">
+        <v>87</v>
+      </c>
+      <c r="E604" t="s">
         <v>42</v>
       </c>
-      <c r="F589" t="s">
+      <c r="F604" t="s">
         <v>37</v>
       </c>
-      <c r="G589">
+      <c r="G604">
+        <v>7</v>
+      </c>
+      <c r="H604" s="8">
+        <v>1.5509259259259259E-3</v>
+      </c>
+      <c r="I604" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A605" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B605">
+        <v>10</v>
+      </c>
+      <c r="C605" t="s">
+        <v>17</v>
+      </c>
+      <c r="D605" t="s">
+        <v>87</v>
+      </c>
+      <c r="E605" t="s">
+        <v>48</v>
+      </c>
+      <c r="F605" t="s">
+        <v>37</v>
+      </c>
+      <c r="G605">
+        <v>4</v>
+      </c>
+      <c r="H605" s="8">
+        <v>2.0370370370370369E-3</v>
+      </c>
+      <c r="I605" s="8">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A606" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B606">
+        <v>10</v>
+      </c>
+      <c r="C606" t="s">
+        <v>17</v>
+      </c>
+      <c r="D606" t="s">
+        <v>87</v>
+      </c>
+      <c r="E606" t="s">
+        <v>49</v>
+      </c>
+      <c r="F606" t="s">
+        <v>37</v>
+      </c>
+      <c r="G606">
+        <v>4</v>
+      </c>
+      <c r="H606" s="8">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="I606" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A607" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B607">
+        <v>10</v>
+      </c>
+      <c r="C607" t="s">
+        <v>17</v>
+      </c>
+      <c r="D607" t="s">
+        <v>87</v>
+      </c>
+      <c r="E607" t="s">
+        <v>60</v>
+      </c>
+      <c r="F607" t="s">
+        <v>37</v>
+      </c>
+      <c r="G607">
+        <v>2</v>
+      </c>
+      <c r="H607" s="8">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="I607" s="8">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A608" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B608">
+        <v>10</v>
+      </c>
+      <c r="C608" t="s">
+        <v>17</v>
+      </c>
+      <c r="D608" t="s">
+        <v>87</v>
+      </c>
+      <c r="E608" t="s">
+        <v>64</v>
+      </c>
+      <c r="F608" t="s">
+        <v>37</v>
+      </c>
+      <c r="G608">
         <v>1</v>
       </c>
-      <c r="H589" s="8">
+      <c r="H608" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="I608" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A609" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B609">
+        <v>10</v>
+      </c>
+      <c r="C609" t="s">
+        <v>17</v>
+      </c>
+      <c r="D609" t="s">
+        <v>87</v>
+      </c>
+      <c r="E609" t="s">
+        <v>61</v>
+      </c>
+      <c r="F609" t="s">
+        <v>10</v>
+      </c>
+      <c r="G609">
+        <v>4</v>
+      </c>
+      <c r="H609" s="8">
+        <v>1.1805555555555556E-3</v>
+      </c>
+      <c r="I609" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A610" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B610">
+        <v>10</v>
+      </c>
+      <c r="C610" t="s">
+        <v>17</v>
+      </c>
+      <c r="D610" t="s">
+        <v>87</v>
+      </c>
+      <c r="E610" t="s">
+        <v>63</v>
+      </c>
+      <c r="F610" t="s">
+        <v>10</v>
+      </c>
+      <c r="G610">
+        <v>1</v>
+      </c>
+      <c r="H610" s="8">
+        <v>2.627314814814815E-3</v>
+      </c>
+      <c r="I610" s="8">
+        <v>2.627314814814815E-3</v>
+      </c>
+    </row>
+    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A611" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B611">
+        <v>10</v>
+      </c>
+      <c r="C611" t="s">
+        <v>17</v>
+      </c>
+      <c r="D611" t="s">
+        <v>87</v>
+      </c>
+      <c r="E611" t="s">
+        <v>90</v>
+      </c>
+      <c r="F611" t="s">
+        <v>10</v>
+      </c>
+      <c r="G611">
+        <v>1</v>
+      </c>
+      <c r="H611" s="8">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="I611" s="8">
+        <v>9.1435185185185185E-4</v>
+      </c>
+    </row>
+    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A612" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B612">
+        <v>10</v>
+      </c>
+      <c r="C612" t="s">
+        <v>17</v>
+      </c>
+      <c r="D612" t="s">
+        <v>87</v>
+      </c>
+      <c r="E612" t="s">
+        <v>54</v>
+      </c>
+      <c r="F612" t="s">
+        <v>11</v>
+      </c>
+      <c r="G612">
+        <v>1</v>
+      </c>
+      <c r="H612" s="8">
+        <v>5.7523148148148151E-3</v>
+      </c>
+      <c r="I612" s="8">
+        <v>5.7523148148148151E-3</v>
+      </c>
+    </row>
+    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A613" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B613">
+        <v>10</v>
+      </c>
+      <c r="C613" t="s">
+        <v>17</v>
+      </c>
+      <c r="D613" t="s">
+        <v>87</v>
+      </c>
+      <c r="E613" t="s">
+        <v>47</v>
+      </c>
+      <c r="F613" t="s">
+        <v>37</v>
+      </c>
+      <c r="G613">
+        <v>2</v>
+      </c>
+      <c r="H613" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="I613" s="8">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A614" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B614">
+        <v>11</v>
+      </c>
+      <c r="C614" t="s">
+        <v>17</v>
+      </c>
+      <c r="D614" t="s">
+        <v>86</v>
+      </c>
+      <c r="E614" t="s">
+        <v>33</v>
+      </c>
+      <c r="F614" t="s">
+        <v>6</v>
+      </c>
+      <c r="G614">
+        <v>367</v>
+      </c>
+      <c r="H614" s="8">
+        <v>0</v>
+      </c>
+      <c r="I614" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A615" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B615">
+        <v>11</v>
+      </c>
+      <c r="C615" t="s">
+        <v>17</v>
+      </c>
+      <c r="D615" t="s">
+        <v>86</v>
+      </c>
+      <c r="E615" t="s">
+        <v>32</v>
+      </c>
+      <c r="F615" t="s">
+        <v>6</v>
+      </c>
+      <c r="G615">
+        <v>1075</v>
+      </c>
+      <c r="H615" s="8">
+        <v>0</v>
+      </c>
+      <c r="I615" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A616" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B616">
+        <v>11</v>
+      </c>
+      <c r="C616" t="s">
+        <v>17</v>
+      </c>
+      <c r="D616" t="s">
+        <v>86</v>
+      </c>
+      <c r="E616" t="s">
+        <v>34</v>
+      </c>
+      <c r="F616" t="s">
+        <v>6</v>
+      </c>
+      <c r="G616">
+        <v>225</v>
+      </c>
+      <c r="H616" s="8">
+        <v>0</v>
+      </c>
+      <c r="I616" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A617" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B617">
+        <v>11</v>
+      </c>
+      <c r="C617" t="s">
+        <v>17</v>
+      </c>
+      <c r="D617" t="s">
+        <v>86</v>
+      </c>
+      <c r="E617" t="s">
+        <v>40</v>
+      </c>
+      <c r="F617" t="s">
+        <v>6</v>
+      </c>
+      <c r="G617">
+        <v>1</v>
+      </c>
+      <c r="H617" s="8">
+        <v>0</v>
+      </c>
+      <c r="I617" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A618" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B618">
+        <v>11</v>
+      </c>
+      <c r="C618" t="s">
+        <v>17</v>
+      </c>
+      <c r="D618" t="s">
+        <v>86</v>
+      </c>
+      <c r="E618" t="s">
+        <v>30</v>
+      </c>
+      <c r="F618" t="s">
+        <v>6</v>
+      </c>
+      <c r="G618">
+        <v>4050</v>
+      </c>
+      <c r="H618" s="8">
+        <v>0</v>
+      </c>
+      <c r="I618" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A619" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B619">
+        <v>11</v>
+      </c>
+      <c r="C619" t="s">
+        <v>17</v>
+      </c>
+      <c r="D619" t="s">
+        <v>86</v>
+      </c>
+      <c r="E619" t="s">
+        <v>29</v>
+      </c>
+      <c r="F619" t="s">
+        <v>6</v>
+      </c>
+      <c r="G619">
+        <v>14779</v>
+      </c>
+      <c r="H619" s="8">
+        <v>0</v>
+      </c>
+      <c r="I619" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A620" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B620">
+        <v>11</v>
+      </c>
+      <c r="C620" t="s">
+        <v>17</v>
+      </c>
+      <c r="D620" t="s">
+        <v>86</v>
+      </c>
+      <c r="E620" t="s">
+        <v>45</v>
+      </c>
+      <c r="F620" t="s">
+        <v>6</v>
+      </c>
+      <c r="G620">
+        <v>1</v>
+      </c>
+      <c r="H620" s="8">
+        <v>0</v>
+      </c>
+      <c r="I620" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A621" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B621">
+        <v>11</v>
+      </c>
+      <c r="C621" t="s">
+        <v>17</v>
+      </c>
+      <c r="D621" t="s">
+        <v>86</v>
+      </c>
+      <c r="E621" t="s">
+        <v>41</v>
+      </c>
+      <c r="F621" t="s">
+        <v>88</v>
+      </c>
+      <c r="G621">
+        <v>1</v>
+      </c>
+      <c r="H621" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I621" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A622" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B622">
+        <v>11</v>
+      </c>
+      <c r="C622" t="s">
+        <v>17</v>
+      </c>
+      <c r="D622" t="s">
+        <v>86</v>
+      </c>
+      <c r="E622" t="s">
+        <v>41</v>
+      </c>
+      <c r="F622" t="s">
+        <v>88</v>
+      </c>
+      <c r="G622">
+        <v>1</v>
+      </c>
+      <c r="H622" s="8">
         <v>2.3148148148148149E-4</v>
       </c>
-      <c r="I589" s="8">
+      <c r="I622" s="8">
         <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A623" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B623">
+        <v>11</v>
+      </c>
+      <c r="C623" t="s">
+        <v>17</v>
+      </c>
+      <c r="D623" t="s">
+        <v>86</v>
+      </c>
+      <c r="E623" t="s">
+        <v>41</v>
+      </c>
+      <c r="F623" t="s">
+        <v>88</v>
+      </c>
+      <c r="G623">
+        <v>1</v>
+      </c>
+      <c r="H623" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="I623" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A624" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B624">
+        <v>11</v>
+      </c>
+      <c r="C624" t="s">
+        <v>17</v>
+      </c>
+      <c r="D624" t="s">
+        <v>86</v>
+      </c>
+      <c r="E624" t="s">
+        <v>41</v>
+      </c>
+      <c r="F624" t="s">
+        <v>88</v>
+      </c>
+      <c r="G624">
+        <v>1</v>
+      </c>
+      <c r="H624" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="I624" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A625" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B625">
+        <v>11</v>
+      </c>
+      <c r="C625" t="s">
+        <v>17</v>
+      </c>
+      <c r="D625" t="s">
+        <v>86</v>
+      </c>
+      <c r="E625" t="s">
+        <v>41</v>
+      </c>
+      <c r="F625" t="s">
+        <v>88</v>
+      </c>
+      <c r="G625">
+        <v>1</v>
+      </c>
+      <c r="H625" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="I625" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A626" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B626">
+        <v>11</v>
+      </c>
+      <c r="C626" t="s">
+        <v>17</v>
+      </c>
+      <c r="D626" t="s">
+        <v>86</v>
+      </c>
+      <c r="E626" t="s">
+        <v>41</v>
+      </c>
+      <c r="F626" t="s">
+        <v>88</v>
+      </c>
+      <c r="G626">
+        <v>2</v>
+      </c>
+      <c r="H626" s="8">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="I626" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A627" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B627">
+        <v>11</v>
+      </c>
+      <c r="C627" t="s">
+        <v>17</v>
+      </c>
+      <c r="D627" t="s">
+        <v>86</v>
+      </c>
+      <c r="E627" t="s">
+        <v>41</v>
+      </c>
+      <c r="F627" t="s">
+        <v>88</v>
+      </c>
+      <c r="G627">
+        <v>2</v>
+      </c>
+      <c r="H627" s="8">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="I627" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A628" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B628">
+        <v>11</v>
+      </c>
+      <c r="C628" t="s">
+        <v>17</v>
+      </c>
+      <c r="D628" t="s">
+        <v>86</v>
+      </c>
+      <c r="E628" t="s">
+        <v>38</v>
+      </c>
+      <c r="F628" t="s">
+        <v>37</v>
+      </c>
+      <c r="G628">
+        <v>14</v>
+      </c>
+      <c r="H628" s="8">
+        <v>2.8587962962962963E-3</v>
+      </c>
+      <c r="I628" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A629" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B629">
+        <v>11</v>
+      </c>
+      <c r="C629" t="s">
+        <v>17</v>
+      </c>
+      <c r="D629" t="s">
+        <v>86</v>
+      </c>
+      <c r="E629" t="s">
+        <v>39</v>
+      </c>
+      <c r="F629" t="s">
+        <v>37</v>
+      </c>
+      <c r="G629">
+        <v>3</v>
+      </c>
+      <c r="H629" s="8">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="I629" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A630" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B630">
+        <v>11</v>
+      </c>
+      <c r="C630" t="s">
+        <v>17</v>
+      </c>
+      <c r="D630" t="s">
+        <v>86</v>
+      </c>
+      <c r="E630" t="s">
+        <v>36</v>
+      </c>
+      <c r="F630" t="s">
+        <v>37</v>
+      </c>
+      <c r="G630">
+        <v>70</v>
+      </c>
+      <c r="H630" s="8">
+        <v>7.9976851851851858E-3</v>
+      </c>
+      <c r="I630" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A631" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B631">
+        <v>11</v>
+      </c>
+      <c r="C631" t="s">
+        <v>17</v>
+      </c>
+      <c r="D631" t="s">
+        <v>86</v>
+      </c>
+      <c r="E631" t="s">
+        <v>53</v>
+      </c>
+      <c r="F631" t="s">
+        <v>37</v>
+      </c>
+      <c r="G631">
+        <v>1</v>
+      </c>
+      <c r="H631" s="8">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="I631" s="8">
+        <v>6.5972222222222224E-4</v>
+      </c>
+    </row>
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A632" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B632">
+        <v>11</v>
+      </c>
+      <c r="C632" t="s">
+        <v>17</v>
+      </c>
+      <c r="D632" t="s">
+        <v>86</v>
+      </c>
+      <c r="E632" t="s">
+        <v>31</v>
+      </c>
+      <c r="F632" t="s">
+        <v>6</v>
+      </c>
+      <c r="G632">
+        <v>1472</v>
+      </c>
+      <c r="H632" s="8">
+        <v>0</v>
+      </c>
+      <c r="I632" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A633" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B633">
+        <v>11</v>
+      </c>
+      <c r="C633" t="s">
+        <v>17</v>
+      </c>
+      <c r="D633" t="s">
+        <v>86</v>
+      </c>
+      <c r="E633" t="s">
+        <v>44</v>
+      </c>
+      <c r="F633" t="s">
+        <v>37</v>
+      </c>
+      <c r="G633">
+        <v>2</v>
+      </c>
+      <c r="H633" s="8">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="I633" s="8">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A634" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B634">
+        <v>11</v>
+      </c>
+      <c r="C634" t="s">
+        <v>17</v>
+      </c>
+      <c r="D634" t="s">
+        <v>86</v>
+      </c>
+      <c r="E634" t="s">
+        <v>35</v>
+      </c>
+      <c r="F634" t="s">
+        <v>6</v>
+      </c>
+      <c r="G634">
+        <v>215</v>
+      </c>
+      <c r="H634" s="8">
+        <v>0</v>
+      </c>
+      <c r="I634" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A635" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B635">
+        <v>11</v>
+      </c>
+      <c r="C635" t="s">
+        <v>17</v>
+      </c>
+      <c r="D635" t="s">
+        <v>87</v>
+      </c>
+      <c r="E635" t="s">
+        <v>46</v>
+      </c>
+      <c r="F635" t="s">
+        <v>37</v>
+      </c>
+      <c r="G635">
+        <v>1</v>
+      </c>
+      <c r="H635" s="8">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="I635" s="8">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A636" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B636">
+        <v>11</v>
+      </c>
+      <c r="C636" t="s">
+        <v>17</v>
+      </c>
+      <c r="D636" t="s">
+        <v>87</v>
+      </c>
+      <c r="E636" t="s">
+        <v>42</v>
+      </c>
+      <c r="F636" t="s">
+        <v>37</v>
+      </c>
+      <c r="G636">
+        <v>1</v>
+      </c>
+      <c r="H636" s="8">
+        <v>2.2800925925925927E-3</v>
+      </c>
+      <c r="I636" s="8">
+        <v>2.2800925925925927E-3</v>
+      </c>
+    </row>
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A637" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B637">
+        <v>11</v>
+      </c>
+      <c r="C637" t="s">
+        <v>17</v>
+      </c>
+      <c r="D637" t="s">
+        <v>87</v>
+      </c>
+      <c r="E637" t="s">
+        <v>49</v>
+      </c>
+      <c r="F637" t="s">
+        <v>37</v>
+      </c>
+      <c r="G637">
+        <v>1</v>
+      </c>
+      <c r="H637" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="I637" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A638" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B638">
+        <v>11</v>
+      </c>
+      <c r="C638" t="s">
+        <v>17</v>
+      </c>
+      <c r="D638" t="s">
+        <v>87</v>
+      </c>
+      <c r="E638" t="s">
+        <v>68</v>
+      </c>
+      <c r="F638" t="s">
+        <v>11</v>
+      </c>
+      <c r="G638">
+        <v>1</v>
+      </c>
+      <c r="H638" s="8">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="I638" s="8">
+        <v>6.5624999999999998E-3</v>
+      </c>
+    </row>
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A639" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B639">
+        <v>11</v>
+      </c>
+      <c r="C639" t="s">
+        <v>17</v>
+      </c>
+      <c r="D639" t="s">
+        <v>87</v>
+      </c>
+      <c r="E639" t="s">
+        <v>58</v>
+      </c>
+      <c r="F639" t="s">
+        <v>11</v>
+      </c>
+      <c r="G639">
+        <v>1</v>
+      </c>
+      <c r="H639" s="8">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="I639" s="8">
+        <v>7.2453703703703708E-3</v>
+      </c>
+    </row>
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A640" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B640">
+        <v>11</v>
+      </c>
+      <c r="C640" t="s">
+        <v>17</v>
+      </c>
+      <c r="D640" t="s">
+        <v>87</v>
+      </c>
+      <c r="E640" t="s">
+        <v>47</v>
+      </c>
+      <c r="F640" t="s">
+        <v>37</v>
+      </c>
+      <c r="G640">
+        <v>2</v>
+      </c>
+      <c r="H640" s="8">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="I640" s="8">
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A9AE015-0C39-4191-9E45-59AF43879E3F}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B4ED3E-6885-4BF1-8712-3D94D11CB437}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="91">
   <si>
     <t>Dt</t>
   </si>
@@ -702,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V208"/>
+  <dimension ref="A1:V211"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -12946,7 +12946,7 @@
         <v>8</v>
       </c>
       <c r="F202" s="1">
-        <v>45998</v>
+        <v>49887</v>
       </c>
       <c r="G202" s="1">
         <v>23526</v>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
       <c r="S202" s="1">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="V202" s="2">
         <v>48.703200000000002</v>
@@ -13073,7 +13073,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="1">
-        <v>45998</v>
+        <v>49887</v>
       </c>
       <c r="G204" s="1">
         <v>38879</v>
@@ -13109,7 +13109,7 @@
         <v>1</v>
       </c>
       <c r="S204" s="1">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="V204" s="2">
         <v>48.9268</v>
@@ -13200,7 +13200,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="1">
-        <v>45998</v>
+        <v>49887</v>
       </c>
       <c r="G206" s="1">
         <v>66649</v>
@@ -13236,7 +13236,7 @@
         <v>0</v>
       </c>
       <c r="S206" s="1">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="V206" s="2">
         <v>82.300399999999996</v>
@@ -13262,52 +13262,52 @@
         <v>25830</v>
       </c>
       <c r="G207" s="1">
-        <v>22284</v>
+        <v>37763</v>
       </c>
       <c r="H207" s="1">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="I207" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J207" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K207" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L207" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M207" s="1">
         <v>2</v>
       </c>
       <c r="N207" s="4">
-        <v>1.3888888888888889E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
       <c r="O207" s="4">
         <v>2.7777777777777778E-4</v>
       </c>
       <c r="P207" s="5">
-        <v>4.4000000000000003E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q207" s="5">
-        <v>0.33329999999999999</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="R207" s="6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S207" s="1">
-        <v>0.86</v>
+        <v>1.46</v>
       </c>
       <c r="T207" s="5">
-        <v>0.16669999999999999</v>
+        <v>9.0899999999999995E-2</v>
       </c>
       <c r="U207" s="5">
-        <v>0.22220000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="V207" s="2">
-        <v>20.404800000000002</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="208" spans="1:22" x14ac:dyDescent="0.3">
@@ -13327,13 +13327,13 @@
         <v>13</v>
       </c>
       <c r="F208" s="1">
-        <v>45998</v>
+        <v>49887</v>
       </c>
       <c r="G208" s="1">
-        <v>33844</v>
+        <v>52946</v>
       </c>
       <c r="H208" s="1">
-        <v>298</v>
+        <v>381</v>
       </c>
       <c r="I208" s="1">
         <v>3</v>
@@ -13351,22 +13351,208 @@
         <v>2</v>
       </c>
       <c r="O208" s="4">
-        <v>2.199074074074074E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="P208" s="5">
-        <v>8.8000000000000005E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="Q208" s="5">
-        <v>1.01E-2</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="R208" s="5">
         <v>0.66669999999999996</v>
       </c>
       <c r="S208" s="1">
-        <v>0.74</v>
+        <v>1.06</v>
       </c>
       <c r="V208" s="2">
-        <v>44.023200000000003</v>
+        <v>57.127200000000002</v>
+      </c>
+    </row>
+    <row r="209" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A209" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B209" s="1">
+        <v>12</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" s="1">
+        <v>12</v>
+      </c>
+      <c r="E209" s="1">
+        <v>1</v>
+      </c>
+      <c r="F209" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G209" s="1">
+        <v>1847</v>
+      </c>
+      <c r="H209" s="1">
+        <v>12</v>
+      </c>
+      <c r="I209" s="1">
+        <v>1</v>
+      </c>
+      <c r="J209" s="1">
+        <v>0</v>
+      </c>
+      <c r="K209" s="1">
+        <v>1</v>
+      </c>
+      <c r="L209" s="1">
+        <v>1</v>
+      </c>
+      <c r="M209" s="1">
+        <v>1</v>
+      </c>
+      <c r="N209" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="O209" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P209" s="5">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="Q209" s="6">
+        <v>1</v>
+      </c>
+      <c r="R209" s="6">
+        <v>1</v>
+      </c>
+      <c r="S209" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="T209" s="6">
+        <v>0</v>
+      </c>
+      <c r="U209" s="6">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2">
+        <v>2.7248000000000001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A210" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B210" s="1">
+        <v>12</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D210" s="1">
+        <v>0</v>
+      </c>
+      <c r="E210" s="1">
+        <v>15</v>
+      </c>
+      <c r="F210" s="1">
+        <v>49887</v>
+      </c>
+      <c r="G210" s="1">
+        <v>28940</v>
+      </c>
+      <c r="H210" s="1">
+        <v>569</v>
+      </c>
+      <c r="I210" s="1">
+        <v>3</v>
+      </c>
+      <c r="J210" s="1">
+        <v>0</v>
+      </c>
+      <c r="K210" s="1">
+        <v>0</v>
+      </c>
+      <c r="L210" s="1">
+        <v>0</v>
+      </c>
+      <c r="M210" s="1">
+        <v>1</v>
+      </c>
+      <c r="O210" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P210" s="5">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="Q210" s="5">
+        <v>5.3E-3</v>
+      </c>
+      <c r="R210" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S210" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="V210" s="2">
+        <v>58.635199999999998</v>
+      </c>
+    </row>
+    <row r="211" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A211" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B211" s="1">
+        <v>13</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D211" s="1">
+        <v>0</v>
+      </c>
+      <c r="E211" s="1">
+        <v>15</v>
+      </c>
+      <c r="F211" s="1">
+        <v>49887</v>
+      </c>
+      <c r="G211" s="1">
+        <v>72585</v>
+      </c>
+      <c r="H211" s="1">
+        <v>667</v>
+      </c>
+      <c r="I211" s="1">
+        <v>6</v>
+      </c>
+      <c r="J211" s="1">
+        <v>0</v>
+      </c>
+      <c r="K211" s="1">
+        <v>0</v>
+      </c>
+      <c r="L211" s="1">
+        <v>0</v>
+      </c>
+      <c r="M211" s="1">
+        <v>2</v>
+      </c>
+      <c r="O211" s="4">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="P211" s="5">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="Q211" s="5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="R211" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S211" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="V211" s="2">
+        <v>90.87</v>
       </c>
     </row>
   </sheetData>
@@ -13377,7 +13563,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I640"/>
+  <dimension ref="A1:I659"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -31188,7 +31374,7 @@
         <v>6</v>
       </c>
       <c r="G614">
-        <v>367</v>
+        <v>510</v>
       </c>
       <c r="H614" s="8">
         <v>0</v>
@@ -31217,7 +31403,7 @@
         <v>6</v>
       </c>
       <c r="G615">
-        <v>1075</v>
+        <v>1394</v>
       </c>
       <c r="H615" s="8">
         <v>0</v>
@@ -31246,7 +31432,7 @@
         <v>6</v>
       </c>
       <c r="G616">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="H616" s="8">
         <v>0</v>
@@ -31275,7 +31461,7 @@
         <v>6</v>
       </c>
       <c r="G617">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H617" s="8">
         <v>0</v>
@@ -31304,7 +31490,7 @@
         <v>6</v>
       </c>
       <c r="G618">
-        <v>4050</v>
+        <v>5661</v>
       </c>
       <c r="H618" s="8">
         <v>0</v>
@@ -31333,7 +31519,7 @@
         <v>6</v>
       </c>
       <c r="G619">
-        <v>14779</v>
+        <v>27306</v>
       </c>
       <c r="H619" s="8">
         <v>0</v>
@@ -31385,19 +31571,19 @@
         <v>86</v>
       </c>
       <c r="E621" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F621" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G621">
         <v>1</v>
       </c>
       <c r="H621" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I621" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.3">
@@ -31539,10 +31725,10 @@
         <v>2</v>
       </c>
       <c r="H626" s="8">
-        <v>4.7453703703703704E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I626" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.3">
@@ -31588,19 +31774,19 @@
         <v>86</v>
       </c>
       <c r="E628" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F628" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G628">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H628" s="8">
-        <v>2.8587962962962963E-3</v>
+        <v>6.7129629629629625E-4</v>
       </c>
       <c r="I628" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.3">
@@ -31617,16 +31803,16 @@
         <v>86</v>
       </c>
       <c r="E629" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F629" t="s">
         <v>37</v>
       </c>
       <c r="G629">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H629" s="8">
-        <v>6.2500000000000001E-4</v>
+        <v>5.7986111111111112E-3</v>
       </c>
       <c r="I629" s="8">
         <v>2.0833333333333335E-4</v>
@@ -31646,19 +31832,19 @@
         <v>86</v>
       </c>
       <c r="E630" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F630" t="s">
         <v>37</v>
       </c>
       <c r="G630">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="H630" s="8">
-        <v>7.9976851851851858E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="I630" s="8">
-        <v>1.0416666666666667E-4</v>
+        <v>6.9444444444444447E-4</v>
       </c>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.3">
@@ -31675,19 +31861,19 @@
         <v>86</v>
       </c>
       <c r="E631" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F631" t="s">
         <v>37</v>
       </c>
       <c r="G631">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H631" s="8">
-        <v>6.5972222222222224E-4</v>
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="I631" s="8">
-        <v>6.5972222222222224E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.3">
@@ -31704,19 +31890,19 @@
         <v>86</v>
       </c>
       <c r="E632" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F632" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G632">
-        <v>1472</v>
+        <v>1</v>
       </c>
       <c r="H632" s="8">
-        <v>0</v>
+        <v>1.6203703703703703E-4</v>
       </c>
       <c r="I632" s="8">
-        <v>0</v>
+        <v>1.6203703703703703E-4</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.3">
@@ -31733,19 +31919,19 @@
         <v>86</v>
       </c>
       <c r="E633" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F633" t="s">
         <v>37</v>
       </c>
       <c r="G633">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="H633" s="8">
-        <v>1.1574074074074075E-4</v>
+        <v>1.2673611111111111E-2</v>
       </c>
       <c r="I633" s="8">
-        <v>5.7870370370370373E-5</v>
+        <v>1.0416666666666667E-4</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.3">
@@ -31762,19 +31948,19 @@
         <v>86</v>
       </c>
       <c r="E634" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F634" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G634">
-        <v>215</v>
+        <v>1</v>
       </c>
       <c r="H634" s="8">
-        <v>0</v>
+        <v>2.8935185185185184E-4</v>
       </c>
       <c r="I634" s="8">
-        <v>0</v>
+        <v>2.8935185185185184E-4</v>
       </c>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.3">
@@ -31788,22 +31974,22 @@
         <v>17</v>
       </c>
       <c r="D635" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E635" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F635" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G635">
         <v>1</v>
       </c>
       <c r="H635" s="8">
-        <v>4.6296296296296294E-5</v>
+        <v>3.4722222222222224E-4</v>
       </c>
       <c r="I635" s="8">
-        <v>4.6296296296296294E-5</v>
+        <v>3.4722222222222224E-4</v>
       </c>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.3">
@@ -31817,10 +32003,10 @@
         <v>17</v>
       </c>
       <c r="D636" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E636" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F636" t="s">
         <v>37</v>
@@ -31829,10 +32015,10 @@
         <v>1</v>
       </c>
       <c r="H636" s="8">
-        <v>2.2800925925925927E-3</v>
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="I636" s="8">
-        <v>2.2800925925925927E-3</v>
+        <v>6.5972222222222224E-4</v>
       </c>
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.3">
@@ -31846,22 +32032,22 @@
         <v>17</v>
       </c>
       <c r="D637" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E637" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F637" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G637">
-        <v>1</v>
+        <v>2083</v>
       </c>
       <c r="H637" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>0</v>
       </c>
       <c r="I637" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.3">
@@ -31875,22 +32061,22 @@
         <v>17</v>
       </c>
       <c r="D638" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E638" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F638" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G638">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H638" s="8">
-        <v>6.5624999999999998E-3</v>
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="I638" s="8">
-        <v>6.5624999999999998E-3</v>
+        <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.3">
@@ -31904,22 +32090,22 @@
         <v>17</v>
       </c>
       <c r="D639" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E639" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F639" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G639">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="H639" s="8">
-        <v>7.2453703703703708E-3</v>
+        <v>0</v>
       </c>
       <c r="I639" s="8">
-        <v>7.2453703703703708E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.3">
@@ -31936,19 +32122,570 @@
         <v>87</v>
       </c>
       <c r="E640" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F640" t="s">
         <v>37</v>
       </c>
       <c r="G640">
+        <v>1</v>
+      </c>
+      <c r="H640" s="8">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="I640" s="8">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A641" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B641">
+        <v>11</v>
+      </c>
+      <c r="C641" t="s">
+        <v>17</v>
+      </c>
+      <c r="D641" t="s">
+        <v>87</v>
+      </c>
+      <c r="E641" t="s">
+        <v>42</v>
+      </c>
+      <c r="F641" t="s">
+        <v>37</v>
+      </c>
+      <c r="G641">
         <v>2</v>
       </c>
-      <c r="H640" s="8">
+      <c r="H641" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I641" s="8">
+        <v>1.25E-3</v>
+      </c>
+    </row>
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A642" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B642">
+        <v>11</v>
+      </c>
+      <c r="C642" t="s">
+        <v>17</v>
+      </c>
+      <c r="D642" t="s">
+        <v>87</v>
+      </c>
+      <c r="E642" t="s">
+        <v>49</v>
+      </c>
+      <c r="F642" t="s">
+        <v>37</v>
+      </c>
+      <c r="G642">
+        <v>1</v>
+      </c>
+      <c r="H642" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="I642" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A643" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B643">
+        <v>11</v>
+      </c>
+      <c r="C643" t="s">
+        <v>17</v>
+      </c>
+      <c r="D643" t="s">
+        <v>87</v>
+      </c>
+      <c r="E643" t="s">
+        <v>60</v>
+      </c>
+      <c r="F643" t="s">
+        <v>37</v>
+      </c>
+      <c r="G643">
+        <v>1</v>
+      </c>
+      <c r="H643" s="8">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="I643" s="8">
+        <v>8.1018518518518516E-4</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A644" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B644">
+        <v>11</v>
+      </c>
+      <c r="C644" t="s">
+        <v>17</v>
+      </c>
+      <c r="D644" t="s">
+        <v>87</v>
+      </c>
+      <c r="E644" t="s">
+        <v>68</v>
+      </c>
+      <c r="F644" t="s">
+        <v>11</v>
+      </c>
+      <c r="G644">
+        <v>1</v>
+      </c>
+      <c r="H644" s="8">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="I644" s="8">
+        <v>6.5624999999999998E-3</v>
+      </c>
+    </row>
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A645" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B645">
+        <v>11</v>
+      </c>
+      <c r="C645" t="s">
+        <v>17</v>
+      </c>
+      <c r="D645" t="s">
+        <v>87</v>
+      </c>
+      <c r="E645" t="s">
+        <v>58</v>
+      </c>
+      <c r="F645" t="s">
+        <v>11</v>
+      </c>
+      <c r="G645">
+        <v>1</v>
+      </c>
+      <c r="H645" s="8">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="I645" s="8">
+        <v>7.2453703703703708E-3</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A646" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B646">
+        <v>11</v>
+      </c>
+      <c r="C646" t="s">
+        <v>17</v>
+      </c>
+      <c r="D646" t="s">
+        <v>87</v>
+      </c>
+      <c r="E646" t="s">
+        <v>47</v>
+      </c>
+      <c r="F646" t="s">
+        <v>37</v>
+      </c>
+      <c r="G646">
+        <v>2</v>
+      </c>
+      <c r="H646" s="8">
         <v>6.134259259259259E-4</v>
       </c>
-      <c r="I640" s="8">
+      <c r="I646" s="8">
         <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A647" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B647">
+        <v>12</v>
+      </c>
+      <c r="C647" t="s">
+        <v>17</v>
+      </c>
+      <c r="D647" t="s">
+        <v>86</v>
+      </c>
+      <c r="E647" t="s">
+        <v>33</v>
+      </c>
+      <c r="F647" t="s">
+        <v>6</v>
+      </c>
+      <c r="G647">
+        <v>44</v>
+      </c>
+      <c r="H647" s="8">
+        <v>0</v>
+      </c>
+      <c r="I647" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A648" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B648">
+        <v>12</v>
+      </c>
+      <c r="C648" t="s">
+        <v>17</v>
+      </c>
+      <c r="D648" t="s">
+        <v>86</v>
+      </c>
+      <c r="E648" t="s">
+        <v>32</v>
+      </c>
+      <c r="F648" t="s">
+        <v>6</v>
+      </c>
+      <c r="G648">
+        <v>100</v>
+      </c>
+      <c r="H648" s="8">
+        <v>0</v>
+      </c>
+      <c r="I648" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A649" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B649">
+        <v>12</v>
+      </c>
+      <c r="C649" t="s">
+        <v>17</v>
+      </c>
+      <c r="D649" t="s">
+        <v>86</v>
+      </c>
+      <c r="E649" t="s">
+        <v>34</v>
+      </c>
+      <c r="F649" t="s">
+        <v>6</v>
+      </c>
+      <c r="G649">
+        <v>24</v>
+      </c>
+      <c r="H649" s="8">
+        <v>0</v>
+      </c>
+      <c r="I649" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A650" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B650">
+        <v>12</v>
+      </c>
+      <c r="C650" t="s">
+        <v>17</v>
+      </c>
+      <c r="D650" t="s">
+        <v>86</v>
+      </c>
+      <c r="E650" t="s">
+        <v>30</v>
+      </c>
+      <c r="F650" t="s">
+        <v>6</v>
+      </c>
+      <c r="G650">
+        <v>568</v>
+      </c>
+      <c r="H650" s="8">
+        <v>0</v>
+      </c>
+      <c r="I650" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A651" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B651">
+        <v>12</v>
+      </c>
+      <c r="C651" t="s">
+        <v>17</v>
+      </c>
+      <c r="D651" t="s">
+        <v>86</v>
+      </c>
+      <c r="E651" t="s">
+        <v>29</v>
+      </c>
+      <c r="F651" t="s">
+        <v>6</v>
+      </c>
+      <c r="G651">
+        <v>864</v>
+      </c>
+      <c r="H651" s="8">
+        <v>0</v>
+      </c>
+      <c r="I651" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A652" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B652">
+        <v>12</v>
+      </c>
+      <c r="C652" t="s">
+        <v>17</v>
+      </c>
+      <c r="D652" t="s">
+        <v>86</v>
+      </c>
+      <c r="E652" t="s">
+        <v>45</v>
+      </c>
+      <c r="F652" t="s">
+        <v>6</v>
+      </c>
+      <c r="G652">
+        <v>1</v>
+      </c>
+      <c r="H652" s="8">
+        <v>0</v>
+      </c>
+      <c r="I652" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A653" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B653">
+        <v>12</v>
+      </c>
+      <c r="C653" t="s">
+        <v>17</v>
+      </c>
+      <c r="D653" t="s">
+        <v>86</v>
+      </c>
+      <c r="E653" t="s">
+        <v>41</v>
+      </c>
+      <c r="F653" t="s">
+        <v>88</v>
+      </c>
+      <c r="G653">
+        <v>1</v>
+      </c>
+      <c r="H653" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I653" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="654" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A654" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B654">
+        <v>12</v>
+      </c>
+      <c r="C654" t="s">
+        <v>17</v>
+      </c>
+      <c r="D654" t="s">
+        <v>86</v>
+      </c>
+      <c r="E654" t="s">
+        <v>38</v>
+      </c>
+      <c r="F654" t="s">
+        <v>37</v>
+      </c>
+      <c r="G654">
+        <v>1</v>
+      </c>
+      <c r="H654" s="8">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="I654" s="8">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A655" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B655">
+        <v>12</v>
+      </c>
+      <c r="C655" t="s">
+        <v>17</v>
+      </c>
+      <c r="D655" t="s">
+        <v>86</v>
+      </c>
+      <c r="E655" t="s">
+        <v>39</v>
+      </c>
+      <c r="F655" t="s">
+        <v>37</v>
+      </c>
+      <c r="G655">
+        <v>1</v>
+      </c>
+      <c r="H655" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="I655" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="656" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A656" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B656">
+        <v>12</v>
+      </c>
+      <c r="C656" t="s">
+        <v>17</v>
+      </c>
+      <c r="D656" t="s">
+        <v>86</v>
+      </c>
+      <c r="E656" t="s">
+        <v>36</v>
+      </c>
+      <c r="F656" t="s">
+        <v>37</v>
+      </c>
+      <c r="G656">
+        <v>9</v>
+      </c>
+      <c r="H656" s="8">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="I656" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A657" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B657">
+        <v>12</v>
+      </c>
+      <c r="C657" t="s">
+        <v>17</v>
+      </c>
+      <c r="D657" t="s">
+        <v>86</v>
+      </c>
+      <c r="E657" t="s">
+        <v>31</v>
+      </c>
+      <c r="F657" t="s">
+        <v>6</v>
+      </c>
+      <c r="G657">
+        <v>206</v>
+      </c>
+      <c r="H657" s="8">
+        <v>0</v>
+      </c>
+      <c r="I657" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A658" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B658">
+        <v>12</v>
+      </c>
+      <c r="C658" t="s">
+        <v>17</v>
+      </c>
+      <c r="D658" t="s">
+        <v>86</v>
+      </c>
+      <c r="E658" t="s">
+        <v>35</v>
+      </c>
+      <c r="F658" t="s">
+        <v>6</v>
+      </c>
+      <c r="G658">
+        <v>28</v>
+      </c>
+      <c r="H658" s="8">
+        <v>0</v>
+      </c>
+      <c r="I658" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A659" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B659">
+        <v>12</v>
+      </c>
+      <c r="C659" t="s">
+        <v>17</v>
+      </c>
+      <c r="D659" t="s">
+        <v>87</v>
+      </c>
+      <c r="E659" t="s">
+        <v>54</v>
+      </c>
+      <c r="F659" t="s">
+        <v>11</v>
+      </c>
+      <c r="G659">
+        <v>1</v>
+      </c>
+      <c r="H659" s="8">
+        <v>6.0648148148148145E-3</v>
+      </c>
+      <c r="I659" s="8">
+        <v>6.0648148148148145E-3</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B4ED3E-6885-4BF1-8712-3D94D11CB437}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08AA15AF-6178-478B-88FD-0652281FB8EC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="91">
   <si>
     <t>Dt</t>
   </si>
@@ -702,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V211"/>
+  <dimension ref="A1:V220"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -12946,7 +12946,7 @@
         <v>8</v>
       </c>
       <c r="F202" s="1">
-        <v>49887</v>
+        <v>53489</v>
       </c>
       <c r="G202" s="1">
         <v>23526</v>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
       <c r="S202" s="1">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="V202" s="2">
         <v>48.703200000000002</v>
@@ -13073,7 +13073,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="1">
-        <v>49887</v>
+        <v>53489</v>
       </c>
       <c r="G204" s="1">
         <v>38879</v>
@@ -13109,7 +13109,7 @@
         <v>1</v>
       </c>
       <c r="S204" s="1">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="V204" s="2">
         <v>48.9268</v>
@@ -13200,7 +13200,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="1">
-        <v>49887</v>
+        <v>53489</v>
       </c>
       <c r="G206" s="1">
         <v>66649</v>
@@ -13236,7 +13236,7 @@
         <v>0</v>
       </c>
       <c r="S206" s="1">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V206" s="2">
         <v>82.300399999999996</v>
@@ -13327,7 +13327,7 @@
         <v>13</v>
       </c>
       <c r="F208" s="1">
-        <v>49887</v>
+        <v>53489</v>
       </c>
       <c r="G208" s="1">
         <v>52946</v>
@@ -13363,7 +13363,7 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="S208" s="1">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="V208" s="2">
         <v>57.127200000000002</v>
@@ -13454,7 +13454,7 @@
         <v>15</v>
       </c>
       <c r="F210" s="1">
-        <v>49887</v>
+        <v>53489</v>
       </c>
       <c r="G210" s="1">
         <v>28940</v>
@@ -13490,7 +13490,7 @@
         <v>0.33329999999999999</v>
       </c>
       <c r="S210" s="1">
-        <v>0.57999999999999996</v>
+        <v>0.54</v>
       </c>
       <c r="V210" s="2">
         <v>58.635199999999998</v>
@@ -13513,13 +13513,13 @@
         <v>15</v>
       </c>
       <c r="F211" s="1">
-        <v>49887</v>
+        <v>53489</v>
       </c>
       <c r="G211" s="1">
-        <v>72585</v>
+        <v>77966</v>
       </c>
       <c r="H211" s="1">
-        <v>667</v>
+        <v>739</v>
       </c>
       <c r="I211" s="1">
         <v>6</v>
@@ -13537,22 +13537,598 @@
         <v>2</v>
       </c>
       <c r="O211" s="4">
-        <v>2.4305555555555555E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
       <c r="P211" s="5">
-        <v>9.1999999999999998E-3</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="Q211" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="R211" s="5">
         <v>0.33329999999999999</v>
       </c>
       <c r="S211" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="V211" s="2">
+        <v>102.99120000000001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A212" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B212" s="1">
+        <v>14</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D212" s="1">
+        <v>30</v>
+      </c>
+      <c r="E212" s="1">
+        <v>4</v>
+      </c>
+      <c r="F212" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G212" s="1">
+        <v>25373</v>
+      </c>
+      <c r="H212" s="1">
+        <v>413</v>
+      </c>
+      <c r="I212" s="1">
+        <v>35</v>
+      </c>
+      <c r="J212" s="1">
+        <v>2</v>
+      </c>
+      <c r="K212" s="1">
+        <v>26</v>
+      </c>
+      <c r="L212" s="1">
+        <v>6</v>
+      </c>
+      <c r="M212" s="1">
+        <v>3</v>
+      </c>
+      <c r="N212" s="4">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="O212" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P212" s="5">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="Q212" s="5">
+        <v>0.23080000000000001</v>
+      </c>
+      <c r="R212" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="S212" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="T212" s="5">
+        <v>0.26919999999999999</v>
+      </c>
+      <c r="U212" s="5">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="V212" s="2">
+        <v>63.554400000000001</v>
+      </c>
+    </row>
+    <row r="213" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A213" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B213" s="1">
+        <v>14</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D213" s="1">
+        <v>0</v>
+      </c>
+      <c r="E213" s="1">
+        <v>17</v>
+      </c>
+      <c r="F213" s="1">
+        <v>53489</v>
+      </c>
+      <c r="G213" s="1">
+        <v>20103</v>
+      </c>
+      <c r="H213" s="1">
+        <v>513</v>
+      </c>
+      <c r="I213" s="1">
+        <v>6</v>
+      </c>
+      <c r="J213" s="1">
+        <v>0</v>
+      </c>
+      <c r="K213" s="1">
+        <v>0</v>
+      </c>
+      <c r="L213" s="1">
+        <v>0</v>
+      </c>
+      <c r="M213" s="1">
+        <v>2</v>
+      </c>
+      <c r="O213" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P213" s="5">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="Q213" s="5">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R213" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S213" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="V213" s="2">
+        <v>53.258400000000002</v>
+      </c>
+    </row>
+    <row r="214" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A214" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B214" s="1">
+        <v>15</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" s="1">
+        <v>30</v>
+      </c>
+      <c r="E214" s="1">
+        <v>3</v>
+      </c>
+      <c r="F214" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G214" s="1">
+        <v>39962</v>
+      </c>
+      <c r="H214" s="1">
+        <v>391</v>
+      </c>
+      <c r="I214" s="1">
+        <v>24</v>
+      </c>
+      <c r="J214" s="1">
+        <v>8</v>
+      </c>
+      <c r="K214" s="1">
+        <v>16</v>
+      </c>
+      <c r="L214" s="1">
+        <v>2</v>
+      </c>
+      <c r="M214" s="1">
+        <v>1</v>
+      </c>
+      <c r="N214" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="O214" s="4">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="P214" s="5">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="Q214" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="R214" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="S214" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="T214" s="6">
+        <v>0</v>
+      </c>
+      <c r="U214" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V214" s="2">
+        <v>66.585999999999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A215" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B215" s="1">
+        <v>15</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D215" s="1">
+        <v>0</v>
+      </c>
+      <c r="E215" s="1">
+        <v>8</v>
+      </c>
+      <c r="F215" s="1">
+        <v>53489</v>
+      </c>
+      <c r="G215" s="1">
+        <v>13447</v>
+      </c>
+      <c r="H215" s="1">
+        <v>284</v>
+      </c>
+      <c r="I215" s="1">
+        <v>3</v>
+      </c>
+      <c r="J215" s="1">
+        <v>0</v>
+      </c>
+      <c r="K215" s="1">
+        <v>0</v>
+      </c>
+      <c r="L215" s="1">
+        <v>0</v>
+      </c>
+      <c r="M215" s="1">
+        <v>1</v>
+      </c>
+      <c r="O215" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P215" s="5">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="Q215" s="5">
+        <v>1.06E-2</v>
+      </c>
+      <c r="R215" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S215" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="V215" s="2">
+        <v>24.273599999999998</v>
+      </c>
+    </row>
+    <row r="216" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A216" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B216" s="1">
+        <v>16</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216" s="1">
+        <v>30</v>
+      </c>
+      <c r="E216" s="1">
+        <v>3</v>
+      </c>
+      <c r="F216" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G216" s="1">
+        <v>72859</v>
+      </c>
+      <c r="H216" s="1">
+        <v>394</v>
+      </c>
+      <c r="I216" s="1">
+        <v>35</v>
+      </c>
+      <c r="J216" s="1">
+        <v>4</v>
+      </c>
+      <c r="K216" s="1">
+        <v>24</v>
+      </c>
+      <c r="L216" s="1">
+        <v>2</v>
+      </c>
+      <c r="M216" s="1">
+        <v>0</v>
+      </c>
+      <c r="N216" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="O216" s="4">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P216" s="5">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="Q216" s="5">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="R216" s="6">
+        <v>0</v>
+      </c>
+      <c r="S216" s="1">
+        <v>2.82</v>
+      </c>
+      <c r="T216" s="5">
+        <v>0.29170000000000001</v>
+      </c>
+      <c r="U216" s="5">
+        <v>0.1143</v>
+      </c>
+      <c r="V216" s="2">
+        <v>55.239600000000003</v>
+      </c>
+    </row>
+    <row r="217" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A217" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B217" s="1">
+        <v>16</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D217" s="1">
+        <v>0</v>
+      </c>
+      <c r="E217" s="1">
+        <v>10</v>
+      </c>
+      <c r="F217" s="1">
+        <v>53489</v>
+      </c>
+      <c r="G217" s="1">
+        <v>11418</v>
+      </c>
+      <c r="H217" s="1">
+        <v>362</v>
+      </c>
+      <c r="I217" s="1">
+        <v>2</v>
+      </c>
+      <c r="J217" s="1">
+        <v>0</v>
+      </c>
+      <c r="K217" s="1">
+        <v>0</v>
+      </c>
+      <c r="L217" s="1">
+        <v>0</v>
+      </c>
+      <c r="M217" s="1">
+        <v>1</v>
+      </c>
+      <c r="O217" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P217" s="5">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="Q217" s="5">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="R217" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="S217" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="V217" s="2">
+        <v>25.454000000000001</v>
+      </c>
+    </row>
+    <row r="218" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A218" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B218" s="1">
+        <v>17</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D218" s="1">
+        <v>30</v>
+      </c>
+      <c r="E218" s="1">
+        <v>5</v>
+      </c>
+      <c r="F218" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G218" s="1">
+        <v>37386</v>
+      </c>
+      <c r="H218" s="1">
+        <v>335</v>
+      </c>
+      <c r="I218" s="1">
+        <v>23</v>
+      </c>
+      <c r="J218" s="1">
+        <v>5</v>
+      </c>
+      <c r="K218" s="1">
+        <v>17</v>
+      </c>
+      <c r="L218" s="1">
+        <v>0</v>
+      </c>
+      <c r="M218" s="1">
+        <v>0</v>
+      </c>
+      <c r="N218" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="O218" s="4">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="P218" s="5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Q218" s="6">
+        <v>0</v>
+      </c>
+      <c r="R218" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S218" s="1">
         <v>1.45</v>
       </c>
-      <c r="V211" s="2">
-        <v>90.87</v>
+      <c r="T218" s="5">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="U218" s="5">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="V218" s="2">
+        <v>58.161999999999999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A219" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B219" s="1">
+        <v>17</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D219" s="1">
+        <v>0</v>
+      </c>
+      <c r="E219" s="1">
+        <v>12</v>
+      </c>
+      <c r="F219" s="1">
+        <v>53489</v>
+      </c>
+      <c r="G219" s="1">
+        <v>13625</v>
+      </c>
+      <c r="H219" s="1">
+        <v>293</v>
+      </c>
+      <c r="I219" s="1">
+        <v>1</v>
+      </c>
+      <c r="J219" s="1">
+        <v>0</v>
+      </c>
+      <c r="K219" s="1">
+        <v>0</v>
+      </c>
+      <c r="L219" s="1">
+        <v>0</v>
+      </c>
+      <c r="M219" s="1">
+        <v>1</v>
+      </c>
+      <c r="O219" s="4">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="P219" s="5">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="Q219" s="5">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="R219" s="6">
+        <v>1</v>
+      </c>
+      <c r="S219" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="V219" s="2">
+        <v>36.223199999999999</v>
+      </c>
+    </row>
+    <row r="220" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A220" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B220" s="1">
+        <v>18</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D220" s="1">
+        <v>0</v>
+      </c>
+      <c r="E220" s="1">
+        <v>0</v>
+      </c>
+      <c r="F220" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G220" s="1">
+        <v>6</v>
+      </c>
+      <c r="H220" s="1">
+        <v>0</v>
+      </c>
+      <c r="I220" s="1">
+        <v>0</v>
+      </c>
+      <c r="J220" s="1">
+        <v>0</v>
+      </c>
+      <c r="K220" s="1">
+        <v>0</v>
+      </c>
+      <c r="L220" s="1">
+        <v>0</v>
+      </c>
+      <c r="M220" s="1">
+        <v>0</v>
+      </c>
+      <c r="N220" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O220" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P220" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S220" s="1">
+        <v>0</v>
+      </c>
+      <c r="T220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V220" s="2">
+        <v>1.2063999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -13563,7 +14139,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I659"/>
+  <dimension ref="A1:I801"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -27308,13 +27884,13 @@
         <v>86</v>
       </c>
       <c r="E474" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F474" t="s">
         <v>6</v>
       </c>
       <c r="G474">
-        <v>2666</v>
+        <v>6772</v>
       </c>
       <c r="H474" s="8">
         <v>0</v>
@@ -27337,13 +27913,13 @@
         <v>86</v>
       </c>
       <c r="E475" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F475" t="s">
         <v>6</v>
       </c>
       <c r="G475">
-        <v>6772</v>
+        <v>2666</v>
       </c>
       <c r="H475" s="8">
         <v>0</v>
@@ -27395,13 +27971,13 @@
         <v>86</v>
       </c>
       <c r="E477" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F477" t="s">
         <v>6</v>
       </c>
       <c r="G477">
-        <v>15</v>
+        <v>28205</v>
       </c>
       <c r="H477" s="8">
         <v>0</v>
@@ -27424,13 +28000,13 @@
         <v>86</v>
       </c>
       <c r="E478" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F478" t="s">
         <v>6</v>
       </c>
       <c r="G478">
-        <v>29573</v>
+        <v>15</v>
       </c>
       <c r="H478" s="8">
         <v>0</v>
@@ -27453,19 +28029,19 @@
         <v>86</v>
       </c>
       <c r="E479" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F479" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G479">
-        <v>28205</v>
+        <v>1</v>
       </c>
       <c r="H479" s="8">
-        <v>0</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I479" s="8">
-        <v>0</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.3">
@@ -27482,13 +28058,13 @@
         <v>86</v>
       </c>
       <c r="E480" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F480" t="s">
         <v>6</v>
       </c>
       <c r="G480">
-        <v>13</v>
+        <v>29573</v>
       </c>
       <c r="H480" s="8">
         <v>0</v>
@@ -27511,19 +28087,19 @@
         <v>86</v>
       </c>
       <c r="E481" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F481" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G481">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="H481" s="8">
-        <v>0</v>
+        <v>2.3148148148148149E-4</v>
       </c>
       <c r="I481" s="8">
-        <v>0</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="482" spans="1:9" x14ac:dyDescent="0.3">
@@ -27540,19 +28116,19 @@
         <v>86</v>
       </c>
       <c r="E482" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F482" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G482">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H482" s="8">
-        <v>7.291666666666667E-4</v>
+        <v>0</v>
       </c>
       <c r="I482" s="8">
-        <v>3.5879629629629629E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483" spans="1:9" x14ac:dyDescent="0.3">
@@ -27578,10 +28154,10 @@
         <v>1</v>
       </c>
       <c r="H483" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
       <c r="I483" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.3">
@@ -27598,19 +28174,19 @@
         <v>86</v>
       </c>
       <c r="E484" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F484" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G484">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="H484" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>0</v>
       </c>
       <c r="I484" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:9" x14ac:dyDescent="0.3">
@@ -27633,13 +28209,13 @@
         <v>88</v>
       </c>
       <c r="G485">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H485" s="8">
-        <v>3.3564814814814812E-4</v>
+        <v>7.8703703703703705E-4</v>
       </c>
       <c r="I485" s="8">
-        <v>3.3564814814814812E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="486" spans="1:9" x14ac:dyDescent="0.3">
@@ -27656,16 +28232,16 @@
         <v>86</v>
       </c>
       <c r="E486" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F486" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G486">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H486" s="8">
-        <v>3.5879629629629629E-4</v>
+        <v>7.291666666666667E-4</v>
       </c>
       <c r="I486" s="8">
         <v>3.5879629629629629E-4</v>
@@ -27691,10 +28267,10 @@
         <v>88</v>
       </c>
       <c r="G487">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H487" s="8">
-        <v>4.3981481481481481E-4</v>
+        <v>1.1111111111111111E-3</v>
       </c>
       <c r="I487" s="8">
         <v>2.199074074074074E-4</v>
@@ -27720,13 +28296,13 @@
         <v>88</v>
       </c>
       <c r="G488">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H488" s="8">
-        <v>5.6712962962962967E-4</v>
+        <v>3.3564814814814812E-4</v>
       </c>
       <c r="I488" s="8">
-        <v>2.7777777777777778E-4</v>
+        <v>3.3564814814814812E-4</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.3">
@@ -27749,13 +28325,13 @@
         <v>88</v>
       </c>
       <c r="G489">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H489" s="8">
-        <v>7.8703703703703705E-4</v>
+        <v>1.1226851851851851E-3</v>
       </c>
       <c r="I489" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="490" spans="1:9" x14ac:dyDescent="0.3">
@@ -27778,13 +28354,13 @@
         <v>88</v>
       </c>
       <c r="G490">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H490" s="8">
-        <v>1.6319444444444445E-3</v>
+        <v>4.3981481481481481E-4</v>
       </c>
       <c r="I490" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="491" spans="1:9" x14ac:dyDescent="0.3">
@@ -27807,10 +28383,10 @@
         <v>88</v>
       </c>
       <c r="G491">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H491" s="8">
-        <v>1.1111111111111111E-3</v>
+        <v>2.5231481481481481E-3</v>
       </c>
       <c r="I491" s="8">
         <v>2.199074074074074E-4</v>
@@ -27836,13 +28412,13 @@
         <v>88</v>
       </c>
       <c r="G492">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H492" s="8">
-        <v>1.1226851851851851E-3</v>
+        <v>5.6712962962962967E-4</v>
       </c>
       <c r="I492" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.3">
@@ -27859,19 +28435,19 @@
         <v>86</v>
       </c>
       <c r="E493" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F493" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G493">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H493" s="8">
-        <v>1.7824074074074075E-3</v>
+        <v>1.0763888888888889E-3</v>
       </c>
       <c r="I493" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.3">
@@ -27894,13 +28470,13 @@
         <v>88</v>
       </c>
       <c r="G494">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H494" s="8">
-        <v>1.8518518518518519E-3</v>
+        <v>1.6319444444444445E-3</v>
       </c>
       <c r="I494" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.3">
@@ -27917,19 +28493,19 @@
         <v>86</v>
       </c>
       <c r="E495" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F495" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G495">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H495" s="8">
-        <v>1.4467592592592592E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="I495" s="8">
-        <v>1.5046296296296297E-4</v>
+        <v>3.4722222222222224E-4</v>
       </c>
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.3">
@@ -27952,13 +28528,13 @@
         <v>88</v>
       </c>
       <c r="G496">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H496" s="8">
-        <v>2.5231481481481481E-3</v>
+        <v>1.7824074074074075E-3</v>
       </c>
       <c r="I496" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.3">
@@ -27975,19 +28551,19 @@
         <v>86</v>
       </c>
       <c r="E497" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F497" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G497">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H497" s="8">
-        <v>1.0763888888888889E-3</v>
+        <v>6.2500000000000001E-4</v>
       </c>
       <c r="I497" s="8">
-        <v>3.5879629629629629E-4</v>
+        <v>6.2500000000000001E-4</v>
       </c>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.3">
@@ -28004,19 +28580,19 @@
         <v>86</v>
       </c>
       <c r="E498" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F498" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G498">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="H498" s="8">
-        <v>3.0474537037037036E-2</v>
+        <v>1.8518518518518519E-3</v>
       </c>
       <c r="I498" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.3">
@@ -28033,7 +28609,7 @@
         <v>86</v>
       </c>
       <c r="E499" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F499" t="s">
         <v>37</v>
@@ -28042,10 +28618,10 @@
         <v>2</v>
       </c>
       <c r="H499" s="8">
-        <v>6.9444444444444447E-4</v>
+        <v>1.1226851851851851E-3</v>
       </c>
       <c r="I499" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.3">
@@ -28062,19 +28638,19 @@
         <v>86</v>
       </c>
       <c r="E500" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F500" t="s">
         <v>88</v>
       </c>
       <c r="G500">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H500" s="8">
-        <v>6.2500000000000001E-4</v>
+        <v>1.4467592592592592E-3</v>
       </c>
       <c r="I500" s="8">
-        <v>6.2500000000000001E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.3">
@@ -28091,19 +28667,19 @@
         <v>86</v>
       </c>
       <c r="E501" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F501" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G501">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="H501" s="8">
-        <v>1.2037037037037038E-3</v>
+        <v>1.1574074074074073E-2</v>
       </c>
       <c r="I501" s="8">
-        <v>1.2037037037037038E-3</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.3">
@@ -28120,19 +28696,19 @@
         <v>86</v>
       </c>
       <c r="E502" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F502" t="s">
         <v>37</v>
       </c>
       <c r="G502">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="H502" s="8">
-        <v>1.6666666666666668E-3</v>
+        <v>3.0474537037037036E-2</v>
       </c>
       <c r="I502" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.3">
@@ -28149,19 +28725,19 @@
         <v>86</v>
       </c>
       <c r="E503" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F503" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G503">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H503" s="8">
-        <v>1.1226851851851851E-3</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="I503" s="8">
-        <v>5.5555555555555556E-4</v>
+        <v>1.3888888888888889E-4</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.3">
@@ -28178,19 +28754,19 @@
         <v>86</v>
       </c>
       <c r="E504" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F504" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G504">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H504" s="8">
-        <v>1.7592592592592592E-3</v>
+        <v>1.2037037037037038E-3</v>
       </c>
       <c r="I504" s="8">
-        <v>8.7962962962962962E-4</v>
+        <v>1.2037037037037038E-3</v>
       </c>
     </row>
     <row r="505" spans="1:9" x14ac:dyDescent="0.3">
@@ -28207,19 +28783,19 @@
         <v>86</v>
       </c>
       <c r="E505" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F505" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G505">
         <v>1</v>
       </c>
       <c r="H505" s="8">
-        <v>5.2083333333333333E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I505" s="8">
-        <v>5.2083333333333333E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.3">
@@ -28236,19 +28812,19 @@
         <v>86</v>
       </c>
       <c r="E506" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F506" t="s">
         <v>37</v>
       </c>
       <c r="G506">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="H506" s="8">
-        <v>1.1574074074074073E-2</v>
+        <v>1.6666666666666668E-3</v>
       </c>
       <c r="I506" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.3">
@@ -28265,19 +28841,19 @@
         <v>86</v>
       </c>
       <c r="E507" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F507" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G507">
-        <v>624</v>
+        <v>12608</v>
       </c>
       <c r="H507" s="8">
-        <v>5.9027777777777776E-2</v>
+        <v>0</v>
       </c>
       <c r="I507" s="8">
-        <v>9.2592592592592588E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.3">
@@ -28294,19 +28870,19 @@
         <v>86</v>
       </c>
       <c r="E508" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F508" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G508">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H508" s="8">
-        <v>1.3888888888888889E-4</v>
+        <v>1.7592592592592592E-3</v>
       </c>
       <c r="I508" s="8">
-        <v>1.3888888888888889E-4</v>
+        <v>8.7962962962962962E-4</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.3">
@@ -28323,19 +28899,19 @@
         <v>86</v>
       </c>
       <c r="E509" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F509" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G509">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H509" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I509" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>4.6296296296296294E-5</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.3">
@@ -28352,19 +28928,19 @@
         <v>86</v>
       </c>
       <c r="E510" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F510" t="s">
         <v>37</v>
       </c>
       <c r="G510">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H510" s="8">
-        <v>8.3333333333333339E-4</v>
+        <v>5.2083333333333333E-4</v>
       </c>
       <c r="I510" s="8">
-        <v>2.7777777777777778E-4</v>
+        <v>5.2083333333333333E-4</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -28381,13 +28957,13 @@
         <v>86</v>
       </c>
       <c r="E511" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F511" t="s">
         <v>6</v>
       </c>
       <c r="G511">
-        <v>12608</v>
+        <v>1736</v>
       </c>
       <c r="H511" s="8">
         <v>0</v>
@@ -28410,19 +28986,19 @@
         <v>86</v>
       </c>
       <c r="E512" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F512" t="s">
         <v>37</v>
       </c>
       <c r="G512">
-        <v>8</v>
+        <v>624</v>
       </c>
       <c r="H512" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>5.9027777777777776E-2</v>
       </c>
       <c r="I512" s="8">
-        <v>4.6296296296296294E-5</v>
+        <v>9.2592592592592588E-5</v>
       </c>
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.3">
@@ -28436,22 +29012,22 @@
         <v>17</v>
       </c>
       <c r="D513" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E513" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F513" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G513">
-        <v>1736</v>
+        <v>5</v>
       </c>
       <c r="H513" s="8">
-        <v>0</v>
+        <v>1.2037037037037038E-3</v>
       </c>
       <c r="I513" s="8">
-        <v>0</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.3">
@@ -28465,22 +29041,22 @@
         <v>17</v>
       </c>
       <c r="D514" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E514" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F514" t="s">
         <v>37</v>
       </c>
       <c r="G514">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H514" s="8">
-        <v>1.2037037037037038E-3</v>
+        <v>8.3333333333333339E-4</v>
       </c>
       <c r="I514" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.3">
@@ -28497,19 +29073,19 @@
         <v>87</v>
       </c>
       <c r="E515" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F515" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G515">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H515" s="8">
-        <v>2.0254629629629629E-3</v>
+        <v>4.363425925925926E-3</v>
       </c>
       <c r="I515" s="8">
-        <v>2.0254629629629629E-3</v>
+        <v>6.134259259259259E-4</v>
       </c>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.3">
@@ -28526,19 +29102,19 @@
         <v>87</v>
       </c>
       <c r="E516" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F516" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G516">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H516" s="8">
-        <v>3.7152777777777778E-3</v>
+        <v>2.0254629629629629E-3</v>
       </c>
       <c r="I516" s="8">
-        <v>3.3564814814814812E-4</v>
+        <v>2.0254629629629629E-3</v>
       </c>
     </row>
     <row r="517" spans="1:9" x14ac:dyDescent="0.3">
@@ -28555,19 +29131,19 @@
         <v>87</v>
       </c>
       <c r="E517" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F517" t="s">
         <v>37</v>
       </c>
       <c r="G517">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H517" s="8">
-        <v>4.363425925925926E-3</v>
+        <v>1.8171296296296297E-3</v>
       </c>
       <c r="I517" s="8">
-        <v>6.134259259259259E-4</v>
+        <v>9.0277777777777774E-4</v>
       </c>
     </row>
     <row r="518" spans="1:9" x14ac:dyDescent="0.3">
@@ -28584,19 +29160,19 @@
         <v>87</v>
       </c>
       <c r="E518" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F518" t="s">
         <v>37</v>
       </c>
       <c r="G518">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H518" s="8">
-        <v>1.712962962962963E-3</v>
+        <v>3.7152777777777778E-3</v>
       </c>
       <c r="I518" s="8">
-        <v>4.2824074074074075E-4</v>
+        <v>3.3564814814814812E-4</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.3">
@@ -28613,19 +29189,19 @@
         <v>87</v>
       </c>
       <c r="E519" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F519" t="s">
         <v>37</v>
       </c>
       <c r="G519">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H519" s="8">
-        <v>1.8171296296296297E-3</v>
+        <v>5.9027777777777778E-4</v>
       </c>
       <c r="I519" s="8">
-        <v>9.0277777777777774E-4</v>
+        <v>5.9027777777777778E-4</v>
       </c>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.3">
@@ -28642,19 +29218,19 @@
         <v>87</v>
       </c>
       <c r="E520" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F520" t="s">
         <v>37</v>
       </c>
       <c r="G520">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H520" s="8">
-        <v>5.9027777777777778E-4</v>
+        <v>1.712962962962963E-3</v>
       </c>
       <c r="I520" s="8">
-        <v>5.9027777777777778E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
     </row>
     <row r="521" spans="1:9" x14ac:dyDescent="0.3">
@@ -28787,19 +29363,19 @@
         <v>87</v>
       </c>
       <c r="E525" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F525" t="s">
         <v>11</v>
       </c>
       <c r="G525">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H525" s="8">
-        <v>1.1435185185185185E-2</v>
+        <v>2.9409722222222223E-2</v>
       </c>
       <c r="I525" s="8">
-        <v>5.7175925925925927E-3</v>
+        <v>4.2013888888888891E-3</v>
       </c>
     </row>
     <row r="526" spans="1:9" x14ac:dyDescent="0.3">
@@ -28816,19 +29392,19 @@
         <v>87</v>
       </c>
       <c r="E526" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F526" t="s">
         <v>11</v>
       </c>
       <c r="G526">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H526" s="8">
-        <v>2.9409722222222223E-2</v>
+        <v>1.1435185185185185E-2</v>
       </c>
       <c r="I526" s="8">
-        <v>4.2013888888888891E-3</v>
+        <v>5.7175925925925927E-3</v>
       </c>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.3">
@@ -28903,13 +29479,13 @@
         <v>86</v>
       </c>
       <c r="E529" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F529" t="s">
         <v>6</v>
       </c>
       <c r="G529">
-        <v>4125</v>
+        <v>9119</v>
       </c>
       <c r="H529" s="8">
         <v>0</v>
@@ -28932,13 +29508,13 @@
         <v>86</v>
       </c>
       <c r="E530" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F530" t="s">
         <v>6</v>
       </c>
       <c r="G530">
-        <v>915</v>
+        <v>4125</v>
       </c>
       <c r="H530" s="8">
         <v>0</v>
@@ -28961,13 +29537,13 @@
         <v>86</v>
       </c>
       <c r="E531" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F531" t="s">
         <v>6</v>
       </c>
       <c r="G531">
-        <v>9</v>
+        <v>86280</v>
       </c>
       <c r="H531" s="8">
         <v>0</v>
@@ -28990,13 +29566,13 @@
         <v>86</v>
       </c>
       <c r="E532" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F532" t="s">
         <v>6</v>
       </c>
       <c r="G532">
-        <v>9119</v>
+        <v>915</v>
       </c>
       <c r="H532" s="8">
         <v>0</v>
@@ -29019,19 +29595,19 @@
         <v>86</v>
       </c>
       <c r="E533" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F533" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G533">
-        <v>86280</v>
+        <v>1</v>
       </c>
       <c r="H533" s="8">
-        <v>0</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="I533" s="8">
-        <v>0</v>
+        <v>4.2824074074074075E-4</v>
       </c>
     </row>
     <row r="534" spans="1:9" x14ac:dyDescent="0.3">
@@ -29048,13 +29624,13 @@
         <v>86</v>
       </c>
       <c r="E534" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F534" t="s">
         <v>6</v>
       </c>
       <c r="G534">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H534" s="8">
         <v>0</v>
@@ -29077,19 +29653,19 @@
         <v>86</v>
       </c>
       <c r="E535" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F535" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G535">
         <v>1</v>
       </c>
       <c r="H535" s="8">
-        <v>4.2824074074074075E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="I535" s="8">
-        <v>4.2824074074074075E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.3">
@@ -29106,19 +29682,19 @@
         <v>86</v>
       </c>
       <c r="E536" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F536" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G536">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H536" s="8">
-        <v>1.7361111111111112E-4</v>
+        <v>0</v>
       </c>
       <c r="I536" s="8">
-        <v>1.7361111111111112E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.3">
@@ -29144,10 +29720,10 @@
         <v>1</v>
       </c>
       <c r="H537" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="I537" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.3">
@@ -29173,10 +29749,10 @@
         <v>1</v>
       </c>
       <c r="H538" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>1.7361111111111112E-4</v>
       </c>
       <c r="I538" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>1.7361111111111112E-4</v>
       </c>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.3">
@@ -29199,13 +29775,13 @@
         <v>88</v>
       </c>
       <c r="G539">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H539" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>6.2500000000000001E-4</v>
       </c>
       <c r="I539" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>3.1250000000000001E-4</v>
       </c>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.3">
@@ -29228,13 +29804,13 @@
         <v>88</v>
       </c>
       <c r="G540">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H540" s="8">
-        <v>6.2500000000000001E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="I540" s="8">
-        <v>3.1250000000000001E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.3">
@@ -29257,13 +29833,13 @@
         <v>88</v>
       </c>
       <c r="G541">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H541" s="8">
-        <v>8.564814814814815E-4</v>
+        <v>7.7546296296296293E-4</v>
       </c>
       <c r="I541" s="8">
-        <v>4.2824074074074075E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="542" spans="1:9" x14ac:dyDescent="0.3">
@@ -29286,13 +29862,13 @@
         <v>88</v>
       </c>
       <c r="G542">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H542" s="8">
-        <v>7.7546296296296293E-4</v>
+        <v>8.564814814814815E-4</v>
       </c>
       <c r="I542" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.3">
@@ -29309,19 +29885,19 @@
         <v>86</v>
       </c>
       <c r="E543" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F543" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G543">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H543" s="8">
-        <v>9.2592592592592596E-4</v>
+        <v>3.9351851851851852E-4</v>
       </c>
       <c r="I543" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>3.9351851851851852E-4</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.3">
@@ -29344,13 +29920,13 @@
         <v>88</v>
       </c>
       <c r="G544">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H544" s="8">
-        <v>1.0069444444444444E-3</v>
+        <v>9.2592592592592596E-4</v>
       </c>
       <c r="I544" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.3">
@@ -29370,16 +29946,16 @@
         <v>57</v>
       </c>
       <c r="F545" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G545">
         <v>1</v>
       </c>
       <c r="H545" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="I545" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.3">
@@ -29396,19 +29972,19 @@
         <v>86</v>
       </c>
       <c r="E546" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F546" t="s">
         <v>88</v>
       </c>
       <c r="G546">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H546" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>1.0069444444444444E-3</v>
       </c>
       <c r="I546" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.3">
@@ -29457,16 +30033,16 @@
         <v>50</v>
       </c>
       <c r="F548" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G548">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H548" s="8">
-        <v>2.2222222222222222E-3</v>
+        <v>8.564814814814815E-4</v>
       </c>
       <c r="I548" s="8">
-        <v>7.407407407407407E-4</v>
+        <v>8.564814814814815E-4</v>
       </c>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.3">
@@ -29486,16 +30062,16 @@
         <v>50</v>
       </c>
       <c r="F549" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G549">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H549" s="8">
-        <v>8.564814814814815E-4</v>
+        <v>2.2222222222222222E-3</v>
       </c>
       <c r="I549" s="8">
-        <v>8.564814814814815E-4</v>
+        <v>7.407407407407407E-4</v>
       </c>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.3">
@@ -29541,19 +30117,19 @@
         <v>86</v>
       </c>
       <c r="E551" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="F551" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G551">
         <v>1</v>
       </c>
       <c r="H551" s="8">
-        <v>6.4814814814814813E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
       <c r="I551" s="8">
-        <v>6.4814814814814813E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
     </row>
     <row r="552" spans="1:9" x14ac:dyDescent="0.3">
@@ -29570,19 +30146,19 @@
         <v>86</v>
       </c>
       <c r="E552" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F552" t="s">
         <v>37</v>
       </c>
       <c r="G552">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H552" s="8">
-        <v>9.1435185185185185E-4</v>
+        <v>6.4814814814814813E-4</v>
       </c>
       <c r="I552" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>6.4814814814814813E-4</v>
       </c>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.3">
@@ -29599,19 +30175,19 @@
         <v>86</v>
       </c>
       <c r="E553" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F553" t="s">
         <v>37</v>
       </c>
       <c r="G553">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H553" s="8">
-        <v>5.7523148148148151E-3</v>
+        <v>5.6712962962962967E-4</v>
       </c>
       <c r="I553" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.3">
@@ -29628,19 +30204,19 @@
         <v>86</v>
       </c>
       <c r="E554" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F554" t="s">
         <v>37</v>
       </c>
       <c r="G554">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="H554" s="8">
-        <v>2.0231481481481482E-2</v>
+        <v>9.1435185185185185E-4</v>
       </c>
       <c r="I554" s="8">
-        <v>1.0416666666666667E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.3">
@@ -29657,19 +30233,19 @@
         <v>86</v>
       </c>
       <c r="E555" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F555" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G555">
-        <v>1</v>
+        <v>3407</v>
       </c>
       <c r="H555" s="8">
-        <v>3.5879629629629629E-4</v>
+        <v>0</v>
       </c>
       <c r="I555" s="8">
-        <v>3.5879629629629629E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.3">
@@ -29686,19 +30262,19 @@
         <v>86</v>
       </c>
       <c r="E556" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F556" t="s">
         <v>37</v>
       </c>
       <c r="G556">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H556" s="8">
-        <v>5.6712962962962967E-4</v>
+        <v>5.7523148148148151E-3</v>
       </c>
       <c r="I556" s="8">
-        <v>2.7777777777777778E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.3">
@@ -29715,19 +30291,19 @@
         <v>86</v>
       </c>
       <c r="E557" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F557" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G557">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H557" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>2.3148148148148147E-5</v>
       </c>
       <c r="I557" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.3">
@@ -29744,19 +30320,19 @@
         <v>86</v>
       </c>
       <c r="E558" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F558" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G558">
-        <v>3407</v>
+        <v>182</v>
       </c>
       <c r="H558" s="8">
-        <v>0</v>
+        <v>2.0231481481481482E-2</v>
       </c>
       <c r="I558" s="8">
-        <v>0</v>
+        <v>1.0416666666666667E-4</v>
       </c>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.3">
@@ -29770,22 +30346,22 @@
         <v>17</v>
       </c>
       <c r="D559" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E559" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F559" t="s">
         <v>37</v>
       </c>
       <c r="G559">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H559" s="8">
-        <v>2.3148148148148147E-5</v>
+        <v>5.0925925925925921E-4</v>
       </c>
       <c r="I559" s="8">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.3">
@@ -29802,19 +30378,19 @@
         <v>86</v>
       </c>
       <c r="E560" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F560" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G560">
-        <v>521</v>
+        <v>1</v>
       </c>
       <c r="H560" s="8">
-        <v>0</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="I560" s="8">
-        <v>0</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.3">
@@ -29831,19 +30407,19 @@
         <v>87</v>
       </c>
       <c r="E561" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F561" t="s">
         <v>37</v>
       </c>
       <c r="G561">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H561" s="8">
-        <v>2.5925925925925925E-3</v>
+        <v>6.4814814814814813E-4</v>
       </c>
       <c r="I561" s="8">
-        <v>8.564814814814815E-4</v>
+        <v>6.4814814814814813E-4</v>
       </c>
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.3">
@@ -29857,22 +30433,22 @@
         <v>17</v>
       </c>
       <c r="D562" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E562" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F562" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G562">
-        <v>4</v>
+        <v>521</v>
       </c>
       <c r="H562" s="8">
-        <v>1.8171296296296297E-3</v>
+        <v>0</v>
       </c>
       <c r="I562" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.3">
@@ -29889,19 +30465,19 @@
         <v>87</v>
       </c>
       <c r="E563" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F563" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G563">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H563" s="8">
-        <v>5.0925925925925921E-4</v>
+        <v>4.9768518518518521E-4</v>
       </c>
       <c r="I563" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>4.9768518518518521E-4</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.3">
@@ -29918,19 +30494,19 @@
         <v>87</v>
       </c>
       <c r="E564" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F564" t="s">
         <v>37</v>
       </c>
       <c r="G564">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H564" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>2.5925925925925925E-3</v>
       </c>
       <c r="I564" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>8.564814814814815E-4</v>
       </c>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.3">
@@ -29947,19 +30523,19 @@
         <v>87</v>
       </c>
       <c r="E565" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="F565" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G565">
         <v>1</v>
       </c>
       <c r="H565" s="8">
-        <v>6.4814814814814813E-4</v>
+        <v>1.3020833333333334E-2</v>
       </c>
       <c r="I565" s="8">
-        <v>6.4814814814814813E-4</v>
+        <v>1.3020833333333334E-2</v>
       </c>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.3">
@@ -29976,19 +30552,19 @@
         <v>87</v>
       </c>
       <c r="E566" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F566" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G566">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H566" s="8">
-        <v>4.9768518518518521E-4</v>
+        <v>1.8171296296296297E-3</v>
       </c>
       <c r="I566" s="8">
-        <v>4.9768518518518521E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.3">
@@ -30005,7 +30581,7 @@
         <v>87</v>
       </c>
       <c r="E567" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F567" t="s">
         <v>11</v>
@@ -30014,10 +30590,10 @@
         <v>1</v>
       </c>
       <c r="H567" s="8">
-        <v>1.3020833333333334E-2</v>
+        <v>4.8958333333333336E-3</v>
       </c>
       <c r="I567" s="8">
-        <v>1.3020833333333334E-2</v>
+        <v>4.8958333333333336E-3</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.3">
@@ -30034,19 +30610,19 @@
         <v>87</v>
       </c>
       <c r="E568" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F568" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G568">
         <v>1</v>
       </c>
       <c r="H568" s="8">
-        <v>4.8958333333333336E-3</v>
+        <v>3.9351851851851852E-4</v>
       </c>
       <c r="I568" s="8">
-        <v>4.8958333333333336E-3</v>
+        <v>3.9351851851851852E-4</v>
       </c>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.3">
@@ -30208,19 +30784,19 @@
         <v>86</v>
       </c>
       <c r="E574" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F574" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G574">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H574" s="8">
-        <v>0</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="I574" s="8">
-        <v>0</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.3">
@@ -30237,13 +30813,13 @@
         <v>86</v>
       </c>
       <c r="E575" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F575" t="s">
         <v>6</v>
       </c>
       <c r="G575">
-        <v>13955</v>
+        <v>22</v>
       </c>
       <c r="H575" s="8">
         <v>0</v>
@@ -30266,19 +30842,19 @@
         <v>86</v>
       </c>
       <c r="E576" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F576" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G576">
-        <v>21808</v>
+        <v>1</v>
       </c>
       <c r="H576" s="8">
-        <v>0</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="I576" s="8">
-        <v>0</v>
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.3">
@@ -30295,13 +30871,13 @@
         <v>86</v>
       </c>
       <c r="E577" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F577" t="s">
         <v>6</v>
       </c>
       <c r="G577">
-        <v>2</v>
+        <v>13955</v>
       </c>
       <c r="H577" s="8">
         <v>0</v>
@@ -30324,19 +30900,19 @@
         <v>86</v>
       </c>
       <c r="E578" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F578" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G578">
         <v>1</v>
       </c>
       <c r="H578" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="I578" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.3">
@@ -30353,19 +30929,19 @@
         <v>86</v>
       </c>
       <c r="E579" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F579" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G579">
-        <v>1</v>
+        <v>21808</v>
       </c>
       <c r="H579" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>0</v>
       </c>
       <c r="I579" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.3">
@@ -30388,13 +30964,13 @@
         <v>88</v>
       </c>
       <c r="G580">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H580" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>4.861111111111111E-4</v>
       </c>
       <c r="I580" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.3">
@@ -30411,19 +30987,19 @@
         <v>86</v>
       </c>
       <c r="E581" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F581" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G581">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H581" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>0</v>
       </c>
       <c r="I581" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.3">
@@ -30446,13 +31022,13 @@
         <v>88</v>
       </c>
       <c r="G582">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H582" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>7.1759259259259259E-4</v>
       </c>
       <c r="I582" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.3">
@@ -30469,19 +31045,19 @@
         <v>86</v>
       </c>
       <c r="E583" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F583" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G583">
         <v>1</v>
       </c>
       <c r="H583" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="I583" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.3">
@@ -30504,10 +31080,10 @@
         <v>88</v>
       </c>
       <c r="G584">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H584" s="8">
-        <v>4.861111111111111E-4</v>
+        <v>9.7222222222222219E-4</v>
       </c>
       <c r="I584" s="8">
         <v>2.4305555555555555E-4</v>
@@ -30533,13 +31109,13 @@
         <v>88</v>
       </c>
       <c r="G585">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H585" s="8">
-        <v>7.1759259259259259E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="I585" s="8">
-        <v>3.5879629629629629E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.3">
@@ -30565,10 +31141,10 @@
         <v>4</v>
       </c>
       <c r="H586" s="8">
-        <v>9.7222222222222219E-4</v>
+        <v>1.1458333333333333E-3</v>
       </c>
       <c r="I586" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.3">
@@ -30591,13 +31167,13 @@
         <v>88</v>
       </c>
       <c r="G587">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H587" s="8">
-        <v>9.837962962962962E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I587" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.3">
@@ -30620,13 +31196,13 @@
         <v>88</v>
       </c>
       <c r="G588">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H588" s="8">
-        <v>1.1458333333333333E-3</v>
+        <v>1.2268518518518518E-3</v>
       </c>
       <c r="I588" s="8">
-        <v>2.7777777777777778E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
@@ -30649,13 +31225,13 @@
         <v>88</v>
       </c>
       <c r="G589">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H589" s="8">
-        <v>1.2268518518518518E-3</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="I589" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="590" spans="1:9" x14ac:dyDescent="0.3">
@@ -30672,19 +31248,19 @@
         <v>86</v>
       </c>
       <c r="E590" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F590" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G590">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="H590" s="8">
-        <v>1.5046296296296296E-3</v>
+        <v>1.4305555555555556E-2</v>
       </c>
       <c r="I590" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.3">
@@ -30701,19 +31277,19 @@
         <v>86</v>
       </c>
       <c r="E591" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F591" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G591">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H591" s="8">
-        <v>9.6064814814814819E-4</v>
+        <v>1.5046296296296296E-3</v>
       </c>
       <c r="I591" s="8">
-        <v>4.7453703703703704E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.3">
@@ -30730,19 +31306,19 @@
         <v>86</v>
       </c>
       <c r="E592" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F592" t="s">
         <v>37</v>
       </c>
       <c r="G592">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H592" s="8">
-        <v>1.4305555555555556E-2</v>
+        <v>2.2569444444444442E-3</v>
       </c>
       <c r="I592" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.3">
@@ -30759,19 +31335,19 @@
         <v>86</v>
       </c>
       <c r="E593" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F593" t="s">
         <v>37</v>
       </c>
       <c r="G593">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H593" s="8">
-        <v>2.2569444444444442E-3</v>
+        <v>9.6064814814814819E-4</v>
       </c>
       <c r="I593" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>4.7453703703703704E-4</v>
       </c>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.3">
@@ -30846,19 +31422,19 @@
         <v>86</v>
       </c>
       <c r="E596" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F596" t="s">
         <v>88</v>
       </c>
       <c r="G596">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H596" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>1.3078703703703703E-3</v>
       </c>
       <c r="I596" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.3">
@@ -30884,10 +31460,10 @@
         <v>1</v>
       </c>
       <c r="H597" s="8">
-        <v>5.4398148148148144E-4</v>
+        <v>3.9351851851851852E-4</v>
       </c>
       <c r="I597" s="8">
-        <v>5.4398148148148144E-4</v>
+        <v>3.9351851851851852E-4</v>
       </c>
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.3">
@@ -30904,19 +31480,19 @@
         <v>86</v>
       </c>
       <c r="E598" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F598" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G598">
-        <v>364</v>
+        <v>5930</v>
       </c>
       <c r="H598" s="8">
-        <v>3.9571759259259258E-2</v>
+        <v>0</v>
       </c>
       <c r="I598" s="8">
-        <v>1.0416666666666667E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.3">
@@ -30933,19 +31509,19 @@
         <v>86</v>
       </c>
       <c r="E599" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F599" t="s">
         <v>88</v>
       </c>
       <c r="G599">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H599" s="8">
-        <v>1.3078703703703703E-3</v>
+        <v>5.4398148148148144E-4</v>
       </c>
       <c r="I599" s="8">
-        <v>4.2824074074074075E-4</v>
+        <v>5.4398148148148144E-4</v>
       </c>
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.3">
@@ -30962,19 +31538,19 @@
         <v>86</v>
       </c>
       <c r="E600" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F600" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G600">
-        <v>5930</v>
+        <v>7</v>
       </c>
       <c r="H600" s="8">
-        <v>0</v>
+        <v>3.7037037037037035E-4</v>
       </c>
       <c r="I600" s="8">
-        <v>0</v>
+        <v>4.6296296296296294E-5</v>
       </c>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.3">
@@ -30991,19 +31567,19 @@
         <v>86</v>
       </c>
       <c r="E601" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F601" t="s">
         <v>37</v>
       </c>
       <c r="G601">
-        <v>7</v>
+        <v>364</v>
       </c>
       <c r="H601" s="8">
-        <v>3.7037037037037035E-4</v>
+        <v>3.9571759259259258E-2</v>
       </c>
       <c r="I601" s="8">
-        <v>4.6296296296296294E-5</v>
+        <v>1.0416666666666667E-4</v>
       </c>
     </row>
     <row r="602" spans="1:9" x14ac:dyDescent="0.3">
@@ -31017,22 +31593,22 @@
         <v>17</v>
       </c>
       <c r="D602" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E602" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F602" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G602">
-        <v>1003</v>
+        <v>4</v>
       </c>
       <c r="H602" s="8">
-        <v>0</v>
+        <v>9.7222222222222219E-4</v>
       </c>
       <c r="I602" s="8">
-        <v>0</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.3">
@@ -31046,22 +31622,22 @@
         <v>17</v>
       </c>
       <c r="D603" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E603" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="F603" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G603">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="H603" s="8">
-        <v>1.3078703703703703E-3</v>
+        <v>0</v>
       </c>
       <c r="I603" s="8">
-        <v>1.3078703703703703E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.3">
@@ -31078,19 +31654,19 @@
         <v>87</v>
       </c>
       <c r="E604" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F604" t="s">
         <v>37</v>
       </c>
       <c r="G604">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H604" s="8">
-        <v>1.5509259259259259E-3</v>
+        <v>3.4722222222222224E-4</v>
       </c>
       <c r="I604" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>3.4722222222222224E-4</v>
       </c>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.3">
@@ -31107,19 +31683,19 @@
         <v>87</v>
       </c>
       <c r="E605" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F605" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G605">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H605" s="8">
-        <v>2.0370370370370369E-3</v>
+        <v>1.3078703703703703E-3</v>
       </c>
       <c r="I605" s="8">
-        <v>5.0925925925925921E-4</v>
+        <v>1.3078703703703703E-3</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.3">
@@ -31136,19 +31712,19 @@
         <v>87</v>
       </c>
       <c r="E606" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F606" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G606">
         <v>4</v>
       </c>
       <c r="H606" s="8">
-        <v>9.7222222222222219E-4</v>
+        <v>1.1805555555555556E-3</v>
       </c>
       <c r="I606" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.3">
@@ -31165,19 +31741,19 @@
         <v>87</v>
       </c>
       <c r="E607" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F607" t="s">
         <v>37</v>
       </c>
       <c r="G607">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H607" s="8">
-        <v>1.0185185185185184E-3</v>
+        <v>1.5509259259259259E-3</v>
       </c>
       <c r="I607" s="8">
-        <v>5.0925925925925921E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.3">
@@ -31194,19 +31770,19 @@
         <v>87</v>
       </c>
       <c r="E608" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="F608" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G608">
         <v>1</v>
       </c>
       <c r="H608" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>9.1435185185185185E-4</v>
       </c>
       <c r="I608" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>9.1435185185185185E-4</v>
       </c>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.3">
@@ -31223,19 +31799,19 @@
         <v>87</v>
       </c>
       <c r="E609" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F609" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G609">
         <v>4</v>
       </c>
       <c r="H609" s="8">
-        <v>1.1805555555555556E-3</v>
+        <v>2.0370370370370369E-3</v>
       </c>
       <c r="I609" s="8">
-        <v>2.8935185185185184E-4</v>
+        <v>5.0925925925925921E-4</v>
       </c>
     </row>
     <row r="610" spans="1:9" x14ac:dyDescent="0.3">
@@ -31252,19 +31828,19 @@
         <v>87</v>
       </c>
       <c r="E610" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F610" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G610">
         <v>1</v>
       </c>
       <c r="H610" s="8">
-        <v>2.627314814814815E-3</v>
+        <v>5.7523148148148151E-3</v>
       </c>
       <c r="I610" s="8">
-        <v>2.627314814814815E-3</v>
+        <v>5.7523148148148151E-3</v>
       </c>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.3">
@@ -31281,19 +31857,19 @@
         <v>87</v>
       </c>
       <c r="E611" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F611" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G611">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H611" s="8">
-        <v>9.1435185185185185E-4</v>
+        <v>1.0185185185185184E-3</v>
       </c>
       <c r="I611" s="8">
-        <v>9.1435185185185185E-4</v>
+        <v>5.0925925925925921E-4</v>
       </c>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.3">
@@ -31310,19 +31886,19 @@
         <v>87</v>
       </c>
       <c r="E612" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F612" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G612">
         <v>1</v>
       </c>
       <c r="H612" s="8">
-        <v>5.7523148148148151E-3</v>
+        <v>2.627314814814815E-3</v>
       </c>
       <c r="I612" s="8">
-        <v>5.7523148148148151E-3</v>
+        <v>2.627314814814815E-3</v>
       </c>
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.3">
@@ -31368,13 +31944,13 @@
         <v>86</v>
       </c>
       <c r="E614" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F614" t="s">
         <v>6</v>
       </c>
       <c r="G614">
-        <v>510</v>
+        <v>4</v>
       </c>
       <c r="H614" s="8">
         <v>0</v>
@@ -31397,13 +31973,13 @@
         <v>86</v>
       </c>
       <c r="E615" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F615" t="s">
         <v>6</v>
       </c>
       <c r="G615">
-        <v>1394</v>
+        <v>510</v>
       </c>
       <c r="H615" s="8">
         <v>0</v>
@@ -31426,13 +32002,13 @@
         <v>86</v>
       </c>
       <c r="E616" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F616" t="s">
         <v>6</v>
       </c>
       <c r="G616">
-        <v>324</v>
+        <v>27306</v>
       </c>
       <c r="H616" s="8">
         <v>0</v>
@@ -31455,13 +32031,13 @@
         <v>86</v>
       </c>
       <c r="E617" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F617" t="s">
         <v>6</v>
       </c>
       <c r="G617">
-        <v>4</v>
+        <v>1394</v>
       </c>
       <c r="H617" s="8">
         <v>0</v>
@@ -31484,19 +32060,19 @@
         <v>86</v>
       </c>
       <c r="E618" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F618" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G618">
-        <v>5661</v>
+        <v>1</v>
       </c>
       <c r="H618" s="8">
-        <v>0</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I618" s="8">
-        <v>0</v>
+        <v>4.0509259259259258E-4</v>
       </c>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.3">
@@ -31513,13 +32089,13 @@
         <v>86</v>
       </c>
       <c r="E619" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F619" t="s">
         <v>6</v>
       </c>
       <c r="G619">
-        <v>27306</v>
+        <v>324</v>
       </c>
       <c r="H619" s="8">
         <v>0</v>
@@ -31542,19 +32118,19 @@
         <v>86</v>
       </c>
       <c r="E620" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F620" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G620">
         <v>1</v>
       </c>
       <c r="H620" s="8">
-        <v>0</v>
+        <v>3.4722222222222224E-4</v>
       </c>
       <c r="I620" s="8">
-        <v>0</v>
+        <v>3.4722222222222224E-4</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.3">
@@ -31571,19 +32147,19 @@
         <v>86</v>
       </c>
       <c r="E621" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F621" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G621">
-        <v>1</v>
+        <v>5661</v>
       </c>
       <c r="H621" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>0</v>
       </c>
       <c r="I621" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.3">
@@ -31606,13 +32182,13 @@
         <v>88</v>
       </c>
       <c r="G622">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H622" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>6.7129629629629625E-4</v>
       </c>
       <c r="I622" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.3">
@@ -31629,19 +32205,19 @@
         <v>86</v>
       </c>
       <c r="E623" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F623" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G623">
         <v>1</v>
       </c>
       <c r="H623" s="8">
-        <v>2.7777777777777778E-4</v>
+        <v>0</v>
       </c>
       <c r="I623" s="8">
-        <v>2.7777777777777778E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.3">
@@ -31658,19 +32234,19 @@
         <v>86</v>
       </c>
       <c r="E624" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F624" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G624">
         <v>1</v>
       </c>
       <c r="H624" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="I624" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>6.9444444444444447E-4</v>
       </c>
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.3">
@@ -31696,10 +32272,10 @@
         <v>1</v>
       </c>
       <c r="H625" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
       <c r="I625" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.3">
@@ -31716,19 +32292,19 @@
         <v>86</v>
       </c>
       <c r="E626" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F626" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G626">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="H626" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>1.2673611111111111E-2</v>
       </c>
       <c r="I626" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>1.0416666666666667E-4</v>
       </c>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.3">
@@ -31751,13 +32327,13 @@
         <v>88</v>
       </c>
       <c r="G627">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H627" s="8">
-        <v>5.9027777777777778E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="I627" s="8">
-        <v>2.8935185185185184E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.3">
@@ -31774,19 +32350,19 @@
         <v>86</v>
       </c>
       <c r="E628" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F628" t="s">
         <v>88</v>
       </c>
       <c r="G628">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H628" s="8">
-        <v>6.7129629629629625E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
       <c r="I628" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.3">
@@ -31803,19 +32379,19 @@
         <v>86</v>
       </c>
       <c r="E629" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F629" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G629">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H629" s="8">
-        <v>5.7986111111111112E-3</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="I629" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.3">
@@ -31832,19 +32408,19 @@
         <v>86</v>
       </c>
       <c r="E630" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F630" t="s">
         <v>37</v>
       </c>
       <c r="G630">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H630" s="8">
-        <v>6.9444444444444447E-4</v>
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="I630" s="8">
-        <v>6.9444444444444447E-4</v>
+        <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.3">
@@ -31861,19 +32437,19 @@
         <v>86</v>
       </c>
       <c r="E631" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F631" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G631">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H631" s="8">
-        <v>1.5740740740740741E-3</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I631" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.3">
@@ -31890,19 +32466,19 @@
         <v>86</v>
       </c>
       <c r="E632" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F632" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G632">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="H632" s="8">
-        <v>1.6203703703703703E-4</v>
+        <v>0</v>
       </c>
       <c r="I632" s="8">
-        <v>1.6203703703703703E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.3">
@@ -31919,19 +32495,19 @@
         <v>86</v>
       </c>
       <c r="E633" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F633" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G633">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="H633" s="8">
-        <v>1.2673611111111111E-2</v>
+        <v>5.9027777777777778E-4</v>
       </c>
       <c r="I633" s="8">
-        <v>1.0416666666666667E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.3">
@@ -31945,22 +32521,22 @@
         <v>17</v>
       </c>
       <c r="D634" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E634" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F634" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G634">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H634" s="8">
-        <v>2.8935185185185184E-4</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I634" s="8">
-        <v>2.8935185185185184E-4</v>
+        <v>1.25E-3</v>
       </c>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.3">
@@ -31977,19 +32553,19 @@
         <v>86</v>
       </c>
       <c r="E635" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F635" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G635">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H635" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>5.7986111111111112E-3</v>
       </c>
       <c r="I635" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.3">
@@ -32003,10 +32579,10 @@
         <v>17</v>
       </c>
       <c r="D636" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E636" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F636" t="s">
         <v>37</v>
@@ -32015,10 +32591,10 @@
         <v>1</v>
       </c>
       <c r="H636" s="8">
-        <v>6.5972222222222224E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
       <c r="I636" s="8">
-        <v>6.5972222222222224E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.3">
@@ -32035,19 +32611,19 @@
         <v>86</v>
       </c>
       <c r="E637" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F637" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G637">
-        <v>2083</v>
+        <v>7</v>
       </c>
       <c r="H637" s="8">
-        <v>0</v>
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="I637" s="8">
-        <v>0</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.3">
@@ -32061,22 +32637,22 @@
         <v>17</v>
       </c>
       <c r="D638" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E638" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F638" t="s">
         <v>37</v>
       </c>
       <c r="G638">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H638" s="8">
-        <v>6.5972222222222224E-4</v>
+        <v>8.1018518518518516E-4</v>
       </c>
       <c r="I638" s="8">
-        <v>1.273148148148148E-4</v>
+        <v>8.1018518518518516E-4</v>
       </c>
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.3">
@@ -32093,19 +32669,19 @@
         <v>86</v>
       </c>
       <c r="E639" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F639" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G639">
-        <v>307</v>
+        <v>1</v>
       </c>
       <c r="H639" s="8">
-        <v>0</v>
+        <v>1.6203703703703703E-4</v>
       </c>
       <c r="I639" s="8">
-        <v>0</v>
+        <v>1.6203703703703703E-4</v>
       </c>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.3">
@@ -32122,19 +32698,19 @@
         <v>87</v>
       </c>
       <c r="E640" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F640" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G640">
         <v>1</v>
       </c>
       <c r="H640" s="8">
-        <v>4.6296296296296294E-5</v>
+        <v>6.5624999999999998E-3</v>
       </c>
       <c r="I640" s="8">
-        <v>4.6296296296296294E-5</v>
+        <v>6.5624999999999998E-3</v>
       </c>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.3">
@@ -32148,22 +32724,22 @@
         <v>17</v>
       </c>
       <c r="D641" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E641" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F641" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G641">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H641" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>3.4722222222222224E-4</v>
       </c>
       <c r="I641" s="8">
-        <v>1.25E-3</v>
+        <v>3.4722222222222224E-4</v>
       </c>
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.3">
@@ -32180,19 +32756,19 @@
         <v>87</v>
       </c>
       <c r="E642" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F642" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G642">
         <v>1</v>
       </c>
       <c r="H642" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>7.2453703703703708E-3</v>
       </c>
       <c r="I642" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>7.2453703703703708E-3</v>
       </c>
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.3">
@@ -32206,10 +32782,10 @@
         <v>17</v>
       </c>
       <c r="D643" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E643" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F643" t="s">
         <v>37</v>
@@ -32218,10 +32794,10 @@
         <v>1</v>
       </c>
       <c r="H643" s="8">
-        <v>8.1018518518518516E-4</v>
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="I643" s="8">
-        <v>8.1018518518518516E-4</v>
+        <v>6.5972222222222224E-4</v>
       </c>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.3">
@@ -32238,19 +32814,19 @@
         <v>87</v>
       </c>
       <c r="E644" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F644" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G644">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H644" s="8">
-        <v>6.5624999999999998E-3</v>
+        <v>6.134259259259259E-4</v>
       </c>
       <c r="I644" s="8">
-        <v>6.5624999999999998E-3</v>
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.3">
@@ -32264,22 +32840,22 @@
         <v>17</v>
       </c>
       <c r="D645" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E645" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="F645" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G645">
-        <v>1</v>
+        <v>2083</v>
       </c>
       <c r="H645" s="8">
-        <v>7.2453703703703708E-3</v>
+        <v>0</v>
       </c>
       <c r="I645" s="8">
-        <v>7.2453703703703708E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.3">
@@ -32296,19 +32872,19 @@
         <v>87</v>
       </c>
       <c r="E646" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F646" t="s">
         <v>37</v>
       </c>
       <c r="G646">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H646" s="8">
-        <v>6.134259259259259E-4</v>
+        <v>4.6296296296296294E-5</v>
       </c>
       <c r="I646" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>4.6296296296296294E-5</v>
       </c>
     </row>
     <row r="647" spans="1:9" x14ac:dyDescent="0.3">
@@ -32383,13 +32959,13 @@
         <v>86</v>
       </c>
       <c r="E649" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F649" t="s">
         <v>6</v>
       </c>
       <c r="G649">
-        <v>24</v>
+        <v>864</v>
       </c>
       <c r="H649" s="8">
         <v>0</v>
@@ -32412,13 +32988,13 @@
         <v>86</v>
       </c>
       <c r="E650" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F650" t="s">
         <v>6</v>
       </c>
       <c r="G650">
-        <v>568</v>
+        <v>24</v>
       </c>
       <c r="H650" s="8">
         <v>0</v>
@@ -32441,13 +33017,13 @@
         <v>86</v>
       </c>
       <c r="E651" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F651" t="s">
         <v>6</v>
       </c>
       <c r="G651">
-        <v>864</v>
+        <v>1</v>
       </c>
       <c r="H651" s="8">
         <v>0</v>
@@ -32470,13 +33046,13 @@
         <v>86</v>
       </c>
       <c r="E652" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F652" t="s">
         <v>6</v>
       </c>
       <c r="G652">
-        <v>1</v>
+        <v>568</v>
       </c>
       <c r="H652" s="8">
         <v>0</v>
@@ -32686,6 +33262,4124 @@
       </c>
       <c r="I659" s="8">
         <v>6.0648148148148145E-3</v>
+      </c>
+    </row>
+    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A660" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B660">
+        <v>14</v>
+      </c>
+      <c r="C660" t="s">
+        <v>17</v>
+      </c>
+      <c r="D660" t="s">
+        <v>86</v>
+      </c>
+      <c r="E660" t="s">
+        <v>32</v>
+      </c>
+      <c r="F660" t="s">
+        <v>6</v>
+      </c>
+      <c r="G660">
+        <v>2927</v>
+      </c>
+      <c r="H660" s="8">
+        <v>0</v>
+      </c>
+      <c r="I660" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A661" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B661">
+        <v>14</v>
+      </c>
+      <c r="C661" t="s">
+        <v>17</v>
+      </c>
+      <c r="D661" t="s">
+        <v>86</v>
+      </c>
+      <c r="E661" t="s">
+        <v>33</v>
+      </c>
+      <c r="F661" t="s">
+        <v>6</v>
+      </c>
+      <c r="G661">
+        <v>1054</v>
+      </c>
+      <c r="H661" s="8">
+        <v>0</v>
+      </c>
+      <c r="I661" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A662" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B662">
+        <v>14</v>
+      </c>
+      <c r="C662" t="s">
+        <v>17</v>
+      </c>
+      <c r="D662" t="s">
+        <v>86</v>
+      </c>
+      <c r="E662" t="s">
+        <v>40</v>
+      </c>
+      <c r="F662" t="s">
+        <v>6</v>
+      </c>
+      <c r="G662">
+        <v>8</v>
+      </c>
+      <c r="H662" s="8">
+        <v>0</v>
+      </c>
+      <c r="I662" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A663" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B663">
+        <v>14</v>
+      </c>
+      <c r="C663" t="s">
+        <v>17</v>
+      </c>
+      <c r="D663" t="s">
+        <v>86</v>
+      </c>
+      <c r="E663" t="s">
+        <v>34</v>
+      </c>
+      <c r="F663" t="s">
+        <v>6</v>
+      </c>
+      <c r="G663">
+        <v>434</v>
+      </c>
+      <c r="H663" s="8">
+        <v>0</v>
+      </c>
+      <c r="I663" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A664" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B664">
+        <v>14</v>
+      </c>
+      <c r="C664" t="s">
+        <v>17</v>
+      </c>
+      <c r="D664" t="s">
+        <v>86</v>
+      </c>
+      <c r="E664" t="s">
+        <v>30</v>
+      </c>
+      <c r="F664" t="s">
+        <v>6</v>
+      </c>
+      <c r="G664">
+        <v>11768</v>
+      </c>
+      <c r="H664" s="8">
+        <v>0</v>
+      </c>
+      <c r="I664" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A665" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B665">
+        <v>14</v>
+      </c>
+      <c r="C665" t="s">
+        <v>17</v>
+      </c>
+      <c r="D665" t="s">
+        <v>86</v>
+      </c>
+      <c r="E665" t="s">
+        <v>43</v>
+      </c>
+      <c r="F665" t="s">
+        <v>6</v>
+      </c>
+      <c r="G665">
+        <v>1</v>
+      </c>
+      <c r="H665" s="8">
+        <v>0</v>
+      </c>
+      <c r="I665" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A666" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B666">
+        <v>14</v>
+      </c>
+      <c r="C666" t="s">
+        <v>17</v>
+      </c>
+      <c r="D666" t="s">
+        <v>86</v>
+      </c>
+      <c r="E666" t="s">
+        <v>29</v>
+      </c>
+      <c r="F666" t="s">
+        <v>6</v>
+      </c>
+      <c r="G666">
+        <v>2865</v>
+      </c>
+      <c r="H666" s="8">
+        <v>0</v>
+      </c>
+      <c r="I666" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A667" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B667">
+        <v>14</v>
+      </c>
+      <c r="C667" t="s">
+        <v>17</v>
+      </c>
+      <c r="D667" t="s">
+        <v>86</v>
+      </c>
+      <c r="E667" t="s">
+        <v>41</v>
+      </c>
+      <c r="F667" t="s">
+        <v>88</v>
+      </c>
+      <c r="G667">
+        <v>2</v>
+      </c>
+      <c r="H667" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I667" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A668" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B668">
+        <v>14</v>
+      </c>
+      <c r="C668" t="s">
+        <v>17</v>
+      </c>
+      <c r="D668" t="s">
+        <v>86</v>
+      </c>
+      <c r="E668" t="s">
+        <v>45</v>
+      </c>
+      <c r="F668" t="s">
+        <v>6</v>
+      </c>
+      <c r="G668">
+        <v>1</v>
+      </c>
+      <c r="H668" s="8">
+        <v>0</v>
+      </c>
+      <c r="I668" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A669" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B669">
+        <v>14</v>
+      </c>
+      <c r="C669" t="s">
+        <v>17</v>
+      </c>
+      <c r="D669" t="s">
+        <v>86</v>
+      </c>
+      <c r="E669" t="s">
+        <v>41</v>
+      </c>
+      <c r="F669" t="s">
+        <v>88</v>
+      </c>
+      <c r="G669">
+        <v>2</v>
+      </c>
+      <c r="H669" s="8">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="I669" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="670" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A670" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B670">
+        <v>14</v>
+      </c>
+      <c r="C670" t="s">
+        <v>17</v>
+      </c>
+      <c r="D670" t="s">
+        <v>86</v>
+      </c>
+      <c r="E670" t="s">
+        <v>41</v>
+      </c>
+      <c r="F670" t="s">
+        <v>88</v>
+      </c>
+      <c r="G670">
+        <v>1</v>
+      </c>
+      <c r="H670" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I670" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="671" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A671" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B671">
+        <v>14</v>
+      </c>
+      <c r="C671" t="s">
+        <v>17</v>
+      </c>
+      <c r="D671" t="s">
+        <v>86</v>
+      </c>
+      <c r="E671" t="s">
+        <v>41</v>
+      </c>
+      <c r="F671" t="s">
+        <v>88</v>
+      </c>
+      <c r="G671">
+        <v>5</v>
+      </c>
+      <c r="H671" s="8">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="I671" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="672" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A672" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B672">
+        <v>14</v>
+      </c>
+      <c r="C672" t="s">
+        <v>17</v>
+      </c>
+      <c r="D672" t="s">
+        <v>86</v>
+      </c>
+      <c r="E672" t="s">
+        <v>41</v>
+      </c>
+      <c r="F672" t="s">
+        <v>88</v>
+      </c>
+      <c r="G672">
+        <v>1</v>
+      </c>
+      <c r="H672" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="I672" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="673" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A673" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B673">
+        <v>14</v>
+      </c>
+      <c r="C673" t="s">
+        <v>17</v>
+      </c>
+      <c r="D673" t="s">
+        <v>86</v>
+      </c>
+      <c r="E673" t="s">
+        <v>41</v>
+      </c>
+      <c r="F673" t="s">
+        <v>88</v>
+      </c>
+      <c r="G673">
+        <v>6</v>
+      </c>
+      <c r="H673" s="8">
+        <v>1.4004629629629629E-3</v>
+      </c>
+      <c r="I673" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="674" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A674" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B674">
+        <v>14</v>
+      </c>
+      <c r="C674" t="s">
+        <v>17</v>
+      </c>
+      <c r="D674" t="s">
+        <v>86</v>
+      </c>
+      <c r="E674" t="s">
+        <v>41</v>
+      </c>
+      <c r="F674" t="s">
+        <v>88</v>
+      </c>
+      <c r="G674">
+        <v>2</v>
+      </c>
+      <c r="H674" s="8">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="I674" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="675" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A675" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B675">
+        <v>14</v>
+      </c>
+      <c r="C675" t="s">
+        <v>17</v>
+      </c>
+      <c r="D675" t="s">
+        <v>86</v>
+      </c>
+      <c r="E675" t="s">
+        <v>38</v>
+      </c>
+      <c r="F675" t="s">
+        <v>37</v>
+      </c>
+      <c r="G675">
+        <v>43</v>
+      </c>
+      <c r="H675" s="8">
+        <v>1.1087962962962963E-2</v>
+      </c>
+      <c r="I675" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="676" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A676" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B676">
+        <v>14</v>
+      </c>
+      <c r="C676" t="s">
+        <v>17</v>
+      </c>
+      <c r="D676" t="s">
+        <v>86</v>
+      </c>
+      <c r="E676" t="s">
+        <v>41</v>
+      </c>
+      <c r="F676" t="s">
+        <v>88</v>
+      </c>
+      <c r="G676">
+        <v>2</v>
+      </c>
+      <c r="H676" s="8">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="I676" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="677" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A677" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B677">
+        <v>14</v>
+      </c>
+      <c r="C677" t="s">
+        <v>17</v>
+      </c>
+      <c r="D677" t="s">
+        <v>86</v>
+      </c>
+      <c r="E677" t="s">
+        <v>50</v>
+      </c>
+      <c r="F677" t="s">
+        <v>88</v>
+      </c>
+      <c r="G677">
+        <v>1</v>
+      </c>
+      <c r="H677" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I677" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="678" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A678" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B678">
+        <v>14</v>
+      </c>
+      <c r="C678" t="s">
+        <v>17</v>
+      </c>
+      <c r="D678" t="s">
+        <v>86</v>
+      </c>
+      <c r="E678" t="s">
+        <v>41</v>
+      </c>
+      <c r="F678" t="s">
+        <v>88</v>
+      </c>
+      <c r="G678">
+        <v>3</v>
+      </c>
+      <c r="H678" s="8">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="I678" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="679" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A679" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B679">
+        <v>14</v>
+      </c>
+      <c r="C679" t="s">
+        <v>17</v>
+      </c>
+      <c r="D679" t="s">
+        <v>86</v>
+      </c>
+      <c r="E679" t="s">
+        <v>59</v>
+      </c>
+      <c r="F679" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679">
+        <v>3</v>
+      </c>
+      <c r="H679" s="8">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="I679" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="680" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A680" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B680">
+        <v>14</v>
+      </c>
+      <c r="C680" t="s">
+        <v>17</v>
+      </c>
+      <c r="D680" t="s">
+        <v>86</v>
+      </c>
+      <c r="E680" t="s">
+        <v>41</v>
+      </c>
+      <c r="F680" t="s">
+        <v>88</v>
+      </c>
+      <c r="G680">
+        <v>8</v>
+      </c>
+      <c r="H680" s="8">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="I680" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="681" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A681" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B681">
+        <v>14</v>
+      </c>
+      <c r="C681" t="s">
+        <v>17</v>
+      </c>
+      <c r="D681" t="s">
+        <v>86</v>
+      </c>
+      <c r="E681" t="s">
+        <v>51</v>
+      </c>
+      <c r="F681" t="s">
+        <v>37</v>
+      </c>
+      <c r="G681">
+        <v>3</v>
+      </c>
+      <c r="H681" s="8">
+        <v>1.25E-3</v>
+      </c>
+      <c r="I681" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="682" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A682" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B682">
+        <v>14</v>
+      </c>
+      <c r="C682" t="s">
+        <v>17</v>
+      </c>
+      <c r="D682" t="s">
+        <v>86</v>
+      </c>
+      <c r="E682" t="s">
+        <v>38</v>
+      </c>
+      <c r="F682" t="s">
+        <v>88</v>
+      </c>
+      <c r="G682">
+        <v>1</v>
+      </c>
+      <c r="H682" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="I682" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+    </row>
+    <row r="683" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A683" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B683">
+        <v>14</v>
+      </c>
+      <c r="C683" t="s">
+        <v>17</v>
+      </c>
+      <c r="D683" t="s">
+        <v>86</v>
+      </c>
+      <c r="E683" t="s">
+        <v>39</v>
+      </c>
+      <c r="F683" t="s">
+        <v>37</v>
+      </c>
+      <c r="G683">
+        <v>22</v>
+      </c>
+      <c r="H683" s="8">
+        <v>5.0694444444444441E-3</v>
+      </c>
+      <c r="I683" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="684" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A684" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B684">
+        <v>14</v>
+      </c>
+      <c r="C684" t="s">
+        <v>17</v>
+      </c>
+      <c r="D684" t="s">
+        <v>86</v>
+      </c>
+      <c r="E684" t="s">
+        <v>50</v>
+      </c>
+      <c r="F684" t="s">
+        <v>37</v>
+      </c>
+      <c r="G684">
+        <v>3</v>
+      </c>
+      <c r="H684" s="8">
+        <v>3.0092592592592593E-3</v>
+      </c>
+      <c r="I684" s="8">
+        <v>9.9537037037037042E-4</v>
+      </c>
+    </row>
+    <row r="685" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A685" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B685">
+        <v>14</v>
+      </c>
+      <c r="C685" t="s">
+        <v>17</v>
+      </c>
+      <c r="D685" t="s">
+        <v>86</v>
+      </c>
+      <c r="E685" t="s">
+        <v>36</v>
+      </c>
+      <c r="F685" t="s">
+        <v>37</v>
+      </c>
+      <c r="G685">
+        <v>296</v>
+      </c>
+      <c r="H685" s="8">
+        <v>3.0694444444444444E-2</v>
+      </c>
+      <c r="I685" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="686" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A686" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B686">
+        <v>14</v>
+      </c>
+      <c r="C686" t="s">
+        <v>17</v>
+      </c>
+      <c r="D686" t="s">
+        <v>86</v>
+      </c>
+      <c r="E686" t="s">
+        <v>52</v>
+      </c>
+      <c r="F686" t="s">
+        <v>37</v>
+      </c>
+      <c r="G686">
+        <v>1</v>
+      </c>
+      <c r="H686" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="I686" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+    </row>
+    <row r="687" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A687" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B687">
+        <v>14</v>
+      </c>
+      <c r="C687" t="s">
+        <v>17</v>
+      </c>
+      <c r="D687" t="s">
+        <v>86</v>
+      </c>
+      <c r="E687" t="s">
+        <v>53</v>
+      </c>
+      <c r="F687" t="s">
+        <v>37</v>
+      </c>
+      <c r="G687">
+        <v>2</v>
+      </c>
+      <c r="H687" s="8">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="I687" s="8">
+        <v>6.9444444444444447E-4</v>
+      </c>
+    </row>
+    <row r="688" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A688" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B688">
+        <v>14</v>
+      </c>
+      <c r="C688" t="s">
+        <v>17</v>
+      </c>
+      <c r="D688" t="s">
+        <v>86</v>
+      </c>
+      <c r="E688" t="s">
+        <v>36</v>
+      </c>
+      <c r="F688" t="s">
+        <v>88</v>
+      </c>
+      <c r="G688">
+        <v>1</v>
+      </c>
+      <c r="H688" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I688" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A689" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B689">
+        <v>14</v>
+      </c>
+      <c r="C689" t="s">
+        <v>17</v>
+      </c>
+      <c r="D689" t="s">
+        <v>86</v>
+      </c>
+      <c r="E689" t="s">
+        <v>31</v>
+      </c>
+      <c r="F689" t="s">
+        <v>6</v>
+      </c>
+      <c r="G689">
+        <v>5100</v>
+      </c>
+      <c r="H689" s="8">
+        <v>0</v>
+      </c>
+      <c r="I689" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A690" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B690">
+        <v>14</v>
+      </c>
+      <c r="C690" t="s">
+        <v>17</v>
+      </c>
+      <c r="D690" t="s">
+        <v>87</v>
+      </c>
+      <c r="E690" t="s">
+        <v>46</v>
+      </c>
+      <c r="F690" t="s">
+        <v>37</v>
+      </c>
+      <c r="G690">
+        <v>6</v>
+      </c>
+      <c r="H690" s="8">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="I690" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A691" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B691">
+        <v>14</v>
+      </c>
+      <c r="C691" t="s">
+        <v>17</v>
+      </c>
+      <c r="D691" t="s">
+        <v>86</v>
+      </c>
+      <c r="E691" t="s">
+        <v>44</v>
+      </c>
+      <c r="F691" t="s">
+        <v>37</v>
+      </c>
+      <c r="G691">
+        <v>5</v>
+      </c>
+      <c r="H691" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I691" s="8">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="692" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A692" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B692">
+        <v>14</v>
+      </c>
+      <c r="C692" t="s">
+        <v>17</v>
+      </c>
+      <c r="D692" t="s">
+        <v>87</v>
+      </c>
+      <c r="E692" t="s">
+        <v>42</v>
+      </c>
+      <c r="F692" t="s">
+        <v>37</v>
+      </c>
+      <c r="G692">
+        <v>8</v>
+      </c>
+      <c r="H692" s="8">
+        <v>3.3217592592592591E-3</v>
+      </c>
+      <c r="I692" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="693" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A693" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B693">
+        <v>14</v>
+      </c>
+      <c r="C693" t="s">
+        <v>17</v>
+      </c>
+      <c r="D693" t="s">
+        <v>86</v>
+      </c>
+      <c r="E693" t="s">
+        <v>35</v>
+      </c>
+      <c r="F693" t="s">
+        <v>6</v>
+      </c>
+      <c r="G693">
+        <v>802</v>
+      </c>
+      <c r="H693" s="8">
+        <v>0</v>
+      </c>
+      <c r="I693" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A694" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B694">
+        <v>14</v>
+      </c>
+      <c r="C694" t="s">
+        <v>17</v>
+      </c>
+      <c r="D694" t="s">
+        <v>87</v>
+      </c>
+      <c r="E694" t="s">
+        <v>48</v>
+      </c>
+      <c r="F694" t="s">
+        <v>37</v>
+      </c>
+      <c r="G694">
+        <v>5</v>
+      </c>
+      <c r="H694" s="8">
+        <v>2.4652777777777776E-3</v>
+      </c>
+      <c r="I694" s="8">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="695" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A695" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B695">
+        <v>14</v>
+      </c>
+      <c r="C695" t="s">
+        <v>17</v>
+      </c>
+      <c r="D695" t="s">
+        <v>87</v>
+      </c>
+      <c r="E695" t="s">
+        <v>62</v>
+      </c>
+      <c r="F695" t="s">
+        <v>10</v>
+      </c>
+      <c r="G695">
+        <v>2</v>
+      </c>
+      <c r="H695" s="8">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="I695" s="8">
+        <v>6.9444444444444447E-4</v>
+      </c>
+    </row>
+    <row r="696" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A696" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B696">
+        <v>14</v>
+      </c>
+      <c r="C696" t="s">
+        <v>17</v>
+      </c>
+      <c r="D696" t="s">
+        <v>87</v>
+      </c>
+      <c r="E696" t="s">
+        <v>49</v>
+      </c>
+      <c r="F696" t="s">
+        <v>37</v>
+      </c>
+      <c r="G696">
+        <v>3</v>
+      </c>
+      <c r="H696" s="8">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="I696" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="697" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A697" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B697">
+        <v>14</v>
+      </c>
+      <c r="C697" t="s">
+        <v>17</v>
+      </c>
+      <c r="D697" t="s">
+        <v>87</v>
+      </c>
+      <c r="E697" t="s">
+        <v>60</v>
+      </c>
+      <c r="F697" t="s">
+        <v>37</v>
+      </c>
+      <c r="G697">
+        <v>2</v>
+      </c>
+      <c r="H697" s="8">
+        <v>1.9097222222222222E-3</v>
+      </c>
+      <c r="I697" s="8">
+        <v>9.4907407407407408E-4</v>
+      </c>
+    </row>
+    <row r="698" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A698" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B698">
+        <v>14</v>
+      </c>
+      <c r="C698" t="s">
+        <v>17</v>
+      </c>
+      <c r="D698" t="s">
+        <v>87</v>
+      </c>
+      <c r="E698" t="s">
+        <v>54</v>
+      </c>
+      <c r="F698" t="s">
+        <v>11</v>
+      </c>
+      <c r="G698">
+        <v>2</v>
+      </c>
+      <c r="H698" s="8">
+        <v>1.480324074074074E-2</v>
+      </c>
+      <c r="I698" s="8">
+        <v>7.3958333333333333E-3</v>
+      </c>
+    </row>
+    <row r="699" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A699" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B699">
+        <v>14</v>
+      </c>
+      <c r="C699" t="s">
+        <v>17</v>
+      </c>
+      <c r="D699" t="s">
+        <v>87</v>
+      </c>
+      <c r="E699" t="s">
+        <v>58</v>
+      </c>
+      <c r="F699" t="s">
+        <v>11</v>
+      </c>
+      <c r="G699">
+        <v>1</v>
+      </c>
+      <c r="H699" s="8">
+        <v>7.3611111111111108E-3</v>
+      </c>
+      <c r="I699" s="8">
+        <v>7.3611111111111108E-3</v>
+      </c>
+    </row>
+    <row r="700" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A700" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B700">
+        <v>14</v>
+      </c>
+      <c r="C700" t="s">
+        <v>17</v>
+      </c>
+      <c r="D700" t="s">
+        <v>87</v>
+      </c>
+      <c r="E700" t="s">
+        <v>69</v>
+      </c>
+      <c r="F700" t="s">
+        <v>10</v>
+      </c>
+      <c r="G700">
+        <v>1</v>
+      </c>
+      <c r="H700" s="8">
+        <v>4.7222222222222223E-3</v>
+      </c>
+      <c r="I700" s="8">
+        <v>4.7222222222222223E-3</v>
+      </c>
+    </row>
+    <row r="701" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A701" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B701">
+        <v>15</v>
+      </c>
+      <c r="C701" t="s">
+        <v>17</v>
+      </c>
+      <c r="D701" t="s">
+        <v>86</v>
+      </c>
+      <c r="E701" t="s">
+        <v>33</v>
+      </c>
+      <c r="F701" t="s">
+        <v>6</v>
+      </c>
+      <c r="G701">
+        <v>1261</v>
+      </c>
+      <c r="H701" s="8">
+        <v>0</v>
+      </c>
+      <c r="I701" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A702" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B702">
+        <v>15</v>
+      </c>
+      <c r="C702" t="s">
+        <v>17</v>
+      </c>
+      <c r="D702" t="s">
+        <v>86</v>
+      </c>
+      <c r="E702" t="s">
+        <v>32</v>
+      </c>
+      <c r="F702" t="s">
+        <v>6</v>
+      </c>
+      <c r="G702">
+        <v>3675</v>
+      </c>
+      <c r="H702" s="8">
+        <v>0</v>
+      </c>
+      <c r="I702" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A703" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B703">
+        <v>15</v>
+      </c>
+      <c r="C703" t="s">
+        <v>17</v>
+      </c>
+      <c r="D703" t="s">
+        <v>86</v>
+      </c>
+      <c r="E703" t="s">
+        <v>34</v>
+      </c>
+      <c r="F703" t="s">
+        <v>6</v>
+      </c>
+      <c r="G703">
+        <v>673</v>
+      </c>
+      <c r="H703" s="8">
+        <v>0</v>
+      </c>
+      <c r="I703" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A704" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B704">
+        <v>15</v>
+      </c>
+      <c r="C704" t="s">
+        <v>17</v>
+      </c>
+      <c r="D704" t="s">
+        <v>86</v>
+      </c>
+      <c r="E704" t="s">
+        <v>30</v>
+      </c>
+      <c r="F704" t="s">
+        <v>6</v>
+      </c>
+      <c r="G704">
+        <v>14454</v>
+      </c>
+      <c r="H704" s="8">
+        <v>0</v>
+      </c>
+      <c r="I704" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A705" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B705">
+        <v>15</v>
+      </c>
+      <c r="C705" t="s">
+        <v>17</v>
+      </c>
+      <c r="D705" t="s">
+        <v>86</v>
+      </c>
+      <c r="E705" t="s">
+        <v>40</v>
+      </c>
+      <c r="F705" t="s">
+        <v>6</v>
+      </c>
+      <c r="G705">
+        <v>15</v>
+      </c>
+      <c r="H705" s="8">
+        <v>0</v>
+      </c>
+      <c r="I705" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A706" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B706">
+        <v>15</v>
+      </c>
+      <c r="C706" t="s">
+        <v>17</v>
+      </c>
+      <c r="D706" t="s">
+        <v>86</v>
+      </c>
+      <c r="E706" t="s">
+        <v>45</v>
+      </c>
+      <c r="F706" t="s">
+        <v>6</v>
+      </c>
+      <c r="G706">
+        <v>4</v>
+      </c>
+      <c r="H706" s="8">
+        <v>0</v>
+      </c>
+      <c r="I706" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A707" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B707">
+        <v>15</v>
+      </c>
+      <c r="C707" t="s">
+        <v>17</v>
+      </c>
+      <c r="D707" t="s">
+        <v>86</v>
+      </c>
+      <c r="E707" t="s">
+        <v>29</v>
+      </c>
+      <c r="F707" t="s">
+        <v>6</v>
+      </c>
+      <c r="G707">
+        <v>13274</v>
+      </c>
+      <c r="H707" s="8">
+        <v>0</v>
+      </c>
+      <c r="I707" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A708" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B708">
+        <v>15</v>
+      </c>
+      <c r="C708" t="s">
+        <v>17</v>
+      </c>
+      <c r="D708" t="s">
+        <v>86</v>
+      </c>
+      <c r="E708" t="s">
+        <v>56</v>
+      </c>
+      <c r="F708" t="s">
+        <v>37</v>
+      </c>
+      <c r="G708">
+        <v>2</v>
+      </c>
+      <c r="H708" s="8">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="I708" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="709" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A709" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B709">
+        <v>15</v>
+      </c>
+      <c r="C709" t="s">
+        <v>17</v>
+      </c>
+      <c r="D709" t="s">
+        <v>86</v>
+      </c>
+      <c r="E709" t="s">
+        <v>43</v>
+      </c>
+      <c r="F709" t="s">
+        <v>6</v>
+      </c>
+      <c r="G709">
+        <v>10</v>
+      </c>
+      <c r="H709" s="8">
+        <v>0</v>
+      </c>
+      <c r="I709" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A710" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B710">
+        <v>15</v>
+      </c>
+      <c r="C710" t="s">
+        <v>17</v>
+      </c>
+      <c r="D710" t="s">
+        <v>86</v>
+      </c>
+      <c r="E710" t="s">
+        <v>41</v>
+      </c>
+      <c r="F710" t="s">
+        <v>88</v>
+      </c>
+      <c r="G710">
+        <v>1</v>
+      </c>
+      <c r="H710" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I710" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A711" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B711">
+        <v>15</v>
+      </c>
+      <c r="C711" t="s">
+        <v>17</v>
+      </c>
+      <c r="D711" t="s">
+        <v>86</v>
+      </c>
+      <c r="E711" t="s">
+        <v>41</v>
+      </c>
+      <c r="F711" t="s">
+        <v>88</v>
+      </c>
+      <c r="G711">
+        <v>1</v>
+      </c>
+      <c r="H711" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I711" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="712" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A712" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B712">
+        <v>15</v>
+      </c>
+      <c r="C712" t="s">
+        <v>17</v>
+      </c>
+      <c r="D712" t="s">
+        <v>86</v>
+      </c>
+      <c r="E712" t="s">
+        <v>41</v>
+      </c>
+      <c r="F712" t="s">
+        <v>88</v>
+      </c>
+      <c r="G712">
+        <v>1</v>
+      </c>
+      <c r="H712" s="8">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="I712" s="8">
+        <v>1.1226851851851851E-3</v>
+      </c>
+    </row>
+    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A713" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B713">
+        <v>15</v>
+      </c>
+      <c r="C713" t="s">
+        <v>17</v>
+      </c>
+      <c r="D713" t="s">
+        <v>86</v>
+      </c>
+      <c r="E713" t="s">
+        <v>41</v>
+      </c>
+      <c r="F713" t="s">
+        <v>88</v>
+      </c>
+      <c r="G713">
+        <v>2</v>
+      </c>
+      <c r="H713" s="8">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="I713" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A714" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B714">
+        <v>15</v>
+      </c>
+      <c r="C714" t="s">
+        <v>17</v>
+      </c>
+      <c r="D714" t="s">
+        <v>86</v>
+      </c>
+      <c r="E714" t="s">
+        <v>41</v>
+      </c>
+      <c r="F714" t="s">
+        <v>88</v>
+      </c>
+      <c r="G714">
+        <v>3</v>
+      </c>
+      <c r="H714" s="8">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="I714" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A715" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B715">
+        <v>15</v>
+      </c>
+      <c r="C715" t="s">
+        <v>17</v>
+      </c>
+      <c r="D715" t="s">
+        <v>86</v>
+      </c>
+      <c r="E715" t="s">
+        <v>41</v>
+      </c>
+      <c r="F715" t="s">
+        <v>88</v>
+      </c>
+      <c r="G715">
+        <v>5</v>
+      </c>
+      <c r="H715" s="8">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="I715" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A716" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B716">
+        <v>15</v>
+      </c>
+      <c r="C716" t="s">
+        <v>17</v>
+      </c>
+      <c r="D716" t="s">
+        <v>86</v>
+      </c>
+      <c r="E716" t="s">
+        <v>50</v>
+      </c>
+      <c r="F716" t="s">
+        <v>37</v>
+      </c>
+      <c r="G716">
+        <v>5</v>
+      </c>
+      <c r="H716" s="8">
+        <v>3.8773148148148148E-3</v>
+      </c>
+      <c r="I716" s="8">
+        <v>7.7546296296296293E-4</v>
+      </c>
+    </row>
+    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A717" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B717">
+        <v>15</v>
+      </c>
+      <c r="C717" t="s">
+        <v>17</v>
+      </c>
+      <c r="D717" t="s">
+        <v>86</v>
+      </c>
+      <c r="E717" t="s">
+        <v>41</v>
+      </c>
+      <c r="F717" t="s">
+        <v>88</v>
+      </c>
+      <c r="G717">
+        <v>8</v>
+      </c>
+      <c r="H717" s="8">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="I717" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A718" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B718">
+        <v>15</v>
+      </c>
+      <c r="C718" t="s">
+        <v>17</v>
+      </c>
+      <c r="D718" t="s">
+        <v>86</v>
+      </c>
+      <c r="E718" t="s">
+        <v>39</v>
+      </c>
+      <c r="F718" t="s">
+        <v>37</v>
+      </c>
+      <c r="G718">
+        <v>25</v>
+      </c>
+      <c r="H718" s="8">
+        <v>6.6319444444444446E-3</v>
+      </c>
+      <c r="I718" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="719" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A719" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B719">
+        <v>15</v>
+      </c>
+      <c r="C719" t="s">
+        <v>17</v>
+      </c>
+      <c r="D719" t="s">
+        <v>86</v>
+      </c>
+      <c r="E719" t="s">
+        <v>38</v>
+      </c>
+      <c r="F719" t="s">
+        <v>37</v>
+      </c>
+      <c r="G719">
+        <v>42</v>
+      </c>
+      <c r="H719" s="8">
+        <v>1.0474537037037037E-2</v>
+      </c>
+      <c r="I719" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="720" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A720" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B720">
+        <v>15</v>
+      </c>
+      <c r="C720" t="s">
+        <v>17</v>
+      </c>
+      <c r="D720" t="s">
+        <v>86</v>
+      </c>
+      <c r="E720" t="s">
+        <v>39</v>
+      </c>
+      <c r="F720" t="s">
+        <v>88</v>
+      </c>
+      <c r="G720">
+        <v>1</v>
+      </c>
+      <c r="H720" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I720" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="721" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A721" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B721">
+        <v>15</v>
+      </c>
+      <c r="C721" t="s">
+        <v>17</v>
+      </c>
+      <c r="D721" t="s">
+        <v>86</v>
+      </c>
+      <c r="E721" t="s">
+        <v>59</v>
+      </c>
+      <c r="F721" t="s">
+        <v>37</v>
+      </c>
+      <c r="G721">
+        <v>1</v>
+      </c>
+      <c r="H721" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="I721" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="722" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A722" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B722">
+        <v>15</v>
+      </c>
+      <c r="C722" t="s">
+        <v>17</v>
+      </c>
+      <c r="D722" t="s">
+        <v>86</v>
+      </c>
+      <c r="E722" t="s">
+        <v>53</v>
+      </c>
+      <c r="F722" t="s">
+        <v>37</v>
+      </c>
+      <c r="G722">
+        <v>1</v>
+      </c>
+      <c r="H722" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="I722" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+    </row>
+    <row r="723" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A723" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B723">
+        <v>15</v>
+      </c>
+      <c r="C723" t="s">
+        <v>17</v>
+      </c>
+      <c r="D723" t="s">
+        <v>86</v>
+      </c>
+      <c r="E723" t="s">
+        <v>51</v>
+      </c>
+      <c r="F723" t="s">
+        <v>37</v>
+      </c>
+      <c r="G723">
+        <v>4</v>
+      </c>
+      <c r="H723" s="8">
+        <v>2.0601851851851853E-3</v>
+      </c>
+      <c r="I723" s="8">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="724" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A724" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B724">
+        <v>15</v>
+      </c>
+      <c r="C724" t="s">
+        <v>17</v>
+      </c>
+      <c r="D724" t="s">
+        <v>86</v>
+      </c>
+      <c r="E724" t="s">
+        <v>31</v>
+      </c>
+      <c r="F724" t="s">
+        <v>6</v>
+      </c>
+      <c r="G724">
+        <v>5395</v>
+      </c>
+      <c r="H724" s="8">
+        <v>0</v>
+      </c>
+      <c r="I724" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A725" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B725">
+        <v>15</v>
+      </c>
+      <c r="C725" t="s">
+        <v>17</v>
+      </c>
+      <c r="D725" t="s">
+        <v>86</v>
+      </c>
+      <c r="E725" t="s">
+        <v>39</v>
+      </c>
+      <c r="F725" t="s">
+        <v>88</v>
+      </c>
+      <c r="G725">
+        <v>1</v>
+      </c>
+      <c r="H725" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="I725" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="726" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A726" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B726">
+        <v>15</v>
+      </c>
+      <c r="C726" t="s">
+        <v>17</v>
+      </c>
+      <c r="D726" t="s">
+        <v>87</v>
+      </c>
+      <c r="E726" t="s">
+        <v>49</v>
+      </c>
+      <c r="F726" t="s">
+        <v>37</v>
+      </c>
+      <c r="G726">
+        <v>2</v>
+      </c>
+      <c r="H726" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="I726" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="727" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A727" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B727">
+        <v>15</v>
+      </c>
+      <c r="C727" t="s">
+        <v>17</v>
+      </c>
+      <c r="D727" t="s">
+        <v>86</v>
+      </c>
+      <c r="E727" t="s">
+        <v>36</v>
+      </c>
+      <c r="F727" t="s">
+        <v>37</v>
+      </c>
+      <c r="G727">
+        <v>284</v>
+      </c>
+      <c r="H727" s="8">
+        <v>2.6724537037037036E-2</v>
+      </c>
+      <c r="I727" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="728" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A728" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B728">
+        <v>15</v>
+      </c>
+      <c r="C728" t="s">
+        <v>17</v>
+      </c>
+      <c r="D728" t="s">
+        <v>87</v>
+      </c>
+      <c r="E728" t="s">
+        <v>63</v>
+      </c>
+      <c r="F728" t="s">
+        <v>10</v>
+      </c>
+      <c r="G728">
+        <v>1</v>
+      </c>
+      <c r="H728" s="8">
+        <v>2.0717592592592593E-3</v>
+      </c>
+      <c r="I728" s="8">
+        <v>2.0717592592592593E-3</v>
+      </c>
+    </row>
+    <row r="729" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A729" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B729">
+        <v>15</v>
+      </c>
+      <c r="C729" t="s">
+        <v>17</v>
+      </c>
+      <c r="D729" t="s">
+        <v>86</v>
+      </c>
+      <c r="E729" t="s">
+        <v>53</v>
+      </c>
+      <c r="F729" t="s">
+        <v>88</v>
+      </c>
+      <c r="G729">
+        <v>1</v>
+      </c>
+      <c r="H729" s="8">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="I729" s="8">
+        <v>5.9027777777777778E-4</v>
+      </c>
+    </row>
+    <row r="730" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A730" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B730">
+        <v>15</v>
+      </c>
+      <c r="C730" t="s">
+        <v>17</v>
+      </c>
+      <c r="D730" t="s">
+        <v>86</v>
+      </c>
+      <c r="E730" t="s">
+        <v>44</v>
+      </c>
+      <c r="F730" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730">
+        <v>3</v>
+      </c>
+      <c r="H730" s="8">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="I730" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A731" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B731">
+        <v>15</v>
+      </c>
+      <c r="C731" t="s">
+        <v>17</v>
+      </c>
+      <c r="D731" t="s">
+        <v>86</v>
+      </c>
+      <c r="E731" t="s">
+        <v>35</v>
+      </c>
+      <c r="F731" t="s">
+        <v>6</v>
+      </c>
+      <c r="G731">
+        <v>810</v>
+      </c>
+      <c r="H731" s="8">
+        <v>0</v>
+      </c>
+      <c r="I731" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A732" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B732">
+        <v>15</v>
+      </c>
+      <c r="C732" t="s">
+        <v>17</v>
+      </c>
+      <c r="D732" t="s">
+        <v>87</v>
+      </c>
+      <c r="E732" t="s">
+        <v>42</v>
+      </c>
+      <c r="F732" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732">
+        <v>5</v>
+      </c>
+      <c r="H732" s="8">
+        <v>1.3310185185185185E-3</v>
+      </c>
+      <c r="I732" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="733" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A733" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B733">
+        <v>15</v>
+      </c>
+      <c r="C733" t="s">
+        <v>17</v>
+      </c>
+      <c r="D733" t="s">
+        <v>87</v>
+      </c>
+      <c r="E733" t="s">
+        <v>48</v>
+      </c>
+      <c r="F733" t="s">
+        <v>37</v>
+      </c>
+      <c r="G733">
+        <v>1</v>
+      </c>
+      <c r="H733" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I733" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="734" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A734" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B734">
+        <v>15</v>
+      </c>
+      <c r="C734" t="s">
+        <v>17</v>
+      </c>
+      <c r="D734" t="s">
+        <v>87</v>
+      </c>
+      <c r="E734" t="s">
+        <v>58</v>
+      </c>
+      <c r="F734" t="s">
+        <v>11</v>
+      </c>
+      <c r="G734">
+        <v>1</v>
+      </c>
+      <c r="H734" s="8">
+        <v>3.9583333333333337E-3</v>
+      </c>
+      <c r="I734" s="8">
+        <v>3.9583333333333337E-3</v>
+      </c>
+    </row>
+    <row r="735" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A735" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B735">
+        <v>15</v>
+      </c>
+      <c r="C735" t="s">
+        <v>17</v>
+      </c>
+      <c r="D735" t="s">
+        <v>87</v>
+      </c>
+      <c r="E735" t="s">
+        <v>47</v>
+      </c>
+      <c r="F735" t="s">
+        <v>37</v>
+      </c>
+      <c r="G735">
+        <v>3</v>
+      </c>
+      <c r="H735" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I735" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="736" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A736" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B736">
+        <v>16</v>
+      </c>
+      <c r="C736" t="s">
+        <v>17</v>
+      </c>
+      <c r="D736" t="s">
+        <v>86</v>
+      </c>
+      <c r="E736" t="s">
+        <v>32</v>
+      </c>
+      <c r="F736" t="s">
+        <v>6</v>
+      </c>
+      <c r="G736">
+        <v>1515</v>
+      </c>
+      <c r="H736" s="8">
+        <v>0</v>
+      </c>
+      <c r="I736" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A737" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B737">
+        <v>16</v>
+      </c>
+      <c r="C737" t="s">
+        <v>17</v>
+      </c>
+      <c r="D737" t="s">
+        <v>86</v>
+      </c>
+      <c r="E737" t="s">
+        <v>33</v>
+      </c>
+      <c r="F737" t="s">
+        <v>6</v>
+      </c>
+      <c r="G737">
+        <v>961</v>
+      </c>
+      <c r="H737" s="8">
+        <v>0</v>
+      </c>
+      <c r="I737" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A738" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B738">
+        <v>16</v>
+      </c>
+      <c r="C738" t="s">
+        <v>17</v>
+      </c>
+      <c r="D738" t="s">
+        <v>86</v>
+      </c>
+      <c r="E738" t="s">
+        <v>34</v>
+      </c>
+      <c r="F738" t="s">
+        <v>6</v>
+      </c>
+      <c r="G738">
+        <v>636</v>
+      </c>
+      <c r="H738" s="8">
+        <v>0</v>
+      </c>
+      <c r="I738" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A739" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B739">
+        <v>16</v>
+      </c>
+      <c r="C739" t="s">
+        <v>17</v>
+      </c>
+      <c r="D739" t="s">
+        <v>86</v>
+      </c>
+      <c r="E739" t="s">
+        <v>30</v>
+      </c>
+      <c r="F739" t="s">
+        <v>6</v>
+      </c>
+      <c r="G739">
+        <v>10129</v>
+      </c>
+      <c r="H739" s="8">
+        <v>0</v>
+      </c>
+      <c r="I739" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A740" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B740">
+        <v>16</v>
+      </c>
+      <c r="C740" t="s">
+        <v>17</v>
+      </c>
+      <c r="D740" t="s">
+        <v>86</v>
+      </c>
+      <c r="E740" t="s">
+        <v>40</v>
+      </c>
+      <c r="F740" t="s">
+        <v>6</v>
+      </c>
+      <c r="G740">
+        <v>4</v>
+      </c>
+      <c r="H740" s="8">
+        <v>0</v>
+      </c>
+      <c r="I740" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A741" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B741">
+        <v>16</v>
+      </c>
+      <c r="C741" t="s">
+        <v>17</v>
+      </c>
+      <c r="D741" t="s">
+        <v>86</v>
+      </c>
+      <c r="E741" t="s">
+        <v>29</v>
+      </c>
+      <c r="F741" t="s">
+        <v>6</v>
+      </c>
+      <c r="G741">
+        <v>54443</v>
+      </c>
+      <c r="H741" s="8">
+        <v>0</v>
+      </c>
+      <c r="I741" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A742" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B742">
+        <v>16</v>
+      </c>
+      <c r="C742" t="s">
+        <v>17</v>
+      </c>
+      <c r="D742" t="s">
+        <v>86</v>
+      </c>
+      <c r="E742" t="s">
+        <v>45</v>
+      </c>
+      <c r="F742" t="s">
+        <v>6</v>
+      </c>
+      <c r="G742">
+        <v>3</v>
+      </c>
+      <c r="H742" s="8">
+        <v>0</v>
+      </c>
+      <c r="I742" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A743" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B743">
+        <v>16</v>
+      </c>
+      <c r="C743" t="s">
+        <v>17</v>
+      </c>
+      <c r="D743" t="s">
+        <v>86</v>
+      </c>
+      <c r="E743" t="s">
+        <v>41</v>
+      </c>
+      <c r="F743" t="s">
+        <v>88</v>
+      </c>
+      <c r="G743">
+        <v>1</v>
+      </c>
+      <c r="H743" s="8">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="I743" s="8">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="744" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A744" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B744">
+        <v>16</v>
+      </c>
+      <c r="C744" t="s">
+        <v>17</v>
+      </c>
+      <c r="D744" t="s">
+        <v>86</v>
+      </c>
+      <c r="E744" t="s">
+        <v>41</v>
+      </c>
+      <c r="F744" t="s">
+        <v>88</v>
+      </c>
+      <c r="G744">
+        <v>4</v>
+      </c>
+      <c r="H744" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="I744" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="745" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A745" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B745">
+        <v>16</v>
+      </c>
+      <c r="C745" t="s">
+        <v>17</v>
+      </c>
+      <c r="D745" t="s">
+        <v>86</v>
+      </c>
+      <c r="E745" t="s">
+        <v>41</v>
+      </c>
+      <c r="F745" t="s">
+        <v>88</v>
+      </c>
+      <c r="G745">
+        <v>2</v>
+      </c>
+      <c r="H745" s="8">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="I745" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="746" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A746" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B746">
+        <v>16</v>
+      </c>
+      <c r="C746" t="s">
+        <v>17</v>
+      </c>
+      <c r="D746" t="s">
+        <v>86</v>
+      </c>
+      <c r="E746" t="s">
+        <v>41</v>
+      </c>
+      <c r="F746" t="s">
+        <v>88</v>
+      </c>
+      <c r="G746">
+        <v>4</v>
+      </c>
+      <c r="H746" s="8">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="I746" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="747" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A747" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B747">
+        <v>16</v>
+      </c>
+      <c r="C747" t="s">
+        <v>17</v>
+      </c>
+      <c r="D747" t="s">
+        <v>86</v>
+      </c>
+      <c r="E747" t="s">
+        <v>51</v>
+      </c>
+      <c r="F747" t="s">
+        <v>37</v>
+      </c>
+      <c r="G747">
+        <v>1</v>
+      </c>
+      <c r="H747" s="8">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="I747" s="8">
+        <v>1.0763888888888889E-3</v>
+      </c>
+    </row>
+    <row r="748" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A748" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B748">
+        <v>16</v>
+      </c>
+      <c r="C748" t="s">
+        <v>17</v>
+      </c>
+      <c r="D748" t="s">
+        <v>86</v>
+      </c>
+      <c r="E748" t="s">
+        <v>41</v>
+      </c>
+      <c r="F748" t="s">
+        <v>88</v>
+      </c>
+      <c r="G748">
+        <v>6</v>
+      </c>
+      <c r="H748" s="8">
+        <v>1.2152777777777778E-3</v>
+      </c>
+      <c r="I748" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="749" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A749" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B749">
+        <v>16</v>
+      </c>
+      <c r="C749" t="s">
+        <v>17</v>
+      </c>
+      <c r="D749" t="s">
+        <v>87</v>
+      </c>
+      <c r="E749" t="s">
+        <v>46</v>
+      </c>
+      <c r="F749" t="s">
+        <v>37</v>
+      </c>
+      <c r="G749">
+        <v>6</v>
+      </c>
+      <c r="H749" s="8">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="I749" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="750" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A750" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B750">
+        <v>16</v>
+      </c>
+      <c r="C750" t="s">
+        <v>17</v>
+      </c>
+      <c r="D750" t="s">
+        <v>86</v>
+      </c>
+      <c r="E750" t="s">
+        <v>41</v>
+      </c>
+      <c r="F750" t="s">
+        <v>88</v>
+      </c>
+      <c r="G750">
+        <v>7</v>
+      </c>
+      <c r="H750" s="8">
+        <v>1.9560185185185184E-3</v>
+      </c>
+      <c r="I750" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="751" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A751" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B751">
+        <v>16</v>
+      </c>
+      <c r="C751" t="s">
+        <v>17</v>
+      </c>
+      <c r="D751" t="s">
+        <v>87</v>
+      </c>
+      <c r="E751" t="s">
+        <v>48</v>
+      </c>
+      <c r="F751" t="s">
+        <v>37</v>
+      </c>
+      <c r="G751">
+        <v>4</v>
+      </c>
+      <c r="H751" s="8">
+        <v>3.0439814814814813E-3</v>
+      </c>
+      <c r="I751" s="8">
+        <v>7.5231481481481482E-4</v>
+      </c>
+    </row>
+    <row r="752" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A752" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B752">
+        <v>16</v>
+      </c>
+      <c r="C752" t="s">
+        <v>17</v>
+      </c>
+      <c r="D752" t="s">
+        <v>86</v>
+      </c>
+      <c r="E752" t="s">
+        <v>41</v>
+      </c>
+      <c r="F752" t="s">
+        <v>88</v>
+      </c>
+      <c r="G752">
+        <v>10</v>
+      </c>
+      <c r="H752" s="8">
+        <v>2.673611111111111E-3</v>
+      </c>
+      <c r="I752" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="753" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A753" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B753">
+        <v>16</v>
+      </c>
+      <c r="C753" t="s">
+        <v>17</v>
+      </c>
+      <c r="D753" t="s">
+        <v>87</v>
+      </c>
+      <c r="E753" t="s">
+        <v>63</v>
+      </c>
+      <c r="F753" t="s">
+        <v>10</v>
+      </c>
+      <c r="G753">
+        <v>2</v>
+      </c>
+      <c r="H753" s="8">
+        <v>3.8541666666666668E-3</v>
+      </c>
+      <c r="I753" s="8">
+        <v>1.9212962962962964E-3</v>
+      </c>
+    </row>
+    <row r="754" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A754" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B754">
+        <v>16</v>
+      </c>
+      <c r="C754" t="s">
+        <v>17</v>
+      </c>
+      <c r="D754" t="s">
+        <v>86</v>
+      </c>
+      <c r="E754" t="s">
+        <v>57</v>
+      </c>
+      <c r="F754" t="s">
+        <v>37</v>
+      </c>
+      <c r="G754">
+        <v>3</v>
+      </c>
+      <c r="H754" s="8">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="I754" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="755" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A755" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B755">
+        <v>16</v>
+      </c>
+      <c r="C755" t="s">
+        <v>17</v>
+      </c>
+      <c r="D755" t="s">
+        <v>87</v>
+      </c>
+      <c r="E755" t="s">
+        <v>44</v>
+      </c>
+      <c r="F755" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755">
+        <v>1</v>
+      </c>
+      <c r="H755" s="8">
+        <v>1.6111111111111111E-2</v>
+      </c>
+      <c r="I755" s="8">
+        <v>1.6111111111111111E-2</v>
+      </c>
+    </row>
+    <row r="756" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A756" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B756">
+        <v>16</v>
+      </c>
+      <c r="C756" t="s">
+        <v>17</v>
+      </c>
+      <c r="D756" t="s">
+        <v>86</v>
+      </c>
+      <c r="E756" t="s">
+        <v>38</v>
+      </c>
+      <c r="F756" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756">
+        <v>33</v>
+      </c>
+      <c r="H756" s="8">
+        <v>8.9814814814814809E-3</v>
+      </c>
+      <c r="I756" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="757" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A757" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B757">
+        <v>16</v>
+      </c>
+      <c r="C757" t="s">
+        <v>17</v>
+      </c>
+      <c r="D757" t="s">
+        <v>86</v>
+      </c>
+      <c r="E757" t="s">
+        <v>50</v>
+      </c>
+      <c r="F757" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757">
+        <v>1</v>
+      </c>
+      <c r="H757" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="I757" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="758" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A758" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B758">
+        <v>16</v>
+      </c>
+      <c r="C758" t="s">
+        <v>17</v>
+      </c>
+      <c r="D758" t="s">
+        <v>86</v>
+      </c>
+      <c r="E758" t="s">
+        <v>59</v>
+      </c>
+      <c r="F758" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758">
+        <v>1</v>
+      </c>
+      <c r="H758" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I758" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="759" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A759" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B759">
+        <v>16</v>
+      </c>
+      <c r="C759" t="s">
+        <v>17</v>
+      </c>
+      <c r="D759" t="s">
+        <v>86</v>
+      </c>
+      <c r="E759" t="s">
+        <v>52</v>
+      </c>
+      <c r="F759" t="s">
+        <v>37</v>
+      </c>
+      <c r="G759">
+        <v>1</v>
+      </c>
+      <c r="H759" s="8">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="I759" s="8">
+        <v>4.9768518518518521E-4</v>
+      </c>
+    </row>
+    <row r="760" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A760" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B760">
+        <v>16</v>
+      </c>
+      <c r="C760" t="s">
+        <v>17</v>
+      </c>
+      <c r="D760" t="s">
+        <v>86</v>
+      </c>
+      <c r="E760" t="s">
+        <v>39</v>
+      </c>
+      <c r="F760" t="s">
+        <v>37</v>
+      </c>
+      <c r="G760">
+        <v>30</v>
+      </c>
+      <c r="H760" s="8">
+        <v>6.0069444444444441E-3</v>
+      </c>
+      <c r="I760" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="761" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A761" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B761">
+        <v>16</v>
+      </c>
+      <c r="C761" t="s">
+        <v>17</v>
+      </c>
+      <c r="D761" t="s">
+        <v>86</v>
+      </c>
+      <c r="E761" t="s">
+        <v>39</v>
+      </c>
+      <c r="F761" t="s">
+        <v>88</v>
+      </c>
+      <c r="G761">
+        <v>1</v>
+      </c>
+      <c r="H761" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="I761" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="762" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A762" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B762">
+        <v>16</v>
+      </c>
+      <c r="C762" t="s">
+        <v>17</v>
+      </c>
+      <c r="D762" t="s">
+        <v>86</v>
+      </c>
+      <c r="E762" t="s">
+        <v>36</v>
+      </c>
+      <c r="F762" t="s">
+        <v>37</v>
+      </c>
+      <c r="G762">
+        <v>274</v>
+      </c>
+      <c r="H762" s="8">
+        <v>2.6493055555555554E-2</v>
+      </c>
+      <c r="I762" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="763" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A763" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B763">
+        <v>16</v>
+      </c>
+      <c r="C763" t="s">
+        <v>17</v>
+      </c>
+      <c r="D763" t="s">
+        <v>86</v>
+      </c>
+      <c r="E763" t="s">
+        <v>53</v>
+      </c>
+      <c r="F763" t="s">
+        <v>37</v>
+      </c>
+      <c r="G763">
+        <v>1</v>
+      </c>
+      <c r="H763" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I763" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="764" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A764" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B764">
+        <v>16</v>
+      </c>
+      <c r="C764" t="s">
+        <v>17</v>
+      </c>
+      <c r="D764" t="s">
+        <v>86</v>
+      </c>
+      <c r="E764" t="s">
+        <v>31</v>
+      </c>
+      <c r="F764" t="s">
+        <v>6</v>
+      </c>
+      <c r="G764">
+        <v>4141</v>
+      </c>
+      <c r="H764" s="8">
+        <v>0</v>
+      </c>
+      <c r="I764" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A765" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B765">
+        <v>16</v>
+      </c>
+      <c r="C765" t="s">
+        <v>17</v>
+      </c>
+      <c r="D765" t="s">
+        <v>86</v>
+      </c>
+      <c r="E765" t="s">
+        <v>44</v>
+      </c>
+      <c r="F765" t="s">
+        <v>37</v>
+      </c>
+      <c r="G765">
+        <v>14</v>
+      </c>
+      <c r="H765" s="8">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="I765" s="8">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="766" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A766" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B766">
+        <v>16</v>
+      </c>
+      <c r="C766" t="s">
+        <v>17</v>
+      </c>
+      <c r="D766" t="s">
+        <v>86</v>
+      </c>
+      <c r="E766" t="s">
+        <v>35</v>
+      </c>
+      <c r="F766" t="s">
+        <v>6</v>
+      </c>
+      <c r="G766">
+        <v>633</v>
+      </c>
+      <c r="H766" s="8">
+        <v>0</v>
+      </c>
+      <c r="I766" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A767" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B767">
+        <v>16</v>
+      </c>
+      <c r="C767" t="s">
+        <v>17</v>
+      </c>
+      <c r="D767" t="s">
+        <v>87</v>
+      </c>
+      <c r="E767" t="s">
+        <v>42</v>
+      </c>
+      <c r="F767" t="s">
+        <v>37</v>
+      </c>
+      <c r="G767">
+        <v>7</v>
+      </c>
+      <c r="H767" s="8">
+        <v>4.3981481481481484E-3</v>
+      </c>
+      <c r="I767" s="8">
+        <v>6.2500000000000001E-4</v>
+      </c>
+    </row>
+    <row r="768" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A768" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B768">
+        <v>16</v>
+      </c>
+      <c r="C768" t="s">
+        <v>17</v>
+      </c>
+      <c r="D768" t="s">
+        <v>87</v>
+      </c>
+      <c r="E768" t="s">
+        <v>47</v>
+      </c>
+      <c r="F768" t="s">
+        <v>37</v>
+      </c>
+      <c r="G768">
+        <v>10</v>
+      </c>
+      <c r="H768" s="8">
+        <v>5.2199074074074075E-3</v>
+      </c>
+      <c r="I768" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="769" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A769" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B769">
+        <v>17</v>
+      </c>
+      <c r="C769" t="s">
+        <v>17</v>
+      </c>
+      <c r="D769" t="s">
+        <v>86</v>
+      </c>
+      <c r="E769" t="s">
+        <v>33</v>
+      </c>
+      <c r="F769" t="s">
+        <v>6</v>
+      </c>
+      <c r="G769">
+        <v>1034</v>
+      </c>
+      <c r="H769" s="8">
+        <v>0</v>
+      </c>
+      <c r="I769" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A770" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B770">
+        <v>17</v>
+      </c>
+      <c r="C770" t="s">
+        <v>17</v>
+      </c>
+      <c r="D770" t="s">
+        <v>86</v>
+      </c>
+      <c r="E770" t="s">
+        <v>30</v>
+      </c>
+      <c r="F770" t="s">
+        <v>6</v>
+      </c>
+      <c r="G770">
+        <v>13078</v>
+      </c>
+      <c r="H770" s="8">
+        <v>0</v>
+      </c>
+      <c r="I770" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A771" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B771">
+        <v>17</v>
+      </c>
+      <c r="C771" t="s">
+        <v>17</v>
+      </c>
+      <c r="D771" t="s">
+        <v>86</v>
+      </c>
+      <c r="E771" t="s">
+        <v>32</v>
+      </c>
+      <c r="F771" t="s">
+        <v>6</v>
+      </c>
+      <c r="G771">
+        <v>1751</v>
+      </c>
+      <c r="H771" s="8">
+        <v>0</v>
+      </c>
+      <c r="I771" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A772" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B772">
+        <v>17</v>
+      </c>
+      <c r="C772" t="s">
+        <v>17</v>
+      </c>
+      <c r="D772" t="s">
+        <v>86</v>
+      </c>
+      <c r="E772" t="s">
+        <v>29</v>
+      </c>
+      <c r="F772" t="s">
+        <v>6</v>
+      </c>
+      <c r="G772">
+        <v>15135</v>
+      </c>
+      <c r="H772" s="8">
+        <v>0</v>
+      </c>
+      <c r="I772" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A773" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B773">
+        <v>17</v>
+      </c>
+      <c r="C773" t="s">
+        <v>17</v>
+      </c>
+      <c r="D773" t="s">
+        <v>86</v>
+      </c>
+      <c r="E773" t="s">
+        <v>34</v>
+      </c>
+      <c r="F773" t="s">
+        <v>6</v>
+      </c>
+      <c r="G773">
+        <v>721</v>
+      </c>
+      <c r="H773" s="8">
+        <v>0</v>
+      </c>
+      <c r="I773" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A774" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B774">
+        <v>17</v>
+      </c>
+      <c r="C774" t="s">
+        <v>17</v>
+      </c>
+      <c r="D774" t="s">
+        <v>86</v>
+      </c>
+      <c r="E774" t="s">
+        <v>41</v>
+      </c>
+      <c r="F774" t="s">
+        <v>88</v>
+      </c>
+      <c r="G774">
+        <v>1</v>
+      </c>
+      <c r="H774" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="I774" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="775" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A775" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B775">
+        <v>17</v>
+      </c>
+      <c r="C775" t="s">
+        <v>17</v>
+      </c>
+      <c r="D775" t="s">
+        <v>86</v>
+      </c>
+      <c r="E775" t="s">
+        <v>40</v>
+      </c>
+      <c r="F775" t="s">
+        <v>6</v>
+      </c>
+      <c r="G775">
+        <v>7</v>
+      </c>
+      <c r="H775" s="8">
+        <v>0</v>
+      </c>
+      <c r="I775" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A776" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B776">
+        <v>17</v>
+      </c>
+      <c r="C776" t="s">
+        <v>17</v>
+      </c>
+      <c r="D776" t="s">
+        <v>86</v>
+      </c>
+      <c r="E776" t="s">
+        <v>41</v>
+      </c>
+      <c r="F776" t="s">
+        <v>88</v>
+      </c>
+      <c r="G776">
+        <v>4</v>
+      </c>
+      <c r="H776" s="8">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="I776" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="777" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A777" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B777">
+        <v>17</v>
+      </c>
+      <c r="C777" t="s">
+        <v>17</v>
+      </c>
+      <c r="D777" t="s">
+        <v>86</v>
+      </c>
+      <c r="E777" t="s">
+        <v>45</v>
+      </c>
+      <c r="F777" t="s">
+        <v>6</v>
+      </c>
+      <c r="G777">
+        <v>8</v>
+      </c>
+      <c r="H777" s="8">
+        <v>0</v>
+      </c>
+      <c r="I777" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A778" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B778">
+        <v>17</v>
+      </c>
+      <c r="C778" t="s">
+        <v>17</v>
+      </c>
+      <c r="D778" t="s">
+        <v>86</v>
+      </c>
+      <c r="E778" t="s">
+        <v>41</v>
+      </c>
+      <c r="F778" t="s">
+        <v>88</v>
+      </c>
+      <c r="G778">
+        <v>4</v>
+      </c>
+      <c r="H778" s="8">
+        <v>1.0879629629629629E-3</v>
+      </c>
+      <c r="I778" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="779" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A779" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B779">
+        <v>17</v>
+      </c>
+      <c r="C779" t="s">
+        <v>17</v>
+      </c>
+      <c r="D779" t="s">
+        <v>86</v>
+      </c>
+      <c r="E779" t="s">
+        <v>56</v>
+      </c>
+      <c r="F779" t="s">
+        <v>37</v>
+      </c>
+      <c r="G779">
+        <v>4</v>
+      </c>
+      <c r="H779" s="8">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="I779" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="780" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A780" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B780">
+        <v>17</v>
+      </c>
+      <c r="C780" t="s">
+        <v>17</v>
+      </c>
+      <c r="D780" t="s">
+        <v>86</v>
+      </c>
+      <c r="E780" t="s">
+        <v>41</v>
+      </c>
+      <c r="F780" t="s">
+        <v>88</v>
+      </c>
+      <c r="G780">
+        <v>5</v>
+      </c>
+      <c r="H780" s="8">
+        <v>1.5740740740740741E-3</v>
+      </c>
+      <c r="I780" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="781" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A781" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B781">
+        <v>17</v>
+      </c>
+      <c r="C781" t="s">
+        <v>17</v>
+      </c>
+      <c r="D781" t="s">
+        <v>86</v>
+      </c>
+      <c r="E781" t="s">
+        <v>41</v>
+      </c>
+      <c r="F781" t="s">
+        <v>88</v>
+      </c>
+      <c r="G781">
+        <v>1</v>
+      </c>
+      <c r="H781" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I781" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="782" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A782" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B782">
+        <v>17</v>
+      </c>
+      <c r="C782" t="s">
+        <v>17</v>
+      </c>
+      <c r="D782" t="s">
+        <v>86</v>
+      </c>
+      <c r="E782" t="s">
+        <v>57</v>
+      </c>
+      <c r="F782" t="s">
+        <v>37</v>
+      </c>
+      <c r="G782">
+        <v>1</v>
+      </c>
+      <c r="H782" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="I782" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="783" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A783" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B783">
+        <v>17</v>
+      </c>
+      <c r="C783" t="s">
+        <v>17</v>
+      </c>
+      <c r="D783" t="s">
+        <v>86</v>
+      </c>
+      <c r="E783" t="s">
+        <v>41</v>
+      </c>
+      <c r="F783" t="s">
+        <v>88</v>
+      </c>
+      <c r="G783">
+        <v>2</v>
+      </c>
+      <c r="H783" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I783" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="784" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A784" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B784">
+        <v>17</v>
+      </c>
+      <c r="C784" t="s">
+        <v>17</v>
+      </c>
+      <c r="D784" t="s">
+        <v>86</v>
+      </c>
+      <c r="E784" t="s">
+        <v>38</v>
+      </c>
+      <c r="F784" t="s">
+        <v>37</v>
+      </c>
+      <c r="G784">
+        <v>30</v>
+      </c>
+      <c r="H784" s="8">
+        <v>7.8356481481481489E-3</v>
+      </c>
+      <c r="I784" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="785" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A785" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B785">
+        <v>17</v>
+      </c>
+      <c r="C785" t="s">
+        <v>17</v>
+      </c>
+      <c r="D785" t="s">
+        <v>86</v>
+      </c>
+      <c r="E785" t="s">
+        <v>41</v>
+      </c>
+      <c r="F785" t="s">
+        <v>88</v>
+      </c>
+      <c r="G785">
+        <v>5</v>
+      </c>
+      <c r="H785" s="8">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="I785" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="786" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A786" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B786">
+        <v>17</v>
+      </c>
+      <c r="C786" t="s">
+        <v>17</v>
+      </c>
+      <c r="D786" t="s">
+        <v>86</v>
+      </c>
+      <c r="E786" t="s">
+        <v>51</v>
+      </c>
+      <c r="F786" t="s">
+        <v>37</v>
+      </c>
+      <c r="G786">
+        <v>3</v>
+      </c>
+      <c r="H786" s="8">
+        <v>2.3495370370370371E-3</v>
+      </c>
+      <c r="I786" s="8">
+        <v>7.7546296296296293E-4</v>
+      </c>
+    </row>
+    <row r="787" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A787" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B787">
+        <v>17</v>
+      </c>
+      <c r="C787" t="s">
+        <v>17</v>
+      </c>
+      <c r="D787" t="s">
+        <v>86</v>
+      </c>
+      <c r="E787" t="s">
+        <v>44</v>
+      </c>
+      <c r="F787" t="s">
+        <v>37</v>
+      </c>
+      <c r="G787">
+        <v>10</v>
+      </c>
+      <c r="H787" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="I787" s="8">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="788" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A788" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B788">
+        <v>17</v>
+      </c>
+      <c r="C788" t="s">
+        <v>17</v>
+      </c>
+      <c r="D788" t="s">
+        <v>86</v>
+      </c>
+      <c r="E788" t="s">
+        <v>52</v>
+      </c>
+      <c r="F788" t="s">
+        <v>37</v>
+      </c>
+      <c r="G788">
+        <v>3</v>
+      </c>
+      <c r="H788" s="8">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="I788" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="789" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A789" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B789">
+        <v>17</v>
+      </c>
+      <c r="C789" t="s">
+        <v>17</v>
+      </c>
+      <c r="D789" t="s">
+        <v>86</v>
+      </c>
+      <c r="E789" t="s">
+        <v>35</v>
+      </c>
+      <c r="F789" t="s">
+        <v>6</v>
+      </c>
+      <c r="G789">
+        <v>708</v>
+      </c>
+      <c r="H789" s="8">
+        <v>0</v>
+      </c>
+      <c r="I789" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A790" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B790">
+        <v>17</v>
+      </c>
+      <c r="C790" t="s">
+        <v>17</v>
+      </c>
+      <c r="D790" t="s">
+        <v>86</v>
+      </c>
+      <c r="E790" t="s">
+        <v>39</v>
+      </c>
+      <c r="F790" t="s">
+        <v>37</v>
+      </c>
+      <c r="G790">
+        <v>17</v>
+      </c>
+      <c r="H790" s="8">
+        <v>4.2361111111111115E-3</v>
+      </c>
+      <c r="I790" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="791" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A791" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B791">
+        <v>17</v>
+      </c>
+      <c r="C791" t="s">
+        <v>17</v>
+      </c>
+      <c r="D791" t="s">
+        <v>86</v>
+      </c>
+      <c r="E791" t="s">
+        <v>80</v>
+      </c>
+      <c r="F791" t="s">
+        <v>88</v>
+      </c>
+      <c r="G791">
+        <v>1</v>
+      </c>
+      <c r="H791" s="8">
+        <v>0</v>
+      </c>
+      <c r="I791" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A792" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B792">
+        <v>17</v>
+      </c>
+      <c r="C792" t="s">
+        <v>17</v>
+      </c>
+      <c r="D792" t="s">
+        <v>86</v>
+      </c>
+      <c r="E792" t="s">
+        <v>36</v>
+      </c>
+      <c r="F792" t="s">
+        <v>37</v>
+      </c>
+      <c r="G792">
+        <v>244</v>
+      </c>
+      <c r="H792" s="8">
+        <v>2.3796296296296298E-2</v>
+      </c>
+      <c r="I792" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="793" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A793" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B793">
+        <v>17</v>
+      </c>
+      <c r="C793" t="s">
+        <v>17</v>
+      </c>
+      <c r="D793" t="s">
+        <v>87</v>
+      </c>
+      <c r="E793" t="s">
+        <v>48</v>
+      </c>
+      <c r="F793" t="s">
+        <v>37</v>
+      </c>
+      <c r="G793">
+        <v>4</v>
+      </c>
+      <c r="H793" s="8">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="I793" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="794" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A794" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B794">
+        <v>17</v>
+      </c>
+      <c r="C794" t="s">
+        <v>17</v>
+      </c>
+      <c r="D794" t="s">
+        <v>86</v>
+      </c>
+      <c r="E794" t="s">
+        <v>31</v>
+      </c>
+      <c r="F794" t="s">
+        <v>6</v>
+      </c>
+      <c r="G794">
+        <v>4609</v>
+      </c>
+      <c r="H794" s="8">
+        <v>0</v>
+      </c>
+      <c r="I794" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A795" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B795">
+        <v>17</v>
+      </c>
+      <c r="C795" t="s">
+        <v>17</v>
+      </c>
+      <c r="D795" t="s">
+        <v>87</v>
+      </c>
+      <c r="E795" t="s">
+        <v>60</v>
+      </c>
+      <c r="F795" t="s">
+        <v>37</v>
+      </c>
+      <c r="G795">
+        <v>1</v>
+      </c>
+      <c r="H795" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I795" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="796" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A796" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B796">
+        <v>17</v>
+      </c>
+      <c r="C796" t="s">
+        <v>17</v>
+      </c>
+      <c r="D796" t="s">
+        <v>87</v>
+      </c>
+      <c r="E796" t="s">
+        <v>46</v>
+      </c>
+      <c r="F796" t="s">
+        <v>37</v>
+      </c>
+      <c r="G796">
+        <v>1</v>
+      </c>
+      <c r="H796" s="8">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="I796" s="8">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="797" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A797" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B797">
+        <v>17</v>
+      </c>
+      <c r="C797" t="s">
+        <v>17</v>
+      </c>
+      <c r="D797" t="s">
+        <v>87</v>
+      </c>
+      <c r="E797" t="s">
+        <v>47</v>
+      </c>
+      <c r="F797" t="s">
+        <v>37</v>
+      </c>
+      <c r="G797">
+        <v>5</v>
+      </c>
+      <c r="H797" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="I797" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="798" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A798" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B798">
+        <v>17</v>
+      </c>
+      <c r="C798" t="s">
+        <v>17</v>
+      </c>
+      <c r="D798" t="s">
+        <v>87</v>
+      </c>
+      <c r="E798" t="s">
+        <v>42</v>
+      </c>
+      <c r="F798" t="s">
+        <v>37</v>
+      </c>
+      <c r="G798">
+        <v>1</v>
+      </c>
+      <c r="H798" s="8">
+        <v>7.9861111111111116E-4</v>
+      </c>
+      <c r="I798" s="8">
+        <v>7.9861111111111116E-4</v>
+      </c>
+    </row>
+    <row r="799" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A799" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B799">
+        <v>17</v>
+      </c>
+      <c r="C799" t="s">
+        <v>17</v>
+      </c>
+      <c r="D799" t="s">
+        <v>87</v>
+      </c>
+      <c r="E799" t="s">
+        <v>42</v>
+      </c>
+      <c r="F799" t="s">
+        <v>37</v>
+      </c>
+      <c r="G799">
+        <v>4</v>
+      </c>
+      <c r="H799" s="8">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="I799" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="800" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A800" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B800">
+        <v>17</v>
+      </c>
+      <c r="C800" t="s">
+        <v>17</v>
+      </c>
+      <c r="D800" t="s">
+        <v>87</v>
+      </c>
+      <c r="E800" t="s">
+        <v>49</v>
+      </c>
+      <c r="F800" t="s">
+        <v>37</v>
+      </c>
+      <c r="G800">
+        <v>2</v>
+      </c>
+      <c r="H800" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="I800" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="801" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A801" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B801">
+        <v>18</v>
+      </c>
+      <c r="C801" t="s">
+        <v>17</v>
+      </c>
+      <c r="D801" t="s">
+        <v>86</v>
+      </c>
+      <c r="E801" t="s">
+        <v>29</v>
+      </c>
+      <c r="F801" t="s">
+        <v>6</v>
+      </c>
+      <c r="G801">
+        <v>6</v>
+      </c>
+      <c r="H801" s="8">
+        <v>0</v>
+      </c>
+      <c r="I801" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08AA15AF-6178-478B-88FD-0652281FB8EC}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E39D31-A1E7-4F9A-8A3C-9688A65E76F3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="91">
   <si>
     <t>Dt</t>
   </si>
@@ -702,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V220"/>
+  <dimension ref="A1:V223"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -13956,19 +13956,19 @@
         <v>25830</v>
       </c>
       <c r="G218" s="1">
-        <v>37386</v>
+        <v>37835</v>
       </c>
       <c r="H218" s="1">
-        <v>335</v>
+        <v>384</v>
       </c>
       <c r="I218" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J218" s="1">
         <v>5</v>
       </c>
       <c r="K218" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L218" s="1">
         <v>0</v>
@@ -13980,10 +13980,10 @@
         <v>1.3888888888888889E-4</v>
       </c>
       <c r="O218" s="4">
-        <v>2.8935185185185184E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="P218" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>1.01E-2</v>
       </c>
       <c r="Q218" s="6">
         <v>0</v>
@@ -13992,13 +13992,13 @@
         <v>20</v>
       </c>
       <c r="S218" s="1">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T218" s="5">
-        <v>5.8799999999999998E-2</v>
+        <v>0.1111</v>
       </c>
       <c r="U218" s="5">
-        <v>0.21740000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="V218" s="2">
         <v>58.161999999999999</v>
@@ -14024,10 +14024,10 @@
         <v>53489</v>
       </c>
       <c r="G219" s="1">
-        <v>13625</v>
+        <v>13711</v>
       </c>
       <c r="H219" s="1">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I219" s="1">
         <v>1</v>
@@ -14057,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="S219" s="1">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="V219" s="2">
         <v>36.223199999999999</v>
@@ -14074,28 +14074,28 @@
         <v>17</v>
       </c>
       <c r="D220" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E220" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F220" s="1">
         <v>25830</v>
       </c>
       <c r="G220" s="1">
-        <v>6</v>
+        <v>17867</v>
       </c>
       <c r="H220" s="1">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I220" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J220" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K220" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L220" s="1">
         <v>0</v>
@@ -14103,32 +14103,218 @@
       <c r="M220" s="1">
         <v>0</v>
       </c>
-      <c r="N220" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O220" s="1" t="s">
-        <v>21</v>
+      <c r="N220" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="O220" s="4">
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="P220" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q220" s="1" t="s">
-        <v>20</v>
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="Q220" s="6">
+        <v>0</v>
       </c>
       <c r="R220" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S220" s="1">
-        <v>0</v>
-      </c>
-      <c r="T220" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U220" s="1" t="s">
-        <v>20</v>
+        <v>0.69</v>
+      </c>
+      <c r="T220" s="5">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="U220" s="5">
+        <v>0.125</v>
       </c>
       <c r="V220" s="2">
-        <v>1.2063999999999999</v>
+        <v>32.661200000000001</v>
+      </c>
+    </row>
+    <row r="221" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A221" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B221" s="1">
+        <v>18</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D221" s="1">
+        <v>0</v>
+      </c>
+      <c r="E221" s="1">
+        <v>8</v>
+      </c>
+      <c r="F221" s="1">
+        <v>53489</v>
+      </c>
+      <c r="G221" s="1">
+        <v>13853</v>
+      </c>
+      <c r="H221" s="1">
+        <v>269</v>
+      </c>
+      <c r="I221" s="1">
+        <v>2</v>
+      </c>
+      <c r="J221" s="1">
+        <v>0</v>
+      </c>
+      <c r="K221" s="1">
+        <v>0</v>
+      </c>
+      <c r="L221" s="1">
+        <v>0</v>
+      </c>
+      <c r="M221" s="1">
+        <v>2</v>
+      </c>
+      <c r="O221" s="4">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="P221" s="5">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="Q221" s="5">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="R221" s="6">
+        <v>1</v>
+      </c>
+      <c r="S221" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="V221" s="2">
+        <v>32.661200000000001</v>
+      </c>
+    </row>
+    <row r="222" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A222" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B222" s="1">
+        <v>19</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D222" s="1">
+        <v>30</v>
+      </c>
+      <c r="E222" s="1">
+        <v>3</v>
+      </c>
+      <c r="F222" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G222" s="1">
+        <v>19738</v>
+      </c>
+      <c r="H222" s="1">
+        <v>146</v>
+      </c>
+      <c r="I222" s="1">
+        <v>8</v>
+      </c>
+      <c r="J222" s="1">
+        <v>3</v>
+      </c>
+      <c r="K222" s="1">
+        <v>5</v>
+      </c>
+      <c r="L222" s="1">
+        <v>1</v>
+      </c>
+      <c r="M222" s="1">
+        <v>1</v>
+      </c>
+      <c r="N222" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="O222" s="4">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="P222" s="5">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="Q222" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="R222" s="6">
+        <v>1</v>
+      </c>
+      <c r="S222" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="T222" s="6">
+        <v>0</v>
+      </c>
+      <c r="U222" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="V222" s="2">
+        <v>27.097200000000001</v>
+      </c>
+    </row>
+    <row r="223" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A223" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B223" s="1">
+        <v>19</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D223" s="1">
+        <v>0</v>
+      </c>
+      <c r="E223" s="1">
+        <v>8</v>
+      </c>
+      <c r="F223" s="1">
+        <v>53489</v>
+      </c>
+      <c r="G223" s="1">
+        <v>5437</v>
+      </c>
+      <c r="H223" s="1">
+        <v>126</v>
+      </c>
+      <c r="I223" s="1">
+        <v>1</v>
+      </c>
+      <c r="J223" s="1">
+        <v>0</v>
+      </c>
+      <c r="K223" s="1">
+        <v>0</v>
+      </c>
+      <c r="L223" s="1">
+        <v>0</v>
+      </c>
+      <c r="M223" s="1">
+        <v>1</v>
+      </c>
+      <c r="O223" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P223" s="5">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="Q223" s="5">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="R223" s="6">
+        <v>1</v>
+      </c>
+      <c r="S223" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="V223" s="2">
+        <v>10.145200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14139,7 +14325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I801"/>
+  <dimension ref="A1:I855"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -36439,13 +36625,13 @@
         <v>86</v>
       </c>
       <c r="E769" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F769" t="s">
         <v>6</v>
       </c>
       <c r="G769">
-        <v>1034</v>
+        <v>1772</v>
       </c>
       <c r="H769" s="8">
         <v>0</v>
@@ -36468,13 +36654,13 @@
         <v>86</v>
       </c>
       <c r="E770" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F770" t="s">
         <v>6</v>
       </c>
       <c r="G770">
-        <v>13078</v>
+        <v>1054</v>
       </c>
       <c r="H770" s="8">
         <v>0</v>
@@ -36497,13 +36683,13 @@
         <v>86</v>
       </c>
       <c r="E771" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F771" t="s">
         <v>6</v>
       </c>
       <c r="G771">
-        <v>1751</v>
+        <v>732</v>
       </c>
       <c r="H771" s="8">
         <v>0</v>
@@ -36526,13 +36712,13 @@
         <v>86</v>
       </c>
       <c r="E772" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F772" t="s">
         <v>6</v>
       </c>
       <c r="G772">
-        <v>15135</v>
+        <v>13223</v>
       </c>
       <c r="H772" s="8">
         <v>0</v>
@@ -36555,13 +36741,13 @@
         <v>86</v>
       </c>
       <c r="E773" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F773" t="s">
         <v>6</v>
       </c>
       <c r="G773">
-        <v>721</v>
+        <v>7</v>
       </c>
       <c r="H773" s="8">
         <v>0</v>
@@ -36613,13 +36799,13 @@
         <v>86</v>
       </c>
       <c r="E775" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F775" t="s">
         <v>6</v>
       </c>
       <c r="G775">
-        <v>7</v>
+        <v>15190</v>
       </c>
       <c r="H775" s="8">
         <v>0</v>
@@ -36706,13 +36892,13 @@
         <v>88</v>
       </c>
       <c r="G778">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H778" s="8">
-        <v>1.0879629629629629E-3</v>
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="I778" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>3.1250000000000001E-4</v>
       </c>
     </row>
     <row r="779" spans="1:9" x14ac:dyDescent="0.3">
@@ -36758,19 +36944,19 @@
         <v>86</v>
       </c>
       <c r="E780" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F780" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G780">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H780" s="8">
-        <v>1.5740740740740741E-3</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I780" s="8">
-        <v>3.1250000000000001E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
     </row>
     <row r="781" spans="1:9" x14ac:dyDescent="0.3">
@@ -36816,19 +37002,19 @@
         <v>86</v>
       </c>
       <c r="E782" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F782" t="s">
         <v>37</v>
       </c>
       <c r="G782">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H782" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>2.3495370370370371E-3</v>
       </c>
       <c r="I782" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>7.7546296296296293E-4</v>
       </c>
     </row>
     <row r="783" spans="1:9" x14ac:dyDescent="0.3">
@@ -36851,13 +37037,13 @@
         <v>88</v>
       </c>
       <c r="G783">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H783" s="8">
-        <v>3.8194444444444446E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="I783" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
     <row r="784" spans="1:9" x14ac:dyDescent="0.3">
@@ -36874,19 +37060,19 @@
         <v>86</v>
       </c>
       <c r="E784" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F784" t="s">
         <v>37</v>
       </c>
       <c r="G784">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H784" s="8">
-        <v>7.8356481481481489E-3</v>
+        <v>1.3194444444444445E-3</v>
       </c>
       <c r="I784" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>4.3981481481481481E-4</v>
       </c>
     </row>
     <row r="785" spans="1:9" x14ac:dyDescent="0.3">
@@ -36909,13 +37095,13 @@
         <v>88</v>
       </c>
       <c r="G785">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H785" s="8">
-        <v>8.1018518518518516E-4</v>
+        <v>3.8194444444444446E-4</v>
       </c>
       <c r="I785" s="8">
-        <v>1.6203703703703703E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.3">
@@ -36932,19 +37118,19 @@
         <v>86</v>
       </c>
       <c r="E786" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F786" t="s">
         <v>37</v>
       </c>
       <c r="G786">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H786" s="8">
-        <v>2.3495370370370371E-3</v>
+        <v>5.0810185185185186E-3</v>
       </c>
       <c r="I786" s="8">
-        <v>7.7546296296296293E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="787" spans="1:9" x14ac:dyDescent="0.3">
@@ -36961,19 +37147,19 @@
         <v>86</v>
       </c>
       <c r="E787" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F787" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G787">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H787" s="8">
-        <v>5.2083333333333333E-4</v>
+        <v>8.1018518518518516E-4</v>
       </c>
       <c r="I787" s="8">
-        <v>4.6296296296296294E-5</v>
+        <v>1.6203703703703703E-4</v>
       </c>
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.3">
@@ -36990,19 +37176,19 @@
         <v>86</v>
       </c>
       <c r="E788" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F788" t="s">
         <v>37</v>
       </c>
       <c r="G788">
-        <v>3</v>
+        <v>277</v>
       </c>
       <c r="H788" s="8">
-        <v>1.3194444444444445E-3</v>
+        <v>2.7731481481481482E-2</v>
       </c>
       <c r="I788" s="8">
-        <v>4.3981481481481481E-4</v>
+        <v>9.2592592592592588E-5</v>
       </c>
     </row>
     <row r="789" spans="1:9" x14ac:dyDescent="0.3">
@@ -37019,19 +37205,19 @@
         <v>86</v>
       </c>
       <c r="E789" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F789" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G789">
-        <v>708</v>
+        <v>5</v>
       </c>
       <c r="H789" s="8">
-        <v>0</v>
+        <v>1.25E-3</v>
       </c>
       <c r="I789" s="8">
-        <v>0</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="790" spans="1:9" x14ac:dyDescent="0.3">
@@ -37048,19 +37234,19 @@
         <v>86</v>
       </c>
       <c r="E790" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F790" t="s">
         <v>37</v>
       </c>
       <c r="G790">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H790" s="8">
-        <v>4.2361111111111115E-3</v>
+        <v>8.564814814814815E-4</v>
       </c>
       <c r="I790" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>5.7870370370370373E-5</v>
       </c>
     </row>
     <row r="791" spans="1:9" x14ac:dyDescent="0.3">
@@ -37077,19 +37263,19 @@
         <v>86</v>
       </c>
       <c r="E791" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="F791" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G791">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H791" s="8">
-        <v>0</v>
+        <v>9.0624999999999994E-3</v>
       </c>
       <c r="I791" s="8">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="792" spans="1:9" x14ac:dyDescent="0.3">
@@ -37106,19 +37292,19 @@
         <v>86</v>
       </c>
       <c r="E792" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F792" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G792">
-        <v>244</v>
+        <v>725</v>
       </c>
       <c r="H792" s="8">
-        <v>2.3796296296296298E-2</v>
+        <v>0</v>
       </c>
       <c r="I792" s="8">
-        <v>9.2592592592592588E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="793" spans="1:9" x14ac:dyDescent="0.3">
@@ -37132,22 +37318,22 @@
         <v>17</v>
       </c>
       <c r="D793" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E793" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F793" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G793">
-        <v>4</v>
+        <v>4740</v>
       </c>
       <c r="H793" s="8">
-        <v>1.3194444444444445E-3</v>
+        <v>0</v>
       </c>
       <c r="I793" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="794" spans="1:9" x14ac:dyDescent="0.3">
@@ -37161,22 +37347,22 @@
         <v>17</v>
       </c>
       <c r="D794" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E794" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F794" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G794">
-        <v>4609</v>
+        <v>1</v>
       </c>
       <c r="H794" s="8">
-        <v>0</v>
+        <v>6.9444444444444444E-5</v>
       </c>
       <c r="I794" s="8">
-        <v>0</v>
+        <v>6.9444444444444444E-5</v>
       </c>
     </row>
     <row r="795" spans="1:9" x14ac:dyDescent="0.3">
@@ -37190,22 +37376,22 @@
         <v>17</v>
       </c>
       <c r="D795" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E795" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F795" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G795">
         <v>1</v>
       </c>
       <c r="H795" s="8">
-        <v>4.1666666666666669E-4</v>
+        <v>0</v>
       </c>
       <c r="I795" s="8">
-        <v>4.1666666666666669E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="796" spans="1:9" x14ac:dyDescent="0.3">
@@ -37222,7 +37408,7 @@
         <v>87</v>
       </c>
       <c r="E796" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F796" t="s">
         <v>37</v>
@@ -37231,10 +37417,10 @@
         <v>1</v>
       </c>
       <c r="H796" s="8">
-        <v>6.9444444444444444E-5</v>
+        <v>7.9861111111111116E-4</v>
       </c>
       <c r="I796" s="8">
-        <v>6.9444444444444444E-5</v>
+        <v>7.9861111111111116E-4</v>
       </c>
     </row>
     <row r="797" spans="1:9" x14ac:dyDescent="0.3">
@@ -37251,19 +37437,19 @@
         <v>87</v>
       </c>
       <c r="E797" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F797" t="s">
         <v>37</v>
       </c>
       <c r="G797">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H797" s="8">
-        <v>7.291666666666667E-4</v>
+        <v>4.1666666666666669E-4</v>
       </c>
       <c r="I797" s="8">
-        <v>1.3888888888888889E-4</v>
+        <v>4.1666666666666669E-4</v>
       </c>
     </row>
     <row r="798" spans="1:9" x14ac:dyDescent="0.3">
@@ -37286,13 +37472,13 @@
         <v>37</v>
       </c>
       <c r="G798">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H798" s="8">
-        <v>7.9861111111111116E-4</v>
+        <v>1.0648148148148149E-3</v>
       </c>
       <c r="I798" s="8">
-        <v>7.9861111111111116E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
     </row>
     <row r="799" spans="1:9" x14ac:dyDescent="0.3">
@@ -37309,19 +37495,19 @@
         <v>87</v>
       </c>
       <c r="E799" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F799" t="s">
         <v>37</v>
       </c>
       <c r="G799">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H799" s="8">
-        <v>1.0648148148148149E-3</v>
+        <v>3.4722222222222222E-5</v>
       </c>
       <c r="I799" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>3.4722222222222222E-5</v>
       </c>
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.3">
@@ -37338,19 +37524,19 @@
         <v>87</v>
       </c>
       <c r="E800" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F800" t="s">
         <v>37</v>
       </c>
       <c r="G800">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H800" s="8">
-        <v>2.8935185185185184E-4</v>
+        <v>1.5856481481481481E-3</v>
       </c>
       <c r="I800" s="8">
-        <v>1.3888888888888889E-4</v>
+        <v>3.1250000000000001E-4</v>
       </c>
     </row>
     <row r="801" spans="1:9" x14ac:dyDescent="0.3">
@@ -37358,28 +37544,1594 @@
         <v>46141</v>
       </c>
       <c r="B801">
+        <v>17</v>
+      </c>
+      <c r="C801" t="s">
+        <v>17</v>
+      </c>
+      <c r="D801" t="s">
+        <v>87</v>
+      </c>
+      <c r="E801" t="s">
+        <v>47</v>
+      </c>
+      <c r="F801" t="s">
+        <v>37</v>
+      </c>
+      <c r="G801">
+        <v>5</v>
+      </c>
+      <c r="H801" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="I801" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="802" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A802" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B802">
+        <v>17</v>
+      </c>
+      <c r="C802" t="s">
+        <v>17</v>
+      </c>
+      <c r="D802" t="s">
+        <v>87</v>
+      </c>
+      <c r="E802" t="s">
+        <v>49</v>
+      </c>
+      <c r="F802" t="s">
+        <v>37</v>
+      </c>
+      <c r="G802">
+        <v>2</v>
+      </c>
+      <c r="H802" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="I802" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="803" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A803" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B803">
         <v>18</v>
       </c>
-      <c r="C801" t="s">
-        <v>17</v>
-      </c>
-      <c r="D801" t="s">
-        <v>86</v>
-      </c>
-      <c r="E801" t="s">
+      <c r="C803" t="s">
+        <v>17</v>
+      </c>
+      <c r="D803" t="s">
+        <v>86</v>
+      </c>
+      <c r="E803" t="s">
+        <v>33</v>
+      </c>
+      <c r="F803" t="s">
+        <v>6</v>
+      </c>
+      <c r="G803">
+        <v>583</v>
+      </c>
+      <c r="H803" s="8">
+        <v>0</v>
+      </c>
+      <c r="I803" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A804" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B804">
+        <v>18</v>
+      </c>
+      <c r="C804" t="s">
+        <v>17</v>
+      </c>
+      <c r="D804" t="s">
+        <v>86</v>
+      </c>
+      <c r="E804" t="s">
+        <v>30</v>
+      </c>
+      <c r="F804" t="s">
+        <v>6</v>
+      </c>
+      <c r="G804">
+        <v>7212</v>
+      </c>
+      <c r="H804" s="8">
+        <v>0</v>
+      </c>
+      <c r="I804" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A805" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B805">
+        <v>18</v>
+      </c>
+      <c r="C805" t="s">
+        <v>17</v>
+      </c>
+      <c r="D805" t="s">
+        <v>86</v>
+      </c>
+      <c r="E805" t="s">
+        <v>32</v>
+      </c>
+      <c r="F805" t="s">
+        <v>6</v>
+      </c>
+      <c r="G805">
+        <v>765</v>
+      </c>
+      <c r="H805" s="8">
+        <v>0</v>
+      </c>
+      <c r="I805" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A806" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B806">
+        <v>18</v>
+      </c>
+      <c r="C806" t="s">
+        <v>17</v>
+      </c>
+      <c r="D806" t="s">
+        <v>86</v>
+      </c>
+      <c r="E806" t="s">
         <v>29</v>
       </c>
-      <c r="F801" t="s">
+      <c r="F806" t="s">
         <v>6</v>
       </c>
-      <c r="G801">
+      <c r="G806">
+        <v>5739</v>
+      </c>
+      <c r="H806" s="8">
+        <v>0</v>
+      </c>
+      <c r="I806" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A807" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B807">
+        <v>18</v>
+      </c>
+      <c r="C807" t="s">
+        <v>17</v>
+      </c>
+      <c r="D807" t="s">
+        <v>86</v>
+      </c>
+      <c r="E807" t="s">
+        <v>34</v>
+      </c>
+      <c r="F807" t="s">
         <v>6</v>
       </c>
-      <c r="H801" s="8">
-        <v>0</v>
-      </c>
-      <c r="I801" s="8">
-        <v>0</v>
+      <c r="G807">
+        <v>277</v>
+      </c>
+      <c r="H807" s="8">
+        <v>0</v>
+      </c>
+      <c r="I807" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A808" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B808">
+        <v>18</v>
+      </c>
+      <c r="C808" t="s">
+        <v>17</v>
+      </c>
+      <c r="D808" t="s">
+        <v>86</v>
+      </c>
+      <c r="E808" t="s">
+        <v>45</v>
+      </c>
+      <c r="F808" t="s">
+        <v>6</v>
+      </c>
+      <c r="G808">
+        <v>1</v>
+      </c>
+      <c r="H808" s="8">
+        <v>0</v>
+      </c>
+      <c r="I808" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A809" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B809">
+        <v>18</v>
+      </c>
+      <c r="C809" t="s">
+        <v>17</v>
+      </c>
+      <c r="D809" t="s">
+        <v>86</v>
+      </c>
+      <c r="E809" t="s">
+        <v>40</v>
+      </c>
+      <c r="F809" t="s">
+        <v>6</v>
+      </c>
+      <c r="G809">
+        <v>1</v>
+      </c>
+      <c r="H809" s="8">
+        <v>0</v>
+      </c>
+      <c r="I809" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A810" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B810">
+        <v>18</v>
+      </c>
+      <c r="C810" t="s">
+        <v>17</v>
+      </c>
+      <c r="D810" t="s">
+        <v>86</v>
+      </c>
+      <c r="E810" t="s">
+        <v>41</v>
+      </c>
+      <c r="F810" t="s">
+        <v>88</v>
+      </c>
+      <c r="G810">
+        <v>2</v>
+      </c>
+      <c r="H810" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="I810" s="8">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="811" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A811" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B811">
+        <v>18</v>
+      </c>
+      <c r="C811" t="s">
+        <v>17</v>
+      </c>
+      <c r="D811" t="s">
+        <v>86</v>
+      </c>
+      <c r="E811" t="s">
+        <v>43</v>
+      </c>
+      <c r="F811" t="s">
+        <v>6</v>
+      </c>
+      <c r="G811">
+        <v>76</v>
+      </c>
+      <c r="H811" s="8">
+        <v>0</v>
+      </c>
+      <c r="I811" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A812" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B812">
+        <v>18</v>
+      </c>
+      <c r="C812" t="s">
+        <v>17</v>
+      </c>
+      <c r="D812" t="s">
+        <v>86</v>
+      </c>
+      <c r="E812" t="s">
+        <v>41</v>
+      </c>
+      <c r="F812" t="s">
+        <v>88</v>
+      </c>
+      <c r="G812">
+        <v>2</v>
+      </c>
+      <c r="H812" s="8">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="I812" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="813" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A813" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B813">
+        <v>18</v>
+      </c>
+      <c r="C813" t="s">
+        <v>17</v>
+      </c>
+      <c r="D813" t="s">
+        <v>86</v>
+      </c>
+      <c r="E813" t="s">
+        <v>41</v>
+      </c>
+      <c r="F813" t="s">
+        <v>88</v>
+      </c>
+      <c r="G813">
+        <v>1</v>
+      </c>
+      <c r="H813" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I813" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="814" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A814" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B814">
+        <v>18</v>
+      </c>
+      <c r="C814" t="s">
+        <v>17</v>
+      </c>
+      <c r="D814" t="s">
+        <v>86</v>
+      </c>
+      <c r="E814" t="s">
+        <v>41</v>
+      </c>
+      <c r="F814" t="s">
+        <v>88</v>
+      </c>
+      <c r="G814">
+        <v>7</v>
+      </c>
+      <c r="H814" s="8">
+        <v>1.7708333333333332E-3</v>
+      </c>
+      <c r="I814" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="815" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A815" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B815">
+        <v>18</v>
+      </c>
+      <c r="C815" t="s">
+        <v>17</v>
+      </c>
+      <c r="D815" t="s">
+        <v>86</v>
+      </c>
+      <c r="E815" t="s">
+        <v>41</v>
+      </c>
+      <c r="F815" t="s">
+        <v>88</v>
+      </c>
+      <c r="G815">
+        <v>1</v>
+      </c>
+      <c r="H815" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="I815" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+    </row>
+    <row r="816" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A816" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B816">
+        <v>18</v>
+      </c>
+      <c r="C816" t="s">
+        <v>17</v>
+      </c>
+      <c r="D816" t="s">
+        <v>86</v>
+      </c>
+      <c r="E816" t="s">
+        <v>57</v>
+      </c>
+      <c r="F816" t="s">
+        <v>37</v>
+      </c>
+      <c r="G816">
+        <v>4</v>
+      </c>
+      <c r="H816" s="8">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="I816" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="817" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A817" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B817">
+        <v>18</v>
+      </c>
+      <c r="C817" t="s">
+        <v>17</v>
+      </c>
+      <c r="D817" t="s">
+        <v>86</v>
+      </c>
+      <c r="E817" t="s">
+        <v>50</v>
+      </c>
+      <c r="F817" t="s">
+        <v>37</v>
+      </c>
+      <c r="G817">
+        <v>2</v>
+      </c>
+      <c r="H817" s="8">
+        <v>1.6203703703703703E-3</v>
+      </c>
+      <c r="I817" s="8">
+        <v>8.1018518518518516E-4</v>
+      </c>
+    </row>
+    <row r="818" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A818" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B818">
+        <v>18</v>
+      </c>
+      <c r="C818" t="s">
+        <v>17</v>
+      </c>
+      <c r="D818" t="s">
+        <v>86</v>
+      </c>
+      <c r="E818" t="s">
+        <v>38</v>
+      </c>
+      <c r="F818" t="s">
+        <v>37</v>
+      </c>
+      <c r="G818">
+        <v>29</v>
+      </c>
+      <c r="H818" s="8">
+        <v>8.2870370370370372E-3</v>
+      </c>
+      <c r="I818" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="819" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A819" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B819">
+        <v>18</v>
+      </c>
+      <c r="C819" t="s">
+        <v>17</v>
+      </c>
+      <c r="D819" t="s">
+        <v>86</v>
+      </c>
+      <c r="E819" t="s">
+        <v>59</v>
+      </c>
+      <c r="F819" t="s">
+        <v>37</v>
+      </c>
+      <c r="G819">
+        <v>1</v>
+      </c>
+      <c r="H819" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I819" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="820" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A820" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B820">
+        <v>18</v>
+      </c>
+      <c r="C820" t="s">
+        <v>17</v>
+      </c>
+      <c r="D820" t="s">
+        <v>86</v>
+      </c>
+      <c r="E820" t="s">
+        <v>39</v>
+      </c>
+      <c r="F820" t="s">
+        <v>88</v>
+      </c>
+      <c r="G820">
+        <v>1</v>
+      </c>
+      <c r="H820" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="I820" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="821" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A821" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B821">
+        <v>18</v>
+      </c>
+      <c r="C821" t="s">
+        <v>17</v>
+      </c>
+      <c r="D821" t="s">
+        <v>86</v>
+      </c>
+      <c r="E821" t="s">
+        <v>52</v>
+      </c>
+      <c r="F821" t="s">
+        <v>37</v>
+      </c>
+      <c r="G821">
+        <v>1</v>
+      </c>
+      <c r="H821" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="I821" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="822" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A822" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B822">
+        <v>18</v>
+      </c>
+      <c r="C822" t="s">
+        <v>17</v>
+      </c>
+      <c r="D822" t="s">
+        <v>86</v>
+      </c>
+      <c r="E822" t="s">
+        <v>36</v>
+      </c>
+      <c r="F822" t="s">
+        <v>37</v>
+      </c>
+      <c r="G822">
+        <v>157</v>
+      </c>
+      <c r="H822" s="8">
+        <v>1.5405092592592592E-2</v>
+      </c>
+      <c r="I822" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="823" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A823" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B823">
+        <v>18</v>
+      </c>
+      <c r="C823" t="s">
+        <v>17</v>
+      </c>
+      <c r="D823" t="s">
+        <v>86</v>
+      </c>
+      <c r="E823" t="s">
+        <v>39</v>
+      </c>
+      <c r="F823" t="s">
+        <v>37</v>
+      </c>
+      <c r="G823">
+        <v>13</v>
+      </c>
+      <c r="H823" s="8">
+        <v>2.0370370370370369E-3</v>
+      </c>
+      <c r="I823" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="824" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A824" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B824">
+        <v>18</v>
+      </c>
+      <c r="C824" t="s">
+        <v>17</v>
+      </c>
+      <c r="D824" t="s">
+        <v>86</v>
+      </c>
+      <c r="E824" t="s">
+        <v>36</v>
+      </c>
+      <c r="F824" t="s">
+        <v>88</v>
+      </c>
+      <c r="G824">
+        <v>1</v>
+      </c>
+      <c r="H824" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I824" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="825" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A825" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B825">
+        <v>18</v>
+      </c>
+      <c r="C825" t="s">
+        <v>17</v>
+      </c>
+      <c r="D825" t="s">
+        <v>86</v>
+      </c>
+      <c r="E825" t="s">
+        <v>39</v>
+      </c>
+      <c r="F825" t="s">
+        <v>88</v>
+      </c>
+      <c r="G825">
+        <v>1</v>
+      </c>
+      <c r="H825" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I825" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="826" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A826" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B826">
+        <v>18</v>
+      </c>
+      <c r="C826" t="s">
+        <v>17</v>
+      </c>
+      <c r="D826" t="s">
+        <v>86</v>
+      </c>
+      <c r="E826" t="s">
+        <v>35</v>
+      </c>
+      <c r="F826" t="s">
+        <v>6</v>
+      </c>
+      <c r="G826">
+        <v>399</v>
+      </c>
+      <c r="H826" s="8">
+        <v>0</v>
+      </c>
+      <c r="I826" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A827" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B827">
+        <v>18</v>
+      </c>
+      <c r="C827" t="s">
+        <v>17</v>
+      </c>
+      <c r="D827" t="s">
+        <v>86</v>
+      </c>
+      <c r="E827" t="s">
+        <v>31</v>
+      </c>
+      <c r="F827" t="s">
+        <v>6</v>
+      </c>
+      <c r="G827">
+        <v>2587</v>
+      </c>
+      <c r="H827" s="8">
+        <v>0</v>
+      </c>
+      <c r="I827" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A828" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B828">
+        <v>18</v>
+      </c>
+      <c r="C828" t="s">
+        <v>17</v>
+      </c>
+      <c r="D828" t="s">
+        <v>87</v>
+      </c>
+      <c r="E828" t="s">
+        <v>44</v>
+      </c>
+      <c r="F828" t="s">
+        <v>37</v>
+      </c>
+      <c r="G828">
+        <v>1</v>
+      </c>
+      <c r="H828" s="8">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="I828" s="8">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="829" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A829" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B829">
+        <v>18</v>
+      </c>
+      <c r="C829" t="s">
+        <v>17</v>
+      </c>
+      <c r="D829" t="s">
+        <v>86</v>
+      </c>
+      <c r="E829" t="s">
+        <v>44</v>
+      </c>
+      <c r="F829" t="s">
+        <v>37</v>
+      </c>
+      <c r="G829">
+        <v>4</v>
+      </c>
+      <c r="H829" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="I829" s="8">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="830" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A830" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B830">
+        <v>18</v>
+      </c>
+      <c r="C830" t="s">
+        <v>17</v>
+      </c>
+      <c r="D830" t="s">
+        <v>87</v>
+      </c>
+      <c r="E830" t="s">
+        <v>48</v>
+      </c>
+      <c r="F830" t="s">
+        <v>37</v>
+      </c>
+      <c r="G830">
+        <v>1</v>
+      </c>
+      <c r="H830" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="I830" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="831" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A831" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B831">
+        <v>18</v>
+      </c>
+      <c r="C831" t="s">
+        <v>17</v>
+      </c>
+      <c r="D831" t="s">
+        <v>87</v>
+      </c>
+      <c r="E831" t="s">
+        <v>49</v>
+      </c>
+      <c r="F831" t="s">
+        <v>37</v>
+      </c>
+      <c r="G831">
+        <v>2</v>
+      </c>
+      <c r="H831" s="8">
+        <v>5.1504629629629626E-3</v>
+      </c>
+      <c r="I831" s="8">
+        <v>2.5694444444444445E-3</v>
+      </c>
+    </row>
+    <row r="832" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A832" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B832">
+        <v>18</v>
+      </c>
+      <c r="C832" t="s">
+        <v>17</v>
+      </c>
+      <c r="D832" t="s">
+        <v>87</v>
+      </c>
+      <c r="E832" t="s">
+        <v>47</v>
+      </c>
+      <c r="F832" t="s">
+        <v>37</v>
+      </c>
+      <c r="G832">
+        <v>7</v>
+      </c>
+      <c r="H832" s="8">
+        <v>3.6342592592592594E-3</v>
+      </c>
+      <c r="I832" s="8">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="833" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A833" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B833">
+        <v>19</v>
+      </c>
+      <c r="C833" t="s">
+        <v>17</v>
+      </c>
+      <c r="D833" t="s">
+        <v>86</v>
+      </c>
+      <c r="E833" t="s">
+        <v>32</v>
+      </c>
+      <c r="F833" t="s">
+        <v>6</v>
+      </c>
+      <c r="G833">
+        <v>574</v>
+      </c>
+      <c r="H833" s="8">
+        <v>0</v>
+      </c>
+      <c r="I833" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A834" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B834">
+        <v>19</v>
+      </c>
+      <c r="C834" t="s">
+        <v>17</v>
+      </c>
+      <c r="D834" t="s">
+        <v>86</v>
+      </c>
+      <c r="E834" t="s">
+        <v>33</v>
+      </c>
+      <c r="F834" t="s">
+        <v>6</v>
+      </c>
+      <c r="G834">
+        <v>471</v>
+      </c>
+      <c r="H834" s="8">
+        <v>0</v>
+      </c>
+      <c r="I834" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A835" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B835">
+        <v>19</v>
+      </c>
+      <c r="C835" t="s">
+        <v>17</v>
+      </c>
+      <c r="D835" t="s">
+        <v>86</v>
+      </c>
+      <c r="E835" t="s">
+        <v>41</v>
+      </c>
+      <c r="F835" t="s">
+        <v>88</v>
+      </c>
+      <c r="G835">
+        <v>1</v>
+      </c>
+      <c r="H835" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I835" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="836" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A836" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B836">
+        <v>19</v>
+      </c>
+      <c r="C836" t="s">
+        <v>17</v>
+      </c>
+      <c r="D836" t="s">
+        <v>86</v>
+      </c>
+      <c r="E836" t="s">
+        <v>34</v>
+      </c>
+      <c r="F836" t="s">
+        <v>6</v>
+      </c>
+      <c r="G836">
+        <v>263</v>
+      </c>
+      <c r="H836" s="8">
+        <v>0</v>
+      </c>
+      <c r="I836" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A837" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B837">
+        <v>19</v>
+      </c>
+      <c r="C837" t="s">
+        <v>17</v>
+      </c>
+      <c r="D837" t="s">
+        <v>86</v>
+      </c>
+      <c r="E837" t="s">
+        <v>41</v>
+      </c>
+      <c r="F837" t="s">
+        <v>88</v>
+      </c>
+      <c r="G837">
+        <v>1</v>
+      </c>
+      <c r="H837" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I837" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="838" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A838" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B838">
+        <v>19</v>
+      </c>
+      <c r="C838" t="s">
+        <v>17</v>
+      </c>
+      <c r="D838" t="s">
+        <v>86</v>
+      </c>
+      <c r="E838" t="s">
+        <v>40</v>
+      </c>
+      <c r="F838" t="s">
+        <v>6</v>
+      </c>
+      <c r="G838">
+        <v>5</v>
+      </c>
+      <c r="H838" s="8">
+        <v>0</v>
+      </c>
+      <c r="I838" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A839" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B839">
+        <v>19</v>
+      </c>
+      <c r="C839" t="s">
+        <v>17</v>
+      </c>
+      <c r="D839" t="s">
+        <v>86</v>
+      </c>
+      <c r="E839" t="s">
+        <v>41</v>
+      </c>
+      <c r="F839" t="s">
+        <v>88</v>
+      </c>
+      <c r="G839">
+        <v>2</v>
+      </c>
+      <c r="H839" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I839" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="840" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A840" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B840">
+        <v>19</v>
+      </c>
+      <c r="C840" t="s">
+        <v>17</v>
+      </c>
+      <c r="D840" t="s">
+        <v>86</v>
+      </c>
+      <c r="E840" t="s">
+        <v>30</v>
+      </c>
+      <c r="F840" t="s">
+        <v>6</v>
+      </c>
+      <c r="G840">
+        <v>5701</v>
+      </c>
+      <c r="H840" s="8">
+        <v>0</v>
+      </c>
+      <c r="I840" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A841" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B841">
+        <v>19</v>
+      </c>
+      <c r="C841" t="s">
+        <v>17</v>
+      </c>
+      <c r="D841" t="s">
+        <v>86</v>
+      </c>
+      <c r="E841" t="s">
+        <v>41</v>
+      </c>
+      <c r="F841" t="s">
+        <v>88</v>
+      </c>
+      <c r="G841">
+        <v>3</v>
+      </c>
+      <c r="H841" s="8">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="I841" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="842" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A842" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B842">
+        <v>19</v>
+      </c>
+      <c r="C842" t="s">
+        <v>17</v>
+      </c>
+      <c r="D842" t="s">
+        <v>86</v>
+      </c>
+      <c r="E842" t="s">
+        <v>29</v>
+      </c>
+      <c r="F842" t="s">
+        <v>6</v>
+      </c>
+      <c r="G842">
+        <v>10232</v>
+      </c>
+      <c r="H842" s="8">
+        <v>0</v>
+      </c>
+      <c r="I842" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A843" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B843">
+        <v>19</v>
+      </c>
+      <c r="C843" t="s">
+        <v>17</v>
+      </c>
+      <c r="D843" t="s">
+        <v>86</v>
+      </c>
+      <c r="E843" t="s">
+        <v>38</v>
+      </c>
+      <c r="F843" t="s">
+        <v>37</v>
+      </c>
+      <c r="G843">
+        <v>24</v>
+      </c>
+      <c r="H843" s="8">
+        <v>5.4629629629629629E-3</v>
+      </c>
+      <c r="I843" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="844" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A844" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B844">
+        <v>19</v>
+      </c>
+      <c r="C844" t="s">
+        <v>17</v>
+      </c>
+      <c r="D844" t="s">
+        <v>86</v>
+      </c>
+      <c r="E844" t="s">
+        <v>45</v>
+      </c>
+      <c r="F844" t="s">
+        <v>6</v>
+      </c>
+      <c r="G844">
+        <v>3</v>
+      </c>
+      <c r="H844" s="8">
+        <v>0</v>
+      </c>
+      <c r="I844" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A845" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B845">
+        <v>19</v>
+      </c>
+      <c r="C845" t="s">
+        <v>17</v>
+      </c>
+      <c r="D845" t="s">
+        <v>86</v>
+      </c>
+      <c r="E845" t="s">
+        <v>39</v>
+      </c>
+      <c r="F845" t="s">
+        <v>88</v>
+      </c>
+      <c r="G845">
+        <v>1</v>
+      </c>
+      <c r="H845" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="I845" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="846" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A846" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B846">
+        <v>19</v>
+      </c>
+      <c r="C846" t="s">
+        <v>17</v>
+      </c>
+      <c r="D846" t="s">
+        <v>86</v>
+      </c>
+      <c r="E846" t="s">
+        <v>43</v>
+      </c>
+      <c r="F846" t="s">
+        <v>6</v>
+      </c>
+      <c r="G846">
+        <v>1</v>
+      </c>
+      <c r="H846" s="8">
+        <v>0</v>
+      </c>
+      <c r="I846" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A847" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B847">
+        <v>19</v>
+      </c>
+      <c r="C847" t="s">
+        <v>17</v>
+      </c>
+      <c r="D847" t="s">
+        <v>86</v>
+      </c>
+      <c r="E847" t="s">
+        <v>53</v>
+      </c>
+      <c r="F847" t="s">
+        <v>37</v>
+      </c>
+      <c r="G847">
+        <v>1</v>
+      </c>
+      <c r="H847" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I847" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="848" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A848" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B848">
+        <v>19</v>
+      </c>
+      <c r="C848" t="s">
+        <v>17</v>
+      </c>
+      <c r="D848" t="s">
+        <v>86</v>
+      </c>
+      <c r="E848" t="s">
+        <v>39</v>
+      </c>
+      <c r="F848" t="s">
+        <v>37</v>
+      </c>
+      <c r="G848">
+        <v>12</v>
+      </c>
+      <c r="H848" s="8">
+        <v>2.685185185185185E-3</v>
+      </c>
+      <c r="I848" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="849" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A849" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B849">
+        <v>19</v>
+      </c>
+      <c r="C849" t="s">
+        <v>17</v>
+      </c>
+      <c r="D849" t="s">
+        <v>86</v>
+      </c>
+      <c r="E849" t="s">
+        <v>31</v>
+      </c>
+      <c r="F849" t="s">
+        <v>6</v>
+      </c>
+      <c r="G849">
+        <v>2027</v>
+      </c>
+      <c r="H849" s="8">
+        <v>0</v>
+      </c>
+      <c r="I849" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A850" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B850">
+        <v>19</v>
+      </c>
+      <c r="C850" t="s">
+        <v>17</v>
+      </c>
+      <c r="D850" t="s">
+        <v>86</v>
+      </c>
+      <c r="E850" t="s">
+        <v>36</v>
+      </c>
+      <c r="F850" t="s">
+        <v>37</v>
+      </c>
+      <c r="G850">
+        <v>100</v>
+      </c>
+      <c r="H850" s="8">
+        <v>9.7337962962962959E-3</v>
+      </c>
+      <c r="I850" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="851" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A851" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B851">
+        <v>19</v>
+      </c>
+      <c r="C851" t="s">
+        <v>17</v>
+      </c>
+      <c r="D851" t="s">
+        <v>86</v>
+      </c>
+      <c r="E851" t="s">
+        <v>35</v>
+      </c>
+      <c r="F851" t="s">
+        <v>6</v>
+      </c>
+      <c r="G851">
+        <v>315</v>
+      </c>
+      <c r="H851" s="8">
+        <v>0</v>
+      </c>
+      <c r="I851" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A852" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B852">
+        <v>19</v>
+      </c>
+      <c r="C852" t="s">
+        <v>17</v>
+      </c>
+      <c r="D852" t="s">
+        <v>86</v>
+      </c>
+      <c r="E852" t="s">
+        <v>44</v>
+      </c>
+      <c r="F852" t="s">
+        <v>37</v>
+      </c>
+      <c r="G852">
+        <v>1</v>
+      </c>
+      <c r="H852" s="8">
+        <v>0</v>
+      </c>
+      <c r="I852" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A853" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B853">
+        <v>19</v>
+      </c>
+      <c r="C853" t="s">
+        <v>17</v>
+      </c>
+      <c r="D853" t="s">
+        <v>87</v>
+      </c>
+      <c r="E853" t="s">
+        <v>49</v>
+      </c>
+      <c r="F853" t="s">
+        <v>37</v>
+      </c>
+      <c r="G853">
+        <v>1</v>
+      </c>
+      <c r="H853" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="I853" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="854" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A854" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B854">
+        <v>19</v>
+      </c>
+      <c r="C854" t="s">
+        <v>17</v>
+      </c>
+      <c r="D854" t="s">
+        <v>87</v>
+      </c>
+      <c r="E854" t="s">
+        <v>58</v>
+      </c>
+      <c r="F854" t="s">
+        <v>11</v>
+      </c>
+      <c r="G854">
+        <v>1</v>
+      </c>
+      <c r="H854" s="8">
+        <v>5.7870370370370367E-3</v>
+      </c>
+      <c r="I854" s="8">
+        <v>5.7870370370370367E-3</v>
+      </c>
+    </row>
+    <row r="855" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A855" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B855">
+        <v>19</v>
+      </c>
+      <c r="C855" t="s">
+        <v>17</v>
+      </c>
+      <c r="D855" t="s">
+        <v>87</v>
+      </c>
+      <c r="E855" t="s">
+        <v>47</v>
+      </c>
+      <c r="F855" t="s">
+        <v>37</v>
+      </c>
+      <c r="G855">
+        <v>2</v>
+      </c>
+      <c r="H855" s="8">
+        <v>1.5856481481481481E-3</v>
+      </c>
+      <c r="I855" s="8">
+        <v>7.8703703703703705E-4</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E39D31-A1E7-4F9A-8A3C-9688A65E76F3}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36F0D9D1-32C3-4A34-BA2F-071A9585F1CF}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="91">
   <si>
     <t>Dt</t>
   </si>
@@ -702,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V223"/>
+  <dimension ref="A1:V225"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -14210,52 +14210,52 @@
         <v>25830</v>
       </c>
       <c r="G222" s="1">
-        <v>19738</v>
+        <v>53120</v>
       </c>
       <c r="H222" s="1">
-        <v>146</v>
+        <v>540</v>
       </c>
       <c r="I222" s="1">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J222" s="1">
+        <v>9</v>
+      </c>
+      <c r="K222" s="1">
+        <v>34</v>
+      </c>
+      <c r="L222" s="1">
         <v>3</v>
       </c>
-      <c r="K222" s="1">
-        <v>5</v>
-      </c>
-      <c r="L222" s="1">
-        <v>1</v>
-      </c>
       <c r="M222" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N222" s="4">
-        <v>1.273148148148148E-4</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="O222" s="4">
-        <v>2.5462962962962961E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
       <c r="P222" s="5">
-        <v>7.4000000000000003E-3</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="Q222" s="6">
-        <v>0.2</v>
+        <v>8.8200000000000001E-2</v>
       </c>
       <c r="R222" s="6">
         <v>1</v>
       </c>
       <c r="S222" s="1">
-        <v>0.76</v>
+        <v>2.06</v>
       </c>
       <c r="T222" s="6">
-        <v>0</v>
+        <v>2.9399999999999999E-2</v>
       </c>
       <c r="U222" s="5">
-        <v>0.375</v>
+        <v>0.20449999999999999</v>
       </c>
       <c r="V222" s="2">
-        <v>27.097200000000001</v>
+        <v>85.571200000000005</v>
       </c>
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.3">
@@ -14278,43 +14278,164 @@
         <v>53489</v>
       </c>
       <c r="G223" s="1">
-        <v>5437</v>
+        <v>14800</v>
       </c>
       <c r="H223" s="1">
-        <v>126</v>
+        <v>377</v>
       </c>
       <c r="I223" s="1">
+        <v>4</v>
+      </c>
+      <c r="J223" s="1">
+        <v>0</v>
+      </c>
+      <c r="K223" s="1">
+        <v>0</v>
+      </c>
+      <c r="L223" s="1">
+        <v>0</v>
+      </c>
+      <c r="M223" s="1">
+        <v>3</v>
+      </c>
+      <c r="O223" s="4">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="P223" s="5">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="Q223" s="5">
+        <v>1.06E-2</v>
+      </c>
+      <c r="R223" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="S223" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V223" s="2">
+        <v>35.718800000000002</v>
+      </c>
+    </row>
+    <row r="224" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A224" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B224" s="1">
+        <v>20</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D224" s="1">
+        <v>6</v>
+      </c>
+      <c r="E224" s="1">
+        <v>0</v>
+      </c>
+      <c r="F224" s="1">
+        <v>25830</v>
+      </c>
+      <c r="G224" s="1">
+        <v>6</v>
+      </c>
+      <c r="H224" s="1">
+        <v>6</v>
+      </c>
+      <c r="I224" s="1">
+        <v>0</v>
+      </c>
+      <c r="J224" s="1">
+        <v>0</v>
+      </c>
+      <c r="K224" s="1">
+        <v>0</v>
+      </c>
+      <c r="L224" s="1">
+        <v>0</v>
+      </c>
+      <c r="M224" s="1">
+        <v>0</v>
+      </c>
+      <c r="N224" s="4">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="O224" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P224" s="6">
         <v>1</v>
       </c>
-      <c r="J223" s="1">
-        <v>0</v>
-      </c>
-      <c r="K223" s="1">
-        <v>0</v>
-      </c>
-      <c r="L223" s="1">
-        <v>0</v>
-      </c>
-      <c r="M223" s="1">
+      <c r="Q224" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R224" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S224" s="1">
+        <v>0</v>
+      </c>
+      <c r="T224" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U224" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A225" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B225" s="1">
+        <v>20</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D225" s="1">
+        <v>0</v>
+      </c>
+      <c r="E225" s="1">
         <v>1</v>
       </c>
-      <c r="O223" s="4">
-        <v>2.199074074074074E-4</v>
-      </c>
-      <c r="P223" s="5">
-        <v>2.3199999999999998E-2</v>
-      </c>
-      <c r="Q223" s="5">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="R223" s="6">
+      <c r="F225" s="1">
+        <v>53489</v>
+      </c>
+      <c r="G225" s="1">
         <v>1</v>
       </c>
-      <c r="S223" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="V223" s="2">
-        <v>10.145200000000001</v>
+      <c r="H225" s="1">
+        <v>1</v>
+      </c>
+      <c r="I225" s="1">
+        <v>0</v>
+      </c>
+      <c r="J225" s="1">
+        <v>0</v>
+      </c>
+      <c r="K225" s="1">
+        <v>0</v>
+      </c>
+      <c r="L225" s="1">
+        <v>0</v>
+      </c>
+      <c r="M225" s="1">
+        <v>0</v>
+      </c>
+      <c r="O225" s="4">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="P225" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q225" s="6">
+        <v>0</v>
+      </c>
+      <c r="R225" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S225" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14325,7 +14446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I855"/>
+  <dimension ref="A1:I869"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -38481,13 +38602,13 @@
         <v>86</v>
       </c>
       <c r="E833" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F833" t="s">
         <v>6</v>
       </c>
       <c r="G833">
-        <v>574</v>
+        <v>845</v>
       </c>
       <c r="H833" s="8">
         <v>0</v>
@@ -38516,7 +38637,7 @@
         <v>6</v>
       </c>
       <c r="G834">
-        <v>471</v>
+        <v>1419</v>
       </c>
       <c r="H834" s="8">
         <v>0</v>
@@ -38539,19 +38660,19 @@
         <v>86</v>
       </c>
       <c r="E835" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F835" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G835">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H835" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>0</v>
       </c>
       <c r="I835" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="836" spans="1:9" x14ac:dyDescent="0.3">
@@ -38568,13 +38689,13 @@
         <v>86</v>
       </c>
       <c r="E836" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F836" t="s">
         <v>6</v>
       </c>
       <c r="G836">
-        <v>263</v>
+        <v>1572</v>
       </c>
       <c r="H836" s="8">
         <v>0</v>
@@ -38597,19 +38718,19 @@
         <v>86</v>
       </c>
       <c r="E837" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F837" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G837">
-        <v>1</v>
+        <v>16521</v>
       </c>
       <c r="H837" s="8">
-        <v>3.8194444444444446E-4</v>
+        <v>0</v>
       </c>
       <c r="I837" s="8">
-        <v>3.8194444444444446E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:9" x14ac:dyDescent="0.3">
@@ -38626,13 +38747,13 @@
         <v>86</v>
       </c>
       <c r="E838" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F838" t="s">
         <v>6</v>
       </c>
       <c r="G838">
-        <v>5</v>
+        <v>24879</v>
       </c>
       <c r="H838" s="8">
         <v>0</v>
@@ -38664,10 +38785,10 @@
         <v>2</v>
       </c>
       <c r="H839" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="I839" s="8">
         <v>3.5879629629629629E-4</v>
-      </c>
-      <c r="I839" s="8">
-        <v>1.7361111111111112E-4</v>
       </c>
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.3">
@@ -38684,13 +38805,13 @@
         <v>86</v>
       </c>
       <c r="E840" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F840" t="s">
         <v>6</v>
       </c>
       <c r="G840">
-        <v>5701</v>
+        <v>11</v>
       </c>
       <c r="H840" s="8">
         <v>0</v>
@@ -38722,10 +38843,10 @@
         <v>3</v>
       </c>
       <c r="H841" s="8">
-        <v>7.0601851851851847E-4</v>
+        <v>6.2500000000000001E-4</v>
       </c>
       <c r="I841" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="842" spans="1:9" x14ac:dyDescent="0.3">
@@ -38742,13 +38863,13 @@
         <v>86</v>
       </c>
       <c r="E842" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F842" t="s">
         <v>6</v>
       </c>
       <c r="G842">
-        <v>10232</v>
+        <v>1</v>
       </c>
       <c r="H842" s="8">
         <v>0</v>
@@ -38771,19 +38892,19 @@
         <v>86</v>
       </c>
       <c r="E843" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F843" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G843">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H843" s="8">
-        <v>5.4629629629629629E-3</v>
+        <v>8.4490740740740739E-4</v>
       </c>
       <c r="I843" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="844" spans="1:9" x14ac:dyDescent="0.3">
@@ -38800,19 +38921,19 @@
         <v>86</v>
       </c>
       <c r="E844" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F844" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G844">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H844" s="8">
-        <v>0</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I844" s="8">
-        <v>0</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="845" spans="1:9" x14ac:dyDescent="0.3">
@@ -38829,19 +38950,19 @@
         <v>86</v>
       </c>
       <c r="E845" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F845" t="s">
         <v>88</v>
       </c>
       <c r="G845">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H845" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>1.8634259259259259E-3</v>
       </c>
       <c r="I845" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="846" spans="1:9" x14ac:dyDescent="0.3">
@@ -38858,19 +38979,19 @@
         <v>86</v>
       </c>
       <c r="E846" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F846" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G846">
         <v>1</v>
       </c>
       <c r="H846" s="8">
-        <v>0</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="I846" s="8">
-        <v>0</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="847" spans="1:9" x14ac:dyDescent="0.3">
@@ -38887,19 +39008,19 @@
         <v>86</v>
       </c>
       <c r="E847" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F847" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G847">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H847" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>4.1666666666666666E-3</v>
       </c>
       <c r="I847" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="848" spans="1:9" x14ac:dyDescent="0.3">
@@ -38916,19 +39037,19 @@
         <v>86</v>
       </c>
       <c r="E848" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F848" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G848">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H848" s="8">
-        <v>2.685185185185185E-3</v>
+        <v>1.4814814814814814E-3</v>
       </c>
       <c r="I848" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="849" spans="1:9" x14ac:dyDescent="0.3">
@@ -38945,19 +39066,19 @@
         <v>86</v>
       </c>
       <c r="E849" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F849" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G849">
-        <v>2027</v>
+        <v>1</v>
       </c>
       <c r="H849" s="8">
-        <v>0</v>
+        <v>3.5879629629629629E-4</v>
       </c>
       <c r="I849" s="8">
-        <v>0</v>
+        <v>3.5879629629629629E-4</v>
       </c>
     </row>
     <row r="850" spans="1:9" x14ac:dyDescent="0.3">
@@ -38974,19 +39095,19 @@
         <v>86</v>
       </c>
       <c r="E850" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F850" t="s">
         <v>37</v>
       </c>
       <c r="G850">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H850" s="8">
-        <v>9.7337962962962959E-3</v>
+        <v>1.8518518518518519E-3</v>
       </c>
       <c r="I850" s="8">
-        <v>9.2592592592592588E-5</v>
+        <v>6.134259259259259E-4</v>
       </c>
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.3">
@@ -39003,19 +39124,19 @@
         <v>86</v>
       </c>
       <c r="E851" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F851" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G851">
-        <v>315</v>
+        <v>63</v>
       </c>
       <c r="H851" s="8">
-        <v>0</v>
+        <v>1.5162037037037036E-2</v>
       </c>
       <c r="I851" s="8">
-        <v>0</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.3">
@@ -39032,19 +39153,19 @@
         <v>86</v>
       </c>
       <c r="E852" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F852" t="s">
         <v>37</v>
       </c>
       <c r="G852">
-        <v>1</v>
+        <v>391</v>
       </c>
       <c r="H852" s="8">
-        <v>0</v>
+        <v>3.9016203703703706E-2</v>
       </c>
       <c r="I852" s="8">
-        <v>0</v>
+        <v>9.2592592592592588E-5</v>
       </c>
     </row>
     <row r="853" spans="1:9" x14ac:dyDescent="0.3">
@@ -39058,10 +39179,10 @@
         <v>17</v>
       </c>
       <c r="D853" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E853" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F853" t="s">
         <v>37</v>
@@ -39070,10 +39191,10 @@
         <v>1</v>
       </c>
       <c r="H853" s="8">
-        <v>1.273148148148148E-4</v>
+        <v>1.1458333333333333E-3</v>
       </c>
       <c r="I853" s="8">
-        <v>1.273148148148148E-4</v>
+        <v>1.1458333333333333E-3</v>
       </c>
     </row>
     <row r="854" spans="1:9" x14ac:dyDescent="0.3">
@@ -39087,22 +39208,22 @@
         <v>17</v>
       </c>
       <c r="D854" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E854" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F854" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G854">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H854" s="8">
-        <v>5.7870370370370367E-3</v>
+        <v>1.7939814814814815E-3</v>
       </c>
       <c r="I854" s="8">
-        <v>5.7870370370370367E-3</v>
+        <v>5.9027777777777778E-4</v>
       </c>
     </row>
     <row r="855" spans="1:9" x14ac:dyDescent="0.3">
@@ -39116,22 +39237,428 @@
         <v>17</v>
       </c>
       <c r="D855" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E855" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F855" t="s">
         <v>37</v>
       </c>
       <c r="G855">
+        <v>32</v>
+      </c>
+      <c r="H855" s="8">
+        <v>6.6550925925925927E-3</v>
+      </c>
+      <c r="I855" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="856" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A856" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B856">
+        <v>19</v>
+      </c>
+      <c r="C856" t="s">
+        <v>17</v>
+      </c>
+      <c r="D856" t="s">
+        <v>87</v>
+      </c>
+      <c r="E856" t="s">
+        <v>48</v>
+      </c>
+      <c r="F856" t="s">
+        <v>37</v>
+      </c>
+      <c r="G856">
+        <v>3</v>
+      </c>
+      <c r="H856" s="8">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="I856" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="857" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A857" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B857">
+        <v>19</v>
+      </c>
+      <c r="C857" t="s">
+        <v>17</v>
+      </c>
+      <c r="D857" t="s">
+        <v>86</v>
+      </c>
+      <c r="E857" t="s">
+        <v>39</v>
+      </c>
+      <c r="F857" t="s">
+        <v>88</v>
+      </c>
+      <c r="G857">
+        <v>1</v>
+      </c>
+      <c r="H857" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="I857" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="858" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A858" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B858">
+        <v>19</v>
+      </c>
+      <c r="C858" t="s">
+        <v>17</v>
+      </c>
+      <c r="D858" t="s">
+        <v>87</v>
+      </c>
+      <c r="E858" t="s">
+        <v>58</v>
+      </c>
+      <c r="F858" t="s">
+        <v>11</v>
+      </c>
+      <c r="G858">
+        <v>3</v>
+      </c>
+      <c r="H858" s="8">
+        <v>1.1886574074074074E-2</v>
+      </c>
+      <c r="I858" s="8">
+        <v>3.9583333333333337E-3</v>
+      </c>
+    </row>
+    <row r="859" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A859" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B859">
+        <v>19</v>
+      </c>
+      <c r="C859" t="s">
+        <v>17</v>
+      </c>
+      <c r="D859" t="s">
+        <v>86</v>
+      </c>
+      <c r="E859" t="s">
+        <v>53</v>
+      </c>
+      <c r="F859" t="s">
+        <v>37</v>
+      </c>
+      <c r="G859">
         <v>2</v>
       </c>
-      <c r="H855" s="8">
-        <v>1.5856481481481481E-3</v>
-      </c>
-      <c r="I855" s="8">
-        <v>7.8703703703703705E-4</v>
+      <c r="H859" s="8">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="I859" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="860" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A860" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B860">
+        <v>19</v>
+      </c>
+      <c r="C860" t="s">
+        <v>17</v>
+      </c>
+      <c r="D860" t="s">
+        <v>87</v>
+      </c>
+      <c r="E860" t="s">
+        <v>44</v>
+      </c>
+      <c r="F860" t="s">
+        <v>37</v>
+      </c>
+      <c r="G860">
+        <v>1</v>
+      </c>
+      <c r="H860" s="8">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="I860" s="8">
+        <v>9.3749999999999997E-4</v>
+      </c>
+    </row>
+    <row r="861" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A861" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B861">
+        <v>19</v>
+      </c>
+      <c r="C861" t="s">
+        <v>17</v>
+      </c>
+      <c r="D861" t="s">
+        <v>86</v>
+      </c>
+      <c r="E861" t="s">
+        <v>31</v>
+      </c>
+      <c r="F861" t="s">
+        <v>6</v>
+      </c>
+      <c r="G861">
+        <v>6260</v>
+      </c>
+      <c r="H861" s="8">
+        <v>0</v>
+      </c>
+      <c r="I861" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A862" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B862">
+        <v>19</v>
+      </c>
+      <c r="C862" t="s">
+        <v>17</v>
+      </c>
+      <c r="D862" t="s">
+        <v>87</v>
+      </c>
+      <c r="E862" t="s">
+        <v>47</v>
+      </c>
+      <c r="F862" t="s">
+        <v>37</v>
+      </c>
+      <c r="G862">
+        <v>18</v>
+      </c>
+      <c r="H862" s="8">
+        <v>1.0335648148148148E-2</v>
+      </c>
+      <c r="I862" s="8">
+        <v>5.6712962962962967E-4</v>
+      </c>
+    </row>
+    <row r="863" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A863" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B863">
+        <v>19</v>
+      </c>
+      <c r="C863" t="s">
+        <v>17</v>
+      </c>
+      <c r="D863" t="s">
+        <v>86</v>
+      </c>
+      <c r="E863" t="s">
+        <v>35</v>
+      </c>
+      <c r="F863" t="s">
+        <v>6</v>
+      </c>
+      <c r="G863">
+        <v>1060</v>
+      </c>
+      <c r="H863" s="8">
+        <v>0</v>
+      </c>
+      <c r="I863" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A864" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B864">
+        <v>19</v>
+      </c>
+      <c r="C864" t="s">
+        <v>17</v>
+      </c>
+      <c r="D864" t="s">
+        <v>87</v>
+      </c>
+      <c r="E864" t="s">
+        <v>42</v>
+      </c>
+      <c r="F864" t="s">
+        <v>37</v>
+      </c>
+      <c r="G864">
+        <v>6</v>
+      </c>
+      <c r="H864" s="8">
+        <v>1.9907407407407408E-3</v>
+      </c>
+      <c r="I864" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A865" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B865">
+        <v>19</v>
+      </c>
+      <c r="C865" t="s">
+        <v>17</v>
+      </c>
+      <c r="D865" t="s">
+        <v>87</v>
+      </c>
+      <c r="E865" t="s">
+        <v>49</v>
+      </c>
+      <c r="F865" t="s">
+        <v>37</v>
+      </c>
+      <c r="G865">
+        <v>2</v>
+      </c>
+      <c r="H865" s="8">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="I865" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A866" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B866">
+        <v>19</v>
+      </c>
+      <c r="C866" t="s">
+        <v>17</v>
+      </c>
+      <c r="D866" t="s">
+        <v>87</v>
+      </c>
+      <c r="E866" t="s">
+        <v>64</v>
+      </c>
+      <c r="F866" t="s">
+        <v>37</v>
+      </c>
+      <c r="G866">
+        <v>1</v>
+      </c>
+      <c r="H866" s="8">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="I866" s="8">
+        <v>6.3657407407407413E-4</v>
+      </c>
+    </row>
+    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A867" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B867">
+        <v>20</v>
+      </c>
+      <c r="C867" t="s">
+        <v>17</v>
+      </c>
+      <c r="D867" t="s">
+        <v>86</v>
+      </c>
+      <c r="E867" t="s">
+        <v>39</v>
+      </c>
+      <c r="F867" t="s">
+        <v>37</v>
+      </c>
+      <c r="G867">
+        <v>2</v>
+      </c>
+      <c r="H867" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="I867" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A868" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B868">
+        <v>20</v>
+      </c>
+      <c r="C868" t="s">
+        <v>17</v>
+      </c>
+      <c r="D868" t="s">
+        <v>86</v>
+      </c>
+      <c r="E868" t="s">
+        <v>44</v>
+      </c>
+      <c r="F868" t="s">
+        <v>37</v>
+      </c>
+      <c r="G868">
+        <v>1</v>
+      </c>
+      <c r="H868" s="8">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="I868" s="8">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A869" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B869">
+        <v>20</v>
+      </c>
+      <c r="C869" t="s">
+        <v>17</v>
+      </c>
+      <c r="D869" t="s">
+        <v>86</v>
+      </c>
+      <c r="E869" t="s">
+        <v>36</v>
+      </c>
+      <c r="F869" t="s">
+        <v>37</v>
+      </c>
+      <c r="G869">
+        <v>3</v>
+      </c>
+      <c r="H869" s="8">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="I869" s="8">
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36F0D9D1-32C3-4A34-BA2F-071A9585F1CF}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{721DF5F0-6A32-4204-8BB8-DE720E868C44}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
+    <workbookView xWindow="3084" yWindow="3504" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4411" uniqueCount="91">
   <si>
     <t>Dt</t>
   </si>
@@ -702,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V225"/>
+  <dimension ref="A1:V233"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -14382,7 +14382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>46141</v>
       </c>
@@ -14436,6 +14436,514 @@
       </c>
       <c r="S225" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A226" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B226" s="1">
+        <v>8</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D226" s="1">
+        <v>30</v>
+      </c>
+      <c r="E226" s="1">
+        <v>4</v>
+      </c>
+      <c r="F226" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G226" s="1">
+        <v>77446</v>
+      </c>
+      <c r="H226" s="1">
+        <v>720</v>
+      </c>
+      <c r="I226" s="1">
+        <v>64</v>
+      </c>
+      <c r="J226" s="1">
+        <v>18</v>
+      </c>
+      <c r="K226" s="1">
+        <v>40</v>
+      </c>
+      <c r="L226" s="1">
+        <v>6</v>
+      </c>
+      <c r="M226" s="1">
+        <v>1</v>
+      </c>
+      <c r="N226" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="O226" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P226" s="5">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="Q226" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="R226" s="5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="S226" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="T226" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="U226" s="5">
+        <v>0.28129999999999999</v>
+      </c>
+      <c r="V226" s="2">
+        <v>126.5836</v>
+      </c>
+    </row>
+    <row r="227" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A227" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B227" s="1">
+        <v>8</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D227" s="1">
+        <v>0</v>
+      </c>
+      <c r="E227" s="1">
+        <v>15</v>
+      </c>
+      <c r="F227" s="1">
+        <v>44686</v>
+      </c>
+      <c r="G227" s="1">
+        <v>18461</v>
+      </c>
+      <c r="H227" s="1">
+        <v>486</v>
+      </c>
+      <c r="I227" s="1">
+        <v>5</v>
+      </c>
+      <c r="J227" s="1">
+        <v>0</v>
+      </c>
+      <c r="K227" s="1">
+        <v>0</v>
+      </c>
+      <c r="L227" s="1">
+        <v>0</v>
+      </c>
+      <c r="M227" s="1">
+        <v>3</v>
+      </c>
+      <c r="O227" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P227" s="5">
+        <v>2.63E-2</v>
+      </c>
+      <c r="Q227" s="5">
+        <v>1.03E-2</v>
+      </c>
+      <c r="R227" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="S227" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="V227" s="2">
+        <v>45.8172</v>
+      </c>
+    </row>
+    <row r="228" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A228" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B228" s="1">
+        <v>9</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D228" s="1">
+        <v>30</v>
+      </c>
+      <c r="E228" s="1">
+        <v>3</v>
+      </c>
+      <c r="F228" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G228" s="1">
+        <v>96897</v>
+      </c>
+      <c r="H228" s="1">
+        <v>257</v>
+      </c>
+      <c r="I228" s="1">
+        <v>9</v>
+      </c>
+      <c r="J228" s="1">
+        <v>1</v>
+      </c>
+      <c r="K228" s="1">
+        <v>7</v>
+      </c>
+      <c r="L228" s="1">
+        <v>3</v>
+      </c>
+      <c r="M228" s="1">
+        <v>2</v>
+      </c>
+      <c r="N228" s="4">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="O228" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P228" s="5">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q228" s="5">
+        <v>0.42859999999999998</v>
+      </c>
+      <c r="R228" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="S228" s="1">
+        <v>3.88</v>
+      </c>
+      <c r="T228" s="5">
+        <v>0.1429</v>
+      </c>
+      <c r="U228" s="5">
+        <v>0.1111</v>
+      </c>
+      <c r="V228" s="2">
+        <v>41.563600000000001</v>
+      </c>
+    </row>
+    <row r="229" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A229" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B229" s="1">
+        <v>9</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D229" s="1">
+        <v>0</v>
+      </c>
+      <c r="E229" s="1">
+        <v>12</v>
+      </c>
+      <c r="F229" s="1">
+        <v>44686</v>
+      </c>
+      <c r="G229" s="1">
+        <v>19205</v>
+      </c>
+      <c r="H229" s="1">
+        <v>424</v>
+      </c>
+      <c r="I229" s="1">
+        <v>6</v>
+      </c>
+      <c r="J229" s="1">
+        <v>0</v>
+      </c>
+      <c r="K229" s="1">
+        <v>0</v>
+      </c>
+      <c r="L229" s="1">
+        <v>0</v>
+      </c>
+      <c r="M229" s="1">
+        <v>4</v>
+      </c>
+      <c r="O229" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P229" s="5">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="Q229" s="5">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="R229" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="S229" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="V229" s="2">
+        <v>36.233600000000003</v>
+      </c>
+    </row>
+    <row r="230" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A230" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B230" s="1">
+        <v>10</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D230" s="1">
+        <v>30</v>
+      </c>
+      <c r="E230" s="1">
+        <v>4</v>
+      </c>
+      <c r="F230" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G230" s="1">
+        <v>81149</v>
+      </c>
+      <c r="H230" s="1">
+        <v>529</v>
+      </c>
+      <c r="I230" s="1">
+        <v>43</v>
+      </c>
+      <c r="J230" s="1">
+        <v>9</v>
+      </c>
+      <c r="K230" s="1">
+        <v>30</v>
+      </c>
+      <c r="L230" s="1">
+        <v>10</v>
+      </c>
+      <c r="M230" s="1">
+        <v>6</v>
+      </c>
+      <c r="N230" s="4">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="O230" s="4">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="P230" s="5">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="Q230" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="R230" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="S230" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="T230" s="5">
+        <v>0.1333</v>
+      </c>
+      <c r="U230" s="5">
+        <v>0.20930000000000001</v>
+      </c>
+      <c r="V230" s="2">
+        <v>82.773600000000002</v>
+      </c>
+    </row>
+    <row r="231" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A231" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B231" s="1">
+        <v>10</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D231" s="1">
+        <v>0</v>
+      </c>
+      <c r="E231" s="1">
+        <v>11</v>
+      </c>
+      <c r="F231" s="1">
+        <v>44686</v>
+      </c>
+      <c r="G231" s="1">
+        <v>32437</v>
+      </c>
+      <c r="H231" s="1">
+        <v>406</v>
+      </c>
+      <c r="I231" s="1">
+        <v>8</v>
+      </c>
+      <c r="J231" s="1">
+        <v>0</v>
+      </c>
+      <c r="K231" s="1">
+        <v>0</v>
+      </c>
+      <c r="L231" s="1">
+        <v>0</v>
+      </c>
+      <c r="M231" s="1">
+        <v>3</v>
+      </c>
+      <c r="O231" s="4">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="P231" s="5">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="Q231" s="5">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="R231" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="S231" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="V231" s="2">
+        <v>42.468400000000003</v>
+      </c>
+    </row>
+    <row r="232" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A232" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B232" s="1">
+        <v>11</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D232" s="1">
+        <v>30</v>
+      </c>
+      <c r="E232" s="1">
+        <v>1</v>
+      </c>
+      <c r="F232" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G232" s="1">
+        <v>12888</v>
+      </c>
+      <c r="H232" s="1">
+        <v>127</v>
+      </c>
+      <c r="I232" s="1">
+        <v>5</v>
+      </c>
+      <c r="J232" s="1">
+        <v>2</v>
+      </c>
+      <c r="K232" s="1">
+        <v>2</v>
+      </c>
+      <c r="L232" s="1">
+        <v>1</v>
+      </c>
+      <c r="M232" s="1">
+        <v>0</v>
+      </c>
+      <c r="N232" s="4">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="O232" s="4">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="P232" s="5">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="Q232" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="R232" s="6">
+        <v>0</v>
+      </c>
+      <c r="S232" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="T232" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="U232" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="V232" s="2">
+        <v>19.6248</v>
+      </c>
+    </row>
+    <row r="233" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A233" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B233" s="1">
+        <v>11</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D233" s="1">
+        <v>0</v>
+      </c>
+      <c r="E233" s="1">
+        <v>9</v>
+      </c>
+      <c r="F233" s="1">
+        <v>44686</v>
+      </c>
+      <c r="G233" s="1">
+        <v>9227</v>
+      </c>
+      <c r="H233" s="1">
+        <v>121</v>
+      </c>
+      <c r="I233" s="1">
+        <v>0</v>
+      </c>
+      <c r="J233" s="1">
+        <v>0</v>
+      </c>
+      <c r="K233" s="1">
+        <v>0</v>
+      </c>
+      <c r="L233" s="1">
+        <v>0</v>
+      </c>
+      <c r="M233" s="1">
+        <v>0</v>
+      </c>
+      <c r="O233" s="4">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="P233" s="5">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="Q233" s="6">
+        <v>0</v>
+      </c>
+      <c r="R233" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S233" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="V233" s="2">
+        <v>12.4696</v>
       </c>
     </row>
   </sheetData>
@@ -14446,7 +14954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I869"/>
+  <dimension ref="A1:I1012"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -39661,6 +40169,4153 @@
         <v>2.0833333333333335E-4</v>
       </c>
     </row>
+    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A870" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B870">
+        <v>8</v>
+      </c>
+      <c r="C870" t="s">
+        <v>17</v>
+      </c>
+      <c r="D870" t="s">
+        <v>86</v>
+      </c>
+      <c r="E870" t="s">
+        <v>33</v>
+      </c>
+      <c r="F870" t="s">
+        <v>6</v>
+      </c>
+      <c r="G870">
+        <v>2341</v>
+      </c>
+      <c r="H870" s="8">
+        <v>0</v>
+      </c>
+      <c r="I870" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A871" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B871">
+        <v>8</v>
+      </c>
+      <c r="C871" t="s">
+        <v>17</v>
+      </c>
+      <c r="D871" t="s">
+        <v>86</v>
+      </c>
+      <c r="E871" t="s">
+        <v>32</v>
+      </c>
+      <c r="F871" t="s">
+        <v>6</v>
+      </c>
+      <c r="G871">
+        <v>5033</v>
+      </c>
+      <c r="H871" s="8">
+        <v>0</v>
+      </c>
+      <c r="I871" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A872" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B872">
+        <v>8</v>
+      </c>
+      <c r="C872" t="s">
+        <v>17</v>
+      </c>
+      <c r="D872" t="s">
+        <v>86</v>
+      </c>
+      <c r="E872" t="s">
+        <v>34</v>
+      </c>
+      <c r="F872" t="s">
+        <v>6</v>
+      </c>
+      <c r="G872">
+        <v>2829</v>
+      </c>
+      <c r="H872" s="8">
+        <v>0</v>
+      </c>
+      <c r="I872" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A873" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B873">
+        <v>8</v>
+      </c>
+      <c r="C873" t="s">
+        <v>17</v>
+      </c>
+      <c r="D873" t="s">
+        <v>86</v>
+      </c>
+      <c r="E873" t="s">
+        <v>40</v>
+      </c>
+      <c r="F873" t="s">
+        <v>6</v>
+      </c>
+      <c r="G873">
+        <v>16</v>
+      </c>
+      <c r="H873" s="8">
+        <v>0</v>
+      </c>
+      <c r="I873" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A874" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B874">
+        <v>8</v>
+      </c>
+      <c r="C874" t="s">
+        <v>17</v>
+      </c>
+      <c r="D874" t="s">
+        <v>86</v>
+      </c>
+      <c r="E874" t="s">
+        <v>30</v>
+      </c>
+      <c r="F874" t="s">
+        <v>6</v>
+      </c>
+      <c r="G874">
+        <v>26863</v>
+      </c>
+      <c r="H874" s="8">
+        <v>0</v>
+      </c>
+      <c r="I874" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A875" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B875">
+        <v>8</v>
+      </c>
+      <c r="C875" t="s">
+        <v>17</v>
+      </c>
+      <c r="D875" t="s">
+        <v>86</v>
+      </c>
+      <c r="E875" t="s">
+        <v>29</v>
+      </c>
+      <c r="F875" t="s">
+        <v>6</v>
+      </c>
+      <c r="G875">
+        <v>26917</v>
+      </c>
+      <c r="H875" s="8">
+        <v>0</v>
+      </c>
+      <c r="I875" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A876" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B876">
+        <v>8</v>
+      </c>
+      <c r="C876" t="s">
+        <v>17</v>
+      </c>
+      <c r="D876" t="s">
+        <v>86</v>
+      </c>
+      <c r="E876" t="s">
+        <v>45</v>
+      </c>
+      <c r="F876" t="s">
+        <v>6</v>
+      </c>
+      <c r="G876">
+        <v>6</v>
+      </c>
+      <c r="H876" s="8">
+        <v>0</v>
+      </c>
+      <c r="I876" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A877" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B877">
+        <v>8</v>
+      </c>
+      <c r="C877" t="s">
+        <v>17</v>
+      </c>
+      <c r="D877" t="s">
+        <v>86</v>
+      </c>
+      <c r="E877" t="s">
+        <v>56</v>
+      </c>
+      <c r="F877" t="s">
+        <v>37</v>
+      </c>
+      <c r="G877">
+        <v>3</v>
+      </c>
+      <c r="H877" s="8">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="I877" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A878" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B878">
+        <v>8</v>
+      </c>
+      <c r="C878" t="s">
+        <v>17</v>
+      </c>
+      <c r="D878" t="s">
+        <v>86</v>
+      </c>
+      <c r="E878" t="s">
+        <v>41</v>
+      </c>
+      <c r="F878" t="s">
+        <v>88</v>
+      </c>
+      <c r="G878">
+        <v>1</v>
+      </c>
+      <c r="H878" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="I878" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A879" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B879">
+        <v>8</v>
+      </c>
+      <c r="C879" t="s">
+        <v>17</v>
+      </c>
+      <c r="D879" t="s">
+        <v>86</v>
+      </c>
+      <c r="E879" t="s">
+        <v>41</v>
+      </c>
+      <c r="F879" t="s">
+        <v>88</v>
+      </c>
+      <c r="G879">
+        <v>1</v>
+      </c>
+      <c r="H879" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I879" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A880" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B880">
+        <v>8</v>
+      </c>
+      <c r="C880" t="s">
+        <v>17</v>
+      </c>
+      <c r="D880" t="s">
+        <v>86</v>
+      </c>
+      <c r="E880" t="s">
+        <v>41</v>
+      </c>
+      <c r="F880" t="s">
+        <v>88</v>
+      </c>
+      <c r="G880">
+        <v>1</v>
+      </c>
+      <c r="H880" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I880" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A881" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B881">
+        <v>8</v>
+      </c>
+      <c r="C881" t="s">
+        <v>17</v>
+      </c>
+      <c r="D881" t="s">
+        <v>86</v>
+      </c>
+      <c r="E881" t="s">
+        <v>41</v>
+      </c>
+      <c r="F881" t="s">
+        <v>88</v>
+      </c>
+      <c r="G881">
+        <v>1</v>
+      </c>
+      <c r="H881" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I881" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A882" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B882">
+        <v>8</v>
+      </c>
+      <c r="C882" t="s">
+        <v>17</v>
+      </c>
+      <c r="D882" t="s">
+        <v>86</v>
+      </c>
+      <c r="E882" t="s">
+        <v>41</v>
+      </c>
+      <c r="F882" t="s">
+        <v>88</v>
+      </c>
+      <c r="G882">
+        <v>2</v>
+      </c>
+      <c r="H882" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I882" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A883" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B883">
+        <v>8</v>
+      </c>
+      <c r="C883" t="s">
+        <v>17</v>
+      </c>
+      <c r="D883" t="s">
+        <v>86</v>
+      </c>
+      <c r="E883" t="s">
+        <v>41</v>
+      </c>
+      <c r="F883" t="s">
+        <v>88</v>
+      </c>
+      <c r="G883">
+        <v>2</v>
+      </c>
+      <c r="H883" s="8">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="I883" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A884" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B884">
+        <v>8</v>
+      </c>
+      <c r="C884" t="s">
+        <v>17</v>
+      </c>
+      <c r="D884" t="s">
+        <v>86</v>
+      </c>
+      <c r="E884" t="s">
+        <v>41</v>
+      </c>
+      <c r="F884" t="s">
+        <v>88</v>
+      </c>
+      <c r="G884">
+        <v>4</v>
+      </c>
+      <c r="H884" s="8">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="I884" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A885" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B885">
+        <v>8</v>
+      </c>
+      <c r="C885" t="s">
+        <v>17</v>
+      </c>
+      <c r="D885" t="s">
+        <v>86</v>
+      </c>
+      <c r="E885" t="s">
+        <v>41</v>
+      </c>
+      <c r="F885" t="s">
+        <v>88</v>
+      </c>
+      <c r="G885">
+        <v>5</v>
+      </c>
+      <c r="H885" s="8">
+        <v>1.3310185185185185E-3</v>
+      </c>
+      <c r="I885" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A886" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B886">
+        <v>8</v>
+      </c>
+      <c r="C886" t="s">
+        <v>17</v>
+      </c>
+      <c r="D886" t="s">
+        <v>86</v>
+      </c>
+      <c r="E886" t="s">
+        <v>41</v>
+      </c>
+      <c r="F886" t="s">
+        <v>88</v>
+      </c>
+      <c r="G886">
+        <v>8</v>
+      </c>
+      <c r="H886" s="8">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="I886" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A887" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B887">
+        <v>8</v>
+      </c>
+      <c r="C887" t="s">
+        <v>17</v>
+      </c>
+      <c r="D887" t="s">
+        <v>86</v>
+      </c>
+      <c r="E887" t="s">
+        <v>41</v>
+      </c>
+      <c r="F887" t="s">
+        <v>88</v>
+      </c>
+      <c r="G887">
+        <v>8</v>
+      </c>
+      <c r="H887" s="8">
+        <v>1.7824074074074075E-3</v>
+      </c>
+      <c r="I887" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A888" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B888">
+        <v>8</v>
+      </c>
+      <c r="C888" t="s">
+        <v>17</v>
+      </c>
+      <c r="D888" t="s">
+        <v>86</v>
+      </c>
+      <c r="E888" t="s">
+        <v>41</v>
+      </c>
+      <c r="F888" t="s">
+        <v>88</v>
+      </c>
+      <c r="G888">
+        <v>10</v>
+      </c>
+      <c r="H888" s="8">
+        <v>2.3263888888888887E-3</v>
+      </c>
+      <c r="I888" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A889" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B889">
+        <v>8</v>
+      </c>
+      <c r="C889" t="s">
+        <v>17</v>
+      </c>
+      <c r="D889" t="s">
+        <v>86</v>
+      </c>
+      <c r="E889" t="s">
+        <v>41</v>
+      </c>
+      <c r="F889" t="s">
+        <v>88</v>
+      </c>
+      <c r="G889">
+        <v>18</v>
+      </c>
+      <c r="H889" s="8">
+        <v>2.8703703703703703E-3</v>
+      </c>
+      <c r="I889" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A890" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B890">
+        <v>8</v>
+      </c>
+      <c r="C890" t="s">
+        <v>17</v>
+      </c>
+      <c r="D890" t="s">
+        <v>86</v>
+      </c>
+      <c r="E890" t="s">
+        <v>38</v>
+      </c>
+      <c r="F890" t="s">
+        <v>37</v>
+      </c>
+      <c r="G890">
+        <v>81</v>
+      </c>
+      <c r="H890" s="8">
+        <v>2.0636574074074075E-2</v>
+      </c>
+      <c r="I890" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A891" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B891">
+        <v>8</v>
+      </c>
+      <c r="C891" t="s">
+        <v>17</v>
+      </c>
+      <c r="D891" t="s">
+        <v>86</v>
+      </c>
+      <c r="E891" t="s">
+        <v>38</v>
+      </c>
+      <c r="F891" t="s">
+        <v>88</v>
+      </c>
+      <c r="G891">
+        <v>1</v>
+      </c>
+      <c r="H891" s="8">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="I891" s="8">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A892" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B892">
+        <v>8</v>
+      </c>
+      <c r="C892" t="s">
+        <v>17</v>
+      </c>
+      <c r="D892" t="s">
+        <v>86</v>
+      </c>
+      <c r="E892" t="s">
+        <v>50</v>
+      </c>
+      <c r="F892" t="s">
+        <v>37</v>
+      </c>
+      <c r="G892">
+        <v>7</v>
+      </c>
+      <c r="H892" s="8">
+        <v>4.363425925925926E-3</v>
+      </c>
+      <c r="I892" s="8">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A893" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B893">
+        <v>8</v>
+      </c>
+      <c r="C893" t="s">
+        <v>17</v>
+      </c>
+      <c r="D893" t="s">
+        <v>86</v>
+      </c>
+      <c r="E893" t="s">
+        <v>59</v>
+      </c>
+      <c r="F893" t="s">
+        <v>37</v>
+      </c>
+      <c r="G893">
+        <v>2</v>
+      </c>
+      <c r="H893" s="8">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="I893" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A894" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B894">
+        <v>8</v>
+      </c>
+      <c r="C894" t="s">
+        <v>17</v>
+      </c>
+      <c r="D894" t="s">
+        <v>86</v>
+      </c>
+      <c r="E894" t="s">
+        <v>51</v>
+      </c>
+      <c r="F894" t="s">
+        <v>37</v>
+      </c>
+      <c r="G894">
+        <v>2</v>
+      </c>
+      <c r="H894" s="8">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="I894" s="8">
+        <v>4.9768518518518521E-4</v>
+      </c>
+    </row>
+    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A895" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B895">
+        <v>8</v>
+      </c>
+      <c r="C895" t="s">
+        <v>17</v>
+      </c>
+      <c r="D895" t="s">
+        <v>86</v>
+      </c>
+      <c r="E895" t="s">
+        <v>52</v>
+      </c>
+      <c r="F895" t="s">
+        <v>37</v>
+      </c>
+      <c r="G895">
+        <v>1</v>
+      </c>
+      <c r="H895" s="8">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="I895" s="8">
+        <v>9.3749999999999997E-4</v>
+      </c>
+    </row>
+    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A896" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B896">
+        <v>8</v>
+      </c>
+      <c r="C896" t="s">
+        <v>17</v>
+      </c>
+      <c r="D896" t="s">
+        <v>86</v>
+      </c>
+      <c r="E896" t="s">
+        <v>39</v>
+      </c>
+      <c r="F896" t="s">
+        <v>37</v>
+      </c>
+      <c r="G896">
+        <v>35</v>
+      </c>
+      <c r="H896" s="8">
+        <v>9.432870370370371E-3</v>
+      </c>
+      <c r="I896" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="897" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A897" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B897">
+        <v>8</v>
+      </c>
+      <c r="C897" t="s">
+        <v>17</v>
+      </c>
+      <c r="D897" t="s">
+        <v>86</v>
+      </c>
+      <c r="E897" t="s">
+        <v>39</v>
+      </c>
+      <c r="F897" t="s">
+        <v>88</v>
+      </c>
+      <c r="G897">
+        <v>1</v>
+      </c>
+      <c r="H897" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I897" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="898" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A898" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B898">
+        <v>8</v>
+      </c>
+      <c r="C898" t="s">
+        <v>17</v>
+      </c>
+      <c r="D898" t="s">
+        <v>86</v>
+      </c>
+      <c r="E898" t="s">
+        <v>36</v>
+      </c>
+      <c r="F898" t="s">
+        <v>37</v>
+      </c>
+      <c r="G898">
+        <v>509</v>
+      </c>
+      <c r="H898" s="8">
+        <v>4.494212962962963E-2</v>
+      </c>
+      <c r="I898" s="8">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="899" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A899" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B899">
+        <v>8</v>
+      </c>
+      <c r="C899" t="s">
+        <v>17</v>
+      </c>
+      <c r="D899" t="s">
+        <v>86</v>
+      </c>
+      <c r="E899" t="s">
+        <v>36</v>
+      </c>
+      <c r="F899" t="s">
+        <v>88</v>
+      </c>
+      <c r="G899">
+        <v>1</v>
+      </c>
+      <c r="H899" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="I899" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="900" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A900" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B900">
+        <v>8</v>
+      </c>
+      <c r="C900" t="s">
+        <v>17</v>
+      </c>
+      <c r="D900" t="s">
+        <v>86</v>
+      </c>
+      <c r="E900" t="s">
+        <v>53</v>
+      </c>
+      <c r="F900" t="s">
+        <v>37</v>
+      </c>
+      <c r="G900">
+        <v>3</v>
+      </c>
+      <c r="H900" s="8">
+        <v>1.1805555555555556E-3</v>
+      </c>
+      <c r="I900" s="8">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="901" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A901" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B901">
+        <v>8</v>
+      </c>
+      <c r="C901" t="s">
+        <v>17</v>
+      </c>
+      <c r="D901" t="s">
+        <v>86</v>
+      </c>
+      <c r="E901" t="s">
+        <v>31</v>
+      </c>
+      <c r="F901" t="s">
+        <v>6</v>
+      </c>
+      <c r="G901">
+        <v>11186</v>
+      </c>
+      <c r="H901" s="8">
+        <v>0</v>
+      </c>
+      <c r="I901" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A902" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B902">
+        <v>8</v>
+      </c>
+      <c r="C902" t="s">
+        <v>17</v>
+      </c>
+      <c r="D902" t="s">
+        <v>86</v>
+      </c>
+      <c r="E902" t="s">
+        <v>44</v>
+      </c>
+      <c r="F902" t="s">
+        <v>37</v>
+      </c>
+      <c r="G902">
+        <v>13</v>
+      </c>
+      <c r="H902" s="8">
+        <v>1.0879629629629629E-3</v>
+      </c>
+      <c r="I902" s="8">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="903" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A903" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B903">
+        <v>8</v>
+      </c>
+      <c r="C903" t="s">
+        <v>17</v>
+      </c>
+      <c r="D903" t="s">
+        <v>86</v>
+      </c>
+      <c r="E903" t="s">
+        <v>35</v>
+      </c>
+      <c r="F903" t="s">
+        <v>6</v>
+      </c>
+      <c r="G903">
+        <v>1535</v>
+      </c>
+      <c r="H903" s="8">
+        <v>0</v>
+      </c>
+      <c r="I903" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A904" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B904">
+        <v>8</v>
+      </c>
+      <c r="C904" t="s">
+        <v>17</v>
+      </c>
+      <c r="D904" t="s">
+        <v>87</v>
+      </c>
+      <c r="E904" t="s">
+        <v>46</v>
+      </c>
+      <c r="F904" t="s">
+        <v>37</v>
+      </c>
+      <c r="G904">
+        <v>5</v>
+      </c>
+      <c r="H904" s="8">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="I904" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="905" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A905" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B905">
+        <v>8</v>
+      </c>
+      <c r="C905" t="s">
+        <v>17</v>
+      </c>
+      <c r="D905" t="s">
+        <v>87</v>
+      </c>
+      <c r="E905" t="s">
+        <v>62</v>
+      </c>
+      <c r="F905" t="s">
+        <v>10</v>
+      </c>
+      <c r="G905">
+        <v>1</v>
+      </c>
+      <c r="H905" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I905" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="906" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A906" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B906">
+        <v>8</v>
+      </c>
+      <c r="C906" t="s">
+        <v>17</v>
+      </c>
+      <c r="D906" t="s">
+        <v>87</v>
+      </c>
+      <c r="E906" t="s">
+        <v>42</v>
+      </c>
+      <c r="F906" t="s">
+        <v>37</v>
+      </c>
+      <c r="G906">
+        <v>8</v>
+      </c>
+      <c r="H906" s="8">
+        <v>4.0740740740740737E-3</v>
+      </c>
+      <c r="I906" s="8">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="907" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A907" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B907">
+        <v>8</v>
+      </c>
+      <c r="C907" t="s">
+        <v>17</v>
+      </c>
+      <c r="D907" t="s">
+        <v>87</v>
+      </c>
+      <c r="E907" t="s">
+        <v>48</v>
+      </c>
+      <c r="F907" t="s">
+        <v>37</v>
+      </c>
+      <c r="G907">
+        <v>8</v>
+      </c>
+      <c r="H907" s="8">
+        <v>3.6921296296296298E-3</v>
+      </c>
+      <c r="I907" s="8">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="908" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A908" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B908">
+        <v>8</v>
+      </c>
+      <c r="C908" t="s">
+        <v>17</v>
+      </c>
+      <c r="D908" t="s">
+        <v>87</v>
+      </c>
+      <c r="E908" t="s">
+        <v>49</v>
+      </c>
+      <c r="F908" t="s">
+        <v>37</v>
+      </c>
+      <c r="G908">
+        <v>4</v>
+      </c>
+      <c r="H908" s="8">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="I908" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="909" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A909" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B909">
+        <v>8</v>
+      </c>
+      <c r="C909" t="s">
+        <v>17</v>
+      </c>
+      <c r="D909" t="s">
+        <v>87</v>
+      </c>
+      <c r="E909" t="s">
+        <v>60</v>
+      </c>
+      <c r="F909" t="s">
+        <v>37</v>
+      </c>
+      <c r="G909">
+        <v>1</v>
+      </c>
+      <c r="H909" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="I909" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="910" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A910" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B910">
+        <v>8</v>
+      </c>
+      <c r="C910" t="s">
+        <v>17</v>
+      </c>
+      <c r="D910" t="s">
+        <v>87</v>
+      </c>
+      <c r="E910" t="s">
+        <v>61</v>
+      </c>
+      <c r="F910" t="s">
+        <v>10</v>
+      </c>
+      <c r="G910">
+        <v>2</v>
+      </c>
+      <c r="H910" s="8">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="I910" s="8">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="911" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A911" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B911">
+        <v>8</v>
+      </c>
+      <c r="C911" t="s">
+        <v>17</v>
+      </c>
+      <c r="D911" t="s">
+        <v>87</v>
+      </c>
+      <c r="E911" t="s">
+        <v>63</v>
+      </c>
+      <c r="F911" t="s">
+        <v>10</v>
+      </c>
+      <c r="G911">
+        <v>2</v>
+      </c>
+      <c r="H911" s="8">
+        <v>3.6342592592592594E-3</v>
+      </c>
+      <c r="I911" s="8">
+        <v>1.8171296296296297E-3</v>
+      </c>
+    </row>
+    <row r="912" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A912" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B912">
+        <v>8</v>
+      </c>
+      <c r="C912" t="s">
+        <v>17</v>
+      </c>
+      <c r="D912" t="s">
+        <v>87</v>
+      </c>
+      <c r="E912" t="s">
+        <v>54</v>
+      </c>
+      <c r="F912" t="s">
+        <v>11</v>
+      </c>
+      <c r="G912">
+        <v>1</v>
+      </c>
+      <c r="H912" s="8">
+        <v>4.6874999999999998E-3</v>
+      </c>
+      <c r="I912" s="8">
+        <v>4.6874999999999998E-3</v>
+      </c>
+    </row>
+    <row r="913" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A913" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B913">
+        <v>8</v>
+      </c>
+      <c r="C913" t="s">
+        <v>17</v>
+      </c>
+      <c r="D913" t="s">
+        <v>87</v>
+      </c>
+      <c r="E913" t="s">
+        <v>44</v>
+      </c>
+      <c r="F913" t="s">
+        <v>37</v>
+      </c>
+      <c r="G913">
+        <v>1</v>
+      </c>
+      <c r="H913" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="I913" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="914" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A914" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B914">
+        <v>8</v>
+      </c>
+      <c r="C914" t="s">
+        <v>17</v>
+      </c>
+      <c r="D914" t="s">
+        <v>87</v>
+      </c>
+      <c r="E914" t="s">
+        <v>47</v>
+      </c>
+      <c r="F914" t="s">
+        <v>37</v>
+      </c>
+      <c r="G914">
+        <v>10</v>
+      </c>
+      <c r="H914" s="8">
+        <v>1.0092592592592592E-2</v>
+      </c>
+      <c r="I914" s="8">
+        <v>1.0069444444444444E-3</v>
+      </c>
+    </row>
+    <row r="915" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A915" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B915">
+        <v>9</v>
+      </c>
+      <c r="C915" t="s">
+        <v>17</v>
+      </c>
+      <c r="D915" t="s">
+        <v>86</v>
+      </c>
+      <c r="E915" t="s">
+        <v>33</v>
+      </c>
+      <c r="F915" t="s">
+        <v>6</v>
+      </c>
+      <c r="G915">
+        <v>760</v>
+      </c>
+      <c r="H915" s="8">
+        <v>0</v>
+      </c>
+      <c r="I915" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A916" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B916">
+        <v>9</v>
+      </c>
+      <c r="C916" t="s">
+        <v>17</v>
+      </c>
+      <c r="D916" t="s">
+        <v>86</v>
+      </c>
+      <c r="E916" t="s">
+        <v>32</v>
+      </c>
+      <c r="F916" t="s">
+        <v>6</v>
+      </c>
+      <c r="G916">
+        <v>2588</v>
+      </c>
+      <c r="H916" s="8">
+        <v>0</v>
+      </c>
+      <c r="I916" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A917" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B917">
+        <v>9</v>
+      </c>
+      <c r="C917" t="s">
+        <v>17</v>
+      </c>
+      <c r="D917" t="s">
+        <v>86</v>
+      </c>
+      <c r="E917" t="s">
+        <v>34</v>
+      </c>
+      <c r="F917" t="s">
+        <v>6</v>
+      </c>
+      <c r="G917">
+        <v>900</v>
+      </c>
+      <c r="H917" s="8">
+        <v>0</v>
+      </c>
+      <c r="I917" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A918" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B918">
+        <v>9</v>
+      </c>
+      <c r="C918" t="s">
+        <v>17</v>
+      </c>
+      <c r="D918" t="s">
+        <v>86</v>
+      </c>
+      <c r="E918" t="s">
+        <v>40</v>
+      </c>
+      <c r="F918" t="s">
+        <v>6</v>
+      </c>
+      <c r="G918">
+        <v>8</v>
+      </c>
+      <c r="H918" s="8">
+        <v>0</v>
+      </c>
+      <c r="I918" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A919" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B919">
+        <v>9</v>
+      </c>
+      <c r="C919" t="s">
+        <v>17</v>
+      </c>
+      <c r="D919" t="s">
+        <v>86</v>
+      </c>
+      <c r="E919" t="s">
+        <v>30</v>
+      </c>
+      <c r="F919" t="s">
+        <v>6</v>
+      </c>
+      <c r="G919">
+        <v>8617</v>
+      </c>
+      <c r="H919" s="8">
+        <v>0</v>
+      </c>
+      <c r="I919" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A920" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B920">
+        <v>9</v>
+      </c>
+      <c r="C920" t="s">
+        <v>17</v>
+      </c>
+      <c r="D920" t="s">
+        <v>86</v>
+      </c>
+      <c r="E920" t="s">
+        <v>29</v>
+      </c>
+      <c r="F920" t="s">
+        <v>6</v>
+      </c>
+      <c r="G920">
+        <v>79683</v>
+      </c>
+      <c r="H920" s="8">
+        <v>0</v>
+      </c>
+      <c r="I920" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A921" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B921">
+        <v>9</v>
+      </c>
+      <c r="C921" t="s">
+        <v>17</v>
+      </c>
+      <c r="D921" t="s">
+        <v>86</v>
+      </c>
+      <c r="E921" t="s">
+        <v>45</v>
+      </c>
+      <c r="F921" t="s">
+        <v>6</v>
+      </c>
+      <c r="G921">
+        <v>5</v>
+      </c>
+      <c r="H921" s="8">
+        <v>0</v>
+      </c>
+      <c r="I921" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A922" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B922">
+        <v>9</v>
+      </c>
+      <c r="C922" t="s">
+        <v>17</v>
+      </c>
+      <c r="D922" t="s">
+        <v>86</v>
+      </c>
+      <c r="E922" t="s">
+        <v>43</v>
+      </c>
+      <c r="F922" t="s">
+        <v>6</v>
+      </c>
+      <c r="G922">
+        <v>5</v>
+      </c>
+      <c r="H922" s="8">
+        <v>0</v>
+      </c>
+      <c r="I922" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A923" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B923">
+        <v>9</v>
+      </c>
+      <c r="C923" t="s">
+        <v>17</v>
+      </c>
+      <c r="D923" t="s">
+        <v>86</v>
+      </c>
+      <c r="E923" t="s">
+        <v>56</v>
+      </c>
+      <c r="F923" t="s">
+        <v>37</v>
+      </c>
+      <c r="G923">
+        <v>2</v>
+      </c>
+      <c r="H923" s="8">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="I923" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="924" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A924" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B924">
+        <v>9</v>
+      </c>
+      <c r="C924" t="s">
+        <v>17</v>
+      </c>
+      <c r="D924" t="s">
+        <v>86</v>
+      </c>
+      <c r="E924" t="s">
+        <v>41</v>
+      </c>
+      <c r="F924" t="s">
+        <v>88</v>
+      </c>
+      <c r="G924">
+        <v>1</v>
+      </c>
+      <c r="H924" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="I924" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="925" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A925" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B925">
+        <v>9</v>
+      </c>
+      <c r="C925" t="s">
+        <v>17</v>
+      </c>
+      <c r="D925" t="s">
+        <v>86</v>
+      </c>
+      <c r="E925" t="s">
+        <v>41</v>
+      </c>
+      <c r="F925" t="s">
+        <v>88</v>
+      </c>
+      <c r="G925">
+        <v>1</v>
+      </c>
+      <c r="H925" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I925" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="926" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A926" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B926">
+        <v>9</v>
+      </c>
+      <c r="C926" t="s">
+        <v>17</v>
+      </c>
+      <c r="D926" t="s">
+        <v>86</v>
+      </c>
+      <c r="E926" t="s">
+        <v>41</v>
+      </c>
+      <c r="F926" t="s">
+        <v>88</v>
+      </c>
+      <c r="G926">
+        <v>1</v>
+      </c>
+      <c r="H926" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I926" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="927" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A927" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B927">
+        <v>9</v>
+      </c>
+      <c r="C927" t="s">
+        <v>17</v>
+      </c>
+      <c r="D927" t="s">
+        <v>86</v>
+      </c>
+      <c r="E927" t="s">
+        <v>41</v>
+      </c>
+      <c r="F927" t="s">
+        <v>88</v>
+      </c>
+      <c r="G927">
+        <v>1</v>
+      </c>
+      <c r="H927" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I927" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="928" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A928" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B928">
+        <v>9</v>
+      </c>
+      <c r="C928" t="s">
+        <v>17</v>
+      </c>
+      <c r="D928" t="s">
+        <v>86</v>
+      </c>
+      <c r="E928" t="s">
+        <v>41</v>
+      </c>
+      <c r="F928" t="s">
+        <v>88</v>
+      </c>
+      <c r="G928">
+        <v>1</v>
+      </c>
+      <c r="H928" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I928" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="929" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A929" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B929">
+        <v>9</v>
+      </c>
+      <c r="C929" t="s">
+        <v>17</v>
+      </c>
+      <c r="D929" t="s">
+        <v>86</v>
+      </c>
+      <c r="E929" t="s">
+        <v>41</v>
+      </c>
+      <c r="F929" t="s">
+        <v>88</v>
+      </c>
+      <c r="G929">
+        <v>1</v>
+      </c>
+      <c r="H929" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="I929" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="930" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A930" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B930">
+        <v>9</v>
+      </c>
+      <c r="C930" t="s">
+        <v>17</v>
+      </c>
+      <c r="D930" t="s">
+        <v>86</v>
+      </c>
+      <c r="E930" t="s">
+        <v>41</v>
+      </c>
+      <c r="F930" t="s">
+        <v>88</v>
+      </c>
+      <c r="G930">
+        <v>2</v>
+      </c>
+      <c r="H930" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I930" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A931" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B931">
+        <v>9</v>
+      </c>
+      <c r="C931" t="s">
+        <v>17</v>
+      </c>
+      <c r="D931" t="s">
+        <v>86</v>
+      </c>
+      <c r="E931" t="s">
+        <v>38</v>
+      </c>
+      <c r="F931" t="s">
+        <v>37</v>
+      </c>
+      <c r="G931">
+        <v>30</v>
+      </c>
+      <c r="H931" s="8">
+        <v>7.6273148148148151E-3</v>
+      </c>
+      <c r="I931" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A932" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B932">
+        <v>9</v>
+      </c>
+      <c r="C932" t="s">
+        <v>17</v>
+      </c>
+      <c r="D932" t="s">
+        <v>86</v>
+      </c>
+      <c r="E932" t="s">
+        <v>67</v>
+      </c>
+      <c r="F932" t="s">
+        <v>37</v>
+      </c>
+      <c r="G932">
+        <v>1</v>
+      </c>
+      <c r="H932" s="8">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="I932" s="8">
+        <v>9.1435185185185185E-4</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A933" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B933">
+        <v>9</v>
+      </c>
+      <c r="C933" t="s">
+        <v>17</v>
+      </c>
+      <c r="D933" t="s">
+        <v>86</v>
+      </c>
+      <c r="E933" t="s">
+        <v>52</v>
+      </c>
+      <c r="F933" t="s">
+        <v>37</v>
+      </c>
+      <c r="G933">
+        <v>1</v>
+      </c>
+      <c r="H933" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="I933" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A934" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B934">
+        <v>9</v>
+      </c>
+      <c r="C934" t="s">
+        <v>17</v>
+      </c>
+      <c r="D934" t="s">
+        <v>86</v>
+      </c>
+      <c r="E934" t="s">
+        <v>39</v>
+      </c>
+      <c r="F934" t="s">
+        <v>37</v>
+      </c>
+      <c r="G934">
+        <v>20</v>
+      </c>
+      <c r="H934" s="8">
+        <v>6.2847222222222219E-3</v>
+      </c>
+      <c r="I934" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A935" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B935">
+        <v>9</v>
+      </c>
+      <c r="C935" t="s">
+        <v>17</v>
+      </c>
+      <c r="D935" t="s">
+        <v>86</v>
+      </c>
+      <c r="E935" t="s">
+        <v>36</v>
+      </c>
+      <c r="F935" t="s">
+        <v>37</v>
+      </c>
+      <c r="G935">
+        <v>188</v>
+      </c>
+      <c r="H935" s="8">
+        <v>1.9849537037037037E-2</v>
+      </c>
+      <c r="I935" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A936" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B936">
+        <v>9</v>
+      </c>
+      <c r="C936" t="s">
+        <v>17</v>
+      </c>
+      <c r="D936" t="s">
+        <v>86</v>
+      </c>
+      <c r="E936" t="s">
+        <v>36</v>
+      </c>
+      <c r="F936" t="s">
+        <v>88</v>
+      </c>
+      <c r="G936">
+        <v>1</v>
+      </c>
+      <c r="H936" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="I936" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A937" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B937">
+        <v>9</v>
+      </c>
+      <c r="C937" t="s">
+        <v>17</v>
+      </c>
+      <c r="D937" t="s">
+        <v>86</v>
+      </c>
+      <c r="E937" t="s">
+        <v>53</v>
+      </c>
+      <c r="F937" t="s">
+        <v>37</v>
+      </c>
+      <c r="G937">
+        <v>2</v>
+      </c>
+      <c r="H937" s="8">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="I937" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A938" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B938">
+        <v>9</v>
+      </c>
+      <c r="C938" t="s">
+        <v>17</v>
+      </c>
+      <c r="D938" t="s">
+        <v>86</v>
+      </c>
+      <c r="E938" t="s">
+        <v>31</v>
+      </c>
+      <c r="F938" t="s">
+        <v>6</v>
+      </c>
+      <c r="G938">
+        <v>3574</v>
+      </c>
+      <c r="H938" s="8">
+        <v>0</v>
+      </c>
+      <c r="I938" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A939" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B939">
+        <v>9</v>
+      </c>
+      <c r="C939" t="s">
+        <v>17</v>
+      </c>
+      <c r="D939" t="s">
+        <v>86</v>
+      </c>
+      <c r="E939" t="s">
+        <v>44</v>
+      </c>
+      <c r="F939" t="s">
+        <v>37</v>
+      </c>
+      <c r="G939">
+        <v>4</v>
+      </c>
+      <c r="H939" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="I939" s="8">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A940" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B940">
+        <v>9</v>
+      </c>
+      <c r="C940" t="s">
+        <v>17</v>
+      </c>
+      <c r="D940" t="s">
+        <v>86</v>
+      </c>
+      <c r="E940" t="s">
+        <v>35</v>
+      </c>
+      <c r="F940" t="s">
+        <v>6</v>
+      </c>
+      <c r="G940">
+        <v>500</v>
+      </c>
+      <c r="H940" s="8">
+        <v>0</v>
+      </c>
+      <c r="I940" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A941" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B941">
+        <v>9</v>
+      </c>
+      <c r="C941" t="s">
+        <v>17</v>
+      </c>
+      <c r="D941" t="s">
+        <v>87</v>
+      </c>
+      <c r="E941" t="s">
+        <v>62</v>
+      </c>
+      <c r="F941" t="s">
+        <v>10</v>
+      </c>
+      <c r="G941">
+        <v>1</v>
+      </c>
+      <c r="H941" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="I941" s="8">
+        <v>7.291666666666667E-4</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A942" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B942">
+        <v>9</v>
+      </c>
+      <c r="C942" t="s">
+        <v>17</v>
+      </c>
+      <c r="D942" t="s">
+        <v>87</v>
+      </c>
+      <c r="E942" t="s">
+        <v>48</v>
+      </c>
+      <c r="F942" t="s">
+        <v>37</v>
+      </c>
+      <c r="G942">
+        <v>2</v>
+      </c>
+      <c r="H942" s="8">
+        <v>7.9861111111111116E-4</v>
+      </c>
+      <c r="I942" s="8">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A943" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B943">
+        <v>9</v>
+      </c>
+      <c r="C943" t="s">
+        <v>17</v>
+      </c>
+      <c r="D943" t="s">
+        <v>87</v>
+      </c>
+      <c r="E943" t="s">
+        <v>49</v>
+      </c>
+      <c r="F943" t="s">
+        <v>37</v>
+      </c>
+      <c r="G943">
+        <v>1</v>
+      </c>
+      <c r="H943" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I943" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A944" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B944">
+        <v>9</v>
+      </c>
+      <c r="C944" t="s">
+        <v>17</v>
+      </c>
+      <c r="D944" t="s">
+        <v>87</v>
+      </c>
+      <c r="E944" t="s">
+        <v>54</v>
+      </c>
+      <c r="F944" t="s">
+        <v>11</v>
+      </c>
+      <c r="G944">
+        <v>1</v>
+      </c>
+      <c r="H944" s="8">
+        <v>4.6759259259259263E-3</v>
+      </c>
+      <c r="I944" s="8">
+        <v>4.6759259259259263E-3</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A945" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B945">
+        <v>9</v>
+      </c>
+      <c r="C945" t="s">
+        <v>17</v>
+      </c>
+      <c r="D945" t="s">
+        <v>87</v>
+      </c>
+      <c r="E945" t="s">
+        <v>58</v>
+      </c>
+      <c r="F945" t="s">
+        <v>11</v>
+      </c>
+      <c r="G945">
+        <v>1</v>
+      </c>
+      <c r="H945" s="8">
+        <v>4.9884259259259257E-3</v>
+      </c>
+      <c r="I945" s="8">
+        <v>4.9884259259259257E-3</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A946" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B946">
+        <v>9</v>
+      </c>
+      <c r="C946" t="s">
+        <v>17</v>
+      </c>
+      <c r="D946" t="s">
+        <v>87</v>
+      </c>
+      <c r="E946" t="s">
+        <v>44</v>
+      </c>
+      <c r="F946" t="s">
+        <v>37</v>
+      </c>
+      <c r="G946">
+        <v>1</v>
+      </c>
+      <c r="H946" s="8">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="I946" s="8">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A947" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B947">
+        <v>10</v>
+      </c>
+      <c r="C947" t="s">
+        <v>17</v>
+      </c>
+      <c r="D947" t="s">
+        <v>86</v>
+      </c>
+      <c r="E947" t="s">
+        <v>33</v>
+      </c>
+      <c r="F947" t="s">
+        <v>6</v>
+      </c>
+      <c r="G947">
+        <v>1552</v>
+      </c>
+      <c r="H947" s="8">
+        <v>0</v>
+      </c>
+      <c r="I947" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A948" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B948">
+        <v>10</v>
+      </c>
+      <c r="C948" t="s">
+        <v>17</v>
+      </c>
+      <c r="D948" t="s">
+        <v>86</v>
+      </c>
+      <c r="E948" t="s">
+        <v>32</v>
+      </c>
+      <c r="F948" t="s">
+        <v>6</v>
+      </c>
+      <c r="G948">
+        <v>5950</v>
+      </c>
+      <c r="H948" s="8">
+        <v>0</v>
+      </c>
+      <c r="I948" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A949" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B949">
+        <v>10</v>
+      </c>
+      <c r="C949" t="s">
+        <v>17</v>
+      </c>
+      <c r="D949" t="s">
+        <v>86</v>
+      </c>
+      <c r="E949" t="s">
+        <v>34</v>
+      </c>
+      <c r="F949" t="s">
+        <v>6</v>
+      </c>
+      <c r="G949">
+        <v>719</v>
+      </c>
+      <c r="H949" s="8">
+        <v>0</v>
+      </c>
+      <c r="I949" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A950" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B950">
+        <v>10</v>
+      </c>
+      <c r="C950" t="s">
+        <v>17</v>
+      </c>
+      <c r="D950" t="s">
+        <v>86</v>
+      </c>
+      <c r="E950" t="s">
+        <v>40</v>
+      </c>
+      <c r="F950" t="s">
+        <v>6</v>
+      </c>
+      <c r="G950">
+        <v>19</v>
+      </c>
+      <c r="H950" s="8">
+        <v>0</v>
+      </c>
+      <c r="I950" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A951" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B951">
+        <v>10</v>
+      </c>
+      <c r="C951" t="s">
+        <v>17</v>
+      </c>
+      <c r="D951" t="s">
+        <v>86</v>
+      </c>
+      <c r="E951" t="s">
+        <v>30</v>
+      </c>
+      <c r="F951" t="s">
+        <v>6</v>
+      </c>
+      <c r="G951">
+        <v>16407</v>
+      </c>
+      <c r="H951" s="8">
+        <v>0</v>
+      </c>
+      <c r="I951" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A952" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B952">
+        <v>10</v>
+      </c>
+      <c r="C952" t="s">
+        <v>17</v>
+      </c>
+      <c r="D952" t="s">
+        <v>86</v>
+      </c>
+      <c r="E952" t="s">
+        <v>29</v>
+      </c>
+      <c r="F952" t="s">
+        <v>6</v>
+      </c>
+      <c r="G952">
+        <v>48837</v>
+      </c>
+      <c r="H952" s="8">
+        <v>0</v>
+      </c>
+      <c r="I952" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A953" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B953">
+        <v>10</v>
+      </c>
+      <c r="C953" t="s">
+        <v>17</v>
+      </c>
+      <c r="D953" t="s">
+        <v>86</v>
+      </c>
+      <c r="E953" t="s">
+        <v>45</v>
+      </c>
+      <c r="F953" t="s">
+        <v>6</v>
+      </c>
+      <c r="G953">
+        <v>7</v>
+      </c>
+      <c r="H953" s="8">
+        <v>0</v>
+      </c>
+      <c r="I953" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A954" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B954">
+        <v>10</v>
+      </c>
+      <c r="C954" t="s">
+        <v>17</v>
+      </c>
+      <c r="D954" t="s">
+        <v>86</v>
+      </c>
+      <c r="E954" t="s">
+        <v>56</v>
+      </c>
+      <c r="F954" t="s">
+        <v>37</v>
+      </c>
+      <c r="G954">
+        <v>2</v>
+      </c>
+      <c r="H954" s="8">
+        <v>8.4490740740740739E-4</v>
+      </c>
+      <c r="I954" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A955" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B955">
+        <v>10</v>
+      </c>
+      <c r="C955" t="s">
+        <v>17</v>
+      </c>
+      <c r="D955" t="s">
+        <v>86</v>
+      </c>
+      <c r="E955" t="s">
+        <v>41</v>
+      </c>
+      <c r="F955" t="s">
+        <v>88</v>
+      </c>
+      <c r="G955">
+        <v>1</v>
+      </c>
+      <c r="H955" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I955" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A956" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B956">
+        <v>10</v>
+      </c>
+      <c r="C956" t="s">
+        <v>17</v>
+      </c>
+      <c r="D956" t="s">
+        <v>86</v>
+      </c>
+      <c r="E956" t="s">
+        <v>41</v>
+      </c>
+      <c r="F956" t="s">
+        <v>88</v>
+      </c>
+      <c r="G956">
+        <v>1</v>
+      </c>
+      <c r="H956" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I956" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A957" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B957">
+        <v>10</v>
+      </c>
+      <c r="C957" t="s">
+        <v>17</v>
+      </c>
+      <c r="D957" t="s">
+        <v>86</v>
+      </c>
+      <c r="E957" t="s">
+        <v>41</v>
+      </c>
+      <c r="F957" t="s">
+        <v>88</v>
+      </c>
+      <c r="G957">
+        <v>1</v>
+      </c>
+      <c r="H957" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I957" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A958" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B958">
+        <v>10</v>
+      </c>
+      <c r="C958" t="s">
+        <v>17</v>
+      </c>
+      <c r="D958" t="s">
+        <v>86</v>
+      </c>
+      <c r="E958" t="s">
+        <v>41</v>
+      </c>
+      <c r="F958" t="s">
+        <v>88</v>
+      </c>
+      <c r="G958">
+        <v>1</v>
+      </c>
+      <c r="H958" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="I958" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A959" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B959">
+        <v>10</v>
+      </c>
+      <c r="C959" t="s">
+        <v>17</v>
+      </c>
+      <c r="D959" t="s">
+        <v>86</v>
+      </c>
+      <c r="E959" t="s">
+        <v>41</v>
+      </c>
+      <c r="F959" t="s">
+        <v>88</v>
+      </c>
+      <c r="G959">
+        <v>1</v>
+      </c>
+      <c r="H959" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I959" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A960" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B960">
+        <v>10</v>
+      </c>
+      <c r="C960" t="s">
+        <v>17</v>
+      </c>
+      <c r="D960" t="s">
+        <v>86</v>
+      </c>
+      <c r="E960" t="s">
+        <v>41</v>
+      </c>
+      <c r="F960" t="s">
+        <v>88</v>
+      </c>
+      <c r="G960">
+        <v>2</v>
+      </c>
+      <c r="H960" s="8">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="I960" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A961" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B961">
+        <v>10</v>
+      </c>
+      <c r="C961" t="s">
+        <v>17</v>
+      </c>
+      <c r="D961" t="s">
+        <v>86</v>
+      </c>
+      <c r="E961" t="s">
+        <v>41</v>
+      </c>
+      <c r="F961" t="s">
+        <v>88</v>
+      </c>
+      <c r="G961">
+        <v>2</v>
+      </c>
+      <c r="H961" s="8">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="I961" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A962" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B962">
+        <v>10</v>
+      </c>
+      <c r="C962" t="s">
+        <v>17</v>
+      </c>
+      <c r="D962" t="s">
+        <v>86</v>
+      </c>
+      <c r="E962" t="s">
+        <v>41</v>
+      </c>
+      <c r="F962" t="s">
+        <v>88</v>
+      </c>
+      <c r="G962">
+        <v>4</v>
+      </c>
+      <c r="H962" s="8">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="I962" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A963" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B963">
+        <v>10</v>
+      </c>
+      <c r="C963" t="s">
+        <v>17</v>
+      </c>
+      <c r="D963" t="s">
+        <v>86</v>
+      </c>
+      <c r="E963" t="s">
+        <v>41</v>
+      </c>
+      <c r="F963" t="s">
+        <v>88</v>
+      </c>
+      <c r="G963">
+        <v>4</v>
+      </c>
+      <c r="H963" s="8">
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="I963" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A964" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B964">
+        <v>10</v>
+      </c>
+      <c r="C964" t="s">
+        <v>17</v>
+      </c>
+      <c r="D964" t="s">
+        <v>86</v>
+      </c>
+      <c r="E964" t="s">
+        <v>41</v>
+      </c>
+      <c r="F964" t="s">
+        <v>88</v>
+      </c>
+      <c r="G964">
+        <v>4</v>
+      </c>
+      <c r="H964" s="8">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="I964" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A965" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B965">
+        <v>10</v>
+      </c>
+      <c r="C965" t="s">
+        <v>17</v>
+      </c>
+      <c r="D965" t="s">
+        <v>86</v>
+      </c>
+      <c r="E965" t="s">
+        <v>41</v>
+      </c>
+      <c r="F965" t="s">
+        <v>88</v>
+      </c>
+      <c r="G965">
+        <v>5</v>
+      </c>
+      <c r="H965" s="8">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="I965" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A966" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B966">
+        <v>10</v>
+      </c>
+      <c r="C966" t="s">
+        <v>17</v>
+      </c>
+      <c r="D966" t="s">
+        <v>86</v>
+      </c>
+      <c r="E966" t="s">
+        <v>41</v>
+      </c>
+      <c r="F966" t="s">
+        <v>88</v>
+      </c>
+      <c r="G966">
+        <v>6</v>
+      </c>
+      <c r="H966" s="8">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="I966" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A967" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B967">
+        <v>10</v>
+      </c>
+      <c r="C967" t="s">
+        <v>17</v>
+      </c>
+      <c r="D967" t="s">
+        <v>86</v>
+      </c>
+      <c r="E967" t="s">
+        <v>41</v>
+      </c>
+      <c r="F967" t="s">
+        <v>88</v>
+      </c>
+      <c r="G967">
+        <v>9</v>
+      </c>
+      <c r="H967" s="8">
+        <v>1.9328703703703704E-3</v>
+      </c>
+      <c r="I967" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A968" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B968">
+        <v>10</v>
+      </c>
+      <c r="C968" t="s">
+        <v>17</v>
+      </c>
+      <c r="D968" t="s">
+        <v>86</v>
+      </c>
+      <c r="E968" t="s">
+        <v>57</v>
+      </c>
+      <c r="F968" t="s">
+        <v>37</v>
+      </c>
+      <c r="G968">
+        <v>1</v>
+      </c>
+      <c r="H968" s="8">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="I968" s="8">
+        <v>9.4907407407407408E-4</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A969" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B969">
+        <v>10</v>
+      </c>
+      <c r="C969" t="s">
+        <v>17</v>
+      </c>
+      <c r="D969" t="s">
+        <v>86</v>
+      </c>
+      <c r="E969" t="s">
+        <v>38</v>
+      </c>
+      <c r="F969" t="s">
+        <v>37</v>
+      </c>
+      <c r="G969">
+        <v>66</v>
+      </c>
+      <c r="H969" s="8">
+        <v>1.667824074074074E-2</v>
+      </c>
+      <c r="I969" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A970" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B970">
+        <v>10</v>
+      </c>
+      <c r="C970" t="s">
+        <v>17</v>
+      </c>
+      <c r="D970" t="s">
+        <v>86</v>
+      </c>
+      <c r="E970" t="s">
+        <v>50</v>
+      </c>
+      <c r="F970" t="s">
+        <v>37</v>
+      </c>
+      <c r="G970">
+        <v>1</v>
+      </c>
+      <c r="H970" s="8">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="I970" s="8">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A971" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B971">
+        <v>10</v>
+      </c>
+      <c r="C971" t="s">
+        <v>17</v>
+      </c>
+      <c r="D971" t="s">
+        <v>86</v>
+      </c>
+      <c r="E971" t="s">
+        <v>59</v>
+      </c>
+      <c r="F971" t="s">
+        <v>37</v>
+      </c>
+      <c r="G971">
+        <v>1</v>
+      </c>
+      <c r="H971" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I971" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A972" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B972">
+        <v>10</v>
+      </c>
+      <c r="C972" t="s">
+        <v>17</v>
+      </c>
+      <c r="D972" t="s">
+        <v>86</v>
+      </c>
+      <c r="E972" t="s">
+        <v>51</v>
+      </c>
+      <c r="F972" t="s">
+        <v>37</v>
+      </c>
+      <c r="G972">
+        <v>3</v>
+      </c>
+      <c r="H972" s="8">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="I972" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A973" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B973">
+        <v>10</v>
+      </c>
+      <c r="C973" t="s">
+        <v>17</v>
+      </c>
+      <c r="D973" t="s">
+        <v>86</v>
+      </c>
+      <c r="E973" t="s">
+        <v>52</v>
+      </c>
+      <c r="F973" t="s">
+        <v>37</v>
+      </c>
+      <c r="G973">
+        <v>1</v>
+      </c>
+      <c r="H973" s="8">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="I973" s="8">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A974" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B974">
+        <v>10</v>
+      </c>
+      <c r="C974" t="s">
+        <v>17</v>
+      </c>
+      <c r="D974" t="s">
+        <v>86</v>
+      </c>
+      <c r="E974" t="s">
+        <v>39</v>
+      </c>
+      <c r="F974" t="s">
+        <v>37</v>
+      </c>
+      <c r="G974">
+        <v>24</v>
+      </c>
+      <c r="H974" s="8">
+        <v>6.8634259259259256E-3</v>
+      </c>
+      <c r="I974" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A975" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B975">
+        <v>10</v>
+      </c>
+      <c r="C975" t="s">
+        <v>17</v>
+      </c>
+      <c r="D975" t="s">
+        <v>86</v>
+      </c>
+      <c r="E975" t="s">
+        <v>39</v>
+      </c>
+      <c r="F975" t="s">
+        <v>88</v>
+      </c>
+      <c r="G975">
+        <v>1</v>
+      </c>
+      <c r="H975" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="I975" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A976" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B976">
+        <v>10</v>
+      </c>
+      <c r="C976" t="s">
+        <v>17</v>
+      </c>
+      <c r="D976" t="s">
+        <v>86</v>
+      </c>
+      <c r="E976" t="s">
+        <v>36</v>
+      </c>
+      <c r="F976" t="s">
+        <v>37</v>
+      </c>
+      <c r="G976">
+        <v>376</v>
+      </c>
+      <c r="H976" s="8">
+        <v>4.0810185185185185E-2</v>
+      </c>
+      <c r="I976" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A977" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B977">
+        <v>10</v>
+      </c>
+      <c r="C977" t="s">
+        <v>17</v>
+      </c>
+      <c r="D977" t="s">
+        <v>86</v>
+      </c>
+      <c r="E977" t="s">
+        <v>53</v>
+      </c>
+      <c r="F977" t="s">
+        <v>88</v>
+      </c>
+      <c r="G977">
+        <v>1</v>
+      </c>
+      <c r="H977" s="8">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="I977" s="8">
+        <v>5.9027777777777778E-4</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A978" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B978">
+        <v>10</v>
+      </c>
+      <c r="C978" t="s">
+        <v>17</v>
+      </c>
+      <c r="D978" t="s">
+        <v>86</v>
+      </c>
+      <c r="E978" t="s">
+        <v>31</v>
+      </c>
+      <c r="F978" t="s">
+        <v>6</v>
+      </c>
+      <c r="G978">
+        <v>6218</v>
+      </c>
+      <c r="H978" s="8">
+        <v>0</v>
+      </c>
+      <c r="I978" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A979" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B979">
+        <v>10</v>
+      </c>
+      <c r="C979" t="s">
+        <v>17</v>
+      </c>
+      <c r="D979" t="s">
+        <v>86</v>
+      </c>
+      <c r="E979" t="s">
+        <v>44</v>
+      </c>
+      <c r="F979" t="s">
+        <v>37</v>
+      </c>
+      <c r="G979">
+        <v>11</v>
+      </c>
+      <c r="H979" s="8">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="I979" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A980" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B980">
+        <v>10</v>
+      </c>
+      <c r="C980" t="s">
+        <v>17</v>
+      </c>
+      <c r="D980" t="s">
+        <v>86</v>
+      </c>
+      <c r="E980" t="s">
+        <v>35</v>
+      </c>
+      <c r="F980" t="s">
+        <v>6</v>
+      </c>
+      <c r="G980">
+        <v>911</v>
+      </c>
+      <c r="H980" s="8">
+        <v>0</v>
+      </c>
+      <c r="I980" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A981" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B981">
+        <v>10</v>
+      </c>
+      <c r="C981" t="s">
+        <v>17</v>
+      </c>
+      <c r="D981" t="s">
+        <v>87</v>
+      </c>
+      <c r="E981" t="s">
+        <v>46</v>
+      </c>
+      <c r="F981" t="s">
+        <v>37</v>
+      </c>
+      <c r="G981">
+        <v>4</v>
+      </c>
+      <c r="H981" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="I981" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A982" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B982">
+        <v>10</v>
+      </c>
+      <c r="C982" t="s">
+        <v>17</v>
+      </c>
+      <c r="D982" t="s">
+        <v>87</v>
+      </c>
+      <c r="E982" t="s">
+        <v>42</v>
+      </c>
+      <c r="F982" t="s">
+        <v>37</v>
+      </c>
+      <c r="G982">
+        <v>5</v>
+      </c>
+      <c r="H982" s="8">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="I982" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A983" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B983">
+        <v>10</v>
+      </c>
+      <c r="C983" t="s">
+        <v>17</v>
+      </c>
+      <c r="D983" t="s">
+        <v>87</v>
+      </c>
+      <c r="E983" t="s">
+        <v>48</v>
+      </c>
+      <c r="F983" t="s">
+        <v>37</v>
+      </c>
+      <c r="G983">
+        <v>4</v>
+      </c>
+      <c r="H983" s="8">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="I983" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A984" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B984">
+        <v>10</v>
+      </c>
+      <c r="C984" t="s">
+        <v>17</v>
+      </c>
+      <c r="D984" t="s">
+        <v>87</v>
+      </c>
+      <c r="E984" t="s">
+        <v>49</v>
+      </c>
+      <c r="F984" t="s">
+        <v>37</v>
+      </c>
+      <c r="G984">
+        <v>2</v>
+      </c>
+      <c r="H984" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="I984" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A985" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B985">
+        <v>10</v>
+      </c>
+      <c r="C985" t="s">
+        <v>17</v>
+      </c>
+      <c r="D985" t="s">
+        <v>87</v>
+      </c>
+      <c r="E985" t="s">
+        <v>60</v>
+      </c>
+      <c r="F985" t="s">
+        <v>37</v>
+      </c>
+      <c r="G985">
+        <v>1</v>
+      </c>
+      <c r="H985" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="I985" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A986" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B986">
+        <v>10</v>
+      </c>
+      <c r="C986" t="s">
+        <v>17</v>
+      </c>
+      <c r="D986" t="s">
+        <v>87</v>
+      </c>
+      <c r="E986" t="s">
+        <v>61</v>
+      </c>
+      <c r="F986" t="s">
+        <v>10</v>
+      </c>
+      <c r="G986">
+        <v>1</v>
+      </c>
+      <c r="H986" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="I986" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A987" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B987">
+        <v>10</v>
+      </c>
+      <c r="C987" t="s">
+        <v>17</v>
+      </c>
+      <c r="D987" t="s">
+        <v>87</v>
+      </c>
+      <c r="E987" t="s">
+        <v>63</v>
+      </c>
+      <c r="F987" t="s">
+        <v>10</v>
+      </c>
+      <c r="G987">
+        <v>1</v>
+      </c>
+      <c r="H987" s="8">
+        <v>1.2152777777777778E-3</v>
+      </c>
+      <c r="I987" s="8">
+        <v>1.2152777777777778E-3</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A988" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B988">
+        <v>10</v>
+      </c>
+      <c r="C988" t="s">
+        <v>17</v>
+      </c>
+      <c r="D988" t="s">
+        <v>87</v>
+      </c>
+      <c r="E988" t="s">
+        <v>65</v>
+      </c>
+      <c r="F988" t="s">
+        <v>10</v>
+      </c>
+      <c r="G988">
+        <v>1</v>
+      </c>
+      <c r="H988" s="8">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="I988" s="8">
+        <v>7.1759259259259259E-4</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A989" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B989">
+        <v>10</v>
+      </c>
+      <c r="C989" t="s">
+        <v>17</v>
+      </c>
+      <c r="D989" t="s">
+        <v>87</v>
+      </c>
+      <c r="E989" t="s">
+        <v>90</v>
+      </c>
+      <c r="F989" t="s">
+        <v>10</v>
+      </c>
+      <c r="G989">
+        <v>1</v>
+      </c>
+      <c r="H989" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="I989" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A990" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B990">
+        <v>10</v>
+      </c>
+      <c r="C990" t="s">
+        <v>17</v>
+      </c>
+      <c r="D990" t="s">
+        <v>87</v>
+      </c>
+      <c r="E990" t="s">
+        <v>54</v>
+      </c>
+      <c r="F990" t="s">
+        <v>11</v>
+      </c>
+      <c r="G990">
+        <v>2</v>
+      </c>
+      <c r="H990" s="8">
+        <v>9.0509259259259258E-3</v>
+      </c>
+      <c r="I990" s="8">
+        <v>4.5254629629629629E-3</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A991" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B991">
+        <v>10</v>
+      </c>
+      <c r="C991" t="s">
+        <v>17</v>
+      </c>
+      <c r="D991" t="s">
+        <v>87</v>
+      </c>
+      <c r="E991" t="s">
+        <v>58</v>
+      </c>
+      <c r="F991" t="s">
+        <v>11</v>
+      </c>
+      <c r="G991">
+        <v>4</v>
+      </c>
+      <c r="H991" s="8">
+        <v>1.5902777777777776E-2</v>
+      </c>
+      <c r="I991" s="8">
+        <v>3.9699074074074072E-3</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A992" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B992">
+        <v>10</v>
+      </c>
+      <c r="C992" t="s">
+        <v>17</v>
+      </c>
+      <c r="D992" t="s">
+        <v>87</v>
+      </c>
+      <c r="E992" t="s">
+        <v>47</v>
+      </c>
+      <c r="F992" t="s">
+        <v>37</v>
+      </c>
+      <c r="G992">
+        <v>6</v>
+      </c>
+      <c r="H992" s="8">
+        <v>5.4745370370370373E-3</v>
+      </c>
+      <c r="I992" s="8">
+        <v>9.0277777777777774E-4</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A993" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B993">
+        <v>11</v>
+      </c>
+      <c r="C993" t="s">
+        <v>17</v>
+      </c>
+      <c r="D993" t="s">
+        <v>86</v>
+      </c>
+      <c r="E993" t="s">
+        <v>33</v>
+      </c>
+      <c r="F993" t="s">
+        <v>6</v>
+      </c>
+      <c r="G993">
+        <v>332</v>
+      </c>
+      <c r="H993" s="8">
+        <v>0</v>
+      </c>
+      <c r="I993" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A994" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B994">
+        <v>11</v>
+      </c>
+      <c r="C994" t="s">
+        <v>17</v>
+      </c>
+      <c r="D994" t="s">
+        <v>86</v>
+      </c>
+      <c r="E994" t="s">
+        <v>32</v>
+      </c>
+      <c r="F994" t="s">
+        <v>6</v>
+      </c>
+      <c r="G994">
+        <v>1578</v>
+      </c>
+      <c r="H994" s="8">
+        <v>0</v>
+      </c>
+      <c r="I994" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A995" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B995">
+        <v>11</v>
+      </c>
+      <c r="C995" t="s">
+        <v>17</v>
+      </c>
+      <c r="D995" t="s">
+        <v>86</v>
+      </c>
+      <c r="E995" t="s">
+        <v>34</v>
+      </c>
+      <c r="F995" t="s">
+        <v>6</v>
+      </c>
+      <c r="G995">
+        <v>176</v>
+      </c>
+      <c r="H995" s="8">
+        <v>0</v>
+      </c>
+      <c r="I995" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A996" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B996">
+        <v>11</v>
+      </c>
+      <c r="C996" t="s">
+        <v>17</v>
+      </c>
+      <c r="D996" t="s">
+        <v>86</v>
+      </c>
+      <c r="E996" t="s">
+        <v>40</v>
+      </c>
+      <c r="F996" t="s">
+        <v>6</v>
+      </c>
+      <c r="G996">
+        <v>6</v>
+      </c>
+      <c r="H996" s="8">
+        <v>0</v>
+      </c>
+      <c r="I996" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A997" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B997">
+        <v>11</v>
+      </c>
+      <c r="C997" t="s">
+        <v>17</v>
+      </c>
+      <c r="D997" t="s">
+        <v>86</v>
+      </c>
+      <c r="E997" t="s">
+        <v>30</v>
+      </c>
+      <c r="F997" t="s">
+        <v>6</v>
+      </c>
+      <c r="G997">
+        <v>4224</v>
+      </c>
+      <c r="H997" s="8">
+        <v>0</v>
+      </c>
+      <c r="I997" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A998" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B998">
+        <v>11</v>
+      </c>
+      <c r="C998" t="s">
+        <v>17</v>
+      </c>
+      <c r="D998" t="s">
+        <v>86</v>
+      </c>
+      <c r="E998" t="s">
+        <v>29</v>
+      </c>
+      <c r="F998" t="s">
+        <v>6</v>
+      </c>
+      <c r="G998">
+        <v>4546</v>
+      </c>
+      <c r="H998" s="8">
+        <v>0</v>
+      </c>
+      <c r="I998" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A999" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B999">
+        <v>11</v>
+      </c>
+      <c r="C999" t="s">
+        <v>17</v>
+      </c>
+      <c r="D999" t="s">
+        <v>86</v>
+      </c>
+      <c r="E999" t="s">
+        <v>45</v>
+      </c>
+      <c r="F999" t="s">
+        <v>6</v>
+      </c>
+      <c r="G999">
+        <v>2</v>
+      </c>
+      <c r="H999" s="8">
+        <v>0</v>
+      </c>
+      <c r="I999" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1000" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1000">
+        <v>11</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1000" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1000">
+        <v>1</v>
+      </c>
+      <c r="H1000" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="I1000" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1001" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1001">
+        <v>11</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1001">
+        <v>1</v>
+      </c>
+      <c r="H1001" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I1001" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1002" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1002">
+        <v>11</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1002" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1002">
+        <v>2</v>
+      </c>
+      <c r="H1002" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="I1002" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1003" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1003">
+        <v>11</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1003" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1003">
+        <v>20</v>
+      </c>
+      <c r="H1003" s="8">
+        <v>5.1967592592592595E-3</v>
+      </c>
+      <c r="I1003" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1004" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1004">
+        <v>11</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1004" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1004" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1004">
+        <v>1</v>
+      </c>
+      <c r="H1004" s="8">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="I1004" s="8">
+        <v>6.9444444444444447E-4</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1005" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1005">
+        <v>11</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1005" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1005" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1005">
+        <v>6</v>
+      </c>
+      <c r="H1005" s="8">
+        <v>1.4236111111111112E-3</v>
+      </c>
+      <c r="I1005" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1006" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1006">
+        <v>11</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1006" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1006">
+        <v>94</v>
+      </c>
+      <c r="H1006" s="8">
+        <v>1.4340277777777778E-2</v>
+      </c>
+      <c r="I1006" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1007" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1007">
+        <v>11</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1007" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1007" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1007">
+        <v>1631</v>
+      </c>
+      <c r="H1007" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1007" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1008" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1008">
+        <v>11</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1008" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1008" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1008">
+        <v>1</v>
+      </c>
+      <c r="H1008" s="8">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="I1008" s="8">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1009" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1009">
+        <v>11</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1009" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1009" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1009">
+        <v>266</v>
+      </c>
+      <c r="H1009" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1009" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1010" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1010">
+        <v>11</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1010" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1010" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1010">
+        <v>1</v>
+      </c>
+      <c r="H1010" s="8">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="I1010" s="8">
+        <v>6.7129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1011" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1011">
+        <v>11</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1011" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1011" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1011">
+        <v>1</v>
+      </c>
+      <c r="H1011" s="8">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="I1011" s="8">
+        <v>8.9120370370370373E-4</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1012" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1012">
+        <v>11</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1012" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1012" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1012">
+        <v>1</v>
+      </c>
+      <c r="H1012" s="8">
+        <v>8.4490740740740739E-4</v>
+      </c>
+      <c r="I1012" s="8">
+        <v>8.4490740740740739E-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{721DF5F0-6A32-4204-8BB8-DE720E868C44}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AF25E1-D92B-429D-8953-C81ED8DF8DA7}"/>
   <bookViews>
-    <workbookView xWindow="3084" yWindow="3504" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4411" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4836" uniqueCount="93">
   <si>
     <t>Dt</t>
   </si>
@@ -313,6 +313,12 @@
   </si>
   <si>
     <t>Ativo - Preventivo - PV-Preventivo Confirmado</t>
+  </si>
+  <si>
+    <t>LOC_Cliente enfermo - hospitalizado</t>
+  </si>
+  <si>
+    <t>NoAgents</t>
   </si>
 </sst>
 </file>
@@ -702,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V233"/>
+  <dimension ref="A1:V239"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -14523,7 +14529,7 @@
         <v>15</v>
       </c>
       <c r="F227" s="1">
-        <v>44686</v>
+        <v>44685</v>
       </c>
       <c r="G227" s="1">
         <v>18461</v>
@@ -14650,7 +14656,7 @@
         <v>12</v>
       </c>
       <c r="F229" s="1">
-        <v>44686</v>
+        <v>44685</v>
       </c>
       <c r="G229" s="1">
         <v>19205</v>
@@ -14777,7 +14783,7 @@
         <v>11</v>
       </c>
       <c r="F231" s="1">
-        <v>44686</v>
+        <v>44685</v>
       </c>
       <c r="G231" s="1">
         <v>32437</v>
@@ -14833,58 +14839,58 @@
         <v>30</v>
       </c>
       <c r="E232" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F232" s="1">
         <v>24959</v>
       </c>
       <c r="G232" s="1">
-        <v>12888</v>
+        <v>63947</v>
       </c>
       <c r="H232" s="1">
-        <v>127</v>
+        <v>384</v>
       </c>
       <c r="I232" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J232" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K232" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L232" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M232" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N232" s="4">
-        <v>1.7361111111111112E-4</v>
+        <v>1.6203703703703703E-4</v>
       </c>
       <c r="O232" s="4">
-        <v>3.3564814814814812E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="P232" s="5">
-        <v>9.9000000000000008E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q232" s="6">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R232" s="6">
-        <v>0</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="S232" s="1">
-        <v>0.52</v>
+        <v>2.56</v>
       </c>
       <c r="T232" s="6">
-        <v>0.5</v>
+        <v>0.1333</v>
       </c>
       <c r="U232" s="6">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="V232" s="2">
-        <v>19.6248</v>
+        <v>60.470799999999997</v>
       </c>
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.3">
@@ -14901,49 +14907,430 @@
         <v>0</v>
       </c>
       <c r="E233" s="1">
+        <v>10</v>
+      </c>
+      <c r="F233" s="1">
+        <v>44685</v>
+      </c>
+      <c r="G233" s="1">
+        <v>23820</v>
+      </c>
+      <c r="H233" s="1">
+        <v>360</v>
+      </c>
+      <c r="I233" s="1">
+        <v>2</v>
+      </c>
+      <c r="J233" s="1">
+        <v>0</v>
+      </c>
+      <c r="K233" s="1">
+        <v>0</v>
+      </c>
+      <c r="L233" s="1">
+        <v>0</v>
+      </c>
+      <c r="M233" s="1">
+        <v>1</v>
+      </c>
+      <c r="O233" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="P233" s="5">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="Q233" s="6">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="R233" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="S233" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="V233" s="2">
+        <v>39.889200000000002</v>
+      </c>
+    </row>
+    <row r="234" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A234" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B234" s="1">
+        <v>12</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D234" s="1">
+        <v>30</v>
+      </c>
+      <c r="E234" s="1">
+        <v>4</v>
+      </c>
+      <c r="F234" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G234" s="1">
+        <v>56061</v>
+      </c>
+      <c r="H234" s="1">
+        <v>267</v>
+      </c>
+      <c r="I234" s="1">
+        <v>28</v>
+      </c>
+      <c r="J234" s="1">
+        <v>12</v>
+      </c>
+      <c r="K234" s="1">
+        <v>16</v>
+      </c>
+      <c r="L234" s="1">
+        <v>3</v>
+      </c>
+      <c r="M234" s="1">
+        <v>0</v>
+      </c>
+      <c r="N234" s="4">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="O234" s="4">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P234" s="5">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="Q234" s="5">
+        <v>0.1875</v>
+      </c>
+      <c r="R234" s="6">
+        <v>0</v>
+      </c>
+      <c r="S234" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="T234" s="6">
+        <v>0</v>
+      </c>
+      <c r="U234" s="5">
+        <v>0.42859999999999998</v>
+      </c>
+      <c r="V234" s="2">
+        <v>40.357199999999999</v>
+      </c>
+    </row>
+    <row r="235" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A235" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B235" s="1">
+        <v>12</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D235" s="1">
+        <v>0</v>
+      </c>
+      <c r="E235" s="1">
         <v>9</v>
       </c>
-      <c r="F233" s="1">
-        <v>44686</v>
-      </c>
-      <c r="G233" s="1">
-        <v>9227</v>
-      </c>
-      <c r="H233" s="1">
-        <v>121</v>
-      </c>
-      <c r="I233" s="1">
-        <v>0</v>
-      </c>
-      <c r="J233" s="1">
-        <v>0</v>
-      </c>
-      <c r="K233" s="1">
-        <v>0</v>
-      </c>
-      <c r="L233" s="1">
-        <v>0</v>
-      </c>
-      <c r="M233" s="1">
-        <v>0</v>
-      </c>
-      <c r="O233" s="4">
+      <c r="F235" s="1">
+        <v>44685</v>
+      </c>
+      <c r="G235" s="1">
+        <v>32308</v>
+      </c>
+      <c r="H235" s="1">
+        <v>330</v>
+      </c>
+      <c r="I235" s="1">
+        <v>3</v>
+      </c>
+      <c r="J235" s="1">
+        <v>0</v>
+      </c>
+      <c r="K235" s="1">
+        <v>0</v>
+      </c>
+      <c r="L235" s="1">
+        <v>0</v>
+      </c>
+      <c r="M235" s="1">
+        <v>2</v>
+      </c>
+      <c r="O235" s="4">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="P235" s="5">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="Q235" s="5">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="R235" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="S235" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="V235" s="2">
+        <v>36.5456</v>
+      </c>
+    </row>
+    <row r="236" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A236" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B236" s="1">
+        <v>13</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D236" s="1">
+        <v>30</v>
+      </c>
+      <c r="E236" s="1">
+        <v>3</v>
+      </c>
+      <c r="F236" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G236" s="1">
+        <v>54192</v>
+      </c>
+      <c r="H236" s="1">
+        <v>424</v>
+      </c>
+      <c r="I236" s="1">
+        <v>34</v>
+      </c>
+      <c r="J236" s="1">
+        <v>5</v>
+      </c>
+      <c r="K236" s="1">
+        <v>28</v>
+      </c>
+      <c r="L236" s="1">
+        <v>2</v>
+      </c>
+      <c r="M236" s="1">
+        <v>2</v>
+      </c>
+      <c r="N236" s="4">
         <v>1.5046296296296297E-4</v>
       </c>
-      <c r="P233" s="5">
-        <v>1.3100000000000001E-2</v>
-      </c>
-      <c r="Q233" s="6">
-        <v>0</v>
-      </c>
-      <c r="R233" s="1" t="s">
+      <c r="O236" s="4">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="P236" s="5">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="Q236" s="5">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="R236" s="6">
+        <v>1</v>
+      </c>
+      <c r="S236" s="1">
+        <v>2.17</v>
+      </c>
+      <c r="T236" s="5">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="U236" s="5">
+        <v>0.14710000000000001</v>
+      </c>
+      <c r="V236" s="2">
+        <v>68.275999999999996</v>
+      </c>
+    </row>
+    <row r="237" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A237" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B237" s="1">
+        <v>13</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D237" s="1">
+        <v>0</v>
+      </c>
+      <c r="E237" s="1">
+        <v>9</v>
+      </c>
+      <c r="F237" s="1">
+        <v>44685</v>
+      </c>
+      <c r="G237" s="1">
+        <v>42045</v>
+      </c>
+      <c r="H237" s="1">
+        <v>538</v>
+      </c>
+      <c r="I237" s="1">
+        <v>11</v>
+      </c>
+      <c r="J237" s="1">
+        <v>0</v>
+      </c>
+      <c r="K237" s="1">
+        <v>0</v>
+      </c>
+      <c r="L237" s="1">
+        <v>0</v>
+      </c>
+      <c r="M237" s="1">
+        <v>4</v>
+      </c>
+      <c r="O237" s="4">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="P237" s="5">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="Q237" s="5">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="R237" s="5">
+        <v>0.36359999999999998</v>
+      </c>
+      <c r="S237" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="V237" s="2">
+        <v>67.641599999999997</v>
+      </c>
+    </row>
+    <row r="238" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A238" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B238" s="1">
+        <v>14</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D238" s="1">
+        <v>30</v>
+      </c>
+      <c r="E238" s="1">
+        <v>2</v>
+      </c>
+      <c r="F238" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G238" s="1">
+        <v>4844</v>
+      </c>
+      <c r="H238" s="1">
+        <v>52</v>
+      </c>
+      <c r="I238" s="1">
+        <v>6</v>
+      </c>
+      <c r="J238" s="1">
+        <v>1</v>
+      </c>
+      <c r="K238" s="1">
+        <v>4</v>
+      </c>
+      <c r="L238" s="1">
+        <v>0</v>
+      </c>
+      <c r="M238" s="1">
+        <v>0</v>
+      </c>
+      <c r="N238" s="4">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="O238" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P238" s="5">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="Q238" s="6">
+        <v>0</v>
+      </c>
+      <c r="R238" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S233" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="V233" s="2">
-        <v>12.4696</v>
+      <c r="S238" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="T238" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="U238" s="5">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="V238" s="2">
+        <v>7.7896000000000001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A239" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B239" s="1">
+        <v>14</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D239" s="1">
+        <v>0</v>
+      </c>
+      <c r="E239" s="1">
+        <v>13</v>
+      </c>
+      <c r="F239" s="1">
+        <v>44685</v>
+      </c>
+      <c r="G239" s="1">
+        <v>12108</v>
+      </c>
+      <c r="H239" s="1">
+        <v>119</v>
+      </c>
+      <c r="I239" s="1">
+        <v>1</v>
+      </c>
+      <c r="J239" s="1">
+        <v>0</v>
+      </c>
+      <c r="K239" s="1">
+        <v>0</v>
+      </c>
+      <c r="L239" s="1">
+        <v>0</v>
+      </c>
+      <c r="M239" s="1">
+        <v>1</v>
+      </c>
+      <c r="O239" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="P239" s="5">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="Q239" s="5">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="R239" s="6">
+        <v>1</v>
+      </c>
+      <c r="S239" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="V239" s="2">
+        <v>18.688800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14954,7 +15341,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I1012"/>
+  <dimension ref="A1:I1117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -40241,13 +40628,13 @@
         <v>86</v>
       </c>
       <c r="E872" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F872" t="s">
         <v>6</v>
       </c>
       <c r="G872">
-        <v>2829</v>
+        <v>26863</v>
       </c>
       <c r="H872" s="8">
         <v>0</v>
@@ -40270,13 +40657,13 @@
         <v>86</v>
       </c>
       <c r="E873" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F873" t="s">
         <v>6</v>
       </c>
       <c r="G873">
-        <v>16</v>
+        <v>2829</v>
       </c>
       <c r="H873" s="8">
         <v>0</v>
@@ -40299,19 +40686,19 @@
         <v>86</v>
       </c>
       <c r="E874" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F874" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G874">
-        <v>26863</v>
+        <v>3</v>
       </c>
       <c r="H874" s="8">
-        <v>0</v>
+        <v>9.9537037037037042E-4</v>
       </c>
       <c r="I874" s="8">
-        <v>0</v>
+        <v>3.2407407407407406E-4</v>
       </c>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.3">
@@ -40328,13 +40715,13 @@
         <v>86</v>
       </c>
       <c r="E875" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F875" t="s">
         <v>6</v>
       </c>
       <c r="G875">
-        <v>26917</v>
+        <v>16</v>
       </c>
       <c r="H875" s="8">
         <v>0</v>
@@ -40357,19 +40744,19 @@
         <v>86</v>
       </c>
       <c r="E876" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F876" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G876">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H876" s="8">
-        <v>0</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="I876" s="8">
-        <v>0</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.3">
@@ -40386,19 +40773,19 @@
         <v>86</v>
       </c>
       <c r="E877" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="F877" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G877">
-        <v>3</v>
+        <v>26917</v>
       </c>
       <c r="H877" s="8">
-        <v>9.9537037037037042E-4</v>
+        <v>0</v>
       </c>
       <c r="I877" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="878" spans="1:9" x14ac:dyDescent="0.3">
@@ -40421,13 +40808,13 @@
         <v>88</v>
       </c>
       <c r="G878">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H878" s="8">
-        <v>1.5046296296296297E-4</v>
+        <v>3.9351851851851852E-4</v>
       </c>
       <c r="I878" s="8">
-        <v>1.5046296296296297E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="879" spans="1:9" x14ac:dyDescent="0.3">
@@ -40444,19 +40831,19 @@
         <v>86</v>
       </c>
       <c r="E879" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F879" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G879">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H879" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>0</v>
       </c>
       <c r="I879" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.3">
@@ -40479,13 +40866,13 @@
         <v>88</v>
       </c>
       <c r="G880">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H880" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>1.3078703703703703E-3</v>
       </c>
       <c r="I880" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
     </row>
     <row r="881" spans="1:9" x14ac:dyDescent="0.3">
@@ -40511,10 +40898,10 @@
         <v>1</v>
       </c>
       <c r="H881" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
       <c r="I881" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
     </row>
     <row r="882" spans="1:9" x14ac:dyDescent="0.3">
@@ -40537,13 +40924,13 @@
         <v>88</v>
       </c>
       <c r="G882">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H882" s="8">
-        <v>3.5879629629629629E-4</v>
+        <v>1.3310185185185185E-3</v>
       </c>
       <c r="I882" s="8">
-        <v>1.7361111111111112E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
     </row>
     <row r="883" spans="1:9" x14ac:dyDescent="0.3">
@@ -40566,13 +40953,13 @@
         <v>88</v>
       </c>
       <c r="G883">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H883" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="I883" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="884" spans="1:9" x14ac:dyDescent="0.3">
@@ -40595,13 +40982,13 @@
         <v>88</v>
       </c>
       <c r="G884">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H884" s="8">
-        <v>1.3078703703703703E-3</v>
+        <v>2.3263888888888887E-3</v>
       </c>
       <c r="I884" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="885" spans="1:9" x14ac:dyDescent="0.3">
@@ -40624,10 +41011,10 @@
         <v>88</v>
       </c>
       <c r="G885">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H885" s="8">
-        <v>1.3310185185185185E-3</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="I885" s="8">
         <v>2.6620370370370372E-4</v>
@@ -40653,13 +41040,13 @@
         <v>88</v>
       </c>
       <c r="G886">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H886" s="8">
-        <v>1.712962962962963E-3</v>
+        <v>2.8703703703703703E-3</v>
       </c>
       <c r="I886" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
     </row>
     <row r="887" spans="1:9" x14ac:dyDescent="0.3">
@@ -40682,13 +41069,13 @@
         <v>88</v>
       </c>
       <c r="G887">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H887" s="8">
-        <v>1.7824074074074075E-3</v>
+        <v>3.5879629629629629E-4</v>
       </c>
       <c r="I887" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>1.7361111111111112E-4</v>
       </c>
     </row>
     <row r="888" spans="1:9" x14ac:dyDescent="0.3">
@@ -40705,19 +41092,19 @@
         <v>86</v>
       </c>
       <c r="E888" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F888" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G888">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H888" s="8">
-        <v>2.3263888888888887E-3</v>
+        <v>4.363425925925926E-3</v>
       </c>
       <c r="I888" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>6.134259259259259E-4</v>
       </c>
     </row>
     <row r="889" spans="1:9" x14ac:dyDescent="0.3">
@@ -40740,13 +41127,13 @@
         <v>88</v>
       </c>
       <c r="G889">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H889" s="8">
-        <v>2.8703703703703703E-3</v>
+        <v>1.712962962962963E-3</v>
       </c>
       <c r="I889" s="8">
-        <v>1.5046296296296297E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="890" spans="1:9" x14ac:dyDescent="0.3">
@@ -40763,19 +41150,19 @@
         <v>86</v>
       </c>
       <c r="E890" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F890" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G890">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="H890" s="8">
-        <v>2.0636574074074075E-2</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="I890" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
     </row>
     <row r="891" spans="1:9" x14ac:dyDescent="0.3">
@@ -40792,19 +41179,19 @@
         <v>86</v>
       </c>
       <c r="E891" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F891" t="s">
         <v>88</v>
       </c>
       <c r="G891">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H891" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>1.7824074074074075E-3</v>
       </c>
       <c r="I891" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="892" spans="1:9" x14ac:dyDescent="0.3">
@@ -40821,19 +41208,19 @@
         <v>86</v>
       </c>
       <c r="E892" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F892" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G892">
-        <v>7</v>
+        <v>11186</v>
       </c>
       <c r="H892" s="8">
-        <v>4.363425925925926E-3</v>
+        <v>0</v>
       </c>
       <c r="I892" s="8">
-        <v>6.134259259259259E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="893" spans="1:9" x14ac:dyDescent="0.3">
@@ -40850,16 +41237,16 @@
         <v>86</v>
       </c>
       <c r="E893" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F893" t="s">
         <v>37</v>
       </c>
       <c r="G893">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="H893" s="8">
-        <v>5.0925925925925921E-4</v>
+        <v>2.0636574074074075E-2</v>
       </c>
       <c r="I893" s="8">
         <v>2.5462962962962961E-4</v>
@@ -40879,19 +41266,19 @@
         <v>86</v>
       </c>
       <c r="E894" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F894" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G894">
-        <v>2</v>
+        <v>1535</v>
       </c>
       <c r="H894" s="8">
-        <v>1.0069444444444444E-3</v>
+        <v>0</v>
       </c>
       <c r="I894" s="8">
-        <v>4.9768518518518521E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="895" spans="1:9" x14ac:dyDescent="0.3">
@@ -40908,19 +41295,19 @@
         <v>86</v>
       </c>
       <c r="E895" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F895" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G895">
         <v>1</v>
       </c>
       <c r="H895" s="8">
-        <v>9.3749999999999997E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="I895" s="8">
-        <v>9.3749999999999997E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="896" spans="1:9" x14ac:dyDescent="0.3">
@@ -40934,22 +41321,22 @@
         <v>17</v>
       </c>
       <c r="D896" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E896" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F896" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G896">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H896" s="8">
-        <v>9.432870370370371E-3</v>
+        <v>4.1666666666666669E-4</v>
       </c>
       <c r="I896" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>4.1666666666666669E-4</v>
       </c>
     </row>
     <row r="897" spans="1:9" x14ac:dyDescent="0.3">
@@ -40966,19 +41353,19 @@
         <v>86</v>
       </c>
       <c r="E897" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F897" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G897">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H897" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>5.0925925925925921E-4</v>
       </c>
       <c r="I897" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="898" spans="1:9" x14ac:dyDescent="0.3">
@@ -40992,22 +41379,22 @@
         <v>17</v>
       </c>
       <c r="D898" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E898" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F898" t="s">
         <v>37</v>
       </c>
       <c r="G898">
-        <v>509</v>
+        <v>8</v>
       </c>
       <c r="H898" s="8">
-        <v>4.494212962962963E-2</v>
+        <v>4.0740740740740737E-3</v>
       </c>
       <c r="I898" s="8">
-        <v>8.1018518518518516E-5</v>
+        <v>5.0925925925925921E-4</v>
       </c>
     </row>
     <row r="899" spans="1:9" x14ac:dyDescent="0.3">
@@ -41024,19 +41411,19 @@
         <v>86</v>
       </c>
       <c r="E899" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F899" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G899">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H899" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>1.0069444444444444E-3</v>
       </c>
       <c r="I899" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>4.9768518518518521E-4</v>
       </c>
     </row>
     <row r="900" spans="1:9" x14ac:dyDescent="0.3">
@@ -41050,22 +41437,22 @@
         <v>17</v>
       </c>
       <c r="D900" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E900" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F900" t="s">
         <v>37</v>
       </c>
       <c r="G900">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H900" s="8">
-        <v>1.1805555555555556E-3</v>
+        <v>3.6921296296296298E-3</v>
       </c>
       <c r="I900" s="8">
-        <v>3.9351851851851852E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="901" spans="1:9" x14ac:dyDescent="0.3">
@@ -41082,19 +41469,19 @@
         <v>86</v>
       </c>
       <c r="E901" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F901" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G901">
-        <v>11186</v>
+        <v>1</v>
       </c>
       <c r="H901" s="8">
-        <v>0</v>
+        <v>9.3749999999999997E-4</v>
       </c>
       <c r="I901" s="8">
-        <v>0</v>
+        <v>9.3749999999999997E-4</v>
       </c>
     </row>
     <row r="902" spans="1:9" x14ac:dyDescent="0.3">
@@ -41108,22 +41495,22 @@
         <v>17</v>
       </c>
       <c r="D902" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E902" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F902" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G902">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H902" s="8">
-        <v>1.0879629629629629E-3</v>
+        <v>3.6342592592592594E-3</v>
       </c>
       <c r="I902" s="8">
-        <v>8.1018518518518516E-5</v>
+        <v>1.8171296296296297E-3</v>
       </c>
     </row>
     <row r="903" spans="1:9" x14ac:dyDescent="0.3">
@@ -41140,19 +41527,19 @@
         <v>86</v>
       </c>
       <c r="E903" t="s">
+        <v>39</v>
+      </c>
+      <c r="F903" t="s">
+        <v>37</v>
+      </c>
+      <c r="G903">
         <v>35</v>
       </c>
-      <c r="F903" t="s">
-        <v>6</v>
-      </c>
-      <c r="G903">
-        <v>1535</v>
-      </c>
       <c r="H903" s="8">
-        <v>0</v>
+        <v>9.432870370370371E-3</v>
       </c>
       <c r="I903" s="8">
-        <v>0</v>
+        <v>2.6620370370370372E-4</v>
       </c>
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.3">
@@ -41169,19 +41556,19 @@
         <v>87</v>
       </c>
       <c r="E904" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F904" t="s">
         <v>37</v>
       </c>
       <c r="G904">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H904" s="8">
-        <v>8.564814814814815E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="I904" s="8">
-        <v>1.6203703703703703E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.3">
@@ -41195,22 +41582,22 @@
         <v>17</v>
       </c>
       <c r="D905" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E905" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="F905" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G905">
-        <v>1</v>
+        <v>509</v>
       </c>
       <c r="H905" s="8">
-        <v>4.1666666666666669E-4</v>
+        <v>4.494212962962963E-2</v>
       </c>
       <c r="I905" s="8">
-        <v>4.1666666666666669E-4</v>
+        <v>8.1018518518518516E-5</v>
       </c>
     </row>
     <row r="906" spans="1:9" x14ac:dyDescent="0.3">
@@ -41227,19 +41614,19 @@
         <v>87</v>
       </c>
       <c r="E906" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F906" t="s">
         <v>37</v>
       </c>
       <c r="G906">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H906" s="8">
-        <v>4.0740740740740737E-3</v>
+        <v>1.0092592592592592E-2</v>
       </c>
       <c r="I906" s="8">
-        <v>5.0925925925925921E-4</v>
+        <v>1.0069444444444444E-3</v>
       </c>
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.3">
@@ -41253,22 +41640,22 @@
         <v>17</v>
       </c>
       <c r="D907" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E907" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F907" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G907">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H907" s="8">
-        <v>3.6921296296296298E-3</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="I907" s="8">
-        <v>4.5138888888888887E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.3">
@@ -41282,22 +41669,22 @@
         <v>17</v>
       </c>
       <c r="D908" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E908" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F908" t="s">
         <v>37</v>
       </c>
       <c r="G908">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H908" s="8">
-        <v>9.837962962962962E-4</v>
+        <v>1.1805555555555556E-3</v>
       </c>
       <c r="I908" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>3.9351851851851852E-4</v>
       </c>
     </row>
     <row r="909" spans="1:9" x14ac:dyDescent="0.3">
@@ -41311,22 +41698,22 @@
         <v>17</v>
       </c>
       <c r="D909" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E909" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F909" t="s">
         <v>37</v>
       </c>
       <c r="G909">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H909" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>1.0879629629629629E-3</v>
       </c>
       <c r="I909" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>8.1018518518518516E-5</v>
       </c>
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.3">
@@ -41343,19 +41730,19 @@
         <v>87</v>
       </c>
       <c r="E910" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F910" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G910">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H910" s="8">
-        <v>9.837962962962962E-4</v>
+        <v>8.564814814814815E-4</v>
       </c>
       <c r="I910" s="8">
-        <v>4.861111111111111E-4</v>
+        <v>1.6203703703703703E-4</v>
       </c>
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.3">
@@ -41372,19 +41759,19 @@
         <v>87</v>
       </c>
       <c r="E911" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F911" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G911">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H911" s="8">
-        <v>3.6342592592592594E-3</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="I911" s="8">
-        <v>1.8171296296296297E-3</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="912" spans="1:9" x14ac:dyDescent="0.3">
@@ -41401,19 +41788,19 @@
         <v>87</v>
       </c>
       <c r="E912" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F912" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G912">
         <v>1</v>
       </c>
       <c r="H912" s="8">
-        <v>4.6874999999999998E-3</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I912" s="8">
-        <v>4.6874999999999998E-3</v>
+        <v>4.0509259259259258E-4</v>
       </c>
     </row>
     <row r="913" spans="1:9" x14ac:dyDescent="0.3">
@@ -41430,19 +41817,19 @@
         <v>87</v>
       </c>
       <c r="E913" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F913" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G913">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H913" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="I913" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>4.861111111111111E-4</v>
       </c>
     </row>
     <row r="914" spans="1:9" x14ac:dyDescent="0.3">
@@ -41459,19 +41846,19 @@
         <v>87</v>
       </c>
       <c r="E914" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F914" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G914">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H914" s="8">
-        <v>1.0092592592592592E-2</v>
+        <v>4.6874999999999998E-3</v>
       </c>
       <c r="I914" s="8">
-        <v>1.0069444444444444E-3</v>
+        <v>4.6874999999999998E-3</v>
       </c>
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.3">
@@ -41488,13 +41875,13 @@
         <v>86</v>
       </c>
       <c r="E915" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F915" t="s">
         <v>6</v>
       </c>
       <c r="G915">
-        <v>760</v>
+        <v>2588</v>
       </c>
       <c r="H915" s="8">
         <v>0</v>
@@ -41517,13 +41904,13 @@
         <v>86</v>
       </c>
       <c r="E916" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F916" t="s">
         <v>6</v>
       </c>
       <c r="G916">
-        <v>2588</v>
+        <v>760</v>
       </c>
       <c r="H916" s="8">
         <v>0</v>
@@ -41546,13 +41933,13 @@
         <v>86</v>
       </c>
       <c r="E917" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F917" t="s">
         <v>6</v>
       </c>
       <c r="G917">
-        <v>900</v>
+        <v>8</v>
       </c>
       <c r="H917" s="8">
         <v>0</v>
@@ -41575,13 +41962,13 @@
         <v>86</v>
       </c>
       <c r="E918" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F918" t="s">
         <v>6</v>
       </c>
       <c r="G918">
-        <v>8</v>
+        <v>900</v>
       </c>
       <c r="H918" s="8">
         <v>0</v>
@@ -41633,13 +42020,13 @@
         <v>86</v>
       </c>
       <c r="E920" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F920" t="s">
         <v>6</v>
       </c>
       <c r="G920">
-        <v>79683</v>
+        <v>5</v>
       </c>
       <c r="H920" s="8">
         <v>0</v>
@@ -41662,13 +42049,13 @@
         <v>86</v>
       </c>
       <c r="E921" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F921" t="s">
         <v>6</v>
       </c>
       <c r="G921">
-        <v>5</v>
+        <v>79683</v>
       </c>
       <c r="H921" s="8">
         <v>0</v>
@@ -41691,19 +42078,19 @@
         <v>86</v>
       </c>
       <c r="E922" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F922" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G922">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H922" s="8">
-        <v>0</v>
+        <v>4.6296296296296298E-4</v>
       </c>
       <c r="I922" s="8">
-        <v>0</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="923" spans="1:9" x14ac:dyDescent="0.3">
@@ -41720,19 +42107,19 @@
         <v>86</v>
       </c>
       <c r="E923" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F923" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G923">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H923" s="8">
-        <v>4.6296296296296298E-4</v>
+        <v>0</v>
       </c>
       <c r="I923" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.3">
@@ -41787,10 +42174,10 @@
         <v>1</v>
       </c>
       <c r="H925" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I925" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="926" spans="1:9" x14ac:dyDescent="0.3">
@@ -41816,10 +42203,10 @@
         <v>1</v>
       </c>
       <c r="H926" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="I926" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="927" spans="1:9" x14ac:dyDescent="0.3">
@@ -41923,19 +42310,19 @@
         <v>86</v>
       </c>
       <c r="E930" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F930" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G930">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H930" s="8">
-        <v>3.8194444444444446E-4</v>
+        <v>6.2847222222222219E-3</v>
       </c>
       <c r="I930" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>3.1250000000000001E-4</v>
       </c>
     </row>
     <row r="931" spans="1:9" x14ac:dyDescent="0.3">
@@ -41952,19 +42339,19 @@
         <v>86</v>
       </c>
       <c r="E931" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F931" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G931">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H931" s="8">
-        <v>7.6273148148148151E-3</v>
+        <v>3.8194444444444446E-4</v>
       </c>
       <c r="I931" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="932" spans="1:9" x14ac:dyDescent="0.3">
@@ -41981,19 +42368,19 @@
         <v>86</v>
       </c>
       <c r="E932" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F932" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G932">
         <v>1</v>
       </c>
       <c r="H932" s="8">
-        <v>9.1435185185185185E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="I932" s="8">
-        <v>9.1435185185185185E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
     <row r="933" spans="1:9" x14ac:dyDescent="0.3">
@@ -42010,19 +42397,19 @@
         <v>86</v>
       </c>
       <c r="E933" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F933" t="s">
         <v>37</v>
       </c>
       <c r="G933">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H933" s="8">
-        <v>7.291666666666667E-4</v>
+        <v>7.6273148148148151E-3</v>
       </c>
       <c r="I933" s="8">
-        <v>7.291666666666667E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="934" spans="1:9" x14ac:dyDescent="0.3">
@@ -42039,19 +42426,19 @@
         <v>86</v>
       </c>
       <c r="E934" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F934" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G934">
-        <v>20</v>
+        <v>3574</v>
       </c>
       <c r="H934" s="8">
-        <v>6.2847222222222219E-3</v>
+        <v>0</v>
       </c>
       <c r="I934" s="8">
-        <v>3.1250000000000001E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.3">
@@ -42068,19 +42455,19 @@
         <v>86</v>
       </c>
       <c r="E935" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F935" t="s">
         <v>37</v>
       </c>
       <c r="G935">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="H935" s="8">
-        <v>1.9849537037037037E-2</v>
+        <v>9.1435185185185185E-4</v>
       </c>
       <c r="I935" s="8">
-        <v>1.0416666666666667E-4</v>
+        <v>9.1435185185185185E-4</v>
       </c>
     </row>
     <row r="936" spans="1:9" x14ac:dyDescent="0.3">
@@ -42097,19 +42484,19 @@
         <v>86</v>
       </c>
       <c r="E936" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F936" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G936">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H936" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
       <c r="I936" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>3.4722222222222222E-5</v>
       </c>
     </row>
     <row r="937" spans="1:9" x14ac:dyDescent="0.3">
@@ -42126,19 +42513,19 @@
         <v>86</v>
       </c>
       <c r="E937" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F937" t="s">
         <v>37</v>
       </c>
       <c r="G937">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H937" s="8">
-        <v>7.6388888888888893E-4</v>
+        <v>7.291666666666667E-4</v>
       </c>
       <c r="I937" s="8">
-        <v>3.8194444444444446E-4</v>
+        <v>7.291666666666667E-4</v>
       </c>
     </row>
     <row r="938" spans="1:9" x14ac:dyDescent="0.3">
@@ -42155,13 +42542,13 @@
         <v>86</v>
       </c>
       <c r="E938" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F938" t="s">
         <v>6</v>
       </c>
       <c r="G938">
-        <v>3574</v>
+        <v>500</v>
       </c>
       <c r="H938" s="8">
         <v>0</v>
@@ -42184,19 +42571,19 @@
         <v>86</v>
       </c>
       <c r="E939" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F939" t="s">
         <v>37</v>
       </c>
       <c r="G939">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="H939" s="8">
-        <v>1.5046296296296297E-4</v>
+        <v>1.9849537037037037E-2</v>
       </c>
       <c r="I939" s="8">
-        <v>3.4722222222222222E-5</v>
+        <v>1.0416666666666667E-4</v>
       </c>
     </row>
     <row r="940" spans="1:9" x14ac:dyDescent="0.3">
@@ -42210,22 +42597,22 @@
         <v>17</v>
       </c>
       <c r="D940" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E940" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="F940" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G940">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H940" s="8">
-        <v>0</v>
+        <v>7.291666666666667E-4</v>
       </c>
       <c r="I940" s="8">
-        <v>0</v>
+        <v>7.291666666666667E-4</v>
       </c>
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.3">
@@ -42239,22 +42626,22 @@
         <v>17</v>
       </c>
       <c r="D941" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E941" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F941" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G941">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H941" s="8">
-        <v>7.291666666666667E-4</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="I941" s="8">
-        <v>7.291666666666667E-4</v>
+        <v>3.8194444444444446E-4</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -42416,13 +42803,13 @@
         <v>86</v>
       </c>
       <c r="E947" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F947" t="s">
         <v>6</v>
       </c>
       <c r="G947">
-        <v>1552</v>
+        <v>5950</v>
       </c>
       <c r="H947" s="8">
         <v>0</v>
@@ -42445,13 +42832,13 @@
         <v>86</v>
       </c>
       <c r="E948" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F948" t="s">
         <v>6</v>
       </c>
       <c r="G948">
-        <v>5950</v>
+        <v>1552</v>
       </c>
       <c r="H948" s="8">
         <v>0</v>
@@ -42503,13 +42890,13 @@
         <v>86</v>
       </c>
       <c r="E950" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F950" t="s">
         <v>6</v>
       </c>
       <c r="G950">
-        <v>19</v>
+        <v>16407</v>
       </c>
       <c r="H950" s="8">
         <v>0</v>
@@ -42532,13 +42919,13 @@
         <v>86</v>
       </c>
       <c r="E951" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F951" t="s">
         <v>6</v>
       </c>
       <c r="G951">
-        <v>16407</v>
+        <v>19</v>
       </c>
       <c r="H951" s="8">
         <v>0</v>
@@ -42561,13 +42948,13 @@
         <v>86</v>
       </c>
       <c r="E952" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F952" t="s">
         <v>6</v>
       </c>
       <c r="G952">
-        <v>48837</v>
+        <v>7</v>
       </c>
       <c r="H952" s="8">
         <v>0</v>
@@ -42590,13 +42977,13 @@
         <v>86</v>
       </c>
       <c r="E953" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F953" t="s">
         <v>6</v>
       </c>
       <c r="G953">
-        <v>7</v>
+        <v>48837</v>
       </c>
       <c r="H953" s="8">
         <v>0</v>
@@ -42657,10 +43044,10 @@
         <v>1</v>
       </c>
       <c r="H955" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I955" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="956" spans="1:9" x14ac:dyDescent="0.3">
@@ -42686,10 +43073,10 @@
         <v>1</v>
       </c>
       <c r="H956" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="I956" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.3">
@@ -42712,13 +43099,13 @@
         <v>88</v>
       </c>
       <c r="G957">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H957" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>7.5231481481481482E-4</v>
       </c>
       <c r="I957" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="958" spans="1:9" x14ac:dyDescent="0.3">
@@ -42744,10 +43131,10 @@
         <v>1</v>
       </c>
       <c r="H958" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="I958" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
     </row>
     <row r="959" spans="1:9" x14ac:dyDescent="0.3">
@@ -42770,13 +43157,13 @@
         <v>88</v>
       </c>
       <c r="G959">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H959" s="8">
-        <v>4.3981481481481481E-4</v>
+        <v>8.3333333333333339E-4</v>
       </c>
       <c r="I959" s="8">
-        <v>4.3981481481481481E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="960" spans="1:9" x14ac:dyDescent="0.3">
@@ -42799,13 +43186,13 @@
         <v>88</v>
       </c>
       <c r="G960">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H960" s="8">
-        <v>4.2824074074074075E-4</v>
+        <v>3.4722222222222224E-4</v>
       </c>
       <c r="I960" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>3.4722222222222224E-4</v>
       </c>
     </row>
     <row r="961" spans="1:9" x14ac:dyDescent="0.3">
@@ -42828,13 +43215,13 @@
         <v>88</v>
       </c>
       <c r="G961">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H961" s="8">
-        <v>5.7870370370370367E-4</v>
+        <v>1.5393518518518519E-3</v>
       </c>
       <c r="I961" s="8">
-        <v>2.8935185185185184E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="962" spans="1:9" x14ac:dyDescent="0.3">
@@ -42857,13 +43244,13 @@
         <v>88</v>
       </c>
       <c r="G962">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H962" s="8">
-        <v>7.5231481481481482E-4</v>
+        <v>4.3981481481481481E-4</v>
       </c>
       <c r="I962" s="8">
-        <v>1.8518518518518518E-4</v>
+        <v>4.3981481481481481E-4</v>
       </c>
     </row>
     <row r="963" spans="1:9" x14ac:dyDescent="0.3">
@@ -42880,19 +43267,19 @@
         <v>86</v>
       </c>
       <c r="E963" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F963" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G963">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H963" s="8">
-        <v>8.3333333333333339E-4</v>
+        <v>1.2268518518518518E-3</v>
       </c>
       <c r="I963" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
     </row>
     <row r="964" spans="1:9" x14ac:dyDescent="0.3">
@@ -42915,13 +43302,13 @@
         <v>88</v>
       </c>
       <c r="G964">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H964" s="8">
-        <v>8.7962962962962962E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="I964" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="965" spans="1:9" x14ac:dyDescent="0.3">
@@ -42938,19 +43325,19 @@
         <v>86</v>
       </c>
       <c r="E965" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F965" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G965">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H965" s="8">
-        <v>1.0185185185185184E-3</v>
+        <v>4.7453703703703704E-4</v>
       </c>
       <c r="I965" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>4.7453703703703704E-4</v>
       </c>
     </row>
     <row r="966" spans="1:9" x14ac:dyDescent="0.3">
@@ -42973,13 +43360,13 @@
         <v>88</v>
       </c>
       <c r="G966">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H966" s="8">
-        <v>1.5393518518518519E-3</v>
+        <v>5.7870370370370367E-4</v>
       </c>
       <c r="I966" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
     </row>
     <row r="967" spans="1:9" x14ac:dyDescent="0.3">
@@ -42996,19 +43383,19 @@
         <v>86</v>
       </c>
       <c r="E967" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F967" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G967">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H967" s="8">
-        <v>1.9328703703703704E-3</v>
+        <v>6.8634259259259256E-3</v>
       </c>
       <c r="I967" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="968" spans="1:9" x14ac:dyDescent="0.3">
@@ -43025,19 +43412,19 @@
         <v>86</v>
       </c>
       <c r="E968" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F968" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G968">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H968" s="8">
-        <v>9.4907407407407408E-4</v>
+        <v>8.7962962962962962E-4</v>
       </c>
       <c r="I968" s="8">
-        <v>9.4907407407407408E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="969" spans="1:9" x14ac:dyDescent="0.3">
@@ -43054,19 +43441,19 @@
         <v>86</v>
       </c>
       <c r="E969" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F969" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G969">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="H969" s="8">
-        <v>1.667824074074074E-2</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="I969" s="8">
-        <v>2.4305555555555555E-4</v>
+        <v>5.3240740740740744E-4</v>
       </c>
     </row>
     <row r="970" spans="1:9" x14ac:dyDescent="0.3">
@@ -43083,19 +43470,19 @@
         <v>86</v>
       </c>
       <c r="E970" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F970" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G970">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H970" s="8">
-        <v>8.1018518518518516E-5</v>
+        <v>1.0185185185185184E-3</v>
       </c>
       <c r="I970" s="8">
-        <v>8.1018518518518516E-5</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="971" spans="1:9" x14ac:dyDescent="0.3">
@@ -43112,19 +43499,19 @@
         <v>86</v>
       </c>
       <c r="E971" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="F971" t="s">
         <v>37</v>
       </c>
       <c r="G971">
-        <v>1</v>
+        <v>376</v>
       </c>
       <c r="H971" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>4.0810185185185185E-2</v>
       </c>
       <c r="I971" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>1.0416666666666667E-4</v>
       </c>
     </row>
     <row r="972" spans="1:9" x14ac:dyDescent="0.3">
@@ -43141,19 +43528,19 @@
         <v>86</v>
       </c>
       <c r="E972" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F972" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G972">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H972" s="8">
-        <v>1.2268518518518518E-3</v>
+        <v>1.9328703703703704E-3</v>
       </c>
       <c r="I972" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="973" spans="1:9" x14ac:dyDescent="0.3">
@@ -43170,19 +43557,19 @@
         <v>86</v>
       </c>
       <c r="E973" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F973" t="s">
         <v>37</v>
       </c>
       <c r="G973">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H973" s="8">
-        <v>4.7453703703703704E-4</v>
+        <v>1.5972222222222223E-3</v>
       </c>
       <c r="I973" s="8">
-        <v>4.7453703703703704E-4</v>
+        <v>1.3888888888888889E-4</v>
       </c>
     </row>
     <row r="974" spans="1:9" x14ac:dyDescent="0.3">
@@ -43199,19 +43586,19 @@
         <v>86</v>
       </c>
       <c r="E974" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F974" t="s">
         <v>37</v>
       </c>
       <c r="G974">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H974" s="8">
-        <v>6.8634259259259256E-3</v>
+        <v>9.4907407407407408E-4</v>
       </c>
       <c r="I974" s="8">
-        <v>2.7777777777777778E-4</v>
+        <v>9.4907407407407408E-4</v>
       </c>
     </row>
     <row r="975" spans="1:9" x14ac:dyDescent="0.3">
@@ -43225,22 +43612,22 @@
         <v>17</v>
       </c>
       <c r="D975" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E975" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F975" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G975">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H975" s="8">
-        <v>5.3240740740740744E-4</v>
+        <v>1.1226851851851851E-3</v>
       </c>
       <c r="I975" s="8">
-        <v>5.3240740740740744E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="976" spans="1:9" x14ac:dyDescent="0.3">
@@ -43257,19 +43644,19 @@
         <v>86</v>
       </c>
       <c r="E976" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F976" t="s">
         <v>37</v>
       </c>
       <c r="G976">
-        <v>376</v>
+        <v>66</v>
       </c>
       <c r="H976" s="8">
-        <v>4.0810185185185185E-2</v>
+        <v>1.667824074074074E-2</v>
       </c>
       <c r="I976" s="8">
-        <v>1.0416666666666667E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="977" spans="1:9" x14ac:dyDescent="0.3">
@@ -43283,22 +43670,22 @@
         <v>17</v>
       </c>
       <c r="D977" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E977" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F977" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G977">
         <v>1</v>
       </c>
       <c r="H977" s="8">
-        <v>5.9027777777777778E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="I977" s="8">
-        <v>5.9027777777777778E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.3">
@@ -43315,19 +43702,19 @@
         <v>86</v>
       </c>
       <c r="E978" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F978" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G978">
-        <v>6218</v>
+        <v>1</v>
       </c>
       <c r="H978" s="8">
-        <v>0</v>
+        <v>8.1018518518518516E-5</v>
       </c>
       <c r="I978" s="8">
-        <v>0</v>
+        <v>8.1018518518518516E-5</v>
       </c>
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.3">
@@ -43341,22 +43728,22 @@
         <v>17</v>
       </c>
       <c r="D979" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E979" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="F979" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G979">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H979" s="8">
-        <v>1.5972222222222223E-3</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="I979" s="8">
-        <v>1.3888888888888889E-4</v>
+        <v>5.3240740740740744E-4</v>
       </c>
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.3">
@@ -43373,19 +43760,19 @@
         <v>86</v>
       </c>
       <c r="E980" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F980" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G980">
-        <v>911</v>
+        <v>1</v>
       </c>
       <c r="H980" s="8">
-        <v>0</v>
+        <v>2.3148148148148149E-4</v>
       </c>
       <c r="I980" s="8">
-        <v>0</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="981" spans="1:9" x14ac:dyDescent="0.3">
@@ -43402,19 +43789,19 @@
         <v>87</v>
       </c>
       <c r="E981" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F981" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G981">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H981" s="8">
-        <v>5.3240740740740744E-4</v>
+        <v>9.0509259259259258E-3</v>
       </c>
       <c r="I981" s="8">
-        <v>1.273148148148148E-4</v>
+        <v>4.5254629629629629E-3</v>
       </c>
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.3">
@@ -43428,22 +43815,22 @@
         <v>17</v>
       </c>
       <c r="D982" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E982" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F982" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G982">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H982" s="8">
-        <v>1.1226851851851851E-3</v>
+        <v>5.9027777777777778E-4</v>
       </c>
       <c r="I982" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>5.9027777777777778E-4</v>
       </c>
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.3">
@@ -43460,19 +43847,19 @@
         <v>87</v>
       </c>
       <c r="E983" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F983" t="s">
         <v>37</v>
       </c>
       <c r="G983">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H983" s="8">
-        <v>1.2268518518518518E-3</v>
+        <v>5.4745370370370373E-3</v>
       </c>
       <c r="I983" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>9.0277777777777774E-4</v>
       </c>
     </row>
     <row r="984" spans="1:9" x14ac:dyDescent="0.3">
@@ -43486,22 +43873,22 @@
         <v>17</v>
       </c>
       <c r="D984" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E984" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F984" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G984">
-        <v>2</v>
+        <v>6218</v>
       </c>
       <c r="H984" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>0</v>
       </c>
       <c r="I984" s="8">
-        <v>1.6203703703703703E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="985" spans="1:9" x14ac:dyDescent="0.3">
@@ -43515,22 +43902,22 @@
         <v>17</v>
       </c>
       <c r="D985" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E985" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F985" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G985">
-        <v>1</v>
+        <v>911</v>
       </c>
       <c r="H985" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>0</v>
       </c>
       <c r="I985" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="986" spans="1:9" x14ac:dyDescent="0.3">
@@ -43547,19 +43934,19 @@
         <v>87</v>
       </c>
       <c r="E986" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F986" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G986">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H986" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="I986" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.3">
@@ -43576,19 +43963,19 @@
         <v>87</v>
       </c>
       <c r="E987" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F987" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G987">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H987" s="8">
-        <v>1.2152777777777778E-3</v>
+        <v>1.2268518518518518E-3</v>
       </c>
       <c r="I987" s="8">
-        <v>1.2152777777777778E-3</v>
+        <v>3.0092592592592595E-4</v>
       </c>
     </row>
     <row r="988" spans="1:9" x14ac:dyDescent="0.3">
@@ -43605,19 +43992,19 @@
         <v>87</v>
       </c>
       <c r="E988" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F988" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G988">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H988" s="8">
-        <v>7.1759259259259259E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="I988" s="8">
-        <v>7.1759259259259259E-4</v>
+        <v>1.6203703703703703E-4</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -43634,7 +44021,7 @@
         <v>87</v>
       </c>
       <c r="E989" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F989" t="s">
         <v>10</v>
@@ -43643,10 +44030,10 @@
         <v>1</v>
       </c>
       <c r="H989" s="8">
-        <v>5.3240740740740744E-4</v>
+        <v>3.4722222222222224E-4</v>
       </c>
       <c r="I989" s="8">
-        <v>5.3240740740740744E-4</v>
+        <v>3.4722222222222224E-4</v>
       </c>
     </row>
     <row r="990" spans="1:9" x14ac:dyDescent="0.3">
@@ -43663,19 +44050,19 @@
         <v>87</v>
       </c>
       <c r="E990" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F990" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G990">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H990" s="8">
-        <v>9.0509259259259258E-3</v>
+        <v>1.2152777777777778E-3</v>
       </c>
       <c r="I990" s="8">
-        <v>4.5254629629629629E-3</v>
+        <v>1.2152777777777778E-3</v>
       </c>
     </row>
     <row r="991" spans="1:9" x14ac:dyDescent="0.3">
@@ -43692,19 +44079,19 @@
         <v>87</v>
       </c>
       <c r="E991" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F991" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G991">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H991" s="8">
-        <v>1.5902777777777776E-2</v>
+        <v>7.1759259259259259E-4</v>
       </c>
       <c r="I991" s="8">
-        <v>3.9699074074074072E-3</v>
+        <v>7.1759259259259259E-4</v>
       </c>
     </row>
     <row r="992" spans="1:9" x14ac:dyDescent="0.3">
@@ -43721,19 +44108,19 @@
         <v>87</v>
       </c>
       <c r="E992" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F992" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G992">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H992" s="8">
-        <v>5.4745370370370373E-3</v>
+        <v>1.5902777777777776E-2</v>
       </c>
       <c r="I992" s="8">
-        <v>9.0277777777777774E-4</v>
+        <v>3.9699074074074072E-3</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">
@@ -43756,7 +44143,7 @@
         <v>6</v>
       </c>
       <c r="G993">
-        <v>332</v>
+        <v>1092</v>
       </c>
       <c r="H993" s="8">
         <v>0</v>
@@ -43779,13 +44166,13 @@
         <v>86</v>
       </c>
       <c r="E994" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F994" t="s">
         <v>6</v>
       </c>
       <c r="G994">
-        <v>1578</v>
+        <v>711</v>
       </c>
       <c r="H994" s="8">
         <v>0</v>
@@ -43808,13 +44195,13 @@
         <v>86</v>
       </c>
       <c r="E995" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F995" t="s">
         <v>6</v>
       </c>
       <c r="G995">
-        <v>176</v>
+        <v>3790</v>
       </c>
       <c r="H995" s="8">
         <v>0</v>
@@ -43843,7 +44230,7 @@
         <v>6</v>
       </c>
       <c r="G996">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H996" s="8">
         <v>0</v>
@@ -43872,7 +44259,7 @@
         <v>6</v>
       </c>
       <c r="G997">
-        <v>4224</v>
+        <v>12430</v>
       </c>
       <c r="H997" s="8">
         <v>0</v>
@@ -43895,13 +44282,13 @@
         <v>86</v>
       </c>
       <c r="E998" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F998" t="s">
         <v>6</v>
       </c>
       <c r="G998">
-        <v>4546</v>
+        <v>7</v>
       </c>
       <c r="H998" s="8">
         <v>0</v>
@@ -43924,13 +44311,13 @@
         <v>86</v>
       </c>
       <c r="E999" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F999" t="s">
         <v>6</v>
       </c>
       <c r="G999">
-        <v>2</v>
+        <v>40179</v>
       </c>
       <c r="H999" s="8">
         <v>0</v>
@@ -43962,10 +44349,10 @@
         <v>1</v>
       </c>
       <c r="H1000" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I1000" s="8">
-        <v>3.0092592592592595E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="1001" spans="1:9" x14ac:dyDescent="0.3">
@@ -43982,19 +44369,19 @@
         <v>86</v>
       </c>
       <c r="E1001" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F1001" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G1001">
         <v>1</v>
       </c>
       <c r="H1001" s="8">
-        <v>3.8194444444444446E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="I1001" s="8">
-        <v>3.8194444444444446E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="1002" spans="1:9" x14ac:dyDescent="0.3">
@@ -44017,13 +44404,13 @@
         <v>88</v>
       </c>
       <c r="G1002">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1002" s="8">
-        <v>3.4722222222222224E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
       <c r="I1002" s="8">
-        <v>1.7361111111111112E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
     </row>
     <row r="1003" spans="1:9" x14ac:dyDescent="0.3">
@@ -44040,19 +44427,19 @@
         <v>86</v>
       </c>
       <c r="E1003" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F1003" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1003">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H1003" s="8">
-        <v>5.1967592592592595E-3</v>
+        <v>5.7870370370370367E-4</v>
       </c>
       <c r="I1003" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
     </row>
     <row r="1004" spans="1:9" x14ac:dyDescent="0.3">
@@ -44069,19 +44456,19 @@
         <v>86</v>
       </c>
       <c r="E1004" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F1004" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1004">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1004" s="8">
-        <v>6.9444444444444447E-4</v>
+        <v>7.291666666666667E-4</v>
       </c>
       <c r="I1004" s="8">
-        <v>6.9444444444444447E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
     </row>
     <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
@@ -44098,19 +44485,19 @@
         <v>86</v>
       </c>
       <c r="E1005" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1005" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1005">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1005" s="8">
-        <v>1.4236111111111112E-3</v>
+        <v>1.1921296296296296E-3</v>
       </c>
       <c r="I1005" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
     </row>
     <row r="1006" spans="1:9" x14ac:dyDescent="0.3">
@@ -44127,19 +44514,19 @@
         <v>86</v>
       </c>
       <c r="E1006" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F1006" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1006">
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="H1006" s="8">
-        <v>1.4340277777777778E-2</v>
+        <v>7.5231481481481482E-4</v>
       </c>
       <c r="I1006" s="8">
-        <v>1.5046296296296297E-4</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
@@ -44156,19 +44543,19 @@
         <v>86</v>
       </c>
       <c r="E1007" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F1007" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G1007">
-        <v>1631</v>
+        <v>25</v>
       </c>
       <c r="H1007" s="8">
-        <v>0</v>
+        <v>6.4583333333333333E-3</v>
       </c>
       <c r="I1007" s="8">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="1008" spans="1:9" x14ac:dyDescent="0.3">
@@ -44185,19 +44572,19 @@
         <v>86</v>
       </c>
       <c r="E1008" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F1008" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1008">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1008" s="8">
-        <v>1.1574074074074073E-5</v>
+        <v>7.8703703703703705E-4</v>
       </c>
       <c r="I1008" s="8">
-        <v>1.1574074074074073E-5</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="1009" spans="1:9" x14ac:dyDescent="0.3">
@@ -44214,19 +44601,19 @@
         <v>86</v>
       </c>
       <c r="E1009" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1009" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G1009">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="H1009" s="8">
-        <v>0</v>
+        <v>3.5509259259259261E-2</v>
       </c>
       <c r="I1009" s="8">
-        <v>0</v>
+        <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.3">
@@ -44240,22 +44627,22 @@
         <v>17</v>
       </c>
       <c r="D1010" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1010" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F1010" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1010">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H1010" s="8">
-        <v>6.7129629629629625E-4</v>
+        <v>1.5277777777777779E-3</v>
       </c>
       <c r="I1010" s="8">
-        <v>6.7129629629629625E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="1011" spans="1:9" x14ac:dyDescent="0.3">
@@ -44269,22 +44656,22 @@
         <v>17</v>
       </c>
       <c r="D1011" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1011" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F1011" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1011">
-        <v>1</v>
+        <v>750</v>
       </c>
       <c r="H1011" s="8">
-        <v>8.9120370370370373E-4</v>
+        <v>0</v>
       </c>
       <c r="I1011" s="8">
-        <v>8.9120370370370373E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1012" spans="1:9" x14ac:dyDescent="0.3">
@@ -44298,22 +44685,3064 @@
         <v>17</v>
       </c>
       <c r="D1012" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1012" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F1012" t="s">
         <v>37</v>
       </c>
       <c r="G1012">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H1012" s="8">
-        <v>8.4490740740740739E-4</v>
+        <v>1.2430555555555556E-2</v>
       </c>
       <c r="I1012" s="8">
-        <v>8.4490740740740739E-4</v>
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1013" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1013">
+        <v>11</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1013" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1013" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1013">
+        <v>1</v>
+      </c>
+      <c r="H1013" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1013" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1014" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1014">
+        <v>11</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1014" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1014" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1014">
+        <v>1</v>
+      </c>
+      <c r="H1014" s="8">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="I1014" s="8">
+        <v>9.837962962962962E-4</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1015" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1015">
+        <v>11</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1015" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1015" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1015">
+        <v>1</v>
+      </c>
+      <c r="H1015" s="8">
+        <v>1.1342592592592593E-3</v>
+      </c>
+      <c r="I1015" s="8">
+        <v>1.1342592592592593E-3</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1016" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1016">
+        <v>11</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1016" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1016" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1016">
+        <v>2</v>
+      </c>
+      <c r="H1016" s="8">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="I1016" s="8">
+        <v>1.0416666666666667E-3</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1017" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1017">
+        <v>11</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1017" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1017">
+        <v>3</v>
+      </c>
+      <c r="H1017" s="8">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="I1017" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1018" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1018">
+        <v>11</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1018" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1018" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1018">
+        <v>1</v>
+      </c>
+      <c r="H1018" s="8">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="I1018" s="8">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1019" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1019">
+        <v>11</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1019" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1019" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1019">
+        <v>1</v>
+      </c>
+      <c r="H1019" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="I1019" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1020" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1020">
+        <v>11</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1020" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1020">
+        <v>4588</v>
+      </c>
+      <c r="H1020" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1020" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1021" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1021">
+        <v>11</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1021">
+        <v>4</v>
+      </c>
+      <c r="H1021" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I1021" s="8">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1022" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1022">
+        <v>11</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1022" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1022">
+        <v>2</v>
+      </c>
+      <c r="H1022" s="8">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="I1022" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1023" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1023">
+        <v>11</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1023">
+        <v>3</v>
+      </c>
+      <c r="H1023" s="8">
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="I1023" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1024" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1024">
+        <v>11</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1024" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1024">
+        <v>2</v>
+      </c>
+      <c r="H1024" s="8">
+        <v>1.4236111111111112E-3</v>
+      </c>
+      <c r="I1024" s="8">
+        <v>7.0601851851851847E-4</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1025" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1025">
+        <v>11</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1025" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1025">
+        <v>1</v>
+      </c>
+      <c r="H1025" s="8">
+        <v>4.4675925925925924E-3</v>
+      </c>
+      <c r="I1025" s="8">
+        <v>4.4675925925925924E-3</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1026" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1026">
+        <v>11</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1026" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1026">
+        <v>4</v>
+      </c>
+      <c r="H1026" s="8">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="I1026" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1027" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1027">
+        <v>12</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1027" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1027">
+        <v>728</v>
+      </c>
+      <c r="H1027" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1027" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1028" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1028">
+        <v>12</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1028">
+        <v>7</v>
+      </c>
+      <c r="H1028" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1028" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1029" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1029">
+        <v>12</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1029" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1029">
+        <v>1625</v>
+      </c>
+      <c r="H1029" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1029" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1030" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1030">
+        <v>12</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1030" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1030">
+        <v>40923</v>
+      </c>
+      <c r="H1030" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1030" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1031" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1031">
+        <v>12</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1031" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1031">
+        <v>532</v>
+      </c>
+      <c r="H1031" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1031" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1032" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1032">
+        <v>12</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1032" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1032">
+        <v>1</v>
+      </c>
+      <c r="H1032" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I1032" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1033" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1033">
+        <v>12</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1033" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1033">
+        <v>8379</v>
+      </c>
+      <c r="H1033" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1033" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1034" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1034">
+        <v>12</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1034" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1034" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1034">
+        <v>1</v>
+      </c>
+      <c r="H1034" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I1034" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1035" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1035">
+        <v>12</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1035" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1035" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1035">
+        <v>1</v>
+      </c>
+      <c r="H1035" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I1035" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1036" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1036">
+        <v>12</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1036" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1036">
+        <v>1</v>
+      </c>
+      <c r="H1036" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I1036" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1037" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1037">
+        <v>12</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1037" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1037">
+        <v>1</v>
+      </c>
+      <c r="H1037" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I1037" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1038" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1038">
+        <v>12</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1038" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1038">
+        <v>1</v>
+      </c>
+      <c r="H1038" s="8">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="I1038" s="8">
+        <v>4.2824074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1039" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1039">
+        <v>12</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1039" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1039">
+        <v>12</v>
+      </c>
+      <c r="H1039" s="8">
+        <v>1.7939814814814815E-3</v>
+      </c>
+      <c r="I1039" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1040" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1040">
+        <v>12</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1040" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1040">
+        <v>3</v>
+      </c>
+      <c r="H1040" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="I1040" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1041" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1041">
+        <v>12</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1041" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1041">
+        <v>35</v>
+      </c>
+      <c r="H1041" s="8">
+        <v>9.6990740740740735E-3</v>
+      </c>
+      <c r="I1041" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1042" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1042">
+        <v>12</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1042" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1042">
+        <v>3</v>
+      </c>
+      <c r="H1042" s="8">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="I1042" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1043" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1043">
+        <v>12</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1043" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1043">
+        <v>1</v>
+      </c>
+      <c r="H1043" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I1043" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1044" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1044">
+        <v>12</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1044" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1044">
+        <v>4</v>
+      </c>
+      <c r="H1044" s="8">
+        <v>7.9861111111111116E-4</v>
+      </c>
+      <c r="I1044" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1045" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1045">
+        <v>12</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1045" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1045">
+        <v>2</v>
+      </c>
+      <c r="H1045" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="I1045" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1046" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1046">
+        <v>12</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1046">
+        <v>177</v>
+      </c>
+      <c r="H1046" s="8">
+        <v>1.9479166666666665E-2</v>
+      </c>
+      <c r="I1046" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1047" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1047">
+        <v>12</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1047">
+        <v>1</v>
+      </c>
+      <c r="H1047" s="8">
+        <v>1.0879629629629629E-3</v>
+      </c>
+      <c r="I1047" s="8">
+        <v>1.0879629629629629E-3</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1048" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1048">
+        <v>12</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1048" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1048">
+        <v>3102</v>
+      </c>
+      <c r="H1048" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1048" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1049" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1049">
+        <v>12</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1049" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1049">
+        <v>18</v>
+      </c>
+      <c r="H1049" s="8">
+        <v>3.425925925925926E-3</v>
+      </c>
+      <c r="I1049" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1050" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1050">
+        <v>12</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1050">
+        <v>3</v>
+      </c>
+      <c r="H1050" s="8">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="I1050" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1051" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1051">
+        <v>12</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1051">
+        <v>1</v>
+      </c>
+      <c r="H1051" s="8">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="I1051" s="8">
+        <v>8.1018518518518516E-4</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1052" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1052">
+        <v>12</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1052">
+        <v>1</v>
+      </c>
+      <c r="H1052" s="8">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="I1052" s="8">
+        <v>8.2175925925925927E-4</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1053" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1053">
+        <v>12</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1053" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1053">
+        <v>3</v>
+      </c>
+      <c r="H1053" s="8">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="I1053" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1054" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1054">
+        <v>12</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1054" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1054" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1054">
+        <v>1</v>
+      </c>
+      <c r="H1054" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="I1054" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1055" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1055">
+        <v>12</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1055" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1055">
+        <v>498</v>
+      </c>
+      <c r="H1055" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1055" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1056" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1056">
+        <v>12</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1056" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1056" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1056">
+        <v>1</v>
+      </c>
+      <c r="H1056" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I1056" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1057" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1057">
+        <v>12</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1057" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1057">
+        <v>3</v>
+      </c>
+      <c r="H1057" s="8">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="I1057" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1058" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1058">
+        <v>12</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1058" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1058">
+        <v>1</v>
+      </c>
+      <c r="H1058" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="I1058" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1059" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1059">
+        <v>12</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1059">
+        <v>1</v>
+      </c>
+      <c r="H1059" s="8">
+        <v>4.363425925925926E-3</v>
+      </c>
+      <c r="I1059" s="8">
+        <v>4.363425925925926E-3</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1060" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1060">
+        <v>12</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1060" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1060">
+        <v>4</v>
+      </c>
+      <c r="H1060" s="8">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="I1060" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1061" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1061">
+        <v>13</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1061" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1061">
+        <v>2908</v>
+      </c>
+      <c r="H1061" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1061" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1062" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1062">
+        <v>13</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1062">
+        <v>1267</v>
+      </c>
+      <c r="H1062" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1062" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1063" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1063">
+        <v>13</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1063" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1063">
+        <v>529</v>
+      </c>
+      <c r="H1063" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1063" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1064" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1064">
+        <v>13</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1064">
+        <v>13649</v>
+      </c>
+      <c r="H1064" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1064" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1065" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1065">
+        <v>13</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1065" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1065">
+        <v>12</v>
+      </c>
+      <c r="H1065" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1065" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1066" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1066">
+        <v>13</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1066" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1066" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1066">
+        <v>29307</v>
+      </c>
+      <c r="H1066" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1066" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1067" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1067">
+        <v>13</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1067" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1067" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1067">
+        <v>1</v>
+      </c>
+      <c r="H1067" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I1067" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1068" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1068">
+        <v>13</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1068" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1068" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1068">
+        <v>8</v>
+      </c>
+      <c r="H1068" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1068" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1069" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1069">
+        <v>13</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1069">
+        <v>1</v>
+      </c>
+      <c r="H1069" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I1069" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1070" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1070">
+        <v>13</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1070">
+        <v>1</v>
+      </c>
+      <c r="H1070" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I1070" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1071" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1071">
+        <v>13</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1071">
+        <v>5</v>
+      </c>
+      <c r="H1071" s="8">
+        <v>1.25E-3</v>
+      </c>
+      <c r="I1071" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1072" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1072">
+        <v>13</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1072">
+        <v>1</v>
+      </c>
+      <c r="H1072" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I1072" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1073" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1073">
+        <v>13</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1073" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1073">
+        <v>7</v>
+      </c>
+      <c r="H1073" s="8">
+        <v>2.0254629629629629E-3</v>
+      </c>
+      <c r="I1073" s="8">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1074" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1074">
+        <v>13</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1074">
+        <v>1</v>
+      </c>
+      <c r="H1074" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I1074" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1075" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1075">
+        <v>13</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1075" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1075">
+        <v>2</v>
+      </c>
+      <c r="H1075" s="8">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="I1075" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1076" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1076">
+        <v>13</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1076">
+        <v>3</v>
+      </c>
+      <c r="H1076" s="8">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="I1076" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1077" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1077">
+        <v>13</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1077">
+        <v>1</v>
+      </c>
+      <c r="H1077" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="I1077" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1078" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1078">
+        <v>13</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1078">
+        <v>5</v>
+      </c>
+      <c r="H1078" s="8">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="I1078" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1079" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1079">
+        <v>13</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1079">
+        <v>314</v>
+      </c>
+      <c r="H1079" s="8">
+        <v>3.5370370370370371E-2</v>
+      </c>
+      <c r="I1079" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1080" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1080">
+        <v>13</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1080" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1080">
+        <v>5</v>
+      </c>
+      <c r="H1080" s="8">
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="I1080" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1081" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1081">
+        <v>13</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1081">
+        <v>1</v>
+      </c>
+      <c r="H1081" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="I1081" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1082" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1082">
+        <v>13</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1082">
+        <v>42</v>
+      </c>
+      <c r="H1082" s="8">
+        <v>1.1354166666666667E-2</v>
+      </c>
+      <c r="I1082" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1083" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1083">
+        <v>13</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1083">
+        <v>799</v>
+      </c>
+      <c r="H1083" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1083" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1084" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1084">
+        <v>13</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1084">
+        <v>4</v>
+      </c>
+      <c r="H1084" s="8">
+        <v>2.8703703703703703E-3</v>
+      </c>
+      <c r="I1084" s="8">
+        <v>7.1759259259259259E-4</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1085" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1085">
+        <v>13</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1085" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1085">
+        <v>1</v>
+      </c>
+      <c r="H1085" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I1085" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1086" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1086">
+        <v>13</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1086">
+        <v>4</v>
+      </c>
+      <c r="H1086" s="8">
+        <v>2.3611111111111111E-3</v>
+      </c>
+      <c r="I1086" s="8">
+        <v>5.9027777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1087" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1087">
+        <v>13</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1087">
+        <v>1</v>
+      </c>
+      <c r="H1087" s="8">
+        <v>6.0879629629629626E-3</v>
+      </c>
+      <c r="I1087" s="8">
+        <v>6.0879629629629626E-3</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1088" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1088">
+        <v>13</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1088">
+        <v>22</v>
+      </c>
+      <c r="H1088" s="8">
+        <v>6.6435185185185182E-3</v>
+      </c>
+      <c r="I1088" s="8">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1089" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1089">
+        <v>13</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1089" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1089">
+        <v>1</v>
+      </c>
+      <c r="H1089" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="I1089" s="8">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1090" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1090">
+        <v>13</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1090">
+        <v>1</v>
+      </c>
+      <c r="H1090" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I1090" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1091" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1091">
+        <v>13</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1091">
+        <v>5289</v>
+      </c>
+      <c r="H1091" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1091" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1092" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1092">
+        <v>13</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1092">
+        <v>2</v>
+      </c>
+      <c r="H1092" s="8">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="I1092" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1093" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1093">
+        <v>13</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1093">
+        <v>7</v>
+      </c>
+      <c r="H1093" s="8">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="I1093" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1094" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1094">
+        <v>13</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1094">
+        <v>5</v>
+      </c>
+      <c r="H1094" s="8">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="I1094" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1095" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1095">
+        <v>13</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1095">
+        <v>3</v>
+      </c>
+      <c r="H1095" s="8">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="I1095" s="8">
+        <v>5.4398148148148144E-4</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1096" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1096">
+        <v>13</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1096" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1096">
+        <v>1</v>
+      </c>
+      <c r="H1096" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I1096" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1097" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1097">
+        <v>13</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1097">
+        <v>1</v>
+      </c>
+      <c r="H1097" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="I1097" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1098" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1098">
+        <v>13</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1098">
+        <v>1</v>
+      </c>
+      <c r="H1098" s="8">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="I1098" s="8">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1099" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1099">
+        <v>13</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1099">
+        <v>5</v>
+      </c>
+      <c r="H1099" s="8">
+        <v>5.6712962962962967E-3</v>
+      </c>
+      <c r="I1099" s="8">
+        <v>1.1342592592592593E-3</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1100" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1100">
+        <v>14</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1100">
+        <v>605</v>
+      </c>
+      <c r="H1100" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1100" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1101" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1101">
+        <v>14</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1101" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1101">
+        <v>144</v>
+      </c>
+      <c r="H1101" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1101" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1102" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1102">
+        <v>14</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1102">
+        <v>97</v>
+      </c>
+      <c r="H1102" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1102" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1103" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1103">
+        <v>14</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1103">
+        <v>1</v>
+      </c>
+      <c r="H1103" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1103" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1104" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1104">
+        <v>14</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1104">
+        <v>1834</v>
+      </c>
+      <c r="H1104" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1104" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1105" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1105">
+        <v>14</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1105" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1105">
+        <v>1336</v>
+      </c>
+      <c r="H1105" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1105" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1106" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1106">
+        <v>14</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1106" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1106">
+        <v>1</v>
+      </c>
+      <c r="H1106" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I1106" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1107" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1107">
+        <v>14</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1107" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1107">
+        <v>2</v>
+      </c>
+      <c r="H1107" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1107" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1108" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1108">
+        <v>14</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1108">
+        <v>7</v>
+      </c>
+      <c r="H1108" s="8">
+        <v>1.4236111111111112E-3</v>
+      </c>
+      <c r="I1108" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1109" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1109">
+        <v>14</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1109">
+        <v>1</v>
+      </c>
+      <c r="H1109" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I1109" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1110" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1110">
+        <v>14</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1110">
+        <v>685</v>
+      </c>
+      <c r="H1110" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1110" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1111" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1111">
+        <v>14</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1111">
+        <v>3</v>
+      </c>
+      <c r="H1111" s="8">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="I1111" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1112" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1112">
+        <v>14</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1112" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1112">
+        <v>6</v>
+      </c>
+      <c r="H1112" s="8">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="I1112" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1113" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1113">
+        <v>14</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1113" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1113">
+        <v>33</v>
+      </c>
+      <c r="H1113" s="8">
+        <v>4.2824074074074075E-3</v>
+      </c>
+      <c r="I1113" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1114" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1114">
+        <v>14</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1114" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1114">
+        <v>88</v>
+      </c>
+      <c r="H1114" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1114" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1115" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1115">
+        <v>14</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1115" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1115" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1115">
+        <v>1</v>
+      </c>
+      <c r="H1115" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="I1115" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1116" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1116">
+        <v>14</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1116" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1116">
+        <v>1</v>
+      </c>
+      <c r="H1116" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1116" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1117" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1117">
+        <v>14</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1117" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1117" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1117">
+        <v>3</v>
+      </c>
+      <c r="H1117" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="I1117" s="8">
+        <v>1.3888888888888889E-4</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AF25E1-D92B-429D-8953-C81ED8DF8DA7}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8B8C2A-1DE5-4C12-961E-C0A3DB9478A8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4836" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="93">
   <si>
     <t>Dt</t>
   </si>
@@ -708,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V239"/>
+  <dimension ref="A1:V241"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -14529,7 +14529,7 @@
         <v>15</v>
       </c>
       <c r="F227" s="1">
-        <v>44685</v>
+        <v>51945</v>
       </c>
       <c r="G227" s="1">
         <v>18461</v>
@@ -14565,7 +14565,7 @@
         <v>0.6</v>
       </c>
       <c r="S227" s="1">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="V227" s="2">
         <v>45.8172</v>
@@ -14656,7 +14656,7 @@
         <v>12</v>
       </c>
       <c r="F229" s="1">
-        <v>44685</v>
+        <v>51945</v>
       </c>
       <c r="G229" s="1">
         <v>19205</v>
@@ -14692,7 +14692,7 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="S229" s="1">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="V229" s="2">
         <v>36.233600000000003</v>
@@ -14783,7 +14783,7 @@
         <v>11</v>
       </c>
       <c r="F231" s="1">
-        <v>44685</v>
+        <v>51945</v>
       </c>
       <c r="G231" s="1">
         <v>32437</v>
@@ -14819,7 +14819,7 @@
         <v>0.375</v>
       </c>
       <c r="S231" s="1">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="V231" s="2">
         <v>42.468400000000003</v>
@@ -14910,7 +14910,7 @@
         <v>10</v>
       </c>
       <c r="F233" s="1">
-        <v>44685</v>
+        <v>51945</v>
       </c>
       <c r="G233" s="1">
         <v>23820</v>
@@ -14946,7 +14946,7 @@
         <v>0.5</v>
       </c>
       <c r="S233" s="1">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="V233" s="2">
         <v>39.889200000000002</v>
@@ -15037,7 +15037,7 @@
         <v>9</v>
       </c>
       <c r="F235" s="1">
-        <v>44685</v>
+        <v>51945</v>
       </c>
       <c r="G235" s="1">
         <v>32308</v>
@@ -15073,7 +15073,7 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="S235" s="1">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="V235" s="2">
         <v>36.5456</v>
@@ -15164,7 +15164,7 @@
         <v>9</v>
       </c>
       <c r="F237" s="1">
-        <v>44685</v>
+        <v>51945</v>
       </c>
       <c r="G237" s="1">
         <v>42045</v>
@@ -15200,7 +15200,7 @@
         <v>0.36359999999999998</v>
       </c>
       <c r="S237" s="1">
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
       <c r="V237" s="2">
         <v>67.641599999999997</v>
@@ -15220,25 +15220,25 @@
         <v>30</v>
       </c>
       <c r="E238" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F238" s="1">
         <v>24959</v>
       </c>
       <c r="G238" s="1">
-        <v>4844</v>
+        <v>37344</v>
       </c>
       <c r="H238" s="1">
-        <v>52</v>
+        <v>268</v>
       </c>
       <c r="I238" s="1">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="J238" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K238" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L238" s="1">
         <v>0</v>
@@ -15247,13 +15247,13 @@
         <v>0</v>
       </c>
       <c r="N238" s="4">
-        <v>1.6203703703703703E-4</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="O238" s="4">
-        <v>2.3148148148148149E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="P238" s="5">
-        <v>1.0699999999999999E-2</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="Q238" s="6">
         <v>0</v>
@@ -15262,16 +15262,16 @@
         <v>20</v>
       </c>
       <c r="S238" s="1">
-        <v>0.19</v>
+        <v>1.5</v>
       </c>
       <c r="T238" s="6">
-        <v>0.25</v>
+        <v>5.5599999999999997E-2</v>
       </c>
       <c r="U238" s="5">
-        <v>0.16669999999999999</v>
+        <v>0.1739</v>
       </c>
       <c r="V238" s="2">
-        <v>7.7896000000000001</v>
+        <v>45.968000000000004</v>
       </c>
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.3">
@@ -15288,19 +15288,19 @@
         <v>0</v>
       </c>
       <c r="E239" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F239" s="1">
-        <v>44685</v>
+        <v>51945</v>
       </c>
       <c r="G239" s="1">
-        <v>12108</v>
+        <v>38980</v>
       </c>
       <c r="H239" s="1">
-        <v>119</v>
+        <v>437</v>
       </c>
       <c r="I239" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J239" s="1">
         <v>0</v>
@@ -15312,25 +15312,152 @@
         <v>0</v>
       </c>
       <c r="M239" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O239" s="4">
-        <v>1.9675925925925926E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="P239" s="5">
-        <v>9.7999999999999997E-3</v>
+        <v>1.12E-2</v>
       </c>
       <c r="Q239" s="5">
-        <v>8.3999999999999995E-3</v>
+        <v>1.83E-2</v>
       </c>
       <c r="R239" s="6">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="S239" s="1">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="V239" s="2">
-        <v>18.688800000000001</v>
+        <v>62.259599999999999</v>
+      </c>
+    </row>
+    <row r="240" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A240" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B240" s="1">
+        <v>15</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D240" s="1">
+        <v>30</v>
+      </c>
+      <c r="E240" s="1">
+        <v>3</v>
+      </c>
+      <c r="F240" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G240" s="1">
+        <v>16490</v>
+      </c>
+      <c r="H240" s="1">
+        <v>142</v>
+      </c>
+      <c r="I240" s="1">
+        <v>10</v>
+      </c>
+      <c r="J240" s="1">
+        <v>3</v>
+      </c>
+      <c r="K240" s="1">
+        <v>7</v>
+      </c>
+      <c r="L240" s="1">
+        <v>2</v>
+      </c>
+      <c r="M240" s="1">
+        <v>2</v>
+      </c>
+      <c r="N240" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="O240" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P240" s="5">
+        <v>8.6E-3</v>
+      </c>
+      <c r="Q240" s="5">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="R240" s="6">
+        <v>1</v>
+      </c>
+      <c r="S240" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="T240" s="6">
+        <v>0</v>
+      </c>
+      <c r="U240" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="V240" s="2">
+        <v>24.0916</v>
+      </c>
+    </row>
+    <row r="241" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A241" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B241" s="1">
+        <v>15</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D241" s="1">
+        <v>0</v>
+      </c>
+      <c r="E241" s="1">
+        <v>9</v>
+      </c>
+      <c r="F241" s="1">
+        <v>51945</v>
+      </c>
+      <c r="G241" s="1">
+        <v>27704</v>
+      </c>
+      <c r="H241" s="1">
+        <v>276</v>
+      </c>
+      <c r="I241" s="1">
+        <v>2</v>
+      </c>
+      <c r="J241" s="1">
+        <v>0</v>
+      </c>
+      <c r="K241" s="1">
+        <v>0</v>
+      </c>
+      <c r="L241" s="1">
+        <v>0</v>
+      </c>
+      <c r="M241" s="1">
+        <v>0</v>
+      </c>
+      <c r="O241" s="4">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P241" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="Q241" s="5">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R241" s="6">
+        <v>0</v>
+      </c>
+      <c r="S241" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="V241" s="2">
+        <v>29.718</v>
       </c>
     </row>
   </sheetData>
@@ -15341,7 +15468,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I1117"/>
+  <dimension ref="A1:I1159"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -47240,13 +47367,13 @@
         <v>86</v>
       </c>
       <c r="E1100" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1100" t="s">
         <v>6</v>
       </c>
       <c r="G1100">
-        <v>605</v>
+        <v>871</v>
       </c>
       <c r="H1100" s="8">
         <v>0</v>
@@ -47269,13 +47396,13 @@
         <v>86</v>
       </c>
       <c r="E1101" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F1101" t="s">
         <v>6</v>
       </c>
       <c r="G1101">
-        <v>144</v>
+        <v>400</v>
       </c>
       <c r="H1101" s="8">
         <v>0</v>
@@ -47298,13 +47425,13 @@
         <v>86</v>
       </c>
       <c r="E1102" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F1102" t="s">
         <v>6</v>
       </c>
       <c r="G1102">
-        <v>97</v>
+        <v>3426</v>
       </c>
       <c r="H1102" s="8">
         <v>0</v>
@@ -47327,13 +47454,13 @@
         <v>86</v>
       </c>
       <c r="E1103" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F1103" t="s">
         <v>6</v>
       </c>
       <c r="G1103">
-        <v>1</v>
+        <v>10133</v>
       </c>
       <c r="H1103" s="8">
         <v>0</v>
@@ -47356,13 +47483,13 @@
         <v>86</v>
       </c>
       <c r="E1104" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F1104" t="s">
         <v>6</v>
       </c>
       <c r="G1104">
-        <v>1834</v>
+        <v>8</v>
       </c>
       <c r="H1104" s="8">
         <v>0</v>
@@ -47391,7 +47518,7 @@
         <v>6</v>
       </c>
       <c r="G1105">
-        <v>1336</v>
+        <v>18007</v>
       </c>
       <c r="H1105" s="8">
         <v>0</v>
@@ -47414,19 +47541,19 @@
         <v>86</v>
       </c>
       <c r="E1106" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F1106" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G1106">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1106" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>0</v>
       </c>
       <c r="I1106" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1107" spans="1:9" x14ac:dyDescent="0.3">
@@ -47443,19 +47570,19 @@
         <v>86</v>
       </c>
       <c r="E1107" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F1107" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G1107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1107" s="8">
-        <v>0</v>
+        <v>4.3981481481481481E-4</v>
       </c>
       <c r="I1107" s="8">
-        <v>0</v>
+        <v>4.3981481481481481E-4</v>
       </c>
     </row>
     <row r="1108" spans="1:9" x14ac:dyDescent="0.3">
@@ -47472,19 +47599,19 @@
         <v>86</v>
       </c>
       <c r="E1108" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F1108" t="s">
         <v>37</v>
       </c>
       <c r="G1108">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1108" s="8">
-        <v>1.4236111111111112E-3</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="I1108" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>2.6620370370370372E-4</v>
       </c>
     </row>
     <row r="1109" spans="1:9" x14ac:dyDescent="0.3">
@@ -47507,13 +47634,13 @@
         <v>88</v>
       </c>
       <c r="G1109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1109" s="8">
-        <v>4.3981481481481481E-4</v>
+        <v>6.3657407407407413E-4</v>
       </c>
       <c r="I1109" s="8">
-        <v>4.3981481481481481E-4</v>
+        <v>1.5046296296296297E-4</v>
       </c>
     </row>
     <row r="1110" spans="1:9" x14ac:dyDescent="0.3">
@@ -47530,19 +47657,19 @@
         <v>86</v>
       </c>
       <c r="E1110" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F1110" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G1110">
-        <v>685</v>
+        <v>1</v>
       </c>
       <c r="H1110" s="8">
-        <v>0</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I1110" s="8">
-        <v>0</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="1111" spans="1:9" x14ac:dyDescent="0.3">
@@ -47559,19 +47686,19 @@
         <v>86</v>
       </c>
       <c r="E1111" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F1111" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G1111">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H1111" s="8">
-        <v>7.0601851851851847E-4</v>
+        <v>6.9560185185185185E-3</v>
       </c>
       <c r="I1111" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="1112" spans="1:9" x14ac:dyDescent="0.3">
@@ -47588,19 +47715,19 @@
         <v>86</v>
       </c>
       <c r="E1112" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F1112" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1112">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1112" s="8">
-        <v>1.4467592592592592E-3</v>
+        <v>3.7037037037037035E-4</v>
       </c>
       <c r="I1112" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>3.7037037037037035E-4</v>
       </c>
     </row>
     <row r="1113" spans="1:9" x14ac:dyDescent="0.3">
@@ -47617,19 +47744,19 @@
         <v>86</v>
       </c>
       <c r="E1113" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1113" t="s">
         <v>37</v>
       </c>
       <c r="G1113">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H1113" s="8">
-        <v>4.2824074074074075E-3</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="I1113" s="8">
-        <v>1.273148148148148E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
     </row>
     <row r="1114" spans="1:9" x14ac:dyDescent="0.3">
@@ -47646,19 +47773,19 @@
         <v>86</v>
       </c>
       <c r="E1114" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F1114" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G1114">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="H1114" s="8">
-        <v>0</v>
+        <v>4.3981481481481481E-4</v>
       </c>
       <c r="I1114" s="8">
-        <v>0</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="1115" spans="1:9" x14ac:dyDescent="0.3">
@@ -47672,22 +47799,22 @@
         <v>17</v>
       </c>
       <c r="D1115" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1115" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F1115" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G1115">
         <v>1</v>
       </c>
       <c r="H1115" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="I1115" s="8">
-        <v>3.2407407407407406E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
     </row>
     <row r="1116" spans="1:9" x14ac:dyDescent="0.3">
@@ -47701,19 +47828,22 @@
         <v>17</v>
       </c>
       <c r="D1116" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1116" t="s">
-        <v>92</v>
+        <v>41</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>88</v>
       </c>
       <c r="G1116">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1116" s="8">
-        <v>0</v>
+        <v>1.3425925925925925E-3</v>
       </c>
       <c r="I1116" s="8">
-        <v>0</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="1117" spans="1:9" x14ac:dyDescent="0.3">
@@ -47727,22 +47857,1237 @@
         <v>17</v>
       </c>
       <c r="D1117" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1117" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F1117" t="s">
         <v>37</v>
       </c>
       <c r="G1117">
+        <v>7</v>
+      </c>
+      <c r="H1117" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="I1117" s="8">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1118" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1118">
+        <v>14</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1118">
+        <v>6</v>
+      </c>
+      <c r="H1118" s="8">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="I1118" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1119" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1119">
+        <v>14</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1119" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1119">
+        <v>2</v>
+      </c>
+      <c r="H1119" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I1119" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1120" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1120">
+        <v>14</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1120" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1120">
+        <v>1</v>
+      </c>
+      <c r="H1120" s="8">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="I1120" s="8">
+        <v>8.6805555555555551E-4</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1121" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1121">
+        <v>14</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1121" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1121">
+        <v>1</v>
+      </c>
+      <c r="H1121" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I1121" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1122" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1122">
+        <v>14</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1122" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1122">
+        <v>1</v>
+      </c>
+      <c r="H1122" s="8">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="I1122" s="8">
+        <v>6.7129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1123" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1123">
+        <v>14</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1123" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1123">
+        <v>1</v>
+      </c>
+      <c r="H1123" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1123" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1124" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1124">
+        <v>14</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1124" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1124">
+        <v>16</v>
+      </c>
+      <c r="H1124" s="8">
+        <v>4.3287037037037035E-3</v>
+      </c>
+      <c r="I1124" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1125" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1125">
+        <v>14</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1125" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1125">
+        <v>192</v>
+      </c>
+      <c r="H1125" s="8">
+        <v>2.0520833333333332E-2</v>
+      </c>
+      <c r="I1125" s="8">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1126" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1126">
+        <v>14</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1126" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1126">
+        <v>3661</v>
+      </c>
+      <c r="H1126" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1126" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1127" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1127">
+        <v>14</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1127" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1127" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1127">
+        <v>566</v>
+      </c>
+      <c r="H1127" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1127" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1128" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1128">
+        <v>14</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1128" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1128" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1128">
+        <v>6</v>
+      </c>
+      <c r="H1128" s="8">
+        <v>3.0439814814814813E-3</v>
+      </c>
+      <c r="I1128" s="8">
+        <v>4.9768518518518521E-4</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1129" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1129">
+        <v>14</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1129">
+        <v>1</v>
+      </c>
+      <c r="H1129" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I1129" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1130" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1130">
+        <v>14</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1130" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1130" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1130" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1130">
+        <v>6</v>
+      </c>
+      <c r="H1130" s="8">
+        <v>1.238425925925926E-3</v>
+      </c>
+      <c r="I1130" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1131" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1131">
+        <v>15</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1131" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1131">
+        <v>415</v>
+      </c>
+      <c r="H1131" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1131" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1132" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1132">
+        <v>15</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1132" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1132">
+        <v>1942</v>
+      </c>
+      <c r="H1132" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1132" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1133" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1133">
+        <v>15</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1133" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1133" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1133">
+        <v>4914</v>
+      </c>
+      <c r="H1133" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1133" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1134" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1134">
+        <v>15</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1134" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1134">
+        <v>165</v>
+      </c>
+      <c r="H1134" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1134" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1135" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1135">
+        <v>15</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1135" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1135">
+        <v>6783</v>
+      </c>
+      <c r="H1135" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1135" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1136" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1136">
+        <v>15</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1136" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1136" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1136">
+        <v>5</v>
+      </c>
+      <c r="H1136" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1136" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1137" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1137">
+        <v>15</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1137" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1137" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1137">
+        <v>4</v>
+      </c>
+      <c r="H1137" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1137" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1138" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1138">
+        <v>15</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1138">
+        <v>2</v>
+      </c>
+      <c r="H1138" s="8">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="I1138" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1139" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1139">
+        <v>15</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1139" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1139">
+        <v>1</v>
+      </c>
+      <c r="H1139" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1139" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1140" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1140">
+        <v>15</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1140" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1140">
         <v>3</v>
       </c>
-      <c r="H1117" s="8">
-        <v>4.1666666666666669E-4</v>
-      </c>
-      <c r="I1117" s="8">
-        <v>1.3888888888888889E-4</v>
+      <c r="H1140" s="8">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="I1140" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1141" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1141">
+        <v>15</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1141" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1141" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1141">
+        <v>1</v>
+      </c>
+      <c r="H1141" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I1141" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1142" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1142">
+        <v>15</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1142" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1142">
+        <v>1</v>
+      </c>
+      <c r="H1142" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I1142" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1143" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1143">
+        <v>15</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1143" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1143">
+        <v>1</v>
+      </c>
+      <c r="H1143" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I1143" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1144" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1144">
+        <v>15</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1144" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1144">
+        <v>1</v>
+      </c>
+      <c r="H1144" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="I1144" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1145" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1145">
+        <v>15</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1145">
+        <v>1</v>
+      </c>
+      <c r="H1145" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I1145" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1146" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1146">
+        <v>15</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1146">
+        <v>1</v>
+      </c>
+      <c r="H1146" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="I1146" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1147" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1147">
+        <v>15</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1147" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1147" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1147">
+        <v>1</v>
+      </c>
+      <c r="H1147" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="I1147" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1148" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1148">
+        <v>15</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1148" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1148">
+        <v>4</v>
+      </c>
+      <c r="H1148" s="8">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="I1148" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1149" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1149">
+        <v>15</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1149">
+        <v>2</v>
+      </c>
+      <c r="H1149" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="I1149" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1150" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1150">
+        <v>15</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1150" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1150">
+        <v>4</v>
+      </c>
+      <c r="H1150" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I1150" s="8">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1151" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1151">
+        <v>15</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1151" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1151">
+        <v>17</v>
+      </c>
+      <c r="H1151" s="8">
+        <v>4.1203703703703706E-3</v>
+      </c>
+      <c r="I1151" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1152" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1152">
+        <v>15</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1152" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1152">
+        <v>1</v>
+      </c>
+      <c r="H1152" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I1152" s="8">
+        <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1153" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1153">
+        <v>15</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1153" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1153">
+        <v>103</v>
+      </c>
+      <c r="H1153" s="8">
+        <v>9.8958333333333329E-3</v>
+      </c>
+      <c r="I1153" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1154" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1154">
+        <v>15</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1154" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1154">
+        <v>1808</v>
+      </c>
+      <c r="H1154" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1154" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1155" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1155">
+        <v>15</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1155" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1155">
+        <v>311</v>
+      </c>
+      <c r="H1155" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1155" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1156" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1156">
+        <v>15</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1156" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1156">
+        <v>2</v>
+      </c>
+      <c r="H1156" s="8">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="I1156" s="8">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1157" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1157">
+        <v>15</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1157" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1157">
+        <v>2</v>
+      </c>
+      <c r="H1157" s="8">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="I1157" s="8">
+        <v>5.6712962962962967E-4</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1158" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1158">
+        <v>15</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1158" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1158">
+        <v>1</v>
+      </c>
+      <c r="H1158" s="8">
+        <v>7.8703703703703696E-3</v>
+      </c>
+      <c r="I1158" s="8">
+        <v>7.8703703703703696E-3</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1159" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1159">
+        <v>15</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1159" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1159">
+        <v>1</v>
+      </c>
+      <c r="H1159" s="8">
+        <v>3.7268518518518519E-3</v>
+      </c>
+      <c r="I1159" s="8">
+        <v>3.7268518518518519E-3</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8B8C2A-1DE5-4C12-961E-C0A3DB9478A8}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4E9247-2EE5-4535-AE64-4A0C2721070E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="93">
   <si>
     <t>Dt</t>
   </si>
@@ -708,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V241"/>
+  <dimension ref="A1:V243"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -15353,52 +15353,52 @@
         <v>24959</v>
       </c>
       <c r="G240" s="1">
-        <v>16490</v>
+        <v>22428</v>
       </c>
       <c r="H240" s="1">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="I240" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J240" s="1">
+        <v>5</v>
+      </c>
+      <c r="K240" s="1">
+        <v>9</v>
+      </c>
+      <c r="L240" s="1">
         <v>3</v>
       </c>
-      <c r="K240" s="1">
-        <v>7</v>
-      </c>
-      <c r="L240" s="1">
-        <v>2</v>
-      </c>
       <c r="M240" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N240" s="4">
         <v>1.273148148148148E-4</v>
       </c>
       <c r="O240" s="4">
-        <v>2.199074074074074E-4</v>
+        <v>2.3148148148148149E-4</v>
       </c>
       <c r="P240" s="5">
-        <v>8.6E-3</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="Q240" s="5">
-        <v>0.28570000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="R240" s="6">
         <v>1</v>
       </c>
       <c r="S240" s="1">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="T240" s="6">
         <v>0</v>
       </c>
       <c r="U240" s="6">
-        <v>0.3</v>
+        <v>0.35709999999999997</v>
       </c>
       <c r="V240" s="2">
-        <v>24.0916</v>
+        <v>32.224400000000003</v>
       </c>
     </row>
     <row r="241" spans="1:22" x14ac:dyDescent="0.3">
@@ -15421,13 +15421,13 @@
         <v>51945</v>
       </c>
       <c r="G241" s="1">
-        <v>27704</v>
+        <v>40220</v>
       </c>
       <c r="H241" s="1">
-        <v>276</v>
+        <v>408</v>
       </c>
       <c r="I241" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J241" s="1">
         <v>0</v>
@@ -15439,25 +15439,152 @@
         <v>0</v>
       </c>
       <c r="M241" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P241" s="6">
+        <v>1.01E-2</v>
+      </c>
+      <c r="Q241" s="5">
+        <v>1.47E-2</v>
+      </c>
+      <c r="R241" s="6">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="S241" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="V241" s="2">
+        <v>50.689599999999999</v>
+      </c>
+    </row>
+    <row r="242" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A242" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B242" s="1">
+        <v>16</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D242" s="1">
+        <v>25</v>
+      </c>
+      <c r="E242" s="1">
+        <v>0</v>
+      </c>
+      <c r="F242" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G242" s="1">
+        <v>2292</v>
+      </c>
+      <c r="H242" s="1">
+        <v>25</v>
+      </c>
+      <c r="I242" s="1">
+        <v>0</v>
+      </c>
+      <c r="J242" s="1">
+        <v>0</v>
+      </c>
+      <c r="K242" s="1">
+        <v>0</v>
+      </c>
+      <c r="L242" s="1">
+        <v>0</v>
+      </c>
+      <c r="M242" s="1">
+        <v>0</v>
+      </c>
+      <c r="N242" s="4">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="P241" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="Q241" s="5">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="R241" s="6">
-        <v>0</v>
-      </c>
-      <c r="S241" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="V241" s="2">
-        <v>29.718</v>
+      <c r="O242" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P242" s="5">
+        <v>1.09E-2</v>
+      </c>
+      <c r="Q242" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R242" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S242" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="T242" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U242" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V242" s="2">
+        <v>2.7143999999999999</v>
+      </c>
+    </row>
+    <row r="243" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A243" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B243" s="1">
+        <v>16</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D243" s="1">
+        <v>0</v>
+      </c>
+      <c r="E243" s="1">
+        <v>9</v>
+      </c>
+      <c r="F243" s="1">
+        <v>51945</v>
+      </c>
+      <c r="G243" s="1">
+        <v>13512</v>
+      </c>
+      <c r="H243" s="1">
+        <v>191</v>
+      </c>
+      <c r="I243" s="1">
+        <v>1</v>
+      </c>
+      <c r="J243" s="1">
+        <v>0</v>
+      </c>
+      <c r="K243" s="1">
+        <v>0</v>
+      </c>
+      <c r="L243" s="1">
+        <v>0</v>
+      </c>
+      <c r="M243" s="1">
+        <v>0</v>
+      </c>
+      <c r="O243" s="4">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P243" s="5">
+        <v>1.41E-2</v>
+      </c>
+      <c r="Q243" s="5">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="R243" s="6">
+        <v>0</v>
+      </c>
+      <c r="S243" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="V243" s="2">
+        <v>20.113600000000002</v>
       </c>
     </row>
   </sheetData>
@@ -15468,7 +15595,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I1159"/>
+  <dimension ref="A1:I1174"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -48263,13 +48390,13 @@
         <v>86</v>
       </c>
       <c r="E1131" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1131" t="s">
         <v>6</v>
       </c>
       <c r="G1131">
-        <v>415</v>
+        <v>2313</v>
       </c>
       <c r="H1131" s="8">
         <v>0</v>
@@ -48292,13 +48419,13 @@
         <v>86</v>
       </c>
       <c r="E1132" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1132" t="s">
         <v>6</v>
       </c>
       <c r="G1132">
-        <v>1942</v>
+        <v>565</v>
       </c>
       <c r="H1132" s="8">
         <v>0</v>
@@ -48321,13 +48448,13 @@
         <v>86</v>
       </c>
       <c r="E1133" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F1133" t="s">
         <v>6</v>
       </c>
       <c r="G1133">
-        <v>4914</v>
+        <v>237</v>
       </c>
       <c r="H1133" s="8">
         <v>0</v>
@@ -48350,13 +48477,13 @@
         <v>86</v>
       </c>
       <c r="E1134" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F1134" t="s">
         <v>6</v>
       </c>
       <c r="G1134">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="H1134" s="8">
         <v>0</v>
@@ -48379,13 +48506,13 @@
         <v>86</v>
       </c>
       <c r="E1135" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1135" t="s">
         <v>6</v>
       </c>
       <c r="G1135">
-        <v>6783</v>
+        <v>6575</v>
       </c>
       <c r="H1135" s="8">
         <v>0</v>
@@ -48408,19 +48535,19 @@
         <v>86</v>
       </c>
       <c r="E1136" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1136" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="G1136">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1136" s="8">
-        <v>0</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="I1136" s="8">
-        <v>0</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="1137" spans="1:9" x14ac:dyDescent="0.3">
@@ -48437,13 +48564,13 @@
         <v>86</v>
       </c>
       <c r="E1137" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F1137" t="s">
         <v>6</v>
       </c>
       <c r="G1137">
-        <v>4</v>
+        <v>9687</v>
       </c>
       <c r="H1137" s="8">
         <v>0</v>
@@ -48495,13 +48622,13 @@
         <v>86</v>
       </c>
       <c r="E1139" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1139" t="s">
         <v>6</v>
       </c>
       <c r="G1139">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1139" s="8">
         <v>0</v>
@@ -48530,13 +48657,13 @@
         <v>88</v>
       </c>
       <c r="G1140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1140" s="8">
-        <v>6.9444444444444447E-4</v>
+        <v>6.4814814814814813E-4</v>
       </c>
       <c r="I1140" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
     </row>
     <row r="1141" spans="1:9" x14ac:dyDescent="0.3">
@@ -48553,19 +48680,19 @@
         <v>86</v>
       </c>
       <c r="E1141" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F1141" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G1141">
         <v>1</v>
       </c>
       <c r="H1141" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>0</v>
       </c>
       <c r="I1141" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1142" spans="1:9" x14ac:dyDescent="0.3">
@@ -48611,19 +48738,19 @@
         <v>86</v>
       </c>
       <c r="E1143" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F1143" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G1143">
         <v>1</v>
       </c>
       <c r="H1143" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="I1143" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
     </row>
     <row r="1144" spans="1:9" x14ac:dyDescent="0.3">
@@ -48678,10 +48805,10 @@
         <v>1</v>
       </c>
       <c r="H1145" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="I1145" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>2.199074074074074E-4</v>
       </c>
     </row>
     <row r="1146" spans="1:9" x14ac:dyDescent="0.3">
@@ -48733,13 +48860,13 @@
         <v>88</v>
       </c>
       <c r="G1147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1147" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I1147" s="8">
-        <v>2.5462962962962961E-4</v>
+        <v>1.9675925925925926E-4</v>
       </c>
     </row>
     <row r="1148" spans="1:9" x14ac:dyDescent="0.3">
@@ -48756,19 +48883,19 @@
         <v>86</v>
       </c>
       <c r="E1148" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F1148" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G1148">
-        <v>4</v>
+        <v>2437</v>
       </c>
       <c r="H1148" s="8">
-        <v>6.4814814814814813E-4</v>
+        <v>0</v>
       </c>
       <c r="I1148" s="8">
-        <v>1.6203703703703703E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1149" spans="1:9" x14ac:dyDescent="0.3">
@@ -48791,13 +48918,13 @@
         <v>88</v>
       </c>
       <c r="G1149">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1149" s="8">
-        <v>4.0509259259259258E-4</v>
+        <v>9.6064814814814819E-4</v>
       </c>
       <c r="I1149" s="8">
-        <v>1.9675925925925926E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="1150" spans="1:9" x14ac:dyDescent="0.3">
@@ -48814,19 +48941,19 @@
         <v>86</v>
       </c>
       <c r="E1150" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F1150" t="s">
         <v>37</v>
       </c>
       <c r="G1150">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H1150" s="8">
-        <v>2.6620370370370372E-4</v>
+        <v>5.7523148148148151E-3</v>
       </c>
       <c r="I1150" s="8">
-        <v>5.7870370370370373E-5</v>
+        <v>2.4305555555555555E-4</v>
       </c>
     </row>
     <row r="1151" spans="1:9" x14ac:dyDescent="0.3">
@@ -48843,19 +48970,19 @@
         <v>86</v>
       </c>
       <c r="E1151" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F1151" t="s">
         <v>37</v>
       </c>
       <c r="G1151">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H1151" s="8">
-        <v>4.1203703703703706E-3</v>
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="I1151" s="8">
-        <v>2.3148148148148149E-4</v>
+        <v>6.5972222222222224E-4</v>
       </c>
     </row>
     <row r="1152" spans="1:9" x14ac:dyDescent="0.3">
@@ -48869,22 +48996,22 @@
         <v>17</v>
       </c>
       <c r="D1152" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1152" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F1152" t="s">
         <v>37</v>
       </c>
       <c r="G1152">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1152" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>1.1226851851851851E-3</v>
       </c>
       <c r="I1152" s="8">
-        <v>2.199074074074074E-4</v>
+        <v>1.8518518518518518E-4</v>
       </c>
     </row>
     <row r="1153" spans="1:9" x14ac:dyDescent="0.3">
@@ -48907,10 +49034,10 @@
         <v>37</v>
       </c>
       <c r="G1153">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="H1153" s="8">
-        <v>9.8958333333333329E-3</v>
+        <v>1.4282407407407407E-2</v>
       </c>
       <c r="I1153" s="8">
         <v>9.2592592592592588E-5</v>
@@ -48930,19 +49057,19 @@
         <v>86</v>
       </c>
       <c r="E1154" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F1154" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G1154">
-        <v>1808</v>
+        <v>1</v>
       </c>
       <c r="H1154" s="8">
-        <v>0</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="I1154" s="8">
-        <v>0</v>
+        <v>4.5138888888888887E-4</v>
       </c>
     </row>
     <row r="1155" spans="1:9" x14ac:dyDescent="0.3">
@@ -48959,19 +49086,19 @@
         <v>86</v>
       </c>
       <c r="E1155" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F1155" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1155">
         <v>6</v>
       </c>
-      <c r="G1155">
-        <v>311</v>
-      </c>
       <c r="H1155" s="8">
-        <v>0</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="I1155" s="8">
-        <v>0</v>
+        <v>4.6296296296296294E-5</v>
       </c>
     </row>
     <row r="1156" spans="1:9" x14ac:dyDescent="0.3">
@@ -48985,22 +49112,22 @@
         <v>17</v>
       </c>
       <c r="D1156" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1156" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F1156" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G1156">
-        <v>2</v>
+        <v>396</v>
       </c>
       <c r="H1156" s="8">
-        <v>1.0185185185185184E-3</v>
+        <v>0</v>
       </c>
       <c r="I1156" s="8">
-        <v>5.0925925925925921E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1157" spans="1:9" x14ac:dyDescent="0.3">
@@ -49017,7 +49144,7 @@
         <v>87</v>
       </c>
       <c r="E1157" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F1157" t="s">
         <v>37</v>
@@ -49026,10 +49153,10 @@
         <v>2</v>
       </c>
       <c r="H1157" s="8">
-        <v>1.1458333333333333E-3</v>
+        <v>1.0185185185185184E-3</v>
       </c>
       <c r="I1157" s="8">
-        <v>5.6712962962962967E-4</v>
+        <v>5.0925925925925921E-4</v>
       </c>
     </row>
     <row r="1158" spans="1:9" x14ac:dyDescent="0.3">
@@ -49046,19 +49173,19 @@
         <v>87</v>
       </c>
       <c r="E1158" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F1158" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G1158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1158" s="8">
-        <v>7.8703703703703696E-3</v>
+        <v>1.1458333333333333E-3</v>
       </c>
       <c r="I1158" s="8">
-        <v>7.8703703703703696E-3</v>
+        <v>5.6712962962962967E-4</v>
       </c>
     </row>
     <row r="1159" spans="1:9" x14ac:dyDescent="0.3">
@@ -49075,7 +49202,7 @@
         <v>87</v>
       </c>
       <c r="E1159" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F1159" t="s">
         <v>11</v>
@@ -49084,10 +49211,445 @@
         <v>1</v>
       </c>
       <c r="H1159" s="8">
-        <v>3.7268518518518519E-3</v>
+        <v>7.8703703703703696E-3</v>
       </c>
       <c r="I1159" s="8">
-        <v>3.7268518518518519E-3</v>
+        <v>7.8703703703703696E-3</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1160" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1160">
+        <v>15</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1160" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1160" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1160">
+        <v>2</v>
+      </c>
+      <c r="H1160" s="8">
+        <v>7.1759259259259259E-3</v>
+      </c>
+      <c r="I1160" s="8">
+        <v>3.5879629629629629E-3</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1161" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1161">
+        <v>15</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1161">
+        <v>2</v>
+      </c>
+      <c r="H1161" s="8">
+        <v>2.627314814814815E-3</v>
+      </c>
+      <c r="I1161" s="8">
+        <v>1.3078703703703703E-3</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1162" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1162">
+        <v>16</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1162" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1162">
+        <v>39</v>
+      </c>
+      <c r="H1162" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1162" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1163" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1163">
+        <v>16</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1163" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1163" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1163">
+        <v>29</v>
+      </c>
+      <c r="H1163" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1163" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1164" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1164">
+        <v>16</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1164" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1164" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1164" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1164">
+        <v>153</v>
+      </c>
+      <c r="H1164" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1164" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1165" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1165">
+        <v>16</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1165" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1165">
+        <v>634</v>
+      </c>
+      <c r="H1165" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1165" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1166" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1166">
+        <v>16</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1166" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1166" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1166">
+        <v>1</v>
+      </c>
+      <c r="H1166" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1166" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1167" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1167">
+        <v>16</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1167" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1167" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1167" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1167">
+        <v>1114</v>
+      </c>
+      <c r="H1167" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1167" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1168" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1168">
+        <v>16</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1168" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1168" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1168">
+        <v>1</v>
+      </c>
+      <c r="H1168" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1168" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1169" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1169">
+        <v>16</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1169" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1169" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1169">
+        <v>4</v>
+      </c>
+      <c r="H1169" s="8">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="I1169" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1170" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1170">
+        <v>16</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1170">
+        <v>1</v>
+      </c>
+      <c r="H1170" s="8">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="I1170" s="8">
+        <v>6.8287037037037036E-4</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1171" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1171">
+        <v>16</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1171">
+        <v>1</v>
+      </c>
+      <c r="H1171" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I1171" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1172" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1172">
+        <v>16</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1172" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1172">
+        <v>36</v>
+      </c>
+      <c r="H1172" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1172" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1173" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1173">
+        <v>16</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1173" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1173">
+        <v>19</v>
+      </c>
+      <c r="H1173" s="8">
+        <v>2.5347222222222221E-3</v>
+      </c>
+      <c r="I1173" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1174" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1174">
+        <v>16</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1174">
+        <v>260</v>
+      </c>
+      <c r="H1174" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1174" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
+++ b/locator_dashboard_flask_v30_tabulacao/data/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Painel/Python/Locator Via Varejo/locator_dashboard_flask_v30_tabulacao/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4E9247-2EE5-4535-AE64-4A0C2721070E}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="8_{C09F9109-FE61-4B56-A24F-C26051BBB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4B74FB2-A9B0-4474-91C9-80F20D6B384E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758EAD73-15E9-4EFA-B679-F151814EE151}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5380" uniqueCount="94">
   <si>
     <t>Dt</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>NoAgents</t>
+  </si>
+  <si>
+    <t>Ativo - Sem previsao de Pagamento - Sem interesse em negociar</t>
   </si>
 </sst>
 </file>
@@ -708,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019BF8A7-7707-48AF-9F4A-92FA2C696C0A}">
-  <dimension ref="A1:V243"/>
+  <dimension ref="A1:V249"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -14529,7 +14532,7 @@
         <v>15</v>
       </c>
       <c r="F227" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G227" s="1">
         <v>18461</v>
@@ -14565,7 +14568,7 @@
         <v>0.6</v>
       </c>
       <c r="S227" s="1">
-        <v>0.36</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="V227" s="2">
         <v>45.8172</v>
@@ -14656,7 +14659,7 @@
         <v>12</v>
       </c>
       <c r="F229" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G229" s="1">
         <v>19205</v>
@@ -14692,7 +14695,7 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="S229" s="1">
-        <v>0.37</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="V229" s="2">
         <v>36.233600000000003</v>
@@ -14783,7 +14786,7 @@
         <v>11</v>
       </c>
       <c r="F231" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G231" s="1">
         <v>32437</v>
@@ -14819,7 +14822,7 @@
         <v>0.375</v>
       </c>
       <c r="S231" s="1">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="V231" s="2">
         <v>42.468400000000003</v>
@@ -14910,7 +14913,7 @@
         <v>10</v>
       </c>
       <c r="F233" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G233" s="1">
         <v>23820</v>
@@ -14946,7 +14949,7 @@
         <v>0.5</v>
       </c>
       <c r="S233" s="1">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="V233" s="2">
         <v>39.889200000000002</v>
@@ -15037,7 +15040,7 @@
         <v>9</v>
       </c>
       <c r="F235" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G235" s="1">
         <v>32308</v>
@@ -15073,7 +15076,7 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="S235" s="1">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="V235" s="2">
         <v>36.5456</v>
@@ -15164,7 +15167,7 @@
         <v>9</v>
       </c>
       <c r="F237" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G237" s="1">
         <v>42045</v>
@@ -15200,7 +15203,7 @@
         <v>0.36359999999999998</v>
       </c>
       <c r="S237" s="1">
-        <v>0.81</v>
+        <v>0.64</v>
       </c>
       <c r="V237" s="2">
         <v>67.641599999999997</v>
@@ -15291,7 +15294,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G239" s="1">
         <v>38980</v>
@@ -15327,7 +15330,7 @@
         <v>0.375</v>
       </c>
       <c r="S239" s="1">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="V239" s="2">
         <v>62.259599999999999</v>
@@ -15418,7 +15421,7 @@
         <v>9</v>
       </c>
       <c r="F241" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G241" s="1">
         <v>40220</v>
@@ -15454,7 +15457,7 @@
         <v>0.16669999999999999</v>
       </c>
       <c r="S241" s="1">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="V241" s="2">
         <v>50.689599999999999</v>
@@ -15471,7 +15474,7 @@
         <v>17</v>
       </c>
       <c r="D242" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E242" s="1">
         <v>0</v>
@@ -15480,10 +15483,10 @@
         <v>24959</v>
       </c>
       <c r="G242" s="1">
-        <v>2292</v>
+        <v>3976</v>
       </c>
       <c r="H242" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I242" s="1">
         <v>0</v>
@@ -15507,7 +15510,7 @@
         <v>21</v>
       </c>
       <c r="P242" s="5">
-        <v>1.09E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="Q242" s="1" t="s">
         <v>20</v>
@@ -15516,7 +15519,7 @@
         <v>20</v>
       </c>
       <c r="S242" s="1">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="T242" s="1" t="s">
         <v>20</v>
@@ -15525,7 +15528,7 @@
         <v>20</v>
       </c>
       <c r="V242" s="2">
-        <v>2.7143999999999999</v>
+        <v>3.0524</v>
       </c>
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.3">
@@ -15545,16 +15548,16 @@
         <v>9</v>
       </c>
       <c r="F243" s="1">
-        <v>51945</v>
+        <v>66013</v>
       </c>
       <c r="G243" s="1">
-        <v>13512</v>
+        <v>45575</v>
       </c>
       <c r="H243" s="1">
-        <v>191</v>
+        <v>592</v>
       </c>
       <c r="I243" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J243" s="1">
         <v>0</v>
@@ -15566,25 +15569,406 @@
         <v>0</v>
       </c>
       <c r="M243" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O243" s="4">
-        <v>1.7361111111111112E-4</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="P243" s="5">
-        <v>1.41E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="Q243" s="5">
-        <v>5.1999999999999998E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="R243" s="6">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="S243" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="V243" s="2">
+        <v>61.8384</v>
+      </c>
+    </row>
+    <row r="244" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A244" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B244" s="1">
+        <v>17</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D244" s="1">
+        <v>30</v>
+      </c>
+      <c r="E244" s="1">
+        <v>2</v>
+      </c>
+      <c r="F244" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G244" s="1">
+        <v>6527</v>
+      </c>
+      <c r="H244" s="1">
+        <v>85</v>
+      </c>
+      <c r="I244" s="1">
+        <v>3</v>
+      </c>
+      <c r="J244" s="1">
+        <v>1</v>
+      </c>
+      <c r="K244" s="1">
+        <v>2</v>
+      </c>
+      <c r="L244" s="1">
+        <v>1</v>
+      </c>
+      <c r="M244" s="1">
+        <v>1</v>
+      </c>
+      <c r="N244" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="O244" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P244" s="5">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="Q244" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="R244" s="6">
+        <v>1</v>
+      </c>
+      <c r="S244" s="1">
         <v>0.26</v>
       </c>
-      <c r="V243" s="2">
-        <v>20.113600000000002</v>
+      <c r="T244" s="6">
+        <v>0</v>
+      </c>
+      <c r="U244" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V244" s="2">
+        <v>13.1976</v>
+      </c>
+    </row>
+    <row r="245" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A245" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B245" s="1">
+        <v>17</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D245" s="1">
+        <v>0</v>
+      </c>
+      <c r="E245" s="1">
+        <v>9</v>
+      </c>
+      <c r="F245" s="1">
+        <v>66013</v>
+      </c>
+      <c r="G245" s="1">
+        <v>42546</v>
+      </c>
+      <c r="H245" s="1">
+        <v>385</v>
+      </c>
+      <c r="I245" s="1">
+        <v>5</v>
+      </c>
+      <c r="J245" s="1">
+        <v>0</v>
+      </c>
+      <c r="K245" s="1">
+        <v>0</v>
+      </c>
+      <c r="L245" s="1">
+        <v>0</v>
+      </c>
+      <c r="M245" s="1">
+        <v>4</v>
+      </c>
+      <c r="O245" s="4">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="P245" s="5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Q245" s="5">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="R245" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="S245" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="V245" s="2">
+        <v>53.539200000000001</v>
+      </c>
+    </row>
+    <row r="246" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A246" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B246" s="1">
+        <v>18</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D246" s="1">
+        <v>30</v>
+      </c>
+      <c r="E246" s="1">
+        <v>4</v>
+      </c>
+      <c r="F246" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G246" s="1">
+        <v>42409</v>
+      </c>
+      <c r="H246" s="1">
+        <v>661</v>
+      </c>
+      <c r="I246" s="1">
+        <v>49</v>
+      </c>
+      <c r="J246" s="1">
+        <v>11</v>
+      </c>
+      <c r="K246" s="1">
+        <v>34</v>
+      </c>
+      <c r="L246" s="1">
+        <v>2</v>
+      </c>
+      <c r="M246" s="1">
+        <v>1</v>
+      </c>
+      <c r="N246" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="O246" s="4">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="P246" s="5">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="Q246" s="5">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="R246" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="S246" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="T246" s="5">
+        <v>0.1176</v>
+      </c>
+      <c r="U246" s="5">
+        <v>0.22450000000000001</v>
+      </c>
+      <c r="V246" s="2">
+        <v>96.251999999999995</v>
+      </c>
+    </row>
+    <row r="247" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A247" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B247" s="1">
+        <v>18</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D247" s="1">
+        <v>0</v>
+      </c>
+      <c r="E247" s="1">
+        <v>9</v>
+      </c>
+      <c r="F247" s="1">
+        <v>66013</v>
+      </c>
+      <c r="G247" s="1">
+        <v>31524</v>
+      </c>
+      <c r="H247" s="1">
+        <v>497</v>
+      </c>
+      <c r="I247" s="1">
+        <v>3</v>
+      </c>
+      <c r="J247" s="1">
+        <v>0</v>
+      </c>
+      <c r="K247" s="1">
+        <v>0</v>
+      </c>
+      <c r="L247" s="1">
+        <v>0</v>
+      </c>
+      <c r="M247" s="1">
+        <v>2</v>
+      </c>
+      <c r="O247" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P247" s="5">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="Q247" s="5">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="R247" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="S247" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="V247" s="2">
+        <v>46.867600000000003</v>
+      </c>
+    </row>
+    <row r="248" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A248" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B248" s="1">
+        <v>19</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D248" s="1">
+        <v>30</v>
+      </c>
+      <c r="E248" s="1">
+        <v>2</v>
+      </c>
+      <c r="F248" s="1">
+        <v>24959</v>
+      </c>
+      <c r="G248" s="1">
+        <v>4631</v>
+      </c>
+      <c r="H248" s="1">
+        <v>64</v>
+      </c>
+      <c r="I248" s="1">
+        <v>5</v>
+      </c>
+      <c r="J248" s="1">
+        <v>2</v>
+      </c>
+      <c r="K248" s="1">
+        <v>3</v>
+      </c>
+      <c r="L248" s="1">
+        <v>0</v>
+      </c>
+      <c r="M248" s="1">
+        <v>0</v>
+      </c>
+      <c r="N248" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="O248" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="P248" s="5">
+        <v>1.38E-2</v>
+      </c>
+      <c r="Q248" s="6">
+        <v>0</v>
+      </c>
+      <c r="R248" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S248" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="T248" s="6">
+        <v>0</v>
+      </c>
+      <c r="U248" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="V248" s="2">
+        <v>7.2228000000000003</v>
+      </c>
+    </row>
+    <row r="249" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A249" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B249" s="1">
+        <v>19</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D249" s="1">
+        <v>0</v>
+      </c>
+      <c r="E249" s="1">
+        <v>9</v>
+      </c>
+      <c r="F249" s="1">
+        <v>66013</v>
+      </c>
+      <c r="G249" s="1">
+        <v>9352</v>
+      </c>
+      <c r="H249" s="1">
+        <v>154</v>
+      </c>
+      <c r="I249" s="1">
+        <v>1</v>
+      </c>
+      <c r="J249" s="1">
+        <v>0</v>
+      </c>
+      <c r="K249" s="1">
+        <v>0</v>
+      </c>
+      <c r="L249" s="1">
+        <v>0</v>
+      </c>
+      <c r="M249" s="1">
+        <v>0</v>
+      </c>
+      <c r="O249" s="4">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="P249" s="5">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="Q249" s="5">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="R249" s="6">
+        <v>0</v>
+      </c>
+      <c r="S249" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="V249" s="2">
+        <v>12.864800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -15595,7 +15979,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC39A14A-0B7A-4F83-A8E3-6BC48A6D5F40}">
-  <dimension ref="A1:I1174"/>
+  <dimension ref="A1:I1249"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -49289,13 +49673,13 @@
         <v>86</v>
       </c>
       <c r="E1162" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1162" t="s">
         <v>6</v>
       </c>
       <c r="G1162">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="H1162" s="8">
         <v>0</v>
@@ -49318,13 +49702,13 @@
         <v>86</v>
       </c>
       <c r="E1163" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F1163" t="s">
         <v>6</v>
       </c>
       <c r="G1163">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H1163" s="8">
         <v>0</v>
@@ -49347,13 +49731,13 @@
         <v>86</v>
       </c>
       <c r="E1164" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F1164" t="s">
         <v>6</v>
       </c>
       <c r="G1164">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="H1164" s="8">
         <v>0</v>
@@ -49376,13 +49760,13 @@
         <v>86</v>
       </c>
       <c r="E1165" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F1165" t="s">
         <v>6</v>
       </c>
       <c r="G1165">
-        <v>634</v>
+        <v>37</v>
       </c>
       <c r="H1165" s="8">
         <v>0</v>
@@ -49405,13 +49789,13 @@
         <v>86</v>
       </c>
       <c r="E1166" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F1166" t="s">
         <v>6</v>
       </c>
       <c r="G1166">
-        <v>1</v>
+        <v>2633</v>
       </c>
       <c r="H1166" s="8">
         <v>0</v>
@@ -49434,13 +49818,13 @@
         <v>86</v>
       </c>
       <c r="E1167" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1167" t="s">
         <v>6</v>
       </c>
       <c r="G1167">
-        <v>1114</v>
+        <v>738</v>
       </c>
       <c r="H1167" s="8">
         <v>0</v>
@@ -49550,19 +49934,19 @@
         <v>86</v>
       </c>
       <c r="E1171" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F1171" t="s">
         <v>37</v>
       </c>
       <c r="G1171">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H1171" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>2.7083333333333334E-3</v>
       </c>
       <c r="I1171" s="8">
-        <v>2.0833333333333335E-4</v>
+        <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.3">
@@ -49579,19 +49963,19 @@
         <v>86</v>
       </c>
       <c r="E1172" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F1172" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G1172">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H1172" s="8">
-        <v>0</v>
+        <v>5.0925925925925921E-4</v>
       </c>
       <c r="I1172" s="8">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
     </row>
     <row r="1173" spans="1:9" x14ac:dyDescent="0.3">
@@ -49608,19 +49992,19 @@
         <v>86</v>
       </c>
       <c r="E1173" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F1173" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G1173">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H1173" s="8">
-        <v>2.5347222222222221E-3</v>
+        <v>0</v>
       </c>
       <c r="I1173" s="8">
-        <v>1.273148148148148E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1174" spans="1:9" x14ac:dyDescent="0.3">
@@ -49643,13 +50027,2188 @@
         <v>6</v>
       </c>
       <c r="G1174">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="H1174" s="8">
         <v>0</v>
       </c>
       <c r="I1174" s="8">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1175" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1175">
+        <v>17</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1175" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1175">
+        <v>155</v>
+      </c>
+      <c r="H1175" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1175" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1176" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1176">
+        <v>17</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1176" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1176">
+        <v>205</v>
+      </c>
+      <c r="H1176" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1176" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1177" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1177">
+        <v>17</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1177" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1177">
+        <v>6</v>
+      </c>
+      <c r="H1177" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1177" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1178" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1178">
+        <v>17</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1178" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1178">
+        <v>27</v>
+      </c>
+      <c r="H1178" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1178" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1179" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1179">
+        <v>17</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1179" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1179">
+        <v>4566</v>
+      </c>
+      <c r="H1179" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1179" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1180" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1180">
+        <v>17</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1180" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1180">
+        <v>569</v>
+      </c>
+      <c r="H1180" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1180" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1181" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1181">
+        <v>17</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1181" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1181">
+        <v>2</v>
+      </c>
+      <c r="H1181" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1181" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1182" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1182">
+        <v>17</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1182">
+        <v>1</v>
+      </c>
+      <c r="H1182" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="I1182" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1183" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1183">
+        <v>17</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1183" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1183">
+        <v>1</v>
+      </c>
+      <c r="H1183" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I1183" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1184" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1184">
+        <v>17</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1184" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1184">
+        <v>1</v>
+      </c>
+      <c r="H1184" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="I1184" s="8">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1185" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1185">
+        <v>17</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1185">
+        <v>63</v>
+      </c>
+      <c r="H1185" s="8">
+        <v>6.5162037037037037E-3</v>
+      </c>
+      <c r="I1185" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1186" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1186">
+        <v>17</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1186" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1186">
+        <v>9</v>
+      </c>
+      <c r="H1186" s="8">
+        <v>1.8634259259259259E-3</v>
+      </c>
+      <c r="I1186" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1187" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1187">
+        <v>17</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1187" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1187">
+        <v>183</v>
+      </c>
+      <c r="H1187" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1187" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1188" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1188">
+        <v>17</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1188" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1188">
+        <v>1</v>
+      </c>
+      <c r="H1188" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="I1188" s="8">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1189" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1189">
+        <v>17</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1189" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1189">
+        <v>7</v>
+      </c>
+      <c r="H1189" s="8">
+        <v>2.0023148148148148E-3</v>
+      </c>
+      <c r="I1189" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1190" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1190">
+        <v>17</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1190" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1190">
+        <v>729</v>
+      </c>
+      <c r="H1190" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1190" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1191" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1191">
+        <v>17</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1191" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1191">
+        <v>2</v>
+      </c>
+      <c r="H1191" s="8">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="I1191" s="8">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1192" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1192">
+        <v>17</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1192" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1192" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1192">
+        <v>1</v>
+      </c>
+      <c r="H1192" s="8">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="I1192" s="8">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1193" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1193">
+        <v>17</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1193" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1193">
+        <v>1</v>
+      </c>
+      <c r="H1193" s="8">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I1193" s="8">
+        <v>7.8009259259259256E-3</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1194" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1194">
+        <v>18</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1194" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1194">
+        <v>1715</v>
+      </c>
+      <c r="H1194" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1194" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1195" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1195">
+        <v>18</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1195">
+        <v>2463</v>
+      </c>
+      <c r="H1195" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1195" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1196" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1196">
+        <v>18</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1196">
+        <v>952</v>
+      </c>
+      <c r="H1196" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1196" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1197" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1197">
+        <v>18</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1197">
+        <v>22</v>
+      </c>
+      <c r="H1197" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1197" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1198" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1198">
+        <v>18</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1198">
+        <v>1</v>
+      </c>
+      <c r="H1198" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1198" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1199" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1199">
+        <v>18</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1199">
+        <v>18590</v>
+      </c>
+      <c r="H1199" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1199" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1200" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1200">
+        <v>18</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1200">
+        <v>1</v>
+      </c>
+      <c r="H1200" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I1200" s="8">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1201" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1201">
+        <v>18</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1201">
+        <v>9457</v>
+      </c>
+      <c r="H1201" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1201" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1202" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1202">
+        <v>18</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1202">
+        <v>2</v>
+      </c>
+      <c r="H1202" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="I1202" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1203" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1203">
+        <v>18</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1203">
+        <v>23</v>
+      </c>
+      <c r="H1203" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1203" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1204" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1204">
+        <v>18</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1204">
+        <v>4</v>
+      </c>
+      <c r="H1204" s="8">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="I1204" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1205" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1205">
+        <v>18</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1205">
+        <v>3</v>
+      </c>
+      <c r="H1205" s="8">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="I1205" s="8">
+        <v>4.2824074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1206" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1206">
+        <v>18</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1206">
+        <v>11</v>
+      </c>
+      <c r="H1206" s="8">
+        <v>2.1412037037037038E-3</v>
+      </c>
+      <c r="I1206" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1207" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1207">
+        <v>18</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1207">
+        <v>1</v>
+      </c>
+      <c r="H1207" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="I1207" s="8">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1208" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1208">
+        <v>18</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1208">
+        <v>27</v>
+      </c>
+      <c r="H1208" s="8">
+        <v>7.037037037037037E-3</v>
+      </c>
+      <c r="I1208" s="8">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1209" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1209">
+        <v>18</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1209">
+        <v>62</v>
+      </c>
+      <c r="H1209" s="8">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="I1209" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1210" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1210">
+        <v>18</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1210">
+        <v>2</v>
+      </c>
+      <c r="H1210" s="8">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="I1210" s="8">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1211" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1211">
+        <v>18</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1211">
+        <v>2</v>
+      </c>
+      <c r="H1211" s="8">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="I1211" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1212" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1212">
+        <v>18</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1212">
+        <v>4</v>
+      </c>
+      <c r="H1212" s="8">
+        <v>2.488425925925926E-3</v>
+      </c>
+      <c r="I1212" s="8">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1213" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1213">
+        <v>18</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1213">
+        <v>5</v>
+      </c>
+      <c r="H1213" s="8">
+        <v>1.9212962962962964E-3</v>
+      </c>
+      <c r="I1213" s="8">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1214" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1214">
+        <v>18</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1214">
+        <v>36</v>
+      </c>
+      <c r="H1214" s="8">
+        <v>8.6458333333333335E-3</v>
+      </c>
+      <c r="I1214" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1215" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1215">
+        <v>18</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1215">
+        <v>1</v>
+      </c>
+      <c r="H1215" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="I1215" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1216" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1216">
+        <v>18</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1216">
+        <v>491</v>
+      </c>
+      <c r="H1216" s="8">
+        <v>4.6608796296296294E-2</v>
+      </c>
+      <c r="I1216" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1217" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1217">
+        <v>18</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1217">
+        <v>4</v>
+      </c>
+      <c r="H1217" s="8">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="I1217" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1218" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1218">
+        <v>18</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1218">
+        <v>1</v>
+      </c>
+      <c r="H1218" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="I1218" s="8">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1219" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1219">
+        <v>18</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1219">
+        <v>1</v>
+      </c>
+      <c r="H1219" s="8">
+        <v>6.8171296296296296E-3</v>
+      </c>
+      <c r="I1219" s="8">
+        <v>6.8171296296296296E-3</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1220" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1220">
+        <v>18</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1220">
+        <v>7371</v>
+      </c>
+      <c r="H1220" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1220" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1221" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1221">
+        <v>18</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1221">
+        <v>1</v>
+      </c>
+      <c r="H1221" s="8">
+        <v>5.9490740740740745E-3</v>
+      </c>
+      <c r="I1221" s="8">
+        <v>5.9490740740740745E-3</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1222" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1222">
+        <v>18</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1222">
+        <v>6</v>
+      </c>
+      <c r="H1222" s="8">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="I1222" s="8">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1223" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1223">
+        <v>18</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1223" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1223">
+        <v>1154</v>
+      </c>
+      <c r="H1223" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1223" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1224" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1224">
+        <v>18</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1224">
+        <v>2</v>
+      </c>
+      <c r="H1224" s="8">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="I1224" s="8">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1225" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1225">
+        <v>18</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1225">
+        <v>2</v>
+      </c>
+      <c r="H1225" s="8">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="I1225" s="8">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1226" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1226">
+        <v>18</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1226">
+        <v>27</v>
+      </c>
+      <c r="H1226" s="8">
+        <v>1.3275462962962963E-2</v>
+      </c>
+      <c r="I1226" s="8">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1227" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1227">
+        <v>19</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1227">
+        <v>1</v>
+      </c>
+      <c r="H1227" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="I1227" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1228" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1228">
+        <v>19</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1228">
+        <v>120</v>
+      </c>
+      <c r="H1228" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1228" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1229" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1229">
+        <v>19</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1229">
+        <v>1</v>
+      </c>
+      <c r="H1229" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="I1229" s="8">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1230" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1230">
+        <v>19</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1230">
+        <v>236</v>
+      </c>
+      <c r="H1230" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1230" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1231" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1231">
+        <v>19</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1231">
+        <v>1</v>
+      </c>
+      <c r="H1231" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I1231" s="8">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1232" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1232">
+        <v>19</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1232">
+        <v>95</v>
+      </c>
+      <c r="H1232" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1232" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1233" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1233">
+        <v>19</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1233">
+        <v>1</v>
+      </c>
+      <c r="H1233" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I1233" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1234" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1234">
+        <v>19</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1234">
+        <v>2</v>
+      </c>
+      <c r="H1234" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1234" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1235" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1235">
+        <v>19</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1235">
+        <v>2</v>
+      </c>
+      <c r="H1235" s="8">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="I1235" s="8">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1236" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1236">
+        <v>19</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1236">
+        <v>1671</v>
+      </c>
+      <c r="H1236" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1236" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1237" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1237">
+        <v>19</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1237">
+        <v>1</v>
+      </c>
+      <c r="H1237" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="I1237" s="8">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1238" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1238">
+        <v>19</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1238">
+        <v>1718</v>
+      </c>
+      <c r="H1238" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1238" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1239" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1239">
+        <v>19</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1239">
+        <v>6</v>
+      </c>
+      <c r="H1239" s="8">
+        <v>1.0300925925925926E-3</v>
+      </c>
+      <c r="I1239" s="8">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1240" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1240">
+        <v>19</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1240">
+        <v>2</v>
+      </c>
+      <c r="H1240" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1240" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1241" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1241">
+        <v>19</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1241">
+        <v>1</v>
+      </c>
+      <c r="H1241" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I1241" s="8">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1242" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1242">
+        <v>19</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1242">
+        <v>8</v>
+      </c>
+      <c r="H1242" s="8">
+        <v>1.9791666666666668E-3</v>
+      </c>
+      <c r="I1242" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1243" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1243">
+        <v>19</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1243">
+        <v>87</v>
+      </c>
+      <c r="H1243" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1243" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1244" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1244">
+        <v>19</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1244">
+        <v>1</v>
+      </c>
+      <c r="H1244" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="I1244" s="8">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1245" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1245">
+        <v>19</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1245">
+        <v>1</v>
+      </c>
+      <c r="H1245" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="I1245" s="8">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1246" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1246">
+        <v>19</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1246">
+        <v>41</v>
+      </c>
+      <c r="H1246" s="8">
+        <v>3.4375E-3</v>
+      </c>
+      <c r="I1246" s="8">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1247" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1247">
+        <v>19</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1247">
+        <v>1</v>
+      </c>
+      <c r="H1247" s="8">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="I1247" s="8">
+        <v>9.9537037037037042E-4</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1248" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1248">
+        <v>19</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1248">
+        <v>636</v>
+      </c>
+      <c r="H1248" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1248" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1249" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B1249">
+        <v>19</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1249">
+        <v>1</v>
+      </c>
+      <c r="H1249" s="8">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="I1249" s="8">
+        <v>1.5046296296296297E-4</v>
       </c>
     </row>
   </sheetData>
